--- a/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003482718094987692</v>
+        <v>0.003482718094987685</v>
       </c>
       <c r="C2" t="n">
         <v>0.003409482763365963</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003461475635370061</v>
+        <v>0.003461475635370055</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00342695134386082</v>
+        <v>0.003426951343860815</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0034444644173427</v>
+        <v>0.003444464417342694</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003540996388361936</v>
+        <v>0.003540996388361932</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003499365171871425</v>
+        <v>0.003499365171871419</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003468216006013866</v>
+        <v>0.003468216006013867</v>
       </c>
       <c r="J2" t="n">
         <v>0.00349202879811478</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003515666027955066</v>
+        <v>0.003515666027955063</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003517042328960007</v>
+        <v>0.003517042328960008</v>
       </c>
       <c r="M2" t="n">
         <v>0.003552698359565792</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003483799050774336</v>
+        <v>0.003483799050774333</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004737691696609891</v>
+        <v>0.004737691696609888</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00348755783355419</v>
+        <v>0.003487557833554187</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003443764693415001</v>
+        <v>0.003443764693414995</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003462958413567018</v>
+        <v>0.003462958413567013</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003476700377155546</v>
+        <v>0.003476700377155541</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003490855224688416</v>
+        <v>0.003490855224688414</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006411035027724749</v>
+        <v>0.006411035027724753</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003437217269852471</v>
+        <v>0.003437217269852469</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006721265072176854</v>
+        <v>0.00672126507217686</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003468547138845929</v>
+        <v>0.003468547138845931</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003484439158637463</v>
+        <v>0.003484439158637458</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00540301481351445</v>
+        <v>0.005403014813514449</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003487552922926361</v>
+        <v>0.003487552922926363</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003557230337617146</v>
+        <v>0.003557230337617145</v>
       </c>
     </row>
     <row r="3">
@@ -674,46 +674,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003571606027893024</v>
+        <v>0.003571606027893029</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00305053263058617</v>
+        <v>0.003050532630586171</v>
       </c>
       <c r="D3" t="n">
         <v>0.003424086364758006</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0031760762900236</v>
+        <v>0.003176076290023601</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003302860951696101</v>
+        <v>0.003302860951696103</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003987418734737413</v>
+        <v>0.003987418734737411</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003697271145376982</v>
+        <v>0.003697271145376989</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003472722219997794</v>
+        <v>0.003472722219997797</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003639883156872715</v>
+        <v>0.003639883156872716</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003811587303347379</v>
+        <v>0.003811587303347376</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003818948031908695</v>
+        <v>0.003818948031908692</v>
       </c>
       <c r="M3" t="n">
         <v>0.004078516476124981</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003582747243428084</v>
+        <v>0.003582747243428082</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005619973206830898</v>
+        <v>0.005619973206830897</v>
       </c>
       <c r="P3" t="n">
         <v>0.003606560164546496</v>
@@ -722,37 +722,37 @@
         <v>0.003296830782403072</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003435466812170523</v>
+        <v>0.003435466812170526</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003529801603299829</v>
+        <v>0.003529801603299828</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003634573517854449</v>
+        <v>0.00363457351785445</v>
       </c>
       <c r="U3" t="n">
         <v>0.008568259007148414</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003248341806860804</v>
+        <v>0.003248341806860812</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008942724809188847</v>
+        <v>0.00894272480918885</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003474281952308647</v>
+        <v>0.003474281952308645</v>
       </c>
       <c r="Y3" t="n">
         <v>0.003586655732176064</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006577554219757161</v>
+        <v>0.00657755421975716</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003609109271222038</v>
+        <v>0.003609109271222037</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004107738579418508</v>
+        <v>0.004107738579418505</v>
       </c>
     </row>
     <row r="4">
@@ -765,22 +765,22 @@
         <v>0.002924152210436021</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00209337334843567</v>
+        <v>0.002093373348435672</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002684208857040641</v>
+        <v>0.002684208857040642</v>
       </c>
       <c r="E4" t="n">
         <v>0.002294241102484997</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002492059323874714</v>
+        <v>0.002492059323874715</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003582432343437595</v>
+        <v>0.003582432343437597</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003112188601871486</v>
+        <v>0.003112188601871488</v>
       </c>
       <c r="I4" t="n">
         <v>0.002760344444186181</v>
@@ -792,19 +792,19 @@
         <v>0.003296314270100526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003311860223081129</v>
+        <v>0.00331186022308113</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00371561507278216</v>
+        <v>0.003715615072782159</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002936362103310403</v>
+        <v>0.002936362103310405</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002877612514875386</v>
+        <v>0.002877612514875385</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002978819283934398</v>
+        <v>0.0029788192839344</v>
       </c>
       <c r="Q4" t="n">
         <v>0.002484155620222424</v>
@@ -816,10 +816,10 @@
         <v>0.00285617931923495</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003016064833670304</v>
+        <v>0.003016064833670306</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003238698371538828</v>
+        <v>0.003238698371538825</v>
       </c>
       <c r="V4" t="n">
         <v>0.002405868393362115</v>
@@ -831,16 +831,16 @@
         <v>0.00276408474185299</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002925942943365011</v>
+        <v>0.00292594294336501</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002583806704016081</v>
+        <v>0.00258380670401608</v>
       </c>
       <c r="AA4" t="n">
         <v>0.002978763816134123</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003756822824495024</v>
+        <v>0.003756822824495023</v>
       </c>
     </row>
     <row r="5">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02135550609223002</v>
+        <v>0.02135550609223003</v>
       </c>
       <c r="C5" t="n">
         <v>0.006331710402465225</v>
@@ -859,76 +859,76 @@
         <v>0.01895375806389143</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01014464361825743</v>
+        <v>0.01014464361825742</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01519393612740646</v>
+        <v>0.01519393612740641</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03453911656375031</v>
+        <v>0.03453911656375029</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02921588682994219</v>
+        <v>0.0292158868299422</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02080166959131082</v>
+        <v>0.0208016695913108</v>
       </c>
       <c r="J5" t="n">
         <v>0.02455810367357783</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03172089844844145</v>
+        <v>0.03172089844844148</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03057067132619425</v>
+        <v>0.03057067132619426</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04140233508310685</v>
+        <v>0.04140233508310687</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02860521978803184</v>
+        <v>0.02860521978803178</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02006673793465809</v>
+        <v>0.0200667379346581</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02270166033794689</v>
+        <v>0.02270166033794686</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01441890455088721</v>
+        <v>0.01441890455088718</v>
       </c>
       <c r="R5" t="n">
         <v>0.01976520366909974</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02066680902856172</v>
+        <v>0.02066680902856169</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02611421898419048</v>
+        <v>0.02611421898419043</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02892520552898379</v>
+        <v>0.02892520552898372</v>
       </c>
       <c r="V5" t="n">
         <v>0.01187938592016035</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02391468173589536</v>
+        <v>0.02391468173589534</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02039938406549874</v>
+        <v>0.0203993840654987</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02339119145794478</v>
+        <v>0.02339119145794471</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01536800282395126</v>
+        <v>0.01536800282395122</v>
       </c>
       <c r="AA5" t="n">
         <v>0.02423643455764278</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04359984515444966</v>
+        <v>0.04359984515444959</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003144348068160689</v>
+        <v>0.003620598805787109</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002789819943786761</v>
+        <v>0.00278981994378676</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002904404714765309</v>
+        <v>0.002904404714765296</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002990687697836086</v>
+        <v>0.00251443696020965</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002712255181599381</v>
+        <v>0.003188505919225803</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003802628201162267</v>
+        <v>0.004278878938788686</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003808635197222577</v>
+        <v>0.003808635197222578</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003456791039537272</v>
+        <v>0.002980540301910835</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003248855888446435</v>
+        <v>0.00372510662607287</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003516510127825178</v>
+        <v>0.003516510127825179</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004008306818432219</v>
+        <v>0.003532056080805786</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003935810930506821</v>
+        <v>0.003935810930506814</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003159614723396097</v>
+        <v>0.003159614723396118</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003578404199111155</v>
+        <v>0.003578404199111156</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003679612185710134</v>
+        <v>0.003679612185710135</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002704351477947091</v>
+        <v>0.002704351477947077</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003397404114238054</v>
+        <v>0.002921153376611619</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003552625914586037</v>
+        <v>0.003552625914586038</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00323626069139497</v>
+        <v>0.003236260691394958</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003476543701987065</v>
+        <v>0.003476543701987051</v>
       </c>
       <c r="V6" t="n">
         <v>0.003102314988713203</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003216735354459786</v>
+        <v>0.003671418258591847</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003460531337204075</v>
+        <v>0.00346053133720408</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003183186642010324</v>
+        <v>0.003183186642010339</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002804002561740747</v>
+        <v>0.002804002561740735</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003675210411485211</v>
+        <v>0.003198959673858777</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003986316668507769</v>
+        <v>0.003986316668507768</v>
       </c>
     </row>
     <row r="7">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00335195478091426</v>
+        <v>0.003351954780914258</v>
       </c>
       <c r="C7" t="n">
         <v>0.00252117591891391</v>
@@ -1041,13 +1041,13 @@
         <v>0.002919861894352953</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004010234913915833</v>
+        <v>0.004010234913915836</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003539991172349728</v>
+        <v>0.003539991172349731</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003188147014664419</v>
+        <v>0.00318814701466442</v>
       </c>
       <c r="J7" t="n">
         <v>0.003456462601200021</v>
@@ -1059,52 +1059,52 @@
         <v>0.00373966279355937</v>
       </c>
       <c r="M7" t="n">
-        <v>0.004143417643260398</v>
+        <v>0.004143417643260397</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003364164673788645</v>
+        <v>0.003364164673788647</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003305386562780504</v>
+        <v>0.003305386562780503</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003406593331839517</v>
+        <v>0.003406593331839518</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00291195819070066</v>
+        <v>0.002911958190700661</v>
       </c>
       <c r="R7" t="n">
         <v>0.003128760089365204</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003283981889713189</v>
+        <v>0.003283981889713187</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003443867404148542</v>
+        <v>0.003443867404148543</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003683714001516331</v>
+        <v>0.003683714001516332</v>
       </c>
       <c r="V7" t="n">
         <v>0.002833670963840353</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003398428392917958</v>
+        <v>0.003398428392917957</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003191887312331228</v>
+        <v>0.003191887312331227</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003371394986566822</v>
+        <v>0.00337139498656682</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00301160927449432</v>
+        <v>0.003011609274494319</v>
       </c>
       <c r="AA7" t="n">
         <v>0.003406566386612361</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.004184625394973264</v>
+        <v>0.004184625394973261</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003810525786729727</v>
+        <v>0.003810525786729729</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003677412452587819</v>
+        <v>0.003677412452587823</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004268247961192791</v>
+        <v>0.004268247961192795</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003878280206637143</v>
+        <v>0.003506793893103149</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003487121035515326</v>
+        <v>0.003487121035515327</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005166471447589743</v>
+        <v>0.005311136939586176</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004696227706023634</v>
+        <v>0.00469622770602364</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004344383548338328</v>
+        <v>0.004344383548338332</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004612699134873932</v>
+        <v>0.004612699134873933</v>
       </c>
       <c r="K8" t="n">
-        <v>0.004880353374252675</v>
+        <v>0.004880353374252679</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00489589932723328</v>
+        <v>0.004895899327233282</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005299654176934309</v>
+        <v>0.005299654176934302</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003979593706231012</v>
+        <v>0.003979593706231016</v>
       </c>
       <c r="O8" t="n">
         <v>0.0040694627143801</v>
       </c>
       <c r="P8" t="n">
-        <v>0.004134239474341627</v>
+        <v>0.004134239474341632</v>
       </c>
       <c r="Q8" t="n">
         <v>0.00323342199713131</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004284996623039113</v>
+        <v>0.004284996623039118</v>
       </c>
       <c r="S8" t="n">
-        <v>0.004440218423387097</v>
+        <v>0.004440218423387102</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004600103937822451</v>
+        <v>0.004600103937822456</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004410783090135811</v>
+        <v>0.004499549610084583</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003989907497514262</v>
+        <v>0.003798876333824872</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00455480203688721</v>
+        <v>0.004554802036887211</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00357729355007052</v>
+        <v>0.003577293550070522</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005220763710312734</v>
+        <v>0.005220763710312735</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00416784580816823</v>
+        <v>0.003457220785044103</v>
       </c>
       <c r="AA8" t="n">
         <v>0.004562802920286269</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.006069631909410091</v>
+        <v>0.006069631909410089</v>
       </c>
     </row>
     <row r="9">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004745634619254793</v>
+        <v>0.004745634619254796</v>
       </c>
       <c r="C9" t="n">
         <v>0.004477126117068521</v>
@@ -1211,76 +1211,76 @@
         <v>0.005067961625673491</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004677993871117845</v>
+        <v>0.004548224271522685</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004875812092507564</v>
+        <v>0.003579625275138087</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005966185112070449</v>
+        <v>0.005966185249863392</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005495941370504341</v>
+        <v>0.00549594137050434</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005144097212819031</v>
+        <v>0.005144097212819029</v>
       </c>
       <c r="J9" t="n">
         <v>0.005412412799354631</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005680067038733379</v>
+        <v>0.005680067038733378</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005695612991713982</v>
+        <v>0.005695612991713978</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00609936784141501</v>
+        <v>0.006099367841415009</v>
       </c>
       <c r="N9" t="n">
         <v>0.005320114871943255</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00544770112797775</v>
+        <v>0.005447701127977746</v>
       </c>
       <c r="P9" t="n">
         <v>0.005589432716256609</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.004867908526648222</v>
+        <v>0.00486790852664822</v>
       </c>
       <c r="R9" t="n">
-        <v>0.005084710287519813</v>
+        <v>0.005084710287519814</v>
       </c>
       <c r="S9" t="n">
         <v>0.005239932087867796</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005399817602303153</v>
+        <v>0.005399817602303152</v>
       </c>
       <c r="U9" t="n">
-        <v>0.005640100612895249</v>
+        <v>0.005640100612895245</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004789621161994965</v>
+        <v>0.005438468728501226</v>
       </c>
       <c r="W9" t="n">
-        <v>0.005354378591072568</v>
+        <v>0.005354378591072569</v>
       </c>
       <c r="X9" t="n">
-        <v>0.005147837510485837</v>
+        <v>0.005147837510485838</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.005327345184721434</v>
+        <v>0.005327345184721432</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.004967559472648928</v>
+        <v>0.004628560499428311</v>
       </c>
       <c r="AA9" t="n">
         <v>0.005362516584766974</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.006140575593127874</v>
+        <v>0.00614057559312787</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003195850799215787</v>
+        <v>0.003195850799215783</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003148103562995352</v>
+        <v>0.003148103562995351</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003201913878285832</v>
+        <v>0.003201913878285828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003197810493083967</v>
+        <v>0.003197810493083964</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00320215483503416</v>
+        <v>0.003202154835034157</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003205914375042589</v>
+        <v>0.003205914375042584</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003214137757680808</v>
+        <v>0.003214137757680804</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003202103594552498</v>
+        <v>0.003202103594552494</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003208997057987461</v>
+        <v>0.003208997057987459</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003208003895776964</v>
+        <v>0.00320800389577696</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003209718259244911</v>
+        <v>0.003209718259244909</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003200601555377754</v>
+        <v>0.003200601555377752</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0032071686233508</v>
+        <v>0.003207168623350797</v>
       </c>
       <c r="O2" t="n">
         <v>0.004339149703015657</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003207770140626147</v>
+        <v>0.003207770140626144</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003200590630183473</v>
+        <v>0.003200590630183469</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003210393521358391</v>
+        <v>0.003210393521358387</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003209106015640172</v>
+        <v>0.00320910601564017</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003203182646542784</v>
+        <v>0.00320318264654278</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005889956539655254</v>
+        <v>0.005889956539655253</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003211047343447922</v>
+        <v>0.003211047343447919</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006294007688428223</v>
+        <v>0.006294007688428215</v>
       </c>
       <c r="X2" t="n">
         <v>0.0032723167155032</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003239760189112791</v>
+        <v>0.003239760189112787</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005123294457085436</v>
+        <v>0.005123294457085432</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003241447485432382</v>
+        <v>0.003241447485432378</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003197358680128566</v>
+        <v>0.003197358680128564</v>
       </c>
     </row>
     <row r="3">
@@ -1534,34 +1534,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002793641658373699</v>
+        <v>0.0027936416583737</v>
       </c>
       <c r="C3" t="n">
         <v>0.002735619463111795</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002837098766957204</v>
+        <v>0.002837098766957202</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002807641245067158</v>
+        <v>0.002807641245067156</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002838904550272428</v>
+        <v>0.002838904550272426</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002865036962509342</v>
+        <v>0.002865036962509341</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002924991647327248</v>
+        <v>0.002924991647327247</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002838575450916544</v>
+        <v>0.002838575450916545</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002887272468497555</v>
+        <v>0.002887272468497552</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002880165351361935</v>
+        <v>0.002880165351361934</v>
       </c>
       <c r="L3" t="n">
         <v>0.00289220345630524</v>
@@ -1570,10 +1570,10 @@
         <v>0.002832518570137255</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002874681944332533</v>
+        <v>0.002874681944332532</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004764132708213468</v>
+        <v>0.004764132708213471</v>
       </c>
       <c r="P3" t="n">
         <v>0.00287819480878171</v>
@@ -1582,37 +1582,37 @@
         <v>0.002827511987137111</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002898058672602192</v>
+        <v>0.002898058672602193</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002887720565165039</v>
+        <v>0.00288772056516504</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002846303489849729</v>
+        <v>0.002846303489849726</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007317475478615154</v>
+        <v>0.007317475478615156</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00290149961057759</v>
+        <v>0.002901499610577589</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008202488035979238</v>
+        <v>0.008202488035979243</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003338778453509832</v>
+        <v>0.00333877845350983</v>
       </c>
       <c r="Y3" t="n">
         <v>0.003107432529850138</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006050848691994851</v>
+        <v>0.006050848691994853</v>
       </c>
       <c r="AA3" t="n">
         <v>0.003119388433598154</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002806849267236193</v>
+        <v>0.002806849267236195</v>
       </c>
     </row>
     <row r="4">
@@ -1622,58 +1622,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001610176186745449</v>
+        <v>0.001610176186745451</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001652768112198285</v>
+        <v>0.001652768112198283</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001678661453995776</v>
+        <v>0.001678661453995779</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001632311830490278</v>
+        <v>0.001632311830490282</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00168138317131373</v>
+        <v>0.001681383171313731</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001723848905182768</v>
+        <v>0.001723848905182775</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001816735795024369</v>
+        <v>0.001816735795024372</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00168080438650157</v>
+        <v>0.001680804386501574</v>
       </c>
       <c r="J4" t="n">
         <v>0.00175838218186322</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001747451003104593</v>
+        <v>0.001747451003104597</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001766815527121197</v>
+        <v>0.001766815527121201</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00167248486386308</v>
+        <v>0.001672484863863083</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00486579578297408</v>
+        <v>0.00486579578297405</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001783047533178338</v>
+        <v>0.00178304753317834</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001744810631143445</v>
+        <v>0.001744810631143446</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00166371475795546</v>
+        <v>0.001663714757955459</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001774442923328879</v>
+        <v>0.001774442923328883</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001759899953959706</v>
+        <v>0.001759899953959709</v>
       </c>
       <c r="T4" t="n">
         <v>0.001692992775120308</v>
@@ -1682,25 +1682,25 @@
         <v>0.001759296337154474</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001780016372623142</v>
+        <v>0.001780016372623143</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002216967335888567</v>
+        <v>0.002216967335888569</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002473893887271182</v>
+        <v>0.002473893887271189</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002096441939730962</v>
+        <v>0.002096441939730961</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001767484014686207</v>
+        <v>0.00176748401468621</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002125211733073858</v>
+        <v>0.002125211733073863</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001631056865197004</v>
+        <v>0.00163105686519701</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002467709649479455</v>
+        <v>0.002467709649479458</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00330204059262448</v>
+        <v>0.003302040592624482</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003774654588646863</v>
+        <v>0.003774654588646866</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002866031691537365</v>
+        <v>0.002866031691537369</v>
       </c>
       <c r="F5" t="n">
         <v>0.003867392615998326</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004255912874212648</v>
+        <v>0.004255912874212665</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006553803150059814</v>
+        <v>0.006553803150059817</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003876126251582251</v>
+        <v>0.003876126251582248</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004992871771287784</v>
+        <v>0.004992871771287776</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004784967668558464</v>
+        <v>0.004784967668558467</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005025167517481459</v>
+        <v>0.005025167517481454</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00371101067303103</v>
+        <v>0.003711010673031032</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00486579578297408</v>
+        <v>0.00486579578297405</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005162889956850246</v>
+        <v>0.005162889956850249</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00458165025588547</v>
+        <v>0.004581650255885457</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003436351013219675</v>
+        <v>0.003436351013219676</v>
       </c>
       <c r="R5" t="n">
-        <v>0.005696866864982049</v>
+        <v>0.005696866864982053</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004844150733424066</v>
+        <v>0.00484415073342406</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004105581818466323</v>
+        <v>0.004105581818466327</v>
       </c>
       <c r="U5" t="n">
-        <v>0.005003177506630594</v>
+        <v>0.005003177506630592</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00519063054660941</v>
+        <v>0.005190630546609418</v>
       </c>
       <c r="W5" t="n">
         <v>0.01322266440671526</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01743083926986415</v>
+        <v>0.01743083926986413</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01145098457995242</v>
+        <v>0.01145098457995241</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004836286941900576</v>
+        <v>0.004836286941900579</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0117432887264953</v>
+        <v>0.01174328872649532</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003020904082970566</v>
+        <v>0.003020904082970577</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002078610616285505</v>
+        <v>0.001789490529507574</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00212120254173834</v>
+        <v>0.001832082454960409</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002147095883535831</v>
+        <v>0.002147095883535839</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002100746260030335</v>
+        <v>0.001811626173252405</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002149817600853785</v>
+        <v>0.001860697514075855</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001903163247944893</v>
+        <v>0.00219228333472283</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001996050137786494</v>
+        <v>0.002285170224564428</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001860118729263694</v>
+        <v>0.002149238816041634</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001937696524625341</v>
+        <v>0.00222681661140328</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00221588543264465</v>
+        <v>0.00192676534586672</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001946129869883321</v>
+        <v>0.002235249956661261</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001851799206625204</v>
+        <v>0.002140919293403144</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00486579578297408</v>
+        <v>0.00486579578297405</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002268020787545424</v>
+        <v>0.002268020787545428</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001913176976299962</v>
+        <v>0.002221369053433895</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002132149187495514</v>
+        <v>0.002132149187495521</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001953757266091004</v>
+        <v>0.002242877352868944</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001939214296721831</v>
+        <v>0.002228334383499768</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002161427204660364</v>
+        <v>0.00187230711788243</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001948321685135057</v>
+        <v>0.002237441771912992</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001959330715385265</v>
+        <v>0.0022484508021632</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002417837191011274</v>
+        <v>0.002417837191011276</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002653208230033308</v>
+        <v>0.002653208230033312</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002307258452986531</v>
+        <v>0.002307258452986542</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002235918444226262</v>
+        <v>0.001946798357448332</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002304526075835981</v>
+        <v>0.002304526075835984</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001810378901556869</v>
+        <v>0.001810378901556871</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001877645831192423</v>
+        <v>0.001877645831192427</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001920237756645261</v>
+        <v>0.001920237756645259</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00194613109844275</v>
+        <v>0.001946131098442752</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001899781474937254</v>
+        <v>0.001899781474937257</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001948852815760705</v>
+        <v>0.001948852815760707</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001991318549629742</v>
+        <v>0.001991318549629749</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002084205439471345</v>
+        <v>0.002084205439471346</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001948274030948544</v>
+        <v>0.001948274030948546</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002025851826310193</v>
+        <v>0.002025851826310194</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002014920647551569</v>
+        <v>0.002014920647551572</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00203428517156817</v>
+        <v>0.002034285171568173</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001939954508310055</v>
+        <v>0.001939954508310058</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00486579578297408</v>
+        <v>0.00486579578297405</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002050493690867355</v>
+        <v>0.002050493690867357</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00201225678883246</v>
+        <v>0.002012256788832464</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001931184402402432</v>
+        <v>0.001931184402402434</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002041912567775853</v>
+        <v>0.002041912567775856</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00202736959840668</v>
+        <v>0.002027369598406681</v>
       </c>
       <c r="T7" t="n">
         <v>0.001960462419567282</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002036025833868677</v>
+        <v>0.002036025833868678</v>
       </c>
       <c r="V7" t="n">
         <v>0.002047486017070116</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002484436980335541</v>
+        <v>0.002484436980335545</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00274136353171816</v>
+        <v>0.002741363531718162</v>
       </c>
       <c r="Y7" t="n">
         <v>0.002373622589396392</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002034953659133182</v>
+        <v>0.002034953659133184</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002392681377520833</v>
+        <v>0.002392681377520837</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001898526509643979</v>
+        <v>0.001898526509643984</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002191247671212854</v>
+        <v>0.00219124767121286</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002693841972033477</v>
+        <v>0.00269384197203348</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002719735313830966</v>
+        <v>0.002719735313830974</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002673385690325469</v>
+        <v>0.002428447994837633</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002334117649614113</v>
+        <v>0.002334117649614114</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002764922765017958</v>
+        <v>0.002860307254124675</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002857809654859559</v>
+        <v>0.002857809654859566</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002721878246336761</v>
+        <v>0.002721878246336769</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00279945604169841</v>
+        <v>0.002799456041698412</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002788524862939786</v>
+        <v>0.002788524862939794</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002807889386956388</v>
+        <v>0.002807889386956393</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002713558723698271</v>
+        <v>0.002713558723698222</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00486579578297408</v>
+        <v>0.00486579578297405</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002565533544514373</v>
+        <v>0.002565533544514378</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002503276693049747</v>
+        <v>0.002503276693049754</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002154385276857846</v>
+        <v>0.002154385276857849</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002815516783164069</v>
+        <v>0.002815516783164077</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002800973813794898</v>
+        <v>0.002800973813794901</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002734066634955498</v>
+        <v>0.002734066634955505</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002526708482887933</v>
+        <v>0.002585228751082075</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00282109023245833</v>
+        <v>0.002694999088313763</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003258131598546555</v>
+        <v>0.003258131598546562</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003006724537403419</v>
+        <v>0.003006724537403423</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003604029714367016</v>
+        <v>0.003604029714367021</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002808557874521397</v>
+        <v>0.002340010718947905</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.00316628559290905</v>
+        <v>0.003166285592909056</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003152641670088211</v>
+        <v>0.003152641670088216</v>
       </c>
     </row>
     <row r="9">
@@ -2062,31 +2062,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002351749990687619</v>
+        <v>0.002351749990687616</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002638947149152458</v>
+        <v>0.002638947149152459</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002664840490949951</v>
+        <v>0.002664840490949952</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002618490867444455</v>
+        <v>0.002562037106933578</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002667562208267906</v>
+        <v>0.002103680167252205</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002710027942136945</v>
+        <v>0.002710028110547027</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002802914831978546</v>
+        <v>0.002802914831978545</v>
       </c>
       <c r="I9" t="n">
         <v>0.002666983423455747</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002744561218817395</v>
+        <v>0.002744561218817396</v>
       </c>
       <c r="K9" t="n">
         <v>0.002733630040058771</v>
@@ -2098,49 +2098,49 @@
         <v>0.002658663900817257</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00486579578297408</v>
+        <v>0.00486579578297405</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002850288648290442</v>
+        <v>0.002850288648290445</v>
       </c>
       <c r="P9" t="n">
         <v>0.002829681320837553</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00264989396331972</v>
+        <v>0.002649893963319721</v>
       </c>
       <c r="R9" t="n">
         <v>0.002760621960283057</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002746078990913883</v>
+        <v>0.002746078990913884</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002679171812074482</v>
+        <v>0.002679171812074483</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002755186379327109</v>
+        <v>0.002755186379327108</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002766195409577316</v>
+        <v>0.003048464759579811</v>
       </c>
       <c r="W9" t="n">
         <v>0.003203146372842743</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003460072924225358</v>
+        <v>0.003460072924225359</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003092331981903589</v>
+        <v>0.003092331981903592</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002753663051640379</v>
+        <v>0.002606187914153907</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003111390770028034</v>
+        <v>0.003111390770028036</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002617235902151181</v>
+        <v>0.002617235902151182</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003415243012044815</v>
+        <v>0.003415243012044817</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003355591742133635</v>
+        <v>0.003355591742133636</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003406974874980482</v>
+        <v>0.003406974874980484</v>
       </c>
       <c r="E2" t="n">
         <v>0.003368874151057622</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00337878070160701</v>
+        <v>0.003378780701607013</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003456532663527141</v>
+        <v>0.003456532663527144</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003420568496129141</v>
+        <v>0.003420568496129143</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003387297950413063</v>
+        <v>0.003387297950413064</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003424802789006209</v>
+        <v>0.003424802789006212</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003443747229661467</v>
+        <v>0.003443747229661464</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003454239182942452</v>
+        <v>0.003454239182942455</v>
       </c>
       <c r="M2" t="n">
         <v>0.003445768423224413</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003407380248936375</v>
+        <v>0.003407380248936377</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004634784399256042</v>
+        <v>0.004634784399256041</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003455738509677778</v>
+        <v>0.003455738509677781</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00338270938662534</v>
+        <v>0.003382709386625342</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00338004520879992</v>
+        <v>0.003380045208799923</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003423539003394938</v>
+        <v>0.003423539003394939</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003411512193833803</v>
+        <v>0.003411512193833804</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006298528834902934</v>
+        <v>0.006298528834902935</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003370734126352728</v>
+        <v>0.00337073412635273</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006643027343733372</v>
+        <v>0.00664302734373337</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003425508322381417</v>
+        <v>0.003425508322381419</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003424429800815407</v>
+        <v>0.003424429800815411</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005323770325602956</v>
+        <v>0.005323770325602962</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003420406442093782</v>
+        <v>0.003420406442093789</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003485081991161679</v>
+        <v>0.003485081991161676</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003410479405739409</v>
+        <v>0.003410479405739415</v>
       </c>
       <c r="C3" t="n">
         <v>0.0030015279203254</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003355139073941073</v>
+        <v>0.003355139073941079</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003081687342559301</v>
+        <v>0.003081687342559302</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003153392443510089</v>
+        <v>0.003153392443510091</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003704942109888999</v>
+        <v>0.003704942109889003</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003453754312815035</v>
+        <v>0.003453754312815038</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003214510902451403</v>
+        <v>0.003214510902451409</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003480158523884254</v>
+        <v>0.003480158523884256</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003615367528448093</v>
+        <v>0.003615367528448101</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003690858763106853</v>
+        <v>0.003690858763106857</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003635993979055333</v>
+        <v>0.003635993979055334</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003357212644044567</v>
+        <v>0.003357212644044571</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005407224967852827</v>
+        <v>0.005407224967852826</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00369907363678069</v>
+        <v>0.003699073636780698</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003180974965853385</v>
+        <v>0.003180974965853387</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003162779729073513</v>
+        <v>0.003162779729073517</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0034702717278251</v>
+        <v>0.003470271727825104</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003387590500051692</v>
+        <v>0.003387590500051696</v>
       </c>
       <c r="U3" t="n">
         <v>0.008352263100639686</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003094080686246021</v>
+        <v>0.003094080686246028</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008932247876403579</v>
+        <v>0.008932247876403577</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003487180693491562</v>
+        <v>0.003487180693491566</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003478133682421374</v>
+        <v>0.003478133682421377</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006419079718662977</v>
+        <v>0.006419079718662973</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003449679840314193</v>
+        <v>0.003449679840314195</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003912160436043103</v>
+        <v>0.003912160436043102</v>
       </c>
     </row>
     <row r="4">
@@ -2488,25 +2488,25 @@
         <v>0.001993322471418175</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002544836621385973</v>
+        <v>0.002544836621385975</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002114471417478302</v>
+        <v>0.002114471417478303</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002226370463172046</v>
+        <v>0.002226370463172045</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003104614640729544</v>
+        <v>0.00310461464072954</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002698382825634719</v>
+        <v>0.00269838282563472</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002322576706564424</v>
+        <v>0.002322576706564423</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002745469058861176</v>
+        <v>0.002745469058861178</v>
       </c>
       <c r="K4" t="n">
         <v>0.002960197283626549</v>
@@ -2515,10 +2515,10 @@
         <v>0.003078708722472302</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002988159518833947</v>
+        <v>0.002988159518833946</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002549415506699025</v>
+        <v>0.002549415506699022</v>
       </c>
       <c r="O4" t="n">
         <v>0.0026057239651734</v>
@@ -2530,37 +2530,37 @@
         <v>0.002270746767738493</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002240653653618017</v>
+        <v>0.002240653653618018</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002731936071702789</v>
+        <v>0.00273193607170279</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002596087725104012</v>
+        <v>0.00259608772510401</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002997996293778563</v>
+        <v>0.002997996293778565</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0021306006638672</v>
+        <v>0.002130600663867199</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003032052167820919</v>
+        <v>0.003032052167820916</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002754180435586538</v>
+        <v>0.002754180435586539</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002728899991716329</v>
+        <v>0.00272889999171633</v>
       </c>
       <c r="Z4" t="n">
         <v>0.002343777536147282</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002696552350756868</v>
+        <v>0.002696552350756867</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003418219148805612</v>
+        <v>0.00341821914880561</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01655892534513687</v>
+        <v>0.01655892534513686</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005716947330772409</v>
+        <v>0.005716947330772404</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01683402395796246</v>
+        <v>0.01683402395796241</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007848606866863221</v>
+        <v>0.007848606866863223</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0105214008612066</v>
+        <v>0.01052140086120661</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02525294598686869</v>
+        <v>0.02525294598686872</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02062537326367019</v>
+        <v>0.02062537326367021</v>
       </c>
       <c r="I5" t="n">
         <v>0.01252422849644921</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01940660441349012</v>
+        <v>0.01940660441349014</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02345425929274535</v>
+        <v>0.02345425929274533</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02603411550299455</v>
+        <v>0.02603411550299459</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02588101083638894</v>
+        <v>0.02588101083638899</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0238080914024577</v>
+        <v>0.02380809140245765</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01564256458866572</v>
+        <v>0.01564256458866573</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02497179528341301</v>
+        <v>0.02497179528341305</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01110646989939333</v>
+        <v>0.01110646989939334</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01099303493088722</v>
+        <v>0.01099303493088723</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01865519845605201</v>
+        <v>0.01865519845605207</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0178410908648441</v>
+        <v>0.01784109086484409</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02426977023617495</v>
+        <v>0.02426977023617491</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007750779691489057</v>
+        <v>0.007750779691489037</v>
       </c>
       <c r="W5" t="n">
         <v>0.02535895969014897</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02066296113050135</v>
+        <v>0.02066296113050142</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01968206287445129</v>
+        <v>0.01968206287445133</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01168437405618242</v>
+        <v>0.0116843740561824</v>
       </c>
       <c r="AA5" t="n">
         <v>0.01896797463314958</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03578825986259651</v>
+        <v>0.03578825986259646</v>
       </c>
     </row>
     <row r="6">
@@ -2658,82 +2658,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003261111295972452</v>
+        <v>0.002851530148649631</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002616204734332054</v>
+        <v>0.002616204734332055</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002758137736977032</v>
+        <v>0.003167718884299852</v>
       </c>
       <c r="E6" t="n">
         <v>0.00232777253306936</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002849252726085923</v>
+        <v>0.002439671578763104</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003727496903643422</v>
+        <v>0.0033179157563206</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002911683941225774</v>
+        <v>0.003321265088548596</v>
       </c>
       <c r="I6" t="n">
         <v>0.002535877822155482</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003368351321775053</v>
+        <v>0.003368351321775051</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003173498399217608</v>
+        <v>0.003583079546540429</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003292009838063359</v>
+        <v>0.003292009838063361</v>
       </c>
       <c r="M6" t="n">
         <v>0.003201460634425005</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002764944034563341</v>
+        <v>0.00276494403456335</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003231335714259998</v>
+        <v>0.00323133571426</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003721256483724976</v>
+        <v>0.003721256483724984</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002484047883329551</v>
+        <v>0.002893629030652371</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002453954769209075</v>
+        <v>0.002863535916531894</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002945237187293846</v>
+        <v>0.003354818334616668</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003218969988017888</v>
+        <v>0.002809388840695067</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003633976603330155</v>
+        <v>0.003224395456007334</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002753482926781076</v>
+        <v>0.002753482926781077</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003657660299062632</v>
+        <v>0.003657660299062634</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002967481551177595</v>
+        <v>0.003377062698500413</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002972969575818358</v>
+        <v>0.002972969575818364</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002557078651738341</v>
+        <v>0.002966659799061159</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003319434613670744</v>
+        <v>0.002909853466347926</v>
       </c>
       <c r="AB6" t="n">
         <v>0.003639276940249485</v>
@@ -2746,22 +2746,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003003764667463884</v>
+        <v>0.003003764667463882</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002358858105823486</v>
+        <v>0.002358858105823484</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002910372255791285</v>
+        <v>0.002910372255791284</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002480007051883612</v>
+        <v>0.002480007051883611</v>
       </c>
       <c r="F7" t="n">
         <v>0.002591906097577356</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003470150275134853</v>
+        <v>0.00347015027513485</v>
       </c>
       <c r="H7" t="n">
         <v>0.003063918460040029</v>
@@ -2770,28 +2770,28 @@
         <v>0.002688112340969734</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003111004693266486</v>
+        <v>0.003111004693266484</v>
       </c>
       <c r="K7" t="n">
         <v>0.003325732918031859</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00344424435687761</v>
+        <v>0.003444244356877611</v>
       </c>
       <c r="M7" t="n">
         <v>0.003353695153239258</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002914951141104331</v>
+        <v>0.002914951141104332</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002971233259549182</v>
+        <v>0.002971233259549181</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003461153602047942</v>
+        <v>0.003461153602047945</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002636282402143804</v>
+        <v>0.002636282402143802</v>
       </c>
       <c r="R7" t="n">
         <v>0.002606189288023328</v>
@@ -2806,25 +2806,25 @@
         <v>0.003376172634774084</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002496136298272509</v>
+        <v>0.002496136298272508</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00339758780222623</v>
+        <v>0.003397587802226228</v>
       </c>
       <c r="X7" t="n">
         <v>0.003119716069991846</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003107533672759356</v>
+        <v>0.003107533672759355</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002709313170552592</v>
+        <v>0.002709313170552591</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003062087985162176</v>
+        <v>0.003062087985162175</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003783754783210921</v>
+        <v>0.003783754783210919</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003407416382667723</v>
+        <v>0.00340741638266772</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003369993062128259</v>
+        <v>0.003369993062128257</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003921507212096056</v>
+        <v>0.003921507212096058</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003491142008188383</v>
+        <v>0.003167675102127262</v>
       </c>
       <c r="F8" t="n">
         <v>0.003090196601841217</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004481285231439626</v>
+        <v>0.004607250838798903</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004075053416344799</v>
+        <v>0.004075053416344798</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003699247297274507</v>
+        <v>0.003699247297274505</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004122139649571254</v>
+        <v>0.004122139649571252</v>
       </c>
       <c r="K8" t="n">
         <v>0.004336867874336631</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004455379313182384</v>
+        <v>0.004455379313182383</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004364830109544029</v>
+        <v>0.004364830109543987</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003455184955599354</v>
+        <v>0.00345518495559935</v>
       </c>
       <c r="O8" t="n">
         <v>0.003640901136137619</v>
       </c>
       <c r="P8" t="n">
-        <v>0.004099100519079854</v>
+        <v>0.004099100519079855</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002920549795601386</v>
+        <v>0.002920549795601384</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003617324244328099</v>
+        <v>0.003617324244328098</v>
       </c>
       <c r="S8" t="n">
-        <v>0.004108606662412868</v>
+        <v>0.004108606662412869</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003972758315814093</v>
+        <v>0.003972758315814087</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004013637740053107</v>
+        <v>0.004090926454161893</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003507271254577279</v>
+        <v>0.003340868516368604</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004408842145491102</v>
+        <v>0.004408842145491101</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003459660509024098</v>
+        <v>0.0034596605090241</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004722103986697829</v>
+        <v>0.004722103986697833</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003720448126857363</v>
+        <v>0.003101680572760143</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.004073222941466947</v>
+        <v>0.004073222941466944</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.005429456780905358</v>
+        <v>0.005429456780905352</v>
       </c>
     </row>
     <row r="9">
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004028211595103113</v>
+        <v>0.004028211595103112</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003819398151858203</v>
+        <v>0.003819398151858202</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004370912301826</v>
+        <v>0.004370912301826005</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003940547097918328</v>
+        <v>0.003839898731737421</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00405244614361207</v>
+        <v>0.003047132235578517</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004930690321169565</v>
+        <v>0.004930690511955522</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004524458506074745</v>
+        <v>0.004524458506074747</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004148652387004448</v>
+        <v>0.004148652387004449</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004571544739301202</v>
+        <v>0.004571544739301203</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004786272964066576</v>
+        <v>0.004786272964066578</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004904784402912326</v>
+        <v>0.004904784402912329</v>
       </c>
       <c r="M9" t="n">
         <v>0.004814235199273972</v>
@@ -2961,46 +2961,46 @@
         <v>0.004375491187139048</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004576320588046652</v>
+        <v>0.004576320588046653</v>
       </c>
       <c r="P9" t="n">
-        <v>0.005097671714470186</v>
+        <v>0.00509767171447019</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.004096822638964476</v>
+        <v>0.004096822638964473</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004066729334058044</v>
+        <v>0.004066729334058043</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004558011752142813</v>
+        <v>0.004558011752142817</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004422163405544034</v>
+        <v>0.004422163405544033</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004837170020856302</v>
+        <v>0.004837170020856306</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003956676344307229</v>
+        <v>0.00445991831261943</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004858127848260946</v>
+        <v>0.004858127848260948</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004580256116026563</v>
+        <v>0.004580256116026564</v>
       </c>
       <c r="Y9" t="n">
         <v>0.004568073718794073</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.004169853216587308</v>
+        <v>0.003906927920866953</v>
       </c>
       <c r="AA9" t="n">
         <v>0.004522628031196892</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.005244294829245642</v>
+        <v>0.005244294829245643</v>
       </c>
     </row>
   </sheetData>
@@ -3166,82 +3166,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003396084549048926</v>
+        <v>0.003396084549048919</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003357032616038267</v>
+        <v>0.003357032616038271</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00341578068799774</v>
+        <v>0.003415780687997735</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00336917170398101</v>
+        <v>0.003369171703981003</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003374995309137169</v>
+        <v>0.003374995309137164</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003445857260364023</v>
+        <v>0.003445857260364017</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003406808248220549</v>
+        <v>0.003406808248220543</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003399783188309244</v>
+        <v>0.003399783188309238</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003414670749174517</v>
+        <v>0.003414670749174512</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003414906797896424</v>
+        <v>0.003414906797896417</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003432872689431469</v>
+        <v>0.003432872689431462</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003408009890226153</v>
+        <v>0.003408009890226155</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003385144597240125</v>
+        <v>0.003385144597240117</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004597909056531415</v>
+        <v>0.004597909056531404</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003450988527227854</v>
+        <v>0.003450988527227849</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003371710736551483</v>
+        <v>0.003371710736551476</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003369576358528916</v>
+        <v>0.003369576358528909</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003413506883579658</v>
+        <v>0.003413506883579653</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003401005950580008</v>
+        <v>0.003401005950580004</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006294149828051283</v>
+        <v>0.006294149828051279</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00337491687834416</v>
+        <v>0.003374916878344153</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006636803964884278</v>
+        <v>0.006636803964884277</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00344995871765411</v>
+        <v>0.003449958717654105</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003468911696439784</v>
+        <v>0.00346891169643978</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005312855698961671</v>
+        <v>0.005312855698961663</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003420318352554268</v>
+        <v>0.00342031835255426</v>
       </c>
       <c r="AB2" t="n">
         <v>0.003470145411704454</v>
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003298371699594723</v>
+        <v>0.003298371699594719</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003004208933947305</v>
+        <v>0.003004208933947307</v>
       </c>
       <c r="D3" t="n">
         <v>0.003441769106936833</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003107649274245901</v>
+        <v>0.003107649274245896</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003149966426708384</v>
+        <v>0.003149966426708381</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003652111513107078</v>
+        <v>0.003652111513107077</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003379150899622007</v>
+        <v>0.003379150899622008</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003327749565746446</v>
+        <v>0.003327749565746444</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003431432153712384</v>
+        <v>0.003431432153712386</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0034323423536803</v>
+        <v>0.003432342353680299</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003562023114880937</v>
+        <v>0.003562023114880934</v>
       </c>
       <c r="M3" t="n">
         <v>0.003391735523159627</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003222185367163612</v>
+        <v>0.00322218536716361</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005275726725260902</v>
+        <v>0.0052757267252609</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003688526525530275</v>
+        <v>0.003688526525530274</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003125952569785912</v>
+        <v>0.003125952569785911</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003111642477861929</v>
+        <v>0.003111642477861923</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003422385814601783</v>
+        <v>0.003422385814601785</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00333632051335647</v>
+        <v>0.003336320513356464</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008338884750935353</v>
+        <v>0.008338884750935359</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0031472871760557</v>
+        <v>0.003147287176055699</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008908300574105646</v>
+        <v>0.008908300574105641</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003685664047240744</v>
+        <v>0.003685664047240742</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00381943129811093</v>
+        <v>0.003819431298110927</v>
       </c>
       <c r="Z3" t="n">
         <v>0.006402550171911663</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003472947791977083</v>
+        <v>0.003472947791977078</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003829931809109401</v>
+        <v>0.003829931809109404</v>
       </c>
     </row>
     <row r="4">
@@ -3348,73 +3348,73 @@
         <v>0.001951802212897825</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002650923799625597</v>
+        <v>0.002650923799625596</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002124453883964654</v>
+        <v>0.002124453883964655</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002190234183194239</v>
+        <v>0.00219023418319424</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002990652520409615</v>
+        <v>0.002990652520409613</v>
       </c>
       <c r="H4" t="n">
         <v>0.002549575964816008</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002470224681430572</v>
+        <v>0.002470224681430575</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002637767262749148</v>
+        <v>0.002637767262749147</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002641052808921913</v>
+        <v>0.002641052808921916</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002843985818528677</v>
+        <v>0.002843985818528678</v>
       </c>
       <c r="M4" t="n">
         <v>0.002572329645581155</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00230487506122029</v>
+        <v>0.002304875061220289</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002417113673657923</v>
+        <v>0.00241711367365793</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003048612540135993</v>
+        <v>0.003048612540136</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002153133424860853</v>
+        <v>0.002153133424860852</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002129024643233583</v>
+        <v>0.002129024643233582</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002625240132721661</v>
+        <v>0.002625240132721662</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002484036343777321</v>
+        <v>0.002484036343777323</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002946118573648476</v>
+        <v>0.002946118573648483</v>
       </c>
       <c r="V4" t="n">
         <v>0.002185289938972421</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002961482839758613</v>
+        <v>0.00296148283975861</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003036980367264715</v>
+        <v>0.003036980367264722</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003240254001695551</v>
+        <v>0.003240254001695554</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002306380041698133</v>
+        <v>0.002306380041698132</v>
       </c>
       <c r="AA4" t="n">
         <v>0.002702178808220386</v>
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01282952747956323</v>
+        <v>0.01282952747956325</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005172505668847312</v>
+        <v>0.005172505668847313</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01822842655015092</v>
+        <v>0.01822842655015096</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008155566721887853</v>
+        <v>0.00815556672188787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009709633551319145</v>
+        <v>0.009709633551319137</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02200064424093843</v>
+        <v>0.02200064424093838</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01717104667194943</v>
+        <v>0.01717104667194941</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01511300259049726</v>
+        <v>0.0151130025904973</v>
       </c>
       <c r="J5" t="n">
         <v>0.0167544153087661</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01640083149557324</v>
+        <v>0.01640083149557325</v>
       </c>
       <c r="L5" t="n">
         <v>0.02074524425736453</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0170658564249745</v>
+        <v>0.01706585642497451</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02149137275900815</v>
+        <v>0.02149137275900825</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01212554542079594</v>
+        <v>0.01212554542079595</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02291844109811376</v>
+        <v>0.02291844109811389</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008757177077568857</v>
+        <v>0.008757177077568883</v>
       </c>
       <c r="R5" t="n">
         <v>0.008809131366045027</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01613915056437282</v>
+        <v>0.01613915056437291</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01527645833276519</v>
+        <v>0.01527645833276524</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0221434252511907</v>
+        <v>0.02214342525119082</v>
       </c>
       <c r="V5" t="n">
-        <v>0.008591536369449024</v>
+        <v>0.008591536369448949</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02309925431496951</v>
+        <v>0.02309925431496948</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02503814894858476</v>
+        <v>0.02503814894858483</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02804664433258773</v>
+        <v>0.02804664433258781</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0104044059113999</v>
+        <v>0.01040440591139991</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01850953488980694</v>
+        <v>0.01850953488980693</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03111161741162918</v>
+        <v>0.03111161741162916</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003028338471259708</v>
+        <v>0.00265124781912988</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002174603182500506</v>
+        <v>0.002174603182500507</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003250815421358106</v>
+        <v>0.003250815421358112</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002347254853567334</v>
+        <v>0.002347254853567337</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00241303515279692</v>
+        <v>0.002790125804926751</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003590544142142124</v>
+        <v>0.003213453490012293</v>
       </c>
       <c r="H6" t="n">
         <v>0.00277237693441869</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003070116303163084</v>
+        <v>0.002693025651033257</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003237658884481655</v>
+        <v>0.003237658884481657</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002863853778524591</v>
+        <v>0.003240944430654426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003443877440261189</v>
+        <v>0.003066786788131359</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003172221267313665</v>
+        <v>0.003172221267313664</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002529746623925991</v>
+        <v>0.00252974662392599</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003019998991933857</v>
+        <v>0.002641985236363626</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003651494064466462</v>
+        <v>0.00365149406446647</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002753025046593363</v>
+        <v>0.002753025046593366</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002728916264966093</v>
+        <v>0.002728916264966094</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002848041102324338</v>
+        <v>0.002848041102324345</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002706837313380002</v>
+        <v>0.002706837313380005</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003556819175135371</v>
+        <v>0.00317972852300555</v>
       </c>
       <c r="V6" t="n">
         <v>0.002785181560704932</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003564365483986693</v>
+        <v>0.003208730388266212</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003259781336867395</v>
+        <v>0.003259781336867403</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003491637390739476</v>
+        <v>0.003491637390739479</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002906271663430642</v>
+        <v>0.002529181011300814</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002924979777823065</v>
+        <v>0.003302070429952895</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003486732407681925</v>
+        <v>0.003486732407681928</v>
       </c>
     </row>
     <row r="7">
@@ -3609,10 +3609,10 @@
         <v>0.002748903019383827</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002272258382754455</v>
+        <v>0.002272258382754454</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002971379969482223</v>
+        <v>0.002971379969482225</v>
       </c>
       <c r="E7" t="n">
         <v>0.002444910053821283</v>
@@ -3624,67 +3624,67 @@
         <v>0.003311108690266245</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002870032134672638</v>
+        <v>0.002870032134672639</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0027906808512872</v>
+        <v>0.002790680851287203</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002958223432605773</v>
+        <v>0.002958223432605774</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002961508978778541</v>
+        <v>0.002961508978778544</v>
       </c>
       <c r="L7" t="n">
         <v>0.003164441988385307</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002892785815437783</v>
+        <v>0.002892785815437781</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002625331231076919</v>
+        <v>0.00262533123107692</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002737545332870897</v>
+        <v>0.0027375453328709</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003369044199348958</v>
+        <v>0.00336904419934897</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00247358959471748</v>
+        <v>0.002473589594717483</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002449480813090211</v>
+        <v>0.002449480813090212</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002945696302578287</v>
+        <v>0.002945696302578291</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00280449251363395</v>
+        <v>0.002804492513633953</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003276933548286638</v>
+        <v>0.003276933548286646</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00250574610882905</v>
+        <v>0.002505746108829049</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003281939009615243</v>
+        <v>0.003281939009615242</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003357436537121346</v>
+        <v>0.003357436537121348</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003571519151306567</v>
+        <v>0.00357151915130657</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002626836211554759</v>
+        <v>0.00262683621155476</v>
       </c>
       <c r="AA7" t="n">
         <v>0.003022634978077012</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003578102980025367</v>
+        <v>0.003578102980025365</v>
       </c>
     </row>
     <row r="8">
@@ -3697,82 +3697,82 @@
         <v>0.003117500797004953</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003188282268484383</v>
+        <v>0.003188282268484382</v>
       </c>
       <c r="D8" t="n">
         <v>0.003887403855212154</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003360933939551213</v>
+        <v>0.003069445685221574</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002964570720320879</v>
+        <v>0.002964570720320878</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004227132575996172</v>
+        <v>0.004340644945598107</v>
       </c>
       <c r="H8" t="n">
         <v>0.003786056020402565</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003706704737017133</v>
+        <v>0.003706704737017134</v>
       </c>
       <c r="J8" t="n">
         <v>0.003874247318335701</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003877532864508467</v>
+        <v>0.003877532864508471</v>
       </c>
       <c r="L8" t="n">
         <v>0.004080465874115233</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003808809701167711</v>
+        <v>0.003808809701167677</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003117008300420192</v>
+        <v>0.003117008300420193</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003345861102101608</v>
+        <v>0.003345861102101613</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003948775013049157</v>
+        <v>0.003948775013049164</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002734605647945954</v>
+        <v>0.002734605647945955</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00336550469882014</v>
+        <v>0.003365504698820142</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003861720188308212</v>
+        <v>0.003861720188308221</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003720516399363875</v>
+        <v>0.003720516399363881</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003856240333251067</v>
+        <v>0.003925886352127662</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003421769994558981</v>
+        <v>0.003271786337198258</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004198070479416608</v>
+        <v>0.00419807047941661</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003668625280386738</v>
+        <v>0.003668625280386742</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005031272028171273</v>
+        <v>0.00503127202817128</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003542860097284689</v>
+        <v>0.002985265268252737</v>
       </c>
       <c r="AA8" t="n">
         <v>0.003938658863806946</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.005065959209894607</v>
+        <v>0.005065959209894608</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00359811196959638</v>
+        <v>0.003598111969596381</v>
       </c>
       <c r="C9" t="n">
         <v>0.003492651703935758</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004191773290663525</v>
+        <v>0.004191773290663528</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003665303375002586</v>
+        <v>0.003579635728171413</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00373108367423217</v>
+        <v>0.002875402067591954</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004531502011447546</v>
+        <v>0.004531502260997617</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004090425455853942</v>
+        <v>0.00409042545585394</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004011074172468506</v>
+        <v>0.004011074172468509</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004178616753787081</v>
+        <v>0.004178616753787078</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004181902299959847</v>
+        <v>0.004181902299959848</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004384835309566609</v>
+        <v>0.004384835309566608</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004113179136619084</v>
+        <v>0.004113179136619082</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003845724552258224</v>
+        <v>0.003845724552258222</v>
       </c>
       <c r="O9" t="n">
         <v>0.004080973511461097</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004739224963585622</v>
+        <v>0.004739224963585625</v>
       </c>
       <c r="Q9" t="n">
         <v>0.003693983165448859</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003669874134271515</v>
+        <v>0.003669874134271514</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00416608962375959</v>
+        <v>0.004166089623759594</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004024885834815254</v>
+        <v>0.004024885834815255</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004497777044440794</v>
+        <v>0.004497777044440801</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003726139430010354</v>
+        <v>0.004154478292944736</v>
       </c>
       <c r="W9" t="n">
         <v>0.00450233233079654</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004577829858302646</v>
+        <v>0.004577829858302649</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.004791912472487874</v>
+        <v>0.004791912472487877</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003847229532736064</v>
+        <v>0.003623438463137587</v>
       </c>
       <c r="AA9" t="n">
         <v>0.004243028299258318</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.004798496301206668</v>
+        <v>0.004798496301206669</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003413635818464767</v>
+        <v>0.003413635818464756</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003343569846040831</v>
+        <v>0.003343569846040829</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003416065807379045</v>
+        <v>0.003416065807379038</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003384636986410311</v>
+        <v>0.003384636986410309</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003407405329143566</v>
+        <v>0.003407405329143564</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003458765902514969</v>
+        <v>0.003458765902514962</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003427321350302211</v>
+        <v>0.003427321350302204</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003423058147015729</v>
+        <v>0.003423058147015727</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003433379783345791</v>
+        <v>0.003433379783345781</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003453824787788844</v>
+        <v>0.003453824787788834</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003443485271773115</v>
+        <v>0.003443485271773113</v>
       </c>
       <c r="M2" t="n">
         <v>0.003423582093751747</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003395978683943361</v>
+        <v>0.003395978683943355</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004617599909400537</v>
+        <v>0.004617599909400528</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003464821348962457</v>
+        <v>0.003464821348962455</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003398523427245106</v>
+        <v>0.003398523427245103</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003402713203479142</v>
+        <v>0.003402713203479139</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003433720646886699</v>
+        <v>0.003433720646886697</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003425921239426201</v>
+        <v>0.003425921239426202</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006234439180551346</v>
+        <v>0.006234439180551356</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003420822142488002</v>
+        <v>0.003420822142487997</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006584200837382886</v>
+        <v>0.006584200837382901</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00348512226882804</v>
+        <v>0.003485122268828036</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003568108420110945</v>
+        <v>0.003568108420110939</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005335682116922592</v>
+        <v>0.00533568211692259</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003449736717808684</v>
+        <v>0.003449736717808679</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003483798645834929</v>
+        <v>0.003483798645834927</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003272984189453392</v>
+        <v>0.003272984189453398</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00296460467807853</v>
+        <v>0.002964604678078529</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003292268586825787</v>
+        <v>0.003292268586825797</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003067357913833736</v>
+        <v>0.003067357913833735</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003230941190923487</v>
+        <v>0.003230941190923492</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003593177955945617</v>
+        <v>0.003593177955945613</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003375142950042319</v>
+        <v>0.003375142950042325</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003343099748957503</v>
+        <v>0.003343099748957505</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003414242268916716</v>
+        <v>0.003414242268916713</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003559457188670412</v>
+        <v>0.003559457188670422</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003486389476405831</v>
+        <v>0.003486389476405832</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003351658384942419</v>
+        <v>0.003351658384942417</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003149092436266022</v>
+        <v>0.003149092436266016</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005240159151975101</v>
+        <v>0.005240159151975103</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00363605408615839</v>
+        <v>0.003636054086158391</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003166694151370784</v>
+        <v>0.003166694151370786</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00319808943677483</v>
+        <v>0.003198089436774825</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00341612902514646</v>
+        <v>0.003416129025146456</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003363857684795552</v>
+        <v>0.003363857684795557</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00828859912340619</v>
+        <v>0.008288599123406194</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003323507999280328</v>
+        <v>0.003323507999280329</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008749437420788415</v>
+        <v>0.008749437420788427</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003784977356147317</v>
+        <v>0.003784977356147318</v>
       </c>
       <c r="Y3" t="n">
         <v>0.004378564507930241</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006394826143632995</v>
+        <v>0.006394826143632989</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003532792264203879</v>
+        <v>0.003532792264203881</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003776331307039924</v>
+        <v>0.003776331307039923</v>
       </c>
     </row>
     <row r="4">
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002371144016354321</v>
+        <v>0.00237114401635432</v>
       </c>
       <c r="C4" t="n">
         <v>0.00197005744844734</v>
@@ -4214,73 +4214,73 @@
         <v>0.00204358886817745</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002300767773304701</v>
+        <v>0.0023007677733047</v>
       </c>
       <c r="G4" t="n">
         <v>0.002880909076565706</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002525728394113922</v>
+        <v>0.002525728394113923</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002477573551822773</v>
+        <v>0.002477573551822775</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002593731291565158</v>
+        <v>0.002593731291565159</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002825096912709025</v>
+        <v>0.002825096912709028</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002708307322899097</v>
+        <v>0.002708307322899098</v>
       </c>
       <c r="M4" t="n">
         <v>0.002493206405966104</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002171698559251857</v>
+        <v>0.002171698559251855</v>
       </c>
       <c r="O4" t="n">
         <v>0.002329885294005128</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00294930812983307</v>
+        <v>0.002949308129833069</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002200442605484835</v>
+        <v>0.002200442605484836</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002247768055440542</v>
+        <v>0.002247768055440543</v>
       </c>
       <c r="S4" t="n">
         <v>0.002598011392857627</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002509913497686655</v>
+        <v>0.002509913497686653</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003105893078664718</v>
+        <v>0.003105893078664719</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002449545332593315</v>
+        <v>0.002449545332593314</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002867012184939951</v>
+        <v>0.002867012184939952</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003178616358599405</v>
+        <v>0.003178616358599406</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004108266411082657</v>
+        <v>0.004108266411082659</v>
       </c>
       <c r="Z4" t="n">
         <v>0.002267696562047655</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00277892028167808</v>
+        <v>0.002778920281678083</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003157167734893112</v>
+        <v>0.003157167734893113</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01114174778722721</v>
+        <v>0.01114174778722722</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004987019456947336</v>
+        <v>0.004987019456947338</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0126333130687416</v>
+        <v>0.01263331306874163</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006042729734109614</v>
+        <v>0.006042729734109625</v>
       </c>
       <c r="F5" t="n">
         <v>0.01115336732600149</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01917217606652665</v>
+        <v>0.01917217606652668</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01619977383072098</v>
+        <v>0.016199773830721</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01451036231897288</v>
+        <v>0.01451036231897289</v>
       </c>
       <c r="J5" t="n">
         <v>0.01526423030478843</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01898529609431735</v>
+        <v>0.01898529609431739</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01729587379474457</v>
+        <v>0.01729587379474458</v>
       </c>
       <c r="M5" t="n">
         <v>0.01454901396933543</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02262531156263639</v>
+        <v>0.02262531156263644</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01033520448876127</v>
+        <v>0.01033520448876128</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02020474882247674</v>
+        <v>0.0202047488224768</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008935110960964844</v>
+        <v>0.008935110960964856</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01054566436119437</v>
+        <v>0.0105456643611944</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01504980485002044</v>
+        <v>0.01504980485002046</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01525020193365784</v>
+        <v>0.01525020193365786</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02356722278382213</v>
+        <v>0.02356722278382202</v>
       </c>
       <c r="V5" t="n">
         <v>0.0121780321969149</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02095101311913308</v>
+        <v>0.02095101311913307</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02635126882607317</v>
+        <v>0.0263512688260732</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04360946305478346</v>
+        <v>0.04360946305478351</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.009000438358639723</v>
+        <v>0.00900043835863972</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01947028094694668</v>
+        <v>0.01947028094694671</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02821636689709557</v>
+        <v>0.0282163668970956</v>
       </c>
     </row>
     <row r="6">
@@ -4378,52 +4378,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002625746383333265</v>
+        <v>0.003014654009254951</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002224659815426287</v>
+        <v>0.002224659815426286</v>
       </c>
       <c r="D6" t="n">
         <v>0.002653194225970163</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002298191235156395</v>
+        <v>0.002687098861078081</v>
       </c>
       <c r="F6" t="n">
         <v>0.002555370140283647</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003135511443544652</v>
+        <v>0.003524419069466336</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003169238387014555</v>
+        <v>0.002780330761092869</v>
       </c>
       <c r="I6" t="n">
         <v>0.002732175918801719</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002848333658544105</v>
+        <v>0.00323724128446579</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003468606905609652</v>
+        <v>0.003468606905609653</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002962909689878043</v>
+        <v>0.003351817315799728</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002747808772945051</v>
+        <v>0.002747808772945049</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002429870110668163</v>
+        <v>0.002429870110668157</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002588056845421431</v>
+        <v>0.002979214127256313</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003598632491414012</v>
+        <v>0.003181673066420465</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002843952598385466</v>
+        <v>0.002843952598385467</v>
       </c>
       <c r="R6" t="n">
         <v>0.002891278048341173</v>
@@ -4432,28 +4432,28 @@
         <v>0.003241521385758259</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002764515864665597</v>
+        <v>0.003153423490587285</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003757119773338143</v>
+        <v>0.003368212147416459</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003093055325493948</v>
+        <v>0.00270414769957226</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003516340120609722</v>
+        <v>0.00351634012060972</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003433218725578346</v>
+        <v>0.003433218725578349</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.004393182860076444</v>
+        <v>0.004393182860076442</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002911206554948286</v>
+        <v>0.002911206554948287</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003422430274578711</v>
+        <v>0.003422430274578712</v>
       </c>
       <c r="AB6" t="n">
         <v>0.003417940181807193</v>
@@ -4472,7 +4472,7 @@
         <v>0.002268085911216162</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002696620321760039</v>
+        <v>0.002696620321760038</v>
       </c>
       <c r="E7" t="n">
         <v>0.002341617330946271</v>
@@ -4487,7 +4487,7 @@
         <v>0.002823756856882745</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002775602014591594</v>
+        <v>0.002775602014591595</v>
       </c>
       <c r="J7" t="n">
         <v>0.00289175975433398</v>
@@ -4496,52 +4496,52 @@
         <v>0.003123125375477846</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003006335785667918</v>
+        <v>0.003006335785667919</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002791234868734927</v>
+        <v>0.002791234868734925</v>
       </c>
       <c r="N7" t="n">
         <v>0.002469727022020678</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002627888891864067</v>
+        <v>0.002627888891864065</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00324731172769201</v>
+        <v>0.003247311727692011</v>
       </c>
       <c r="Q7" t="n">
         <v>0.002498471068253657</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002545796518209364</v>
+        <v>0.002545796518209363</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00289603985562645</v>
+        <v>0.002896039855626452</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002807941960455474</v>
+        <v>0.002807941960455475</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003411212950295684</v>
+        <v>0.003411212950295687</v>
       </c>
       <c r="V7" t="n">
         <v>0.002747573795362137</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003165040647708772</v>
+        <v>0.003165040647708771</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003476644821368227</v>
+        <v>0.003476644821368226</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.004414011575624274</v>
+        <v>0.004414011575624279</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002565725024816477</v>
+        <v>0.002565725024816475</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003076948744446902</v>
+        <v>0.003076948744446904</v>
       </c>
       <c r="AB7" t="n">
         <v>0.003455196197661933</v>
@@ -4554,25 +4554,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00305540497092347</v>
+        <v>0.003055404970923468</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003213900689617773</v>
+        <v>0.003213900689617771</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003642435100161652</v>
+        <v>0.003642435100161651</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003287432109347881</v>
+        <v>0.002989471048555471</v>
       </c>
       <c r="F8" t="n">
         <v>0.003072205108059309</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004124752317736141</v>
+        <v>0.004240785350138814</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003769571635284357</v>
+        <v>0.003769571635284356</v>
       </c>
       <c r="I8" t="n">
         <v>0.003721416792993204</v>
@@ -4584,55 +4584,55 @@
         <v>0.004068940153879457</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003952150564069533</v>
+        <v>0.00395215056406953</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003737049647136539</v>
+        <v>0.003737049647136516</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002981771912019446</v>
+        <v>0.002981771912019445</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003259162378026094</v>
+        <v>0.003259162378026092</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003849365499004804</v>
+        <v>0.003849365499004803</v>
       </c>
       <c r="Q8" t="n">
         <v>0.002774732869135601</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003491611296610976</v>
+        <v>0.003491611296610975</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003841854634028062</v>
+        <v>0.00384185463402806</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003753756738857087</v>
+        <v>0.003753756738857085</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004012823830814726</v>
+        <v>0.00408401805380589</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003693388573763748</v>
+        <v>0.003540104020917052</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004110965399219675</v>
+        <v>0.004110965399219674</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0038041934502011</v>
+        <v>0.003804193450201101</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005915675413996246</v>
+        <v>0.005915675413996251</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003511539803218089</v>
+        <v>0.002941562988436645</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.004022763522848515</v>
+        <v>0.004022763522848513</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004985541465122631</v>
+        <v>0.004985541465122628</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003433315150703595</v>
+        <v>0.003433315150703594</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003380301514284639</v>
+        <v>0.003380301514284638</v>
       </c>
       <c r="D9" t="n">
         <v>0.003808835924828518</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003453832934014749</v>
+        <v>0.003373499296582244</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003711011839142001</v>
+        <v>0.002908608436322187</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004291153142403002</v>
+        <v>0.004291153370419604</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003935972459951221</v>
+        <v>0.003935972459951219</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003887817617660073</v>
+        <v>0.00388781761766007</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004003975357402459</v>
+        <v>0.004003975357402458</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004235340978546324</v>
+        <v>0.004235340978546325</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004118551388736397</v>
+        <v>0.004118551388736394</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003903450471803403</v>
+        <v>0.003903450471803401</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003581942625089155</v>
+        <v>0.003581942625089153</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003855480577155965</v>
+        <v>0.003855480577155964</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004499990274066311</v>
+        <v>0.004499990274066312</v>
       </c>
       <c r="Q9" t="n">
         <v>0.003610686899338735</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003658012121277842</v>
+        <v>0.003658012121277841</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004008255458694929</v>
+        <v>0.00400825545869493</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003920157563523949</v>
+        <v>0.003920157563523953</v>
       </c>
       <c r="U9" t="n">
-        <v>0.00452385384627481</v>
+        <v>0.004523853846274813</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003859789398430614</v>
+        <v>0.004261458194035648</v>
       </c>
       <c r="W9" t="n">
         <v>0.00427725625077725</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004588860424436702</v>
+        <v>0.004588860424436704</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.005526227178692753</v>
+        <v>0.005526227178692755</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003677940627884953</v>
+        <v>0.003468083692593268</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004189164347515377</v>
+        <v>0.00418916434751538</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.004567411800730409</v>
+        <v>0.00456741180073041</v>
       </c>
     </row>
   </sheetData>
@@ -4886,82 +4886,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003248440077933581</v>
+        <v>0.003248440077933588</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00323384221070438</v>
+        <v>0.003233842210704379</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003266025227196107</v>
+        <v>0.003266025227196108</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003248877253571244</v>
+        <v>0.003248877253571247</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003246339729023157</v>
+        <v>0.003246339729023156</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003267434431001305</v>
+        <v>0.003267434431001308</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003274258069680537</v>
+        <v>0.003274258069680541</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003258267503816911</v>
+        <v>0.003258267503816914</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003265425892744286</v>
+        <v>0.00326542589274429</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003281800457481921</v>
+        <v>0.003281800457481923</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003279752879889515</v>
+        <v>0.003279752879889518</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003271267341650376</v>
+        <v>0.003271267341650375</v>
       </c>
       <c r="N2" t="n">
         <v>0.003273979045118133</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004396074500982762</v>
+        <v>0.004396074500982766</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003269808479259127</v>
+        <v>0.003269808479259128</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003258281884346659</v>
+        <v>0.003258281884346662</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003256144355494818</v>
+        <v>0.003256144355494822</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0032637684466677</v>
+        <v>0.003263768446667708</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003253808494652089</v>
+        <v>0.003253808494652091</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006108284203276397</v>
+        <v>0.006108284203276406</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003247557610837942</v>
+        <v>0.003247557610837944</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006487224736783422</v>
+        <v>0.006487224736783434</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003272115239063008</v>
+        <v>0.003272115239063018</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003252593734529487</v>
+        <v>0.00325259373452949</v>
       </c>
       <c r="Z2" t="n">
         <v>0.005178316764125656</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003276405455973661</v>
+        <v>0.003276405455973663</v>
       </c>
       <c r="AB2" t="n">
         <v>0.003295675402262591</v>
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002907230507640975</v>
+        <v>0.002907230507640977</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002823350404786823</v>
+        <v>0.002823350404786821</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0030337402676934</v>
+        <v>0.003033740267693406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002910771473244274</v>
+        <v>0.002910771473244276</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002892976351274892</v>
+        <v>0.002892976351274895</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003041584518473836</v>
+        <v>0.003041584518473843</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003093486388630115</v>
+        <v>0.003093486388630114</v>
       </c>
       <c r="I3" t="n">
         <v>0.002978410427514052</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00302810153983108</v>
+        <v>0.003028101539831085</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003144942427564307</v>
+        <v>0.003144942427564318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003129239730897479</v>
+        <v>0.003129239730897485</v>
       </c>
       <c r="M3" t="n">
         <v>0.003074134397130445</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003089873866500112</v>
+        <v>0.003089873866500117</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004819847521666088</v>
+        <v>0.004819847521666089</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003059221824979075</v>
+        <v>0.003059221824979081</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002977799458107342</v>
+        <v>0.002977799458107346</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002963436734512784</v>
+        <v>0.002963436734512787</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003015245058510854</v>
+        <v>0.003015245058510858</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002946149192051845</v>
+        <v>0.002946149192051852</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007833052386066415</v>
+        <v>0.007833052386066422</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002900973188902633</v>
+        <v>0.002900973188902646</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008675668803819071</v>
+        <v>0.008675668803819083</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003077081676465348</v>
+        <v>0.003077081676465352</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002937329788108479</v>
+        <v>0.002937329788108484</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006153035771507223</v>
+        <v>0.006153035771507225</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003107332411036131</v>
+        <v>0.003107332411036136</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003244778129333421</v>
+        <v>0.003244778129333419</v>
       </c>
     </row>
     <row r="4">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001803598249057346</v>
+        <v>0.001803598249057347</v>
       </c>
       <c r="C4" t="n">
         <v>0.001679146816890058</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002002230599545907</v>
+        <v>0.002002230599545906</v>
       </c>
       <c r="E4" t="n">
         <v>0.001808536348995456</v>
@@ -5077,55 +5077,55 @@
         <v>0.001779873841905828</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002018148204791392</v>
+        <v>0.002018148204791393</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002095224342702222</v>
+        <v>0.002095224342702221</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001914603545248816</v>
+        <v>0.001914603545248815</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001995011638833215</v>
+        <v>0.001995011638833216</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002180419082588638</v>
+        <v>0.002180419082588636</v>
       </c>
       <c r="L4" t="n">
         <v>0.002157290751750185</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00206855602020471</v>
+        <v>0.002068556020204712</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002092072631912167</v>
+        <v>0.002092072631912166</v>
       </c>
       <c r="O4" t="n">
         <v>0.001841679038623355</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002044964171979644</v>
+        <v>0.002044964171979643</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001914765979947689</v>
+        <v>0.001914765979947688</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001890621608254312</v>
+        <v>0.001890621608254311</v>
       </c>
       <c r="S4" t="n">
         <v>0.001976739225307265</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001864236985486592</v>
+        <v>0.001864236985486591</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002221264806625509</v>
+        <v>0.002221264806625511</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001790728842571609</v>
+        <v>0.001790728842571608</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002671627742193018</v>
+        <v>0.002671627742193017</v>
       </c>
       <c r="X4" t="n">
         <v>0.002071020085126459</v>
@@ -5134,10 +5134,10 @@
         <v>0.001844965976942967</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001928720598155432</v>
+        <v>0.00192872059815543</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002119480058729532</v>
+        <v>0.002119480058729533</v>
       </c>
       <c r="AB4" t="n">
         <v>0.002334224259484352</v>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004765564716450151</v>
+        <v>0.004765564716450157</v>
       </c>
       <c r="C5" t="n">
         <v>0.002737373185482389</v>
@@ -5159,76 +5159,76 @@
         <v>0.009079481292572442</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005092974542807284</v>
+        <v>0.005092974542807286</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004726390983825509</v>
+        <v>0.004726390983825549</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00814951416453286</v>
+        <v>0.00814951416453288</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01138722853785357</v>
+        <v>0.01138722853785358</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007443447598226817</v>
+        <v>0.00744344759822682</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008193969004577696</v>
+        <v>0.008193969004577698</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01167757754699384</v>
+        <v>0.01167757754699382</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01063460094619217</v>
+        <v>0.01063460094619218</v>
       </c>
       <c r="M5" t="n">
-        <v>0.009841964373457279</v>
+        <v>0.009841964373457272</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01233487162682349</v>
+        <v>0.0123348716268235</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005340946457779324</v>
+        <v>0.005340946457779323</v>
       </c>
       <c r="P5" t="n">
-        <v>0.009042298304552157</v>
+        <v>0.009042298304552169</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.007049646446299837</v>
+        <v>0.007049646446299839</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007089729989435722</v>
+        <v>0.007089729989435721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.007269148726498227</v>
+        <v>0.007269148726498222</v>
       </c>
       <c r="T5" t="n">
-        <v>0.006248046944041804</v>
+        <v>0.006248046944041803</v>
       </c>
       <c r="U5" t="n">
         <v>0.01246961353567841</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004596934303377205</v>
+        <v>0.00459693430337718</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02152129042790472</v>
+        <v>0.0215212904279047</v>
       </c>
       <c r="X5" t="n">
         <v>0.0103115674491398</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005905405804064547</v>
+        <v>0.005905405804064551</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.006807003119350289</v>
+        <v>0.006807003119350283</v>
       </c>
       <c r="AA5" t="n">
         <v>0.01102275874614978</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01591787447927929</v>
+        <v>0.01591787447927928</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002003753743612138</v>
+        <v>0.002003753743612133</v>
       </c>
       <c r="C6" t="n">
         <v>0.002216382694789458</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002539466477445306</v>
+        <v>0.002202386094100693</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002345772226894855</v>
+        <v>0.002008691843550242</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002317109719805225</v>
+        <v>0.002317109719805229</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002218303699346186</v>
+        <v>0.002555384082690792</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002295379837257013</v>
+        <v>0.002295379837257008</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002451839423148214</v>
+        <v>0.002114759039803602</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002195167133388007</v>
+        <v>0.002195167133388002</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002717654960488038</v>
+        <v>0.002380574577143424</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002694526629649584</v>
+        <v>0.002357446246304971</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002268711514759503</v>
+        <v>0.002605791898104113</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002292964361355324</v>
+        <v>0.002292964361355323</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002382869526951176</v>
+        <v>0.002382869526951178</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002586153960105155</v>
+        <v>0.002224978823226821</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002452001857847089</v>
+        <v>0.002452001857847088</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00242785748615371</v>
+        <v>0.002090777102809098</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002513975103206664</v>
+        <v>0.002176894719862052</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002064392480041382</v>
+        <v>0.00240147286338599</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002764050418666478</v>
+        <v>0.002426970035321867</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001990884337126403</v>
+        <v>0.002327964720471008</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002895227323846324</v>
+        <v>0.002895227323846329</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002271175579681254</v>
+        <v>0.002271175579681247</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002066685140842772</v>
+        <v>0.002066685140842771</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002128876092710221</v>
+        <v>0.002465956476054829</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002319635553284325</v>
+        <v>0.002656715936628933</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002537517228471916</v>
+        <v>0.002537517228471917</v>
       </c>
     </row>
     <row r="7">
@@ -5326,37 +5326,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002110451927606962</v>
+        <v>0.002110451927606963</v>
       </c>
       <c r="C7" t="n">
         <v>0.001986000495439674</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002309084278095521</v>
+        <v>0.002309084278095522</v>
       </c>
       <c r="E7" t="n">
         <v>0.00211539002754507</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002086727520455443</v>
+        <v>0.002086727520455441</v>
       </c>
       <c r="G7" t="n">
         <v>0.002325001883341008</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002402078021251836</v>
+        <v>0.002402078021251835</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002221457223798431</v>
+        <v>0.00222145722379843</v>
       </c>
       <c r="J7" t="n">
         <v>0.00230186531738283</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002487272761138252</v>
+        <v>0.002487272761138251</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002464144430299798</v>
+        <v>0.002464144430299799</v>
       </c>
       <c r="M7" t="n">
         <v>0.002375409698754327</v>
@@ -5365,22 +5365,22 @@
         <v>0.002398926310461781</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002148507109726909</v>
+        <v>0.002148507109726907</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002351792243083196</v>
+        <v>0.002351792243083198</v>
       </c>
       <c r="Q7" t="n">
         <v>0.002221619658497304</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002197475286803927</v>
+        <v>0.002197475286803926</v>
       </c>
       <c r="S7" t="n">
         <v>0.00228359290385688</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002171090664036206</v>
+        <v>0.002171090664036207</v>
       </c>
       <c r="U7" t="n">
         <v>0.002533232708410363</v>
@@ -5389,22 +5389,22 @@
         <v>0.002097582521121224</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002978481420742631</v>
+        <v>0.002978481420742632</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002377873763676075</v>
+        <v>0.002377873763676074</v>
       </c>
       <c r="Y7" t="n">
         <v>0.002157369389634151</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002235574276705045</v>
+        <v>0.002235574276705046</v>
       </c>
       <c r="AA7" t="n">
         <v>0.002426333737279148</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.002641077938033966</v>
+        <v>0.002641077938033964</v>
       </c>
     </row>
     <row r="8">
@@ -5414,25 +5414,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002464462370473047</v>
+        <v>0.002464462370473049</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002864672856612303</v>
+        <v>0.002864672856612304</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003187756639268154</v>
+        <v>0.003187756639268151</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002994062388717701</v>
+        <v>0.00271469539396519</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002522474158244914</v>
+        <v>0.002522474158244918</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003203674244513639</v>
+        <v>0.003312466311061698</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003280750382424466</v>
+        <v>0.003280750382424465</v>
       </c>
       <c r="I8" t="n">
         <v>0.00310012958497106</v>
@@ -5441,58 +5441,58 @@
         <v>0.00318053767855546</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003365945122310884</v>
+        <v>0.003365945122310881</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00334281679147243</v>
+        <v>0.003342816791472431</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003254082059926954</v>
+        <v>0.003254082059926901</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002870897910699255</v>
+        <v>0.002870897910699254</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002732269217374925</v>
+        <v>0.002732269217374924</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002908158073180808</v>
+        <v>0.002908158073180807</v>
       </c>
       <c r="Q8" t="n">
         <v>0.002472522059846314</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003076147647976555</v>
+        <v>0.003076147647976556</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003162265265029512</v>
+        <v>0.003162265265029511</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003049763025208839</v>
+        <v>0.003049763025208836</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003089192670896788</v>
+        <v>0.003155942435099867</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002976254882293857</v>
+        <v>0.002832506493222887</v>
       </c>
       <c r="W8" t="n">
         <v>0.003857256892126759</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002676862471806204</v>
+        <v>0.002676862471806202</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003557157721245663</v>
+        <v>0.003557157721245661</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003114246637877678</v>
+        <v>0.002579838855164729</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003305006098451779</v>
+        <v>0.003305006098451778</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004067803543545113</v>
+        <v>0.004067803543545112</v>
       </c>
     </row>
     <row r="9">
@@ -5502,52 +5502,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002905795438849806</v>
+        <v>0.002905795438849808</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003131757706413462</v>
+        <v>0.003131757706413463</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003454841489069307</v>
+        <v>0.00345484148906931</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003261147238518859</v>
+        <v>0.003180273314442497</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00323248473142923</v>
+        <v>0.002424685298506604</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003470759094314795</v>
+        <v>0.003470759261383722</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003547835232225625</v>
+        <v>0.003547835232225628</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003367214434772218</v>
+        <v>0.00336721443477222</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003447622528356619</v>
+        <v>0.003447622528356618</v>
       </c>
       <c r="K9" t="n">
         <v>0.003633029972112042</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003609901641273588</v>
+        <v>0.003609901641273591</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003521166909728113</v>
+        <v>0.003521166909728115</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00354468352143557</v>
+        <v>0.003544683521435572</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003410416791845339</v>
+        <v>0.003410416791845343</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003638957489320012</v>
+        <v>0.003638957489320014</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003367377036540015</v>
+        <v>0.003367377036540016</v>
       </c>
       <c r="R9" t="n">
         <v>0.003343232497777716</v>
@@ -5556,31 +5556,31 @@
         <v>0.00342935011483067</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003316847875009994</v>
+        <v>0.003316847875009996</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003679425430290484</v>
+        <v>0.003679425430290486</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003243339732095012</v>
+        <v>0.003647709672159818</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004124238631716421</v>
+        <v>0.004124238631716423</v>
       </c>
       <c r="X9" t="n">
         <v>0.003523630974649863</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003303126600607942</v>
+        <v>0.003303126600607943</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003381331487678833</v>
+        <v>0.003170063253084247</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003572090948252938</v>
+        <v>0.003572090948252939</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.003786835149007754</v>
+        <v>0.003786835149007757</v>
       </c>
     </row>
   </sheetData>
@@ -5746,52 +5746,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00322010254493989</v>
+        <v>0.003220102544939891</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00322444628797921</v>
+        <v>0.003224446287979212</v>
       </c>
       <c r="D2" t="n">
         <v>0.00322483238586867</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003224466878008614</v>
+        <v>0.003224466878008615</v>
       </c>
       <c r="F2" t="n">
         <v>0.003225912949153983</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003227780740363666</v>
+        <v>0.003227780740363664</v>
       </c>
       <c r="H2" t="n">
         <v>0.003236402580929124</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003227934856761112</v>
+        <v>0.003227934856761116</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003230551714502017</v>
+        <v>0.003230551714502022</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003224971946399331</v>
+        <v>0.00322497194639933</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003225573877907566</v>
+        <v>0.003225573877907563</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003220432120052087</v>
+        <v>0.003220432120052091</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003231237593441959</v>
+        <v>0.003231237593441961</v>
       </c>
       <c r="O2" t="n">
         <v>0.004359882007103534</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003226341074867534</v>
+        <v>0.003226341074867533</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003221264913489842</v>
+        <v>0.003221264913489841</v>
       </c>
       <c r="R2" t="n">
         <v>0.003234145965201572</v>
@@ -5803,28 +5803,28 @@
         <v>0.00322164942423962</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006041154143935398</v>
+        <v>0.0060411541439354</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003229844100513548</v>
+        <v>0.003229844100513549</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006433979992998526</v>
+        <v>0.006433979992998518</v>
       </c>
       <c r="X2" t="n">
         <v>0.003274019741949374</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003236718228145117</v>
+        <v>0.00323671822814512</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005146357658223281</v>
+        <v>0.005146357658223283</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003252137978735125</v>
+        <v>0.003252137978735124</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003216226994458186</v>
+        <v>0.003216226994458187</v>
       </c>
     </row>
     <row r="3">
@@ -5840,43 +5840,43 @@
         <v>0.002854026863144224</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002870121163122573</v>
+        <v>0.002870121163122574</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002867417228144992</v>
+        <v>0.002867417228144994</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002877932405918288</v>
+        <v>0.00287793240591829</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002890389781066636</v>
+        <v>0.002890389781066638</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002953435187990597</v>
+        <v>0.002953435187990598</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002892451688774345</v>
+        <v>0.002892451688774343</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002910409775958612</v>
+        <v>0.002910409775958613</v>
       </c>
       <c r="K3" t="n">
         <v>0.002870945332509265</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002874749510781509</v>
+        <v>0.002874749510781505</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002843864428698092</v>
+        <v>0.002843864428698095</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002915637410113895</v>
+        <v>0.002915637410113896</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004773078851816328</v>
+        <v>0.004773078851816327</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002880421045487301</v>
+        <v>0.002880421045487306</v>
       </c>
       <c r="Q3" t="n">
         <v>0.002844435625592203</v>
@@ -5885,7 +5885,7 @@
         <v>0.002937025713330329</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00292102445746194</v>
+        <v>0.002921024457461941</v>
       </c>
       <c r="T3" t="n">
         <v>0.002847446199761581</v>
@@ -5894,22 +5894,22 @@
         <v>0.007489570490277321</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002905170039072516</v>
+        <v>0.002905170039072515</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008430733751921268</v>
+        <v>0.008430733751921266</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00322039975829596</v>
+        <v>0.003220399758295961</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002954954018489656</v>
+        <v>0.002954954018489658</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006095600204713978</v>
+        <v>0.006095600204713982</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003064984493883779</v>
+        <v>0.003064984493883777</v>
       </c>
       <c r="AB3" t="n">
         <v>0.002811519051162224</v>
@@ -5925,22 +5925,22 @@
         <v>0.001663096967850608</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001684722772329322</v>
+        <v>0.00168472277232932</v>
       </c>
       <c r="D4" t="n">
         <v>0.001716522696975508</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001712394117554254</v>
+        <v>0.001712394117554251</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001728728156366793</v>
+        <v>0.001728728156366796</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001749825717306529</v>
+        <v>0.001749825717306527</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001847213372736031</v>
+        <v>0.001847213372736028</v>
       </c>
       <c r="I4" t="n">
         <v>0.001751566532912777</v>
@@ -5949,58 +5949,58 @@
         <v>0.001780827491514234</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001718099097370341</v>
+        <v>0.001718099097370338</v>
       </c>
       <c r="L4" t="n">
         <v>0.001724898190658034</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00167630212547909</v>
+        <v>0.001676302125479088</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001788872463056874</v>
+        <v>0.001788872463056876</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001778530653054317</v>
+        <v>0.00177853065305432</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0017335640332489</v>
+        <v>0.001733564033248899</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001676226455338275</v>
+        <v>0.001676226455338276</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001821723859998806</v>
+        <v>0.001821723859998805</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001798835211816099</v>
+        <v>0.001798835211816096</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001680569681140691</v>
+        <v>0.001680569681140689</v>
       </c>
       <c r="U4" t="n">
         <v>0.001653390925014099</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001771246426754047</v>
+        <v>0.001771246426754048</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002261263652312401</v>
+        <v>0.002261263652312399</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002272116511208768</v>
+        <v>0.002272116511208773</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001848057389377502</v>
+        <v>0.001848057389377503</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001829063358318975</v>
+        <v>0.001829063358318971</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002024951929595427</v>
+        <v>0.002024951929595425</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001624262326457244</v>
+        <v>0.001624262326457247</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003070647092542421</v>
+        <v>0.003070647092542423</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003580208392358243</v>
+        <v>0.003580208392358241</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004136505416478884</v>
+        <v>0.004136505416478877</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004014104519395573</v>
+        <v>0.004014104519395578</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004403791534236461</v>
+        <v>0.004403791534236456</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004324452034059616</v>
+        <v>0.004324452034059612</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00682989960294451</v>
+        <v>0.006829899602944501</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0048537584957085</v>
+        <v>0.004853758495708521</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005003879717734003</v>
+        <v>0.005003879717733998</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004075313642442527</v>
+        <v>0.004075313642442524</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003940684802618965</v>
+        <v>0.003940684802618968</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003423155576028675</v>
+        <v>0.003423155576028674</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003116239495737733</v>
+        <v>0.00311623949573773</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004835399402401284</v>
+        <v>0.004835399402401279</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004195532657855401</v>
+        <v>0.0041955326578554</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003307557265404243</v>
+        <v>0.00330755726540424</v>
       </c>
       <c r="R5" t="n">
-        <v>0.006221589249610536</v>
+        <v>0.006221589249610546</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005019199153229214</v>
+        <v>0.005019199153229213</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003522378534574175</v>
+        <v>0.003522378534574173</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002983479321563002</v>
+        <v>0.002983479321563003</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004762742026625432</v>
+        <v>0.00476274202662546</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01311739582271722</v>
+        <v>0.01311739582271723</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01356198397800641</v>
+        <v>0.01356198397800644</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.006512603358069587</v>
+        <v>0.006512603358069603</v>
       </c>
       <c r="Z5" t="n">
         <v>0.005602111733471487</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.009582233065460924</v>
+        <v>0.009582233065460908</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002572195231932242</v>
+        <v>0.00257219523193224</v>
       </c>
     </row>
     <row r="6">
@@ -6098,82 +6098,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001860678920361313</v>
+        <v>0.001860678920361315</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00218393047032614</v>
+        <v>0.001882304724840028</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001914104649486218</v>
+        <v>0.001914104649486216</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00221160181555107</v>
+        <v>0.002211601815551069</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002227935854363612</v>
+        <v>0.002227935854363611</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002249033415303347</v>
+        <v>0.001947407669817235</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002346421070732846</v>
+        <v>0.002044795325246736</v>
       </c>
       <c r="I6" t="n">
         <v>0.001949148485423485</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002280035189511052</v>
+        <v>0.001978409444024942</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001915681049881044</v>
+        <v>0.001915681049881046</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002224105888654849</v>
+        <v>0.00222410588865485</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001873884077989795</v>
+        <v>0.002175509823475905</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001986673349532837</v>
+        <v>0.001986673349532841</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001976331539530281</v>
+        <v>0.001976331539530282</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002235669672694909</v>
+        <v>0.001911472925959926</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002175434153335096</v>
+        <v>0.001873808407848984</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002320931557995625</v>
+        <v>0.002320931557995623</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002298042909812916</v>
+        <v>0.001996417164326805</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002179777379137509</v>
+        <v>0.002179777379137508</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001853694241392857</v>
+        <v>0.001853694241392856</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001968828379264756</v>
+        <v>0.002270454124750864</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002479355227980536</v>
+        <v>0.002479355227980521</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002469698463719479</v>
+        <v>0.002469698463719481</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00206362279554605</v>
+        <v>0.002063622795546052</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00232827105631579</v>
+        <v>0.002328271056315789</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002222533882106133</v>
+        <v>0.002524159627592242</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001821370564039079</v>
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001925144203399808</v>
+        <v>0.001925144203399806</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001946770007878519</v>
+        <v>0.001946770007878518</v>
       </c>
       <c r="D7" t="n">
         <v>0.001978569932524707</v>
@@ -6201,19 +6201,19 @@
         <v>0.001990775391915994</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002011872952855728</v>
+        <v>0.002011872952855725</v>
       </c>
       <c r="H7" t="n">
         <v>0.002109260608285227</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002013613768461976</v>
+        <v>0.002013613768461975</v>
       </c>
       <c r="J7" t="n">
         <v>0.002042874727063433</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001980146332919537</v>
+        <v>0.001980146332919536</v>
       </c>
       <c r="L7" t="n">
         <v>0.001986945426207233</v>
@@ -6225,13 +6225,13 @@
         <v>0.002050919698606076</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002040554113136089</v>
+        <v>0.002040554113136086</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001995587493330666</v>
+        <v>0.001995587493330664</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001938273690887475</v>
+        <v>0.001938273690887474</v>
       </c>
       <c r="R7" t="n">
         <v>0.002083771095548004</v>
@@ -6243,19 +6243,19 @@
         <v>0.001942616916689889</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001917774874042114</v>
+        <v>0.001917774874042111</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002033293662303249</v>
+        <v>0.002033293662303247</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002523310887861602</v>
+        <v>0.002523310887861599</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002534163746757969</v>
+        <v>0.00253416374675797</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00211282598879475</v>
+        <v>0.002112825988794752</v>
       </c>
       <c r="Z7" t="n">
         <v>0.002091110593868171</v>
@@ -6274,49 +6274,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002240494597277621</v>
+        <v>0.002240494597277624</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002724216212602537</v>
+        <v>0.002724216212602538</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002756016137248726</v>
+        <v>0.002756016137248724</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00275188755782747</v>
+        <v>0.002505835169699298</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002378114912407685</v>
+        <v>0.002378114912407686</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002789319157579745</v>
+        <v>0.002885137734170605</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002886706813009246</v>
+        <v>0.002886706813009244</v>
       </c>
       <c r="I8" t="n">
         <v>0.002791059973185994</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002820320931787451</v>
+        <v>0.00282032093178745</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002757592537643557</v>
+        <v>0.002757592537643553</v>
       </c>
       <c r="L8" t="n">
         <v>0.00276439163093125</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002715795565752304</v>
+        <v>0.00271579556575222</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002470164342774935</v>
+        <v>0.002470164342774934</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002558259431395048</v>
+        <v>0.00255825943139505</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002489163549214124</v>
+        <v>0.002489163549214123</v>
       </c>
       <c r="Q8" t="n">
         <v>0.002162811711347573</v>
@@ -6325,34 +6325,34 @@
         <v>0.002861217300272021</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002838328652089312</v>
+        <v>0.002838328652089313</v>
       </c>
       <c r="T8" t="n">
         <v>0.002720063121413906</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00241099342203083</v>
+        <v>0.002469783261709629</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002810739867027265</v>
+        <v>0.002684133646927398</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003300847906829873</v>
+        <v>0.003300847906829871</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002801053765970151</v>
+        <v>0.002801053765970154</v>
       </c>
       <c r="Y8" t="n">
         <v>0.003349245107379008</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002868556798592188</v>
+        <v>0.00239787732090095</v>
       </c>
       <c r="AA8" t="n">
         <v>0.003064445369868642</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003146453480195947</v>
+        <v>0.003146453480195945</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002551855559985949</v>
+        <v>0.002551855559985946</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002860718476269619</v>
+        <v>0.002860718476269617</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002892518400915808</v>
+        <v>0.002892518400915807</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002888389821494552</v>
+        <v>0.002822096812711418</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002904723860307094</v>
+        <v>0.002242563677094213</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002925821421246829</v>
+        <v>0.002925821609756768</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003023209076676328</v>
+        <v>0.003023209076676326</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002927562236853079</v>
+        <v>0.002927562236853076</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002956823195454532</v>
+        <v>0.002956823195454531</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002894094801310638</v>
+        <v>0.002894094801310631</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002900893894598335</v>
+        <v>0.002900893894598333</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002852297829419387</v>
+        <v>0.002852297829419384</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002964868166997175</v>
+        <v>0.002964868166997172</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003049716610723767</v>
+        <v>0.003049716610723763</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003025452196917049</v>
+        <v>0.003025452196917047</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00285222234778852</v>
+        <v>0.002852222347788515</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002997719563939105</v>
+        <v>0.002997719563939102</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002974830915756396</v>
+        <v>0.002974830915756392</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002856565385080987</v>
+        <v>0.002856565385080985</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002832107992822449</v>
+        <v>0.002832107992822447</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002947242130694349</v>
+        <v>0.003278707777790112</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003437259356252701</v>
+        <v>0.003437259356252698</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003448112215149071</v>
+        <v>0.003448112215149068</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00302677445718585</v>
+        <v>0.003026774457185849</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003005059062259271</v>
+        <v>0.002831880700816649</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003200947633535723</v>
+        <v>0.00320094763353572</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002800258030397547</v>
+        <v>0.002800258030397543</v>
       </c>
     </row>
   </sheetData>
@@ -6606,52 +6606,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003251324870157428</v>
+        <v>0.003251324870157429</v>
       </c>
       <c r="C2" t="n">
         <v>0.003216426575154256</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003253183749929129</v>
+        <v>0.003253183749929127</v>
       </c>
       <c r="E2" t="n">
         <v>0.003256242851490673</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003252588119749606</v>
+        <v>0.003252588119749608</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003251372844463717</v>
+        <v>0.003251372844463718</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003257567321553535</v>
+        <v>0.003257567321553536</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003251701606537471</v>
+        <v>0.003251701606537472</v>
       </c>
       <c r="J2" t="n">
         <v>0.003256174549732494</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003249765177982867</v>
+        <v>0.00324976517798287</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003254312670127213</v>
+        <v>0.003254312670127214</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003248996306772381</v>
+        <v>0.003248996306772379</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003254253145918337</v>
+        <v>0.003254253145918339</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004402998456516657</v>
+        <v>0.004402998456516656</v>
       </c>
       <c r="P2" t="n">
         <v>0.003255732828611327</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003248589916753858</v>
+        <v>0.003248589916753859</v>
       </c>
       <c r="R2" t="n">
         <v>0.003263641795620334</v>
@@ -6660,31 +6660,31 @@
         <v>0.00325711415575856</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003249341687415566</v>
+        <v>0.003249341687415565</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005972788022912996</v>
+        <v>0.005972788022912991</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003260558735286042</v>
+        <v>0.003260558735286041</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006382576469878973</v>
+        <v>0.006382576469878975</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003315774350847969</v>
+        <v>0.003315774350847968</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003262173140667697</v>
+        <v>0.003262173140667698</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005170061285675901</v>
+        <v>0.005170061285675906</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003283084122029732</v>
+        <v>0.003283084122029733</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003247103275978104</v>
+        <v>0.003247103275978106</v>
       </c>
     </row>
     <row r="3">
@@ -6697,82 +6697,82 @@
         <v>0.002890531419152468</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002824703039634834</v>
+        <v>0.002824703039634832</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002904217222740868</v>
+        <v>0.002904217222740866</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002925615822273881</v>
+        <v>0.00292561582227388</v>
       </c>
       <c r="F3" t="n">
         <v>0.002900104020253332</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002890821844422357</v>
+        <v>0.002890821844422358</v>
       </c>
       <c r="H3" t="n">
         <v>0.002935944632960049</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002893768873278707</v>
+        <v>0.002893768873278705</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002925179783084896</v>
+        <v>0.002925179783084894</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002879745825033725</v>
+        <v>0.002879745825033724</v>
       </c>
       <c r="L3" t="n">
         <v>0.002911652193157239</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002879419765359424</v>
+        <v>0.002879419765359423</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002911747652233948</v>
+        <v>0.002911747652233949</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004832718094322945</v>
+        <v>0.004832718094322943</v>
       </c>
       <c r="P3" t="n">
         <v>0.002921724598551781</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002871273578865981</v>
+        <v>0.002871273578865982</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002979362117864625</v>
+        <v>0.002979362117864624</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002931552666716138</v>
+        <v>0.002931552666716137</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00287683660049647</v>
+        <v>0.002876836600496468</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007371244316622542</v>
+        <v>0.007371244316622538</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002956049904515819</v>
+        <v>0.00295604990451582</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008271357309862188</v>
+        <v>0.008271357309862191</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003349497874625241</v>
+        <v>0.003349497874625239</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002968407219777792</v>
+        <v>0.002968407219777791</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006090960827013894</v>
+        <v>0.006090960827013895</v>
       </c>
       <c r="AA3" t="n">
         <v>0.003117604826394767</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00286321820072839</v>
+        <v>0.002863218200728389</v>
       </c>
     </row>
     <row r="4">
@@ -6782,22 +6782,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001736887845097216</v>
+        <v>0.001736887845097217</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001719235481439128</v>
+        <v>0.001719235481439129</v>
       </c>
       <c r="D4" t="n">
         <v>0.001757884747245513</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00179243870663942</v>
+        <v>0.001792438706639421</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001751156830364416</v>
+        <v>0.001751156830364418</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001737429736956033</v>
+        <v>0.001737429736956036</v>
       </c>
       <c r="H4" t="n">
         <v>0.001807399205285787</v>
@@ -6806,22 +6806,22 @@
         <v>0.001741143255817124</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001791401878496619</v>
+        <v>0.001791401878496618</v>
       </c>
       <c r="K4" t="n">
         <v>0.001719270404491723</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001770636420211834</v>
+        <v>0.001770636420211833</v>
       </c>
       <c r="M4" t="n">
         <v>0.001719876994747388</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001769964066890106</v>
+        <v>0.001769964066890107</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001822459557310065</v>
+        <v>0.001822459557310066</v>
       </c>
       <c r="P4" t="n">
         <v>0.001786677763595071</v>
@@ -6830,13 +6830,13 @@
         <v>0.001705995288263204</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001876013184266347</v>
+        <v>0.001876013184266349</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00180228048916497</v>
+        <v>0.001802280489164971</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001714486883718737</v>
+        <v>0.001714486883718738</v>
       </c>
       <c r="U4" t="n">
         <v>0.001712347060006094</v>
@@ -6845,22 +6845,22 @@
         <v>0.001839525280567041</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002174304651168832</v>
+        <v>0.002174304651168833</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002464874377722758</v>
+        <v>0.002464874377722759</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001859112534386965</v>
+        <v>0.001859112534386968</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001806293207255497</v>
+        <v>0.001806293207255499</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002095623204972576</v>
+        <v>0.002095623204972577</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001693319372728908</v>
+        <v>0.001693319372728909</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003734849555067495</v>
+        <v>0.003734849555067496</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00362503597801151</v>
+        <v>0.003625035978011512</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004323291473911124</v>
+        <v>0.004323291473911119</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004709338771438139</v>
+        <v>0.00470933877143814</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004275729146345881</v>
+        <v>0.004275729146345879</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003717501802047865</v>
+        <v>0.003717501802047864</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00542790563784094</v>
+        <v>0.005427905637840937</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004094446709986249</v>
+        <v>0.004094446709986232</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004722082494073075</v>
+        <v>0.00472208249407308</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003602565249662343</v>
+        <v>0.003602565249662341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004226391994237607</v>
+        <v>0.004226391994237604</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003671976987082557</v>
+        <v>0.003671976987082558</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003419633206489508</v>
+        <v>0.003419633206489505</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005028172852415148</v>
+        <v>0.005028172852415147</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004477287082766067</v>
+        <v>0.004477287082766063</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003324061601317642</v>
+        <v>0.003324061601317644</v>
       </c>
       <c r="R5" t="n">
-        <v>0.006674447605989372</v>
+        <v>0.006674447605989378</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004737424311504414</v>
+        <v>0.004737424311504409</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00357664909012617</v>
+        <v>0.003576649090126171</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003362327716180229</v>
+        <v>0.00336232771618023</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005378882437470141</v>
+        <v>0.005378882437470147</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01129627106993109</v>
+        <v>0.01129627106993106</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01608568593099599</v>
+        <v>0.01608568593099597</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.006135903271035636</v>
+        <v>0.006135903271035643</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004699405143313867</v>
+        <v>0.004699405143313866</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01029009804867714</v>
+        <v>0.01029009804867712</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003264839612700269</v>
+        <v>0.00326483961270027</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002289157769562618</v>
+        <v>0.002289157769562619</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00227150540590453</v>
+        <v>0.002271505405904529</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002310154671710915</v>
+        <v>0.002310154671710914</v>
       </c>
       <c r="E6" t="n">
         <v>0.002344708631104823</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00198199095538236</v>
+        <v>0.002303426754829819</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001968263861973979</v>
+        <v>0.002289699661421439</v>
       </c>
       <c r="H6" t="n">
         <v>0.002038233330303731</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002293413180282527</v>
+        <v>0.001971977380835068</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002343671802962023</v>
+        <v>0.002022236003514563</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001950104529509669</v>
+        <v>0.002271540328957126</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002322906344677236</v>
+        <v>0.002322906344677235</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00227214691921279</v>
+        <v>0.002272146919212791</v>
       </c>
       <c r="N6" t="n">
         <v>0.002000820321354517</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002053315811774473</v>
+        <v>0.002376058241029829</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00234027331219422</v>
+        <v>0.002340273312194219</v>
       </c>
       <c r="Q6" t="n">
         <v>0.002258265212728605</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002428283108731749</v>
+        <v>0.00210684730928429</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002033114614182914</v>
+        <v>0.002033114614182913</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00226675680818414</v>
+        <v>0.002266756808184139</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002264928501046232</v>
+        <v>0.002264928501046231</v>
       </c>
       <c r="V6" t="n">
         <v>0.002070359405584986</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002727906623074245</v>
+        <v>0.002727906623074243</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003017144302188161</v>
+        <v>0.0026957085027407</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002107961553583392</v>
+        <v>0.002107961553583393</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002358563131720898</v>
+        <v>0.002037127332273441</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002647893129437977</v>
+        <v>0.00232645732999052</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001923614838220568</v>
+        <v>0.001923614838220569</v>
       </c>
     </row>
     <row r="7">
@@ -7046,61 +7046,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001978928363383294</v>
+        <v>0.001978928363383293</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001961275999725206</v>
+        <v>0.001961275999725204</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001999925265531592</v>
+        <v>0.001999925265531591</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002034479224925498</v>
+        <v>0.002034479224925497</v>
       </c>
       <c r="F7" t="n">
         <v>0.001993197348650493</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001979470255242111</v>
+        <v>0.001979470255242114</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002049439723571865</v>
+        <v>0.002049439723571864</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001983183774103202</v>
+        <v>0.0019831837741032</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002033442396782697</v>
+        <v>0.002033442396782695</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001961310922777801</v>
+        <v>0.0019613109227778</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002012676938497912</v>
+        <v>0.002012676938497911</v>
       </c>
       <c r="M7" t="n">
         <v>0.001961917513033466</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002012004585176185</v>
+        <v>0.002012004585176183</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002064475846313885</v>
+        <v>0.002064475846313884</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002028694052598889</v>
+        <v>0.00202869405259889</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00194803580654928</v>
+        <v>0.001948035806549279</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002118053702552423</v>
+        <v>0.002118053702552422</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002044321007451047</v>
+        <v>0.002044321007451046</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001956527402004815</v>
+        <v>0.001956527402004814</v>
       </c>
       <c r="U7" t="n">
         <v>0.001954351171131167</v>
@@ -7112,19 +7112,19 @@
         <v>0.00241634516945491</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002706914896008832</v>
+        <v>0.002706914896008833</v>
       </c>
       <c r="Y7" t="n">
         <v>0.002101464569247778</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002048333725541574</v>
+        <v>0.002048333725541573</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002337663723258655</v>
+        <v>0.002337663723258652</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001935359891014985</v>
+        <v>0.001935359891014984</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002314058759505513</v>
+        <v>0.002314058759505511</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002773118866407662</v>
+        <v>0.002773118866407658</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002811768132214047</v>
+        <v>0.002811768132214044</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002846322091607954</v>
+        <v>0.002592486763345093</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002402593976141875</v>
+        <v>0.002402593976141873</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002791313121924566</v>
+        <v>0.002890162558126399</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002861282590254323</v>
+        <v>0.00286128259025432</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002795026640785658</v>
+        <v>0.002795026640785655</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002845285263465158</v>
+        <v>0.002845285263465151</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002773153789460258</v>
+        <v>0.002773153789460256</v>
       </c>
       <c r="L8" t="n">
         <v>0.002824519805180367</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002773760379715922</v>
+        <v>0.002773760379715829</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002454315534712454</v>
+        <v>0.002454315534712452</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002608361604129354</v>
+        <v>0.002608361604129352</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002547687309741694</v>
+        <v>0.00254768730974169</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002189481322008836</v>
+        <v>0.002189481322008837</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00292989656923488</v>
+        <v>0.002929896569234879</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002856163874133505</v>
+        <v>0.002856163874133503</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002768370268687271</v>
+        <v>0.00276837026868727</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002472962378979573</v>
+        <v>0.002533614111537263</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002893408665535576</v>
+        <v>0.002762839272890638</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003228281722980016</v>
+        <v>0.003228281722980011</v>
       </c>
       <c r="X8" t="n">
         <v>0.00299205205613083</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003386862654135315</v>
+        <v>0.003386862654135311</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002860176592224032</v>
+        <v>0.002374608942859401</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003149506589941109</v>
+        <v>0.003149506589941104</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003245168794465804</v>
+        <v>0.0032451687944658</v>
       </c>
     </row>
     <row r="9">
@@ -7228,28 +7228,28 @@
         <v>0.002801655085579784</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002840304351386171</v>
+        <v>0.002840304351386169</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002874858310780077</v>
+        <v>0.002812082546117786</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002833576434505069</v>
+        <v>0.002206547870613682</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002819849341096689</v>
+        <v>0.002819849516690315</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002889818809426445</v>
+        <v>0.002889818809426444</v>
       </c>
       <c r="I9" t="n">
         <v>0.002823562859957779</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002873821482637277</v>
+        <v>0.002873821482637275</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002801690008632379</v>
+        <v>0.00280169000863238</v>
       </c>
       <c r="L9" t="n">
         <v>0.002853056024352489</v>
@@ -7258,46 +7258,46 @@
         <v>0.002802296598888045</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002852383671030763</v>
+        <v>0.002852383671030762</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002995018990751809</v>
+        <v>0.002995018990751808</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00297884102518218</v>
+        <v>0.002978841025182179</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002788415067997486</v>
+        <v>0.002788415067997487</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002958432788407004</v>
+        <v>0.002958432788407</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002884700093305626</v>
+        <v>0.002884700093305625</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002796906487859396</v>
+        <v>0.002796906487859393</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002795078180721486</v>
+        <v>0.002795078180721485</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002921944884707698</v>
+        <v>0.00323582425941921</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003256724255309489</v>
+        <v>0.003256724255309488</v>
       </c>
       <c r="X9" t="n">
         <v>0.003547293981863415</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002941843655102355</v>
+        <v>0.002941843655102357</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002888712811396152</v>
+        <v>0.002724722611667152</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003178042809113232</v>
+        <v>0.003178042809113233</v>
       </c>
       <c r="AB9" t="n">
         <v>0.002775738976869564</v>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003364284648874903</v>
+        <v>0.003364284648874905</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003323973162958618</v>
+        <v>0.003323973162958619</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003367235487719654</v>
+        <v>0.003367235487719653</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003339209433714963</v>
+        <v>0.003339209433714966</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003343985306649531</v>
+        <v>0.003343985306649533</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003427876455421734</v>
+        <v>0.003427876455421739</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003389108478982826</v>
+        <v>0.003389108478982829</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003364046177860797</v>
+        <v>0.003364046177860798</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003392483329456451</v>
+        <v>0.003392483329456453</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00339050104654439</v>
+        <v>0.003390501046544392</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003418478521182891</v>
+        <v>0.003418478521182893</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003420753807935961</v>
+        <v>0.00342075380793596</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003392433053723198</v>
+        <v>0.003392433053723201</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004551124696832399</v>
+        <v>0.004551124696832398</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003404880569153872</v>
+        <v>0.003404880569153875</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003351735221335661</v>
+        <v>0.00335173522133566</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00335640165588828</v>
+        <v>0.003356401655888282</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003373801760155793</v>
+        <v>0.003373801760155795</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003367871927852868</v>
+        <v>0.003367871927852867</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006247248155862598</v>
+        <v>0.006247248155862605</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003343705263107209</v>
+        <v>0.003343705263107211</v>
       </c>
       <c r="W2" t="n">
         <v>0.006581178751786499</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003409321713634095</v>
+        <v>0.003409321713634098</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003390693262864062</v>
+        <v>0.003390693262864068</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005288373105211372</v>
+        <v>0.005288373105211371</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003388642316913213</v>
+        <v>0.003388642316913216</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003442592332757899</v>
+        <v>0.003442592332757898</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003196355676711716</v>
+        <v>0.003196355676711712</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002930214376346461</v>
+        <v>0.002930214376346462</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003219979796410405</v>
+        <v>0.003219979796410399</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003018803465203757</v>
+        <v>0.003018803465203758</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003053503326504091</v>
+        <v>0.003053503326504087</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0036476696700113</v>
+        <v>0.003647669670011305</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003377689870001165</v>
+        <v>0.003377689870001163</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003197180125729498</v>
+        <v>0.003197180125729495</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003397457063684067</v>
+        <v>0.003397457063684069</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003383515071841582</v>
+        <v>0.003383515071841584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00358313677147691</v>
+        <v>0.003583136771476906</v>
       </c>
       <c r="M3" t="n">
         <v>0.003602330545160935</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003399397756761504</v>
+        <v>0.003399397756761499</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005145229860133139</v>
+        <v>0.00514522986013313</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003485510939403897</v>
+        <v>0.00348551093940389</v>
       </c>
       <c r="Q3" t="n">
         <v>0.003108350488830704</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003142842389083082</v>
+        <v>0.003142842389083079</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003263442274749294</v>
+        <v>0.003263442274749289</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003224500478231832</v>
+        <v>0.00322450047823183</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008212513049056985</v>
+        <v>0.008212513049056991</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00305009898030328</v>
+        <v>0.003050098980303284</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008729420377985814</v>
+        <v>0.00872942037798582</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003520536946728509</v>
+        <v>0.003520536946728505</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003386110673095549</v>
+        <v>0.003386110673095545</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006354386874070055</v>
+        <v>0.006354386874070056</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00337174776080413</v>
+        <v>0.003371747760804126</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003757617500693882</v>
+        <v>0.003757617500693884</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002289724208541358</v>
+        <v>0.002289724208541371</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00187479773770249</v>
+        <v>0.001874797737702497</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002323055290745783</v>
+        <v>0.002323055290745788</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002006488118140988</v>
+        <v>0.002006488118141001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002060433799947027</v>
+        <v>0.002060433799947034</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003008022917164131</v>
+        <v>0.003008022917164142</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002570120789136396</v>
+        <v>0.002570120789136402</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002287030568734969</v>
+        <v>0.002287030568734974</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002607520175599605</v>
+        <v>0.002607520175599614</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002585850480357012</v>
+        <v>0.002585850480357021</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002901868926673039</v>
+        <v>0.002901868926673051</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002931385404634922</v>
+        <v>0.002931385404634928</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002607673390208857</v>
+        <v>0.00260767339020886</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00226933622766556</v>
+        <v>0.002269336227665565</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002748273803138332</v>
+        <v>0.00274827380313833</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00214797265146374</v>
+        <v>0.002147972651463749</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002200682176401544</v>
+        <v>0.002200682176401557</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002397224358546515</v>
+        <v>0.00239722435854653</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002330244174827364</v>
+        <v>0.002330244174827375</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002806297374172151</v>
+        <v>0.002806297374172159</v>
       </c>
       <c r="V4" t="n">
         <v>0.002052529686730408</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002745472444614658</v>
+        <v>0.002745472444614662</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002798438573069808</v>
+        <v>0.002798438573069817</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002575771153140408</v>
+        <v>0.002575771153140417</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002252105809634449</v>
+        <v>0.002252105809634461</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002564855274114973</v>
+        <v>0.002564855274114983</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003166951262059165</v>
+        <v>0.003166951262059173</v>
       </c>
     </row>
     <row r="5">
@@ -7730,73 +7730,73 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01105123149318306</v>
+        <v>0.01105123149318307</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004117314089968057</v>
+        <v>0.004117314089968066</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0131073354429919</v>
+        <v>0.01310733544299187</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006480477467539381</v>
+        <v>0.00648047746753941</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007842076035807449</v>
+        <v>0.007842076035807447</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02321795905796066</v>
+        <v>0.02321795905796067</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01866947327724584</v>
+        <v>0.01866947327724583</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01240537932696389</v>
+        <v>0.01240537932696391</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01698735210596411</v>
+        <v>0.01698735210596413</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01667908848899232</v>
+        <v>0.0166790884889923</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0226237847660199</v>
+        <v>0.02262378476601991</v>
       </c>
       <c r="M5" t="n">
         <v>0.0236721793256433</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02102973230600588</v>
+        <v>0.0210297323060059</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01048784880396214</v>
+        <v>0.01048784880396215</v>
       </c>
       <c r="P5" t="n">
         <v>0.0193989618236929</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009238994564488347</v>
+        <v>0.009238994564488352</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01089595426685681</v>
+        <v>0.01089595426685682</v>
       </c>
       <c r="S5" t="n">
         <v>0.01261805676398286</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01323123642032084</v>
+        <v>0.01323123642032086</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02124060678894035</v>
+        <v>0.02124060678894039</v>
       </c>
       <c r="V5" t="n">
-        <v>0.006995763476761665</v>
+        <v>0.006995763476761662</v>
       </c>
       <c r="W5" t="n">
         <v>0.02057423577800525</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0221990912006837</v>
+        <v>0.02219909120068374</v>
       </c>
       <c r="Y5" t="n">
         <v>0.01740072866614136</v>
@@ -7808,7 +7808,7 @@
         <v>0.01711552674979334</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03116326024937718</v>
+        <v>0.03116326024937716</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002895816593998977</v>
+        <v>0.002895816593998983</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002082569150654201</v>
+        <v>0.002082569150654213</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002929147676203398</v>
+        <v>0.002929147676203403</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002612580503598608</v>
+        <v>0.002612580503598615</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002666526185404645</v>
+        <v>0.002666526185404646</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003215794330115847</v>
+        <v>0.003215794330115856</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00317621317459401</v>
+        <v>0.003176213174594015</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002494801981686685</v>
+        <v>0.002494801981686691</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00321361256105722</v>
+        <v>0.00281529158855133</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002793621893308728</v>
+        <v>0.002793621893308738</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003109640339624754</v>
+        <v>0.003507961312130663</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003537477790092532</v>
+        <v>0.003537477790092541</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002817473730049407</v>
+        <v>0.002817473730049427</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00247913656750611</v>
+        <v>0.002479136567506134</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003359059786736861</v>
+        <v>0.003359059786736869</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002355744064415457</v>
+        <v>0.002754065036921363</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00280677456185916</v>
+        <v>0.002806774561859172</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003003316744004131</v>
+        <v>0.003003316744004143</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002936336560284978</v>
+        <v>0.002538015587779091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003424640258600922</v>
+        <v>0.003424640258600931</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002260301099682124</v>
+        <v>0.002658622072188023</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002977127378923311</v>
+        <v>0.002977127378923309</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003404530958527423</v>
+        <v>0.003006209986021533</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002812860384195672</v>
+        <v>0.002812860384195705</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002459877222586166</v>
+        <v>0.002459877222586178</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003170947659572592</v>
+        <v>0.003170947659572596</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003381629631055243</v>
+        <v>0.003381629631055249</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00263553477581912</v>
+        <v>0.002635534775819124</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002220608304980247</v>
+        <v>0.002220608304980251</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002668865858023544</v>
+        <v>0.002668865858023542</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002352298685418749</v>
+        <v>0.002352298685418754</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002406244367224783</v>
+        <v>0.002406244367224786</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003353833484441893</v>
+        <v>0.003353833484441895</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002915931356414148</v>
+        <v>0.002915931356414156</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002632841136012731</v>
+        <v>0.002632841136012727</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002953330742877372</v>
+        <v>0.002953330742877369</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002931661047634772</v>
+        <v>0.002931661047634776</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003247679493950795</v>
+        <v>0.003247679493950805</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003277195971912683</v>
+        <v>0.003277195971912681</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002953483957486613</v>
+        <v>0.002953483957486614</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002615120689053704</v>
+        <v>0.002615120689053711</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003094058264526463</v>
+        <v>0.003094058264526473</v>
       </c>
       <c r="Q7" t="n">
         <v>0.002493783218741503</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002546492743679307</v>
+        <v>0.002546492743679312</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002743034925824279</v>
+        <v>0.002743034925824284</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002676054742105131</v>
+        <v>0.002676054742105129</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00316386578945791</v>
+        <v>0.003163865789457917</v>
       </c>
       <c r="V7" t="n">
         <v>0.002398340254008162</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003091283011892409</v>
+        <v>0.003091283011892416</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00314424914034757</v>
+        <v>0.003144249140347571</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002933832219389323</v>
+        <v>0.002933832219389328</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002597916376912211</v>
+        <v>0.002597916376912214</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002910665841392734</v>
+        <v>0.002910665841392737</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003512761829336927</v>
+        <v>0.003512761829336928</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003023531459734015</v>
+        <v>0.003023531459734024</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00318966393412383</v>
+        <v>0.003189663934123841</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003637921487167127</v>
+        <v>0.003637921487167131</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003321354314562335</v>
+        <v>0.003011957566585367</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002884763243729927</v>
+        <v>0.002884763243729939</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004322889113585478</v>
+        <v>0.004443375471057247</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003884986985557737</v>
+        <v>0.003884986985557743</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003601896765156304</v>
+        <v>0.003601896765156316</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003922386372020944</v>
+        <v>0.003922386372020956</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003900716676778357</v>
+        <v>0.003900716676778367</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004216735123094379</v>
+        <v>0.004216735123094392</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004246251601056258</v>
+        <v>0.004246251601056223</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003472121694809524</v>
+        <v>0.00347212169480953</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003257563279379427</v>
+        <v>0.003257563279379435</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00370615969307125</v>
+        <v>0.003706159693071262</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002767588558154419</v>
+        <v>0.002767588558154429</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003515548372822889</v>
+        <v>0.003515548372822898</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003712090554967859</v>
+        <v>0.003712090554967868</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003645110371248703</v>
+        <v>0.003645110371248715</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003775521148504206</v>
+        <v>0.003849445392188135</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003367395883151747</v>
+        <v>0.003208184920400916</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004060452834863673</v>
+        <v>0.004060452834863683</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003471309686111897</v>
+        <v>0.003471309686111903</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004480003006111626</v>
+        <v>0.004480003006111633</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003566972006055793</v>
+        <v>0.002975119592692976</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003879721470536317</v>
+        <v>0.003879721470536327</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.005088782113266915</v>
+        <v>0.00508878211326692</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003634104553236121</v>
+        <v>0.003634104553236127</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003640942990599189</v>
+        <v>0.003640942990599197</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004089200543642486</v>
+        <v>0.004089200543642485</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003772633371037689</v>
+        <v>0.003675291868504225</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003826579052843724</v>
+        <v>0.002854295628753529</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004774168170060835</v>
+        <v>0.004774168323377512</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004336266042033094</v>
+        <v>0.004336266042033099</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004053175821631663</v>
+        <v>0.004053175821631673</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004373665428496308</v>
+        <v>0.004373665428496315</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004351995733253712</v>
+        <v>0.004351995733253722</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004668014179569735</v>
+        <v>0.004668014179569748</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004697530657531613</v>
+        <v>0.004697530657531625</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004373818643105553</v>
+        <v>0.004373818643105559</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004175254023011963</v>
+        <v>0.004175254023011977</v>
       </c>
       <c r="P9" t="n">
         <v>0.004684589695030847</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003914118057677101</v>
+        <v>0.003914118057677113</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003966827429298248</v>
+        <v>0.003966827429298256</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004163369611443222</v>
+        <v>0.004163369611443229</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004096389427724063</v>
+        <v>0.004096389427724075</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004584693126040007</v>
+        <v>0.004584693126040016</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003818674939627107</v>
+        <v>0.004305382433691511</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004511617697511356</v>
+        <v>0.00451161769751136</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004564583825966501</v>
+        <v>0.004564583825966514</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.004354166905008268</v>
+        <v>0.004354166905008277</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.004018251062531152</v>
+        <v>0.003763964388564708</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004331000527011675</v>
+        <v>0.004331000527011681</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.00493309651495587</v>
+        <v>0.004933096514955876</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003280902559926497</v>
+        <v>0.003280902559926499</v>
       </c>
       <c r="C2" t="n">
         <v>0.003288662323458335</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003290507797645507</v>
+        <v>0.003290507797645508</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003287389373274917</v>
+        <v>0.003287389373274919</v>
       </c>
       <c r="F2" t="n">
         <v>0.003285552394997308</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003366652225261922</v>
+        <v>0.003366652225261924</v>
       </c>
       <c r="H2" t="n">
         <v>0.003322461991219102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003288815054236307</v>
+        <v>0.0032888150542363</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003320899561921553</v>
+        <v>0.003320899561921556</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003297288989873222</v>
+        <v>0.003297288989873221</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003319804606442535</v>
+        <v>0.003319804606442529</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003289869309989601</v>
+        <v>0.003289869309989604</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003297124007695787</v>
+        <v>0.003297124007695791</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00443757176270345</v>
+        <v>0.004437571762703444</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003327205166569644</v>
+        <v>0.003327205166569642</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003293559640593607</v>
+        <v>0.0032935596405936</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003301408559839759</v>
+        <v>0.003301408559839758</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00329808534616373</v>
+        <v>0.003298085346163728</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003287718413133214</v>
+        <v>0.003287718413133213</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006124193744635191</v>
+        <v>0.006124193744635193</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003294260932803563</v>
+        <v>0.003294260932803565</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006520953530480848</v>
+        <v>0.006520953530480862</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003353341390092119</v>
+        <v>0.003353341390092118</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003373256423600502</v>
+        <v>0.003373256423600498</v>
       </c>
       <c r="Z2" t="n">
         <v>0.005203043711383509</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003307920674451198</v>
+        <v>0.003307920674451205</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003523013586154498</v>
+        <v>0.003523013586154492</v>
       </c>
     </row>
     <row r="3">
@@ -8414,25 +8414,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002871909448528163</v>
+        <v>0.002871909448528157</v>
       </c>
       <c r="C3" t="n">
         <v>0.002904730136117582</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002940778823228431</v>
+        <v>0.002940778823228427</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002918285583994732</v>
+        <v>0.002918285583994726</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002905404074883626</v>
+        <v>0.002905404074883623</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003479463460964169</v>
+        <v>0.00347946346096416</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003170550724025751</v>
+        <v>0.003170550724025749</v>
       </c>
       <c r="I3" t="n">
         <v>0.002928832247082989</v>
@@ -8441,58 +8441,58 @@
         <v>0.003156038168217353</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002988558817820946</v>
+        <v>0.002988558817820949</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003148192119911874</v>
+        <v>0.003148192119911867</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002941950840887339</v>
+        <v>0.002941950840887337</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002988010006039426</v>
+        <v>0.002988010006039421</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004829653063312961</v>
+        <v>0.004829653063312957</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003200827147559361</v>
+        <v>0.003200827147559358</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002962024223969895</v>
+        <v>0.002962024223969888</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003019181815558423</v>
+        <v>0.003019181815558422</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002993747945127204</v>
+        <v>0.0029937479451272</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002920913924371874</v>
+        <v>0.002920913924371871</v>
       </c>
       <c r="U3" t="n">
         <v>0.007639901889049023</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002966695983236185</v>
+        <v>0.002966695983236182</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008598880323767938</v>
+        <v>0.008598880323767939</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003389125419308775</v>
+        <v>0.003389125419308773</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003530938867155049</v>
+        <v>0.003530938867155045</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006120355640394726</v>
+        <v>0.006120355640394721</v>
       </c>
       <c r="AA3" t="n">
         <v>0.003064925018117475</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004589911601309917</v>
+        <v>0.004589911601309906</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001731298014857587</v>
+        <v>0.001731298014857588</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001771916262128284</v>
+        <v>0.00177191626212828</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001839793593521452</v>
+        <v>0.00183979359352145</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001804569555709541</v>
+        <v>0.001804569555709537</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001783820041012193</v>
+        <v>0.001783820041012189</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002699879931616165</v>
+        <v>0.002699879931616154</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002200730909590479</v>
+        <v>0.002200730909590477</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001820673278013995</v>
+        <v>0.001820673278013997</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002182499411448574</v>
+        <v>0.002182499411448575</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001916390279235991</v>
+        <v>0.001916390279235987</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00217071452608167</v>
+        <v>0.002170714526081662</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001843391701196129</v>
+        <v>0.001843391701196124</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001914526729646357</v>
+        <v>0.001914526729646358</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001831881147029272</v>
+        <v>0.001831881147029265</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002254307257143302</v>
+        <v>0.002254307257143306</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001874265563537265</v>
+        <v>0.001874265563537262</v>
       </c>
       <c r="R4" t="n">
         <v>0.001962922717103847</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001925385489879269</v>
+        <v>0.001925385489879271</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001808286212274799</v>
+        <v>0.001808286212274798</v>
       </c>
       <c r="U4" t="n">
         <v>0.001875485243576695</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001878367491881852</v>
+        <v>0.001878367491881851</v>
       </c>
       <c r="W4" t="n">
         <v>0.002510393620007962</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002549527925086499</v>
+        <v>0.002549527925086497</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002764501901627016</v>
+        <v>0.002764501901627014</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001888321620395568</v>
+        <v>0.001888321620395563</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002036480047360866</v>
+        <v>0.002036480047360867</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004434516945488763</v>
+        <v>0.004434516945488766</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002793485119167743</v>
+        <v>0.002793485119167739</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003620516677094921</v>
+        <v>0.003620516677094914</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004876330315120934</v>
+        <v>0.004876330315120931</v>
       </c>
       <c r="E5" t="n">
         <v>0.004130573335060291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003882307353507659</v>
+        <v>0.003882307353507662</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01762062261514103</v>
+        <v>0.01762062261514092</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01214793951891991</v>
+        <v>0.01214793951891989</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004607918329509186</v>
+        <v>0.004607918329509183</v>
       </c>
       <c r="J5" t="n">
-        <v>0.010093245242943</v>
+        <v>0.01009324524294297</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005910955290950488</v>
+        <v>0.005910955290950497</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009858860836570031</v>
+        <v>0.009858860836570019</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004865127447112542</v>
+        <v>0.004865127447112536</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00536324011310373</v>
+        <v>0.005363240113103729</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004362414702217599</v>
+        <v>0.004362414702217612</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01124242912056162</v>
+        <v>0.01124242912056163</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005208382774841328</v>
+        <v>0.005208382774841322</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007366929011828613</v>
+        <v>0.007366929011828597</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005813784579781009</v>
+        <v>0.005813784579781006</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004341394091374977</v>
+        <v>0.004341394091374964</v>
       </c>
       <c r="U5" t="n">
         <v>0.005334174115338724</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005171891465715347</v>
+        <v>0.005171891465715351</v>
       </c>
       <c r="W5" t="n">
         <v>0.01670558311280412</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01737738994618655</v>
+        <v>0.01737738994618654</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02118957021798122</v>
+        <v>0.02118957021798121</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005224387422156345</v>
+        <v>0.005224387422156337</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008287491298741529</v>
+        <v>0.008287491298741538</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05432423829962701</v>
+        <v>0.05432423829962695</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002294835652121763</v>
+        <v>0.001933283470863676</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002335453899392454</v>
+        <v>0.00233545389939245</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002041779049527546</v>
+        <v>0.002041779049527537</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002006555011715632</v>
+        <v>0.002368107192973709</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001985805497018274</v>
+        <v>0.002347357678276361</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003263417568880331</v>
+        <v>0.002901865387622241</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002402716365596567</v>
+        <v>0.002764268546854649</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002022658734020087</v>
+        <v>0.002384210915278169</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002746037048712751</v>
+        <v>0.002384484867454662</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00211837573524207</v>
+        <v>0.002479927916500159</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002734252163345842</v>
+        <v>0.002372699982087752</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00204537715720222</v>
+        <v>0.002406929338460295</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002117430141696605</v>
+        <v>0.002117430141696575</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002399372667113013</v>
+        <v>0.002034784559079501</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002436316190816082</v>
+        <v>0.002436316190816081</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002076251019543358</v>
+        <v>0.002437803200801434</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002526460354368025</v>
+        <v>0.002526460354368017</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002127370945885363</v>
+        <v>0.00212737094588536</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002010271668280894</v>
+        <v>0.002010271668280886</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002448998369145533</v>
+        <v>0.002087446187887448</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002441905129146025</v>
+        <v>0.002441905129146022</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00273463333793777</v>
+        <v>0.002734633337937773</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003113065562350676</v>
+        <v>0.002751513381092585</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002991944506821888</v>
+        <v>0.002991944506821885</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002090307076401659</v>
+        <v>0.002090307076401652</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002600017684625041</v>
+        <v>0.002600017684625038</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004651052348165944</v>
+        <v>0.004651052348165952</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002017357652630707</v>
+        <v>0.002017357652630706</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002057975899901401</v>
+        <v>0.0020579758999014</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00212585323129457</v>
+        <v>0.002125853231294569</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002090629193482658</v>
+        <v>0.002090629193482656</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002069879678785314</v>
+        <v>0.002069879678785308</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002985939569389283</v>
+        <v>0.00298593956938927</v>
       </c>
       <c r="H7" t="n">
         <v>0.002486790547363596</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002106732915787114</v>
+        <v>0.002106732915787116</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002468559049221697</v>
+        <v>0.002468559049221693</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002202449917009108</v>
+        <v>0.002202449917009107</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002456774163854786</v>
+        <v>0.002456774163854781</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002129451338969244</v>
+        <v>0.002129451338969243</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002200586367419478</v>
+        <v>0.002200586367419476</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002117916768344468</v>
+        <v>0.002117916768344467</v>
       </c>
       <c r="P7" t="n">
         <v>0.002540342878458506</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002160325201310389</v>
+        <v>0.002160325201310381</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002248982354876967</v>
+        <v>0.002248982354876965</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002211445127652388</v>
+        <v>0.00221144512765239</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002094345850047914</v>
+        <v>0.002094345850047917</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002171001764193227</v>
+        <v>0.002171001764193229</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002164427129654969</v>
+        <v>0.00216442712965497</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002796453257781083</v>
+        <v>0.002796453257781079</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002835587562859625</v>
+        <v>0.002835587562859616</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003060537027704802</v>
+        <v>0.003060537027704798</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002174381258168684</v>
+        <v>0.002174381258168683</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002322539685133981</v>
+        <v>0.002322539685133986</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.004720576583261886</v>
+        <v>0.004720576583261883</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002359367311546639</v>
+        <v>0.002359367311546641</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002902578602794078</v>
+        <v>0.002902578602794072</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002970455934187249</v>
+        <v>0.002970455934187242</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002935231896375338</v>
+        <v>0.002667615926202418</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002490187459933909</v>
+        <v>0.002490187459933905</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00383054227228195</v>
+        <v>0.003934758213976076</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003331393250256273</v>
+        <v>0.003331393250256272</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002951335618679796</v>
+        <v>0.00295133561867979</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003313161752114372</v>
+        <v>0.003313161752114366</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003047052619901782</v>
+        <v>0.003047052619901779</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003301376866747462</v>
+        <v>0.003301376866747456</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002974054041861923</v>
+        <v>0.002974054041861861</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00265559537903711</v>
+        <v>0.002655595379037108</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002680013525128958</v>
+        <v>0.002680013525128957</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003076195728360826</v>
+        <v>0.003076195728360816</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002403563856199122</v>
+        <v>0.00240356385619912</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003093585057769646</v>
+        <v>0.00309358505776964</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003056047830545068</v>
+        <v>0.003056047830545062</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002938948552940596</v>
+        <v>0.002938948552940592</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002706493574264107</v>
+        <v>0.002770430820980079</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003009029832547643</v>
+        <v>0.002871240812512384</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003641154733767688</v>
+        <v>0.003641154733767689</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003124889868375546</v>
+        <v>0.003124889868375543</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004404200849128312</v>
+        <v>0.004404200849128317</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003018983961061365</v>
+        <v>0.002507054993344623</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003167142388026662</v>
+        <v>0.003167142388026659</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.006090179745932135</v>
+        <v>0.006090179745932126</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002782625567110844</v>
+        <v>0.002782625567110842</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003159053230515621</v>
+        <v>0.003159053230515613</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003226930561908791</v>
+        <v>0.003226930561908783</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003191706524096878</v>
+        <v>0.003114203244719483</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003170957009399524</v>
+        <v>0.002396824375619913</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004087016900003495</v>
+        <v>0.004087017113372998</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003587867877977814</v>
+        <v>0.00358786787797781</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003207810246401336</v>
+        <v>0.003207810246401328</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003569636379835913</v>
+        <v>0.003569636379835909</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003303527247623322</v>
+        <v>0.00330352724762332</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003557851494469005</v>
+        <v>0.003557851494468996</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003230528669583466</v>
+        <v>0.003230528669583458</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003301663698033698</v>
+        <v>0.00330166369803369</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00333030520029841</v>
+        <v>0.003330305200298408</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003776934295605224</v>
+        <v>0.00377693429560522</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003261402745294116</v>
+        <v>0.003261402745294112</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003350059685491194</v>
+        <v>0.003350059685491184</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003312522458266613</v>
+        <v>0.003312522458266606</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003195423180662136</v>
+        <v>0.003195423180662133</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003272597700268701</v>
+        <v>0.003272597700268695</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003265504460269188</v>
+        <v>0.003653021463224839</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0038975305883953</v>
+        <v>0.003897530588395296</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003936664893473835</v>
+        <v>0.00393666489347383</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.004161614358319017</v>
+        <v>0.004161614358319016</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003275458588782901</v>
+        <v>0.003072995456919104</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003423617015748209</v>
+        <v>0.0034236170157482</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.005821653913876108</v>
+        <v>0.005821653913876096</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003482718094987685</v>
+        <v>0.003379880253782322</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003409482763365963</v>
+        <v>0.003325854392308249</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003461475635370055</v>
+        <v>0.003376520947755857</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003426951343860815</v>
+        <v>0.003336145697251985</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003444464417342694</v>
+        <v>0.003358075331239024</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003540996388361932</v>
+        <v>0.003372885293708079</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003499365171871419</v>
+        <v>0.003414882234511164</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003468216006013867</v>
+        <v>0.00338438098140304</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00349202879811478</v>
+        <v>0.003381164599560408</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003515666027955063</v>
+        <v>0.003438115978442368</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003517042328960008</v>
+        <v>0.003383714169405924</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003552698359565792</v>
+        <v>0.003518215749416017</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003483799050774333</v>
+        <v>0.003402459284957599</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004737691696609888</v>
+        <v>0.004595310309725842</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003487557833554187</v>
+        <v>0.003361866183865387</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003443764693414995</v>
+        <v>0.003356670465772349</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003462958413567013</v>
+        <v>0.003381856584698206</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003476700377155541</v>
+        <v>0.003374024143502304</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003490855224688414</v>
+        <v>0.003409254494469885</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006411035027724753</v>
+        <v>0.006310884754047705</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003437217269852469</v>
+        <v>0.00335061732814394</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00672126507217686</v>
+        <v>0.006634457555150799</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003468547138845931</v>
+        <v>0.003361961458760159</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003484439158637458</v>
+        <v>0.003378153022955299</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005403014813514449</v>
+        <v>0.005300635787075625</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003487552922926363</v>
+        <v>0.003407770591347273</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003557230337617145</v>
+        <v>0.0034262535132357</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003571606027893029</v>
+        <v>0.003352337311084484</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003050532630586171</v>
+        <v>0.002976053014467282</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003424086364758006</v>
+        <v>0.00333172281263654</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003176076290023601</v>
+        <v>0.003042075189076776</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003302860951696103</v>
+        <v>0.00320016633694094</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003987418734737411</v>
+        <v>0.003303228733442828</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003697271145376989</v>
+        <v>0.003608207286143352</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003472722219997797</v>
+        <v>0.003388356694653492</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003639883156872716</v>
+        <v>0.003363325101682439</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003811587303347376</v>
+        <v>0.003772221670382007</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003818948031908692</v>
+        <v>0.003381514009983326</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004078516476124981</v>
+        <v>0.004342028120513455</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003582747243428082</v>
+        <v>0.003516272482026386</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005619973206830897</v>
+        <v>0.005342534090490369</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003606560164546496</v>
+        <v>0.003224551199227042</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003296830782403072</v>
+        <v>0.003189209524599309</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003435466812170526</v>
+        <v>0.003370676349071686</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003529801603299828</v>
+        <v>0.003311426071078948</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00363457351785445</v>
+        <v>0.003566217712521374</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008568259007148414</v>
+        <v>0.008399915985011925</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003248341806860812</v>
+        <v>0.003144473415467694</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00894272480918885</v>
+        <v>0.00887048952145408</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003474281952308645</v>
+        <v>0.003227216339653312</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003586655732176064</v>
+        <v>0.003342093417673242</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00657755421975716</v>
+        <v>0.00640455920333285</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003609109271222037</v>
+        <v>0.00355376391900558</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004107738579418505</v>
+        <v>0.00368657159874456</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002924152210436021</v>
+        <v>0.002391108291286597</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002093373348435672</v>
+        <v>0.001794941720227691</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002684208857040642</v>
+        <v>0.002353163384360573</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002294241102484997</v>
+        <v>0.001897106356386452</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002492059323874715</v>
+        <v>0.002144811660400106</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003582432343437597</v>
+        <v>0.002312096999407436</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003112188601871488</v>
+        <v>0.002786471765325498</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002760344444186181</v>
+        <v>0.002441946080199612</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003028660030721783</v>
+        <v>0.002405292297796564</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003296314270100526</v>
+        <v>0.003048907591078722</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00331186022308113</v>
+        <v>0.002434414131943505</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003715615072782159</v>
+        <v>0.00394431406762263</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002936362103310405</v>
+        <v>0.02313503278494857</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002877612514875385</v>
+        <v>0.00235890251553495</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0029788192839344</v>
+        <v>0.002187631084693238</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002484155620222424</v>
+        <v>0.002128943058683968</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002700957518886966</v>
+        <v>0.002413431858138653</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00285617931923495</v>
+        <v>0.002324960831729998</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003016064833670306</v>
+        <v>0.002722903852670955</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003238698371538825</v>
+        <v>0.002812666870848889</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002405868393362115</v>
+        <v>0.002058525301986644</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002970625822439719</v>
+        <v>0.00268711572074822</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00276408474185299</v>
+        <v>0.002188707258458321</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00292594294336501</v>
+        <v>0.002364202019668497</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00258380670401608</v>
+        <v>0.002145253997696869</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002978763816134123</v>
+        <v>0.002706142484271923</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003756822824495023</v>
+        <v>0.002908827023519378</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02135550609223003</v>
+        <v>0.01634231509053272</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006331710402465225</v>
+        <v>0.005650943396059401</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01895375806389143</v>
+        <v>0.01757581713115809</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01014464361825742</v>
+        <v>0.007507745298858103</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01519393612740641</v>
+        <v>0.01343403382877253</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03453911656375029</v>
+        <v>0.01523547443083899</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0292158868299422</v>
+        <v>0.02790530562040267</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0208016695913108</v>
+        <v>0.01968253669620082</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02455810367357783</v>
+        <v>0.01771665645376183</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03172089844844148</v>
+        <v>0.03211680044687295</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03057067132619426</v>
+        <v>0.01829246396146003</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04140233508310687</v>
+        <v>0.05205883368590176</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02860521978803178</v>
+        <v>0.02313503278494857</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0200667379346581</v>
+        <v>0.01542616598719596</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02270166033794686</v>
+        <v>0.01270902969991266</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01441890455088718</v>
+        <v>0.01256159983914947</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01976520366909974</v>
+        <v>0.01930826056945059</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02066680902856169</v>
+        <v>0.01553571865192514</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02611421898419043</v>
+        <v>0.02554102391940678</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02892520552898372</v>
+        <v>0.02555827519962865</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01187938592016035</v>
+        <v>0.0102706026909351</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02391468173589534</v>
+        <v>0.02355229933704015</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0203993840654987</v>
+        <v>0.01391058005299624</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02339119145794471</v>
+        <v>0.01718771976715741</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01536800282395122</v>
+        <v>0.01203216925278257</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02423643455764278</v>
+        <v>0.02409615131277516</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04359984515444959</v>
+        <v>0.0306753492801571</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003620598805787109</v>
+        <v>0.002612028706696427</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00278981994378676</v>
+        <v>0.002423558877283052</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002904404714765296</v>
+        <v>0.002981780541415935</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00251443696020965</v>
+        <v>0.002525723513441811</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003188505919225803</v>
+        <v>0.002365732075809936</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004278878938788686</v>
+        <v>0.002940714156462795</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003808635197222578</v>
+        <v>0.003415088922380862</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002980540301910835</v>
+        <v>0.002662866495609444</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00372510662607287</v>
+        <v>0.002626212713206394</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003516510127825179</v>
+        <v>0.003677524748134085</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003532056080805786</v>
+        <v>0.003063031288998875</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003935810930506814</v>
+        <v>0.00457293122467799</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003159614723396118</v>
+        <v>0.02313503278494857</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003578404199111156</v>
+        <v>0.002582890637273386</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003679612185710135</v>
+        <v>0.00281790585840062</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002704351477947077</v>
+        <v>0.002757560215739333</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002921153376611619</v>
+        <v>0.003042049015194015</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003552625914586038</v>
+        <v>0.00254588124713983</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003236260691394958</v>
+        <v>0.002943824268080785</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003476543701987051</v>
+        <v>0.003040983691120148</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003102314988713203</v>
+        <v>0.002687142459042005</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003671418258591847</v>
+        <v>0.003317390273797475</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00346053133720408</v>
+        <v>0.002817324415513685</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003183186642010339</v>
+        <v>0.002612785758773918</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002804002561740735</v>
+        <v>0.002366174413106702</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003198959673858777</v>
+        <v>0.003334759641327286</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003986316668507768</v>
+        <v>0.003136174283229182</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003351954780914258</v>
+        <v>0.002779170621092496</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00252117591891391</v>
+        <v>0.002183004050033592</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003112011427518881</v>
+        <v>0.002741225714166472</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002722043672963235</v>
+        <v>0.002285168686192352</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002919861894352953</v>
+        <v>0.002532873990206004</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004010234913915836</v>
+        <v>0.002700159329213336</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003539991172349731</v>
+        <v>0.0031745340951314</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00318814701466442</v>
+        <v>0.002830008410005515</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003456462601200021</v>
+        <v>0.002793354627602465</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003724116840578767</v>
+        <v>0.003436969920884622</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00373966279355937</v>
+        <v>0.00282247646174941</v>
       </c>
       <c r="M7" t="n">
-        <v>0.004143417643260397</v>
+        <v>0.004332376397428526</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003364164673788647</v>
+        <v>0.02313503278494857</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003305386562780503</v>
+        <v>0.002746936562052616</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003406593331839518</v>
+        <v>0.002575665131210903</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002911958190700661</v>
+        <v>0.002517005388489864</v>
       </c>
       <c r="R7" t="n">
-        <v>0.003128760089365204</v>
+        <v>0.002801494187944554</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003283981889713187</v>
+        <v>0.002713023161535898</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003443867404148543</v>
+        <v>0.003110966182476857</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003683714001516332</v>
+        <v>0.003207903677788184</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002833670963840353</v>
+        <v>0.002446587631792543</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003398428392917957</v>
+        <v>0.003075178050554118</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003191887312331227</v>
+        <v>0.002576769588264223</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00337139498656682</v>
+        <v>0.002759660754335825</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.003011609274494319</v>
+        <v>0.002533316327502772</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003406566386612361</v>
+        <v>0.003094204814077823</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.004184625394973261</v>
+        <v>0.003296889353325276</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003810525786729729</v>
+        <v>0.003212822812300527</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003677412452587823</v>
+        <v>0.003260181495651696</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004268247961192795</v>
+        <v>0.003818403159784578</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003506793893103149</v>
+        <v>0.003019687916845895</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003487121035515327</v>
+        <v>0.003066779894910225</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005311136939586176</v>
+        <v>0.003910775928438573</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00469622770602364</v>
+        <v>0.004251711540749504</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004344383548338332</v>
+        <v>0.003907185855623619</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004612699134873933</v>
+        <v>0.00387053207322057</v>
       </c>
       <c r="K8" t="n">
-        <v>0.004880353374252679</v>
+        <v>0.004514147366502731</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004895899327233282</v>
+        <v>0.003899653907367517</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005299654176934302</v>
+        <v>0.005409553843046654</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003979593706231016</v>
+        <v>0.02313503278494857</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0040694627143801</v>
+        <v>0.003462388048287229</v>
       </c>
       <c r="P8" t="n">
-        <v>0.004134239474341632</v>
+        <v>0.003257513651655025</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00323342199713131</v>
+        <v>0.002824190179732115</v>
       </c>
       <c r="R8" t="n">
-        <v>0.004284996623039118</v>
+        <v>0.003878671633562662</v>
       </c>
       <c r="S8" t="n">
-        <v>0.004440218423387102</v>
+        <v>0.003790200607154003</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004600103937822456</v>
+        <v>0.004188143628094962</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004499549610084583</v>
+        <v>0.003971056893236998</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003798876333824872</v>
+        <v>0.003347714399158619</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004554802036887211</v>
+        <v>0.00415248196636969</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003577293550070522</v>
+        <v>0.002942934747185879</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005220763710312735</v>
+        <v>0.004476423986979945</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003457220785044103</v>
+        <v>0.002955014706818316</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.004562802920286269</v>
+        <v>0.004171382259695929</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.006069631909410089</v>
+        <v>0.005046282736969936</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004745634619254796</v>
+        <v>0.003905824511852236</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004477126117068521</v>
+        <v>0.003781407922290549</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005067961625673491</v>
+        <v>0.00433962958642343</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004548224271522685</v>
+        <v>0.003774694442932671</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003579625275138087</v>
+        <v>0.003043765646716306</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005966185249863392</v>
+        <v>0.004298563014237519</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00549594137050434</v>
+        <v>0.004772937967388358</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005144097212819029</v>
+        <v>0.004428412282262469</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005412412799354631</v>
+        <v>0.004391758499859424</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005680067038733378</v>
+        <v>0.005035373793141585</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005695612991713978</v>
+        <v>0.004420880334006369</v>
       </c>
       <c r="M9" t="n">
-        <v>0.006099367841415009</v>
+        <v>0.005930780269685488</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005320114871943255</v>
+        <v>0.02313503278494857</v>
       </c>
       <c r="O9" t="n">
-        <v>0.005447701127977746</v>
+        <v>0.004501705794480617</v>
       </c>
       <c r="P9" t="n">
-        <v>0.005589432716256609</v>
+        <v>0.004364435036288327</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00486790852664822</v>
+        <v>0.004115409073514054</v>
       </c>
       <c r="R9" t="n">
-        <v>0.005084710287519814</v>
+        <v>0.004399898060201511</v>
       </c>
       <c r="S9" t="n">
-        <v>0.005239932087867796</v>
+        <v>0.004311427033792855</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005399817602303152</v>
+        <v>0.004709370054733816</v>
       </c>
       <c r="U9" t="n">
-        <v>0.005640100612895245</v>
+        <v>0.004806529477773176</v>
       </c>
       <c r="V9" t="n">
-        <v>0.005438468728501226</v>
+        <v>0.004589379982556628</v>
       </c>
       <c r="W9" t="n">
-        <v>0.005354378591072569</v>
+        <v>0.004673581922811075</v>
       </c>
       <c r="X9" t="n">
-        <v>0.005147837510485838</v>
+        <v>0.00417517346052118</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.005327345184721432</v>
+        <v>0.004358064626592781</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.004628560499428311</v>
+        <v>0.003847296836213959</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.005362516584766974</v>
+        <v>0.004692608686334782</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.00614057559312787</v>
+        <v>0.004895293225582236</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003195850799215783</v>
+        <v>0.003200573851843659</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003148103562995351</v>
+        <v>0.003152642105242251</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003201913878285828</v>
+        <v>0.003206575799650074</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003197810493083964</v>
+        <v>0.003202387975601704</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003202154835034157</v>
+        <v>0.003206798648925135</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003205914375042584</v>
+        <v>0.003209219060872485</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003214137757680804</v>
+        <v>0.003218863634937049</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003202103594552494</v>
+        <v>0.003212288965466983</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003208997057987459</v>
+        <v>0.003213842789914237</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00320800389577696</v>
+        <v>0.003220093937840519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003209718259244909</v>
+        <v>0.00321381970470412</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003200601555377752</v>
+        <v>0.003206719776709564</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003207168623350797</v>
+        <v>0.003212076020843857</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004339149703015657</v>
+        <v>0.004343883978538652</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003207770140626144</v>
+        <v>0.00321233231505488</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003200590630183469</v>
+        <v>0.003205236817143534</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003210393521358387</v>
+        <v>0.003217087471392941</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00320910601564017</v>
+        <v>0.003213204328180961</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00320318264654278</v>
+        <v>0.003214902188449446</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005889956539655253</v>
+        <v>0.005890727067848783</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003211047343447919</v>
+        <v>0.003215653317197112</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006294007688428215</v>
+        <v>0.006296979299138666</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0032723167155032</v>
+        <v>0.003276556104814535</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003239760189112787</v>
+        <v>0.00324442104439951</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005123294457085432</v>
+        <v>0.005127629073673269</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003241447485432378</v>
+        <v>0.003247687489793039</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003197358680128564</v>
+        <v>0.003203763438100412</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0027936416583737</v>
+        <v>0.002799240474143168</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002735619463111795</v>
+        <v>0.002740475654368666</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002837098766957202</v>
+        <v>0.00284226735992899</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002807641245067156</v>
+        <v>0.002812226758712669</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002838904550272426</v>
+        <v>0.002843941740909517</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002865036962509341</v>
+        <v>0.002860584419070611</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002924991647327247</v>
+        <v>0.002930615804856276</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002838575450916545</v>
+        <v>0.002883231723208217</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002887272468497552</v>
+        <v>0.002893776158051723</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002880165351361934</v>
+        <v>0.002938095259246093</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00289220345630524</v>
+        <v>0.002893394872283814</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002832518570137255</v>
+        <v>0.002847968340273352</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002874681944332532</v>
+        <v>0.002881597936607009</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004764132708213471</v>
+        <v>0.004769342421205767</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00287819480878171</v>
+        <v>0.002882652756013272</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002827511987137111</v>
+        <v>0.002832566446595536</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002898058672602193</v>
+        <v>0.002917777246926493</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00288772056516504</v>
+        <v>0.002888888000411601</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002846303489849726</v>
+        <v>0.002901959292562491</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007317475478615156</v>
+        <v>0.007303235156345443</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002901499610577589</v>
+        <v>0.002906272196409675</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008202488035979243</v>
+        <v>0.008204309524936129</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00333877845350983</v>
+        <v>0.003340934182459194</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003107432529850138</v>
+        <v>0.003112586031364393</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006050848691994853</v>
+        <v>0.006055603773516219</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003119388433598154</v>
+        <v>0.003135819666916479</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002806849267236195</v>
+        <v>0.002824332737207742</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001610176186745451</v>
+        <v>0.001535239602819822</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001652768112198283</v>
+        <v>0.001576916933692524</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001678661453995779</v>
+        <v>0.001603034364325658</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001632311830490282</v>
+        <v>0.0015557309652051</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001681383171313731</v>
+        <v>0.001605551549403238</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001723848905182775</v>
+        <v>0.001632891215793057</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001816735795024372</v>
+        <v>0.001741831116575579</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001680804386501574</v>
+        <v>0.001667567200413759</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00175838218186322</v>
+        <v>0.001684836214024479</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001747451003104597</v>
+        <v>0.001755727953837494</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001766815527121201</v>
+        <v>0.001684857604272087</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001672484863863083</v>
+        <v>0.001613093312427834</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00486579578297405</v>
+        <v>0.004849682996968022</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00178304753317834</v>
+        <v>0.001707257153246579</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001744810631143446</v>
+        <v>0.001668056853950879</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001663714757955459</v>
+        <v>0.001587909940951921</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001774442923328883</v>
+        <v>0.001721768532269268</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001759899953959709</v>
+        <v>0.001677906643355791</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001692992775120308</v>
+        <v>0.001697084756142658</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001759296337154474</v>
+        <v>0.001657214531110617</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001780016372623143</v>
+        <v>0.001703789959482119</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002216967335888569</v>
+        <v>0.002140206986097457</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002473893887271189</v>
+        <v>0.002393494103689128</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002096441939730961</v>
+        <v>0.002021308945985792</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00176748401468621</v>
+        <v>0.001692120214841456</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002125211733073863</v>
+        <v>0.002067409816802274</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00163105686519701</v>
+        <v>0.001574802044600427</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002467709649479458</v>
+        <v>0.002413992351481186</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003302040592624482</v>
+        <v>0.003235911806793521</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003774654588646866</v>
+        <v>0.003711872294442504</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002866031691537369</v>
+        <v>0.002796519331620902</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003867392615998326</v>
+        <v>0.003799869115653521</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004255912874212665</v>
+        <v>0.003955938359781445</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006553803150059817</v>
+        <v>0.006503335720868777</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003876126251582248</v>
+        <v>0.004951297368776421</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004992871771287776</v>
+        <v>0.004978854939300562</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004784967668558467</v>
+        <v>0.006074769450470766</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005025167517481454</v>
+        <v>0.004862316307673461</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003711010673031032</v>
+        <v>0.003937341535517464</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00486579578297405</v>
+        <v>0.004849682996968022</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005162889956850249</v>
+        <v>0.005097737132804943</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004581650255885457</v>
+        <v>0.004499590026756218</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003436351013219676</v>
+        <v>0.003369473708959751</v>
       </c>
       <c r="R5" t="n">
-        <v>0.005696866864982053</v>
+        <v>0.00606454850772447</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00484415073342406</v>
+        <v>0.004679833623201128</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004105581818466327</v>
+        <v>0.005513198246749927</v>
       </c>
       <c r="U5" t="n">
-        <v>0.005003177506630592</v>
+        <v>0.004520455105890222</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005190630546609418</v>
+        <v>0.005118410649835893</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01322266440671526</v>
+        <v>0.01313647206850887</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01743083926986413</v>
+        <v>0.0172850786113047</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01145098457995241</v>
+        <v>0.01138411152965548</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004836286941900579</v>
+        <v>0.004777581656879603</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01174328872649532</v>
+        <v>0.01199566175428379</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003020904082970577</v>
+        <v>0.003324952535378976</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001789490529507574</v>
+        <v>0.001714738643527875</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001832082454960409</v>
+        <v>0.002045743527791275</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002147095883535839</v>
+        <v>0.001782533405033713</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001811626173252405</v>
+        <v>0.002024557559303851</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001860697514075855</v>
+        <v>0.002074378143501988</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00219228333472283</v>
+        <v>0.001812390256501111</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002285170224564428</v>
+        <v>0.001921330157283633</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002149238816041634</v>
+        <v>0.001847066241121814</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00222681661140328</v>
+        <v>0.00215366280812323</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00192676534586672</v>
+        <v>0.001935226994545548</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002235249956661261</v>
+        <v>0.002153684198370835</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002140919293403144</v>
+        <v>0.001792592353135888</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00486579578297405</v>
+        <v>0.004849682996968022</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002268020787545428</v>
+        <v>0.002192359159804678</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002221369053433895</v>
+        <v>0.001836655815542314</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002132149187495521</v>
+        <v>0.001767408981659976</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002242877352868944</v>
+        <v>0.001901267572977323</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002228334383499768</v>
+        <v>0.002146733237454541</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00187230711788243</v>
+        <v>0.001876583796850712</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002237441771912992</v>
+        <v>0.002135245992666867</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0022484508021632</v>
+        <v>0.001883289000190173</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002417837191011276</v>
+        <v>0.002341265857054062</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002653208230033312</v>
+        <v>0.002862320697787881</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002307258452986542</v>
+        <v>0.002231823467007373</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001946798357448332</v>
+        <v>0.001871619255549511</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002304526075835984</v>
+        <v>0.002536236410901024</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001810378901556871</v>
+        <v>0.001754456378348171</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001877645831192427</v>
+        <v>0.00180362968333953</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001920237756645259</v>
+        <v>0.001845307014212234</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001946131098442752</v>
+        <v>0.001871424444845367</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001899781474937257</v>
+        <v>0.00182412104572481</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001948852815760707</v>
+        <v>0.001873941629922947</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001991318549629749</v>
+        <v>0.001901281296312766</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002084205439471346</v>
+        <v>0.002010221197095286</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001948274030948546</v>
+        <v>0.001935957280933467</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002025851826310194</v>
+        <v>0.001953226294544187</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002014920647551572</v>
+        <v>0.002024118034357203</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002034285171568173</v>
+        <v>0.001953247684791795</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001939954508310058</v>
+        <v>0.001881483392947543</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00486579578297405</v>
+        <v>0.004849682996968022</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002050493690867357</v>
+        <v>0.001975623651455258</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002012256788832464</v>
+        <v>0.001936423352159557</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001931184402402434</v>
+        <v>0.001856300021471629</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002041912567775856</v>
+        <v>0.001990158612788976</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002027369598406681</v>
+        <v>0.001946296723875499</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001960462419567282</v>
+        <v>0.001965474836662367</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002036025833868678</v>
+        <v>0.001934480068010903</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002047486017070116</v>
+        <v>0.001972180040001828</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002484436980335545</v>
+        <v>0.002408597066617167</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002741363531718162</v>
+        <v>0.002661884184208839</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002373622589396392</v>
+        <v>0.002298903893963001</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002034953659133184</v>
+        <v>0.001960510295361164</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002392681377520837</v>
+        <v>0.002335799897321983</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001898526509643984</v>
+        <v>0.001843192125120136</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00219124767121286</v>
+        <v>0.002117061982309944</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00269384197203348</v>
+        <v>0.002618682525402014</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002719735313830974</v>
+        <v>0.002644799956035146</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002428447994837633</v>
+        <v>0.002352590364055102</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002334117649614114</v>
+        <v>0.002259027705800724</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002860307254124675</v>
+        <v>0.0027700290287462</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002857809654859566</v>
+        <v>0.002783596708285065</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002721878246336769</v>
+        <v>0.002709332792123246</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002799456041698412</v>
+        <v>0.002726601805733967</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002788524862939794</v>
+        <v>0.002797493545546981</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002807889386956393</v>
+        <v>0.002726623195981575</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002713558723698222</v>
+        <v>0.002654858904137335</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00486579578297405</v>
+        <v>0.004849682996968022</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002565533544514378</v>
+        <v>0.002490468154710769</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002503276693049754</v>
+        <v>0.002427250995305812</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002154385276857849</v>
+        <v>0.002079342981781902</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002815516783164077</v>
+        <v>0.002763534123978756</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002800973813794901</v>
+        <v>0.002719672235065279</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002734066634955505</v>
+        <v>0.002738850347852146</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002585228751082075</v>
+        <v>0.002483455836918335</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002694999088313763</v>
+        <v>0.002619584720852447</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003258131598546562</v>
+        <v>0.003182062969016612</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003006724537403423</v>
+        <v>0.002927081853337594</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003604029714367021</v>
+        <v>0.003529185017053579</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002340010718947905</v>
+        <v>0.002265398913110248</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003166285592909056</v>
+        <v>0.003109175408511762</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003152641670088216</v>
+        <v>0.003097016780524015</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002351749990687616</v>
+        <v>0.002358252379033494</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002638947149152459</v>
+        <v>0.002666823895395213</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002664840490949952</v>
+        <v>0.002692941326028347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002562037106933578</v>
+        <v>0.002584039962424808</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002103680167252205</v>
+        <v>0.002080194359298244</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002710028110547027</v>
+        <v>0.002722798339853609</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002802914831978545</v>
+        <v>0.002831738078278267</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002666983423455747</v>
+        <v>0.002757474162116447</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002744561218817396</v>
+        <v>0.002774743175727168</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002733630040058771</v>
+        <v>0.002845634915540182</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002752994564075373</v>
+        <v>0.002774764565974776</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002658663900817257</v>
+        <v>0.002703000274130523</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00486579578297405</v>
+        <v>0.004849682996968022</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002850288648290445</v>
+        <v>0.00288561271471526</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002829681320837553</v>
+        <v>0.002865648433036206</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002649893963319721</v>
+        <v>0.002677817065012473</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002760621960283057</v>
+        <v>0.002811675493971956</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002746078990913884</v>
+        <v>0.002767813605058479</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002679171812074483</v>
+        <v>0.002786991717845346</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002755186379327108</v>
+        <v>0.002756326360270807</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003048464759579811</v>
+        <v>0.003101687238085939</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003203146372842743</v>
+        <v>0.003230113947800146</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003460072924225359</v>
+        <v>0.00348340106539182</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003092331981903592</v>
+        <v>0.003120420775145981</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002606187914153907</v>
+        <v>0.00262111378032175</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003111390770028036</v>
+        <v>0.003157316778504964</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002617235902151182</v>
+        <v>0.002664709006303116</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003415243012044817</v>
+        <v>0.003335920147755507</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003355591742133636</v>
+        <v>0.003293565343382777</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003406974874980484</v>
+        <v>0.003337868187543564</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003368874151057622</v>
+        <v>0.003304524596611437</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003378780701607013</v>
+        <v>0.0033110563259108</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003456532663527144</v>
+        <v>0.003339599407772806</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003420568496129143</v>
+        <v>0.003359814199114126</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003387297950413064</v>
+        <v>0.003338306064159599</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003424802789006212</v>
+        <v>0.003347841798345835</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003443747229661464</v>
+        <v>0.003387775152342452</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003454239182942455</v>
+        <v>0.003344487266418563</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003445768423224413</v>
+        <v>0.00347100786867144</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003407380248936377</v>
+        <v>0.003346257955834301</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004634784399256041</v>
+        <v>0.004520400051220009</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003455738509677781</v>
+        <v>0.003336433832513157</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003382709386625342</v>
+        <v>0.003316281438625586</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003380045208799923</v>
+        <v>0.003347649563789791</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003423539003394939</v>
+        <v>0.003341014857950993</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003411512193833804</v>
+        <v>0.003355518563345607</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006298528834902935</v>
+        <v>0.006215219357105718</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00337073412635273</v>
+        <v>0.003307531705719521</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00664302734373337</v>
+        <v>0.006578255268157533</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003425508322381419</v>
+        <v>0.003340266913832582</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003424429800815411</v>
+        <v>0.003342713469535262</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005323770325602962</v>
+        <v>0.00524697828008481</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003420406442093789</v>
+        <v>0.003364966968620433</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003485081991161676</v>
+        <v>0.00339152639873409</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003410479405739415</v>
+        <v>0.003227172831762293</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0030015279203254</v>
+        <v>0.002948104282955317</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003355139073941079</v>
+        <v>0.003243961314191961</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003081687342559302</v>
+        <v>0.003004673093833877</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003153392443510091</v>
+        <v>0.003052099183717246</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003704942109889003</v>
+        <v>0.003253839701840211</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003453754312815038</v>
+        <v>0.003402351108731297</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003214510902451409</v>
+        <v>0.003247382262250206</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003480158523884256</v>
+        <v>0.003313807526229689</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003615367528448101</v>
+        <v>0.003598059156096527</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003690858763106857</v>
+        <v>0.003289860534702483</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003635993979055334</v>
+        <v>0.004192739057441728</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003357212644044571</v>
+        <v>0.003303205763086549</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005407224967852826</v>
+        <v>0.00515526855885171</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003699073636780698</v>
+        <v>0.003231191660523878</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003180974965853387</v>
+        <v>0.003089043238887311</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003162779729073517</v>
+        <v>0.003314693625086578</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003470271727825104</v>
+        <v>0.003263984508188714</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003387590500051696</v>
+        <v>0.003370279343098805</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008352263100639686</v>
+        <v>0.008168103269949243</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003094080686246028</v>
+        <v>0.003025334063065592</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008932247876403577</v>
+        <v>0.008874536731466091</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003487180693491566</v>
+        <v>0.003260693024453184</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003478133682421377</v>
+        <v>0.003277203671643539</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006419079718662973</v>
+        <v>0.006288527064659035</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003449679840314195</v>
+        <v>0.003436245119460324</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003912160436043102</v>
+        <v>0.003626271080415073</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002638229033058573</v>
+        <v>0.002178485792244447</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001993322471418175</v>
+        <v>0.001743772433408474</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002544836621385975</v>
+        <v>0.00220048979779314</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002114471417478303</v>
+        <v>0.001823858599405105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002226370463172045</v>
+        <v>0.001897637486585362</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00310461464072954</v>
+        <v>0.002220044726683068</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00269838282563472</v>
+        <v>0.002448380094146712</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002322576706564423</v>
+        <v>0.00220543581560443</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002745469058861178</v>
+        <v>0.002312627629690464</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002960197283626549</v>
+        <v>0.002764211923534643</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003078708722472302</v>
+        <v>0.002275255338612955</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002988159518833946</v>
+        <v>0.003695405108040186</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002549415506699022</v>
+        <v>0.01598055496191955</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0026057239651734</v>
+        <v>0.002123252924817895</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003095644307672163</v>
+        <v>0.002184288097888773</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002270746767738493</v>
+        <v>0.001956657538369455</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002240653653618018</v>
+        <v>0.002310974942149617</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00273193607170279</v>
+        <v>0.002236032887584939</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00259608772510401</v>
+        <v>0.002399858912051217</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002997996293778565</v>
+        <v>0.002540072347155859</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002130600663867199</v>
+        <v>0.001854458586013107</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003032052167820916</v>
+        <v>0.002782649960604389</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002754180435586539</v>
+        <v>0.002227584514696172</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00272889999171633</v>
+        <v>0.002231305210856883</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002343777536147282</v>
+        <v>0.001984817513931991</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002696552350756867</v>
+        <v>0.002506582996111539</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00341821914880561</v>
+        <v>0.002799423766757515</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01655892534513686</v>
+        <v>0.01252050781210806</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005716947330772404</v>
+        <v>0.005315860459276896</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01683402395796241</v>
+        <v>0.01454118202240898</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007848606866863223</v>
+        <v>0.006689452933651316</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01052140086120661</v>
+        <v>0.008534279843587955</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02525294598686872</v>
+        <v>0.01353310346674114</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02062537326367021</v>
+        <v>0.02020710488480325</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01252422849644921</v>
+        <v>0.0147992111473389</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01940660441349014</v>
+        <v>0.01592777301711192</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02345425929274533</v>
+        <v>0.02403726431182509</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02603411550299459</v>
+        <v>0.01520877716731808</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02588101083638899</v>
+        <v>0.04470927676428883</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02380809140245765</v>
+        <v>0.01598055496191955</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01564256458866573</v>
+        <v>0.01132167026494337</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02497179528341305</v>
+        <v>0.01282633602362164</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01110646989939334</v>
+        <v>0.009456776263102032</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01099303493088723</v>
+        <v>0.01714307537748683</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01865519845605207</v>
+        <v>0.01385913591485955</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01784109086484409</v>
+        <v>0.01850349473645701</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02426977023617491</v>
+        <v>0.02024216284010717</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007750779691489037</v>
+        <v>0.006882892436030897</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02535895969014897</v>
+        <v>0.02497009586165133</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02066296113050142</v>
+        <v>0.01483763317281946</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01968206287445133</v>
+        <v>0.01483150605425747</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0116843740561824</v>
+        <v>0.009342713546569546</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01896797463314958</v>
+        <v>0.01970501253926476</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03578825986259646</v>
+        <v>0.02766699187266138</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002851530148649631</v>
+        <v>0.002370877611488317</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002616204734332055</v>
+        <v>0.00229601171286357</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003167718884299852</v>
+        <v>0.002392881617037018</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00232777253306936</v>
+        <v>0.002376097878860201</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002439671578763104</v>
+        <v>0.002090029305829241</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0033179157563206</v>
+        <v>0.002772284006138163</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003321265088548596</v>
+        <v>0.00300061937360181</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002535877822155482</v>
+        <v>0.002757675095059526</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003368351321775051</v>
+        <v>0.00286486690914556</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003583079546540429</v>
+        <v>0.002956603742778519</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003292009838063361</v>
+        <v>0.00282749461806805</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003201460634425005</v>
+        <v>0.004247644387495279</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00276494403456335</v>
+        <v>0.01598055496191955</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00323133571426</v>
+        <v>0.002317515605447477</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003721256483724984</v>
+        <v>0.002742702535364356</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002893629030652371</v>
+        <v>0.002149049357613332</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002863535916531894</v>
+        <v>0.002863214221604711</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003354818334616668</v>
+        <v>0.002428424706828817</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002809388840695067</v>
+        <v>0.002592250731295093</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003224395456007334</v>
+        <v>0.00275637844237203</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002753482926781077</v>
+        <v>0.002046850405256985</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003657660299062634</v>
+        <v>0.002999702324603123</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003377062698500413</v>
+        <v>0.002779823794151268</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002972969575818364</v>
+        <v>0.002464609751280777</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002966659799061159</v>
+        <v>0.002177209333175873</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002909853466347926</v>
+        <v>0.003058822275566636</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003639276940249485</v>
+        <v>0.002997827926142918</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003003764667463882</v>
+        <v>0.00252274401005906</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002358858105823484</v>
+        <v>0.00208803065122309</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002910372255791284</v>
+        <v>0.002544748015607756</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002480007051883611</v>
+        <v>0.00216811681721972</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002591906097577356</v>
+        <v>0.002241895704399979</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00347015027513485</v>
+        <v>0.002564302944497682</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003063918460040029</v>
+        <v>0.002792638311961327</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002688112340969734</v>
+        <v>0.002549694033419046</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003111004693266484</v>
+        <v>0.002656885847505078</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003325732918031859</v>
+        <v>0.003108470141349257</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003444244356877611</v>
+        <v>0.00261951355642758</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003353695153239258</v>
+        <v>0.004039663325854803</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002914951141104332</v>
+        <v>0.01598055496191955</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002971233259549181</v>
+        <v>0.002467485534560383</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003461153602047945</v>
+        <v>0.002528520707631258</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002636282402143802</v>
+        <v>0.002300915756184072</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002606189288023328</v>
+        <v>0.002655233159964232</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003097471706108097</v>
+        <v>0.002580291105399552</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002961623359509317</v>
+        <v>0.002744117129865831</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003376172634774084</v>
+        <v>0.002907922265056208</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002496136298272508</v>
+        <v>0.002198716803827716</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003397587802226228</v>
+        <v>0.003126908178419002</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003119716069991846</v>
+        <v>0.00257184273251079</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003107533672759355</v>
+        <v>0.002599477704643794</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002709313170552591</v>
+        <v>0.002329075731746609</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003062087985162175</v>
+        <v>0.002850841213926153</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003783754783210919</v>
+        <v>0.003143681984572129</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00340741638266772</v>
+        <v>0.002910274379947596</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003369993062128257</v>
+        <v>0.003049188878786274</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003921507212096058</v>
+        <v>0.003505906243170942</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003167675102127262</v>
+        <v>0.002823835131722317</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003090196601841217</v>
+        <v>0.002718790590288315</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004607250838798903</v>
+        <v>0.003644406645120468</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004075053416344798</v>
+        <v>0.003753796539524511</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003699247297274505</v>
+        <v>0.003510852260982231</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004122139649571252</v>
+        <v>0.003618044075068262</v>
       </c>
       <c r="K8" t="n">
-        <v>0.004336867874336631</v>
+        <v>0.004069628368912447</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004455379313182383</v>
+        <v>0.00358067178399075</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004364830109543987</v>
+        <v>0.005000821553418062</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00345518495559935</v>
+        <v>0.01598055496191955</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003640901136137619</v>
+        <v>0.003106207571183866</v>
       </c>
       <c r="P8" t="n">
-        <v>0.004099100519079855</v>
+        <v>0.003137289611659745</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002920549795601384</v>
+        <v>0.002575715159877479</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003617324244328098</v>
+        <v>0.003616391387527418</v>
       </c>
       <c r="S8" t="n">
-        <v>0.004108606662412869</v>
+        <v>0.003541449332962738</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003972758315814087</v>
+        <v>0.003705275357429017</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004090926454161893</v>
+        <v>0.003589192824004115</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003340868516368604</v>
+        <v>0.003002840047366674</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004408842145491101</v>
+        <v>0.004088179139401911</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0034596605090241</v>
+        <v>0.002899216268623945</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004722103986697833</v>
+        <v>0.004130587346904026</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003101680572760143</v>
+        <v>0.002705950669766172</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.004073222941466944</v>
+        <v>0.00381199944148934</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.005429456780905352</v>
+        <v>0.004704042474607186</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004028211595103112</v>
+        <v>0.003397038187723336</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003819398151858202</v>
+        <v>0.003346615559042383</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004370912301826005</v>
+        <v>0.003803332923427054</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003839898731737421</v>
+        <v>0.003338008867062955</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003047132235578517</v>
+        <v>0.002614585808349611</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004930690511955522</v>
+        <v>0.003822887689876833</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004524458506074747</v>
+        <v>0.004051223219780626</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004148652387004449</v>
+        <v>0.003808278941238342</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004571544739301203</v>
+        <v>0.003915470755324374</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004786272964066578</v>
+        <v>0.004367055049168554</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004904784402912329</v>
+        <v>0.003878098464246865</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004814235199273972</v>
+        <v>0.005298248233674107</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004375491187139048</v>
+        <v>0.01598055496191955</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004576320588046653</v>
+        <v>0.003853449278966805</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00509767171447019</v>
+        <v>0.003942181629554222</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.004096822638964473</v>
+        <v>0.003559500501563221</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004066729334058043</v>
+        <v>0.003913818067783527</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004558011752142817</v>
+        <v>0.003838876013218847</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004422163405544033</v>
+        <v>0.004002702037685127</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004837170020856306</v>
+        <v>0.004166829748762064</v>
       </c>
       <c r="V9" t="n">
-        <v>0.00445991831261943</v>
+        <v>0.003900764199362263</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004858127848260948</v>
+        <v>0.004385493086238299</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004580256116026564</v>
+        <v>0.003830427640330088</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.004568073718794073</v>
+        <v>0.00385806261246309</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003906927920866953</v>
+        <v>0.003355967437244289</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004522628031196892</v>
+        <v>0.004109426121745451</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.005244294829245643</v>
+        <v>0.004402266892391427</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003396084549048919</v>
+        <v>0.003316617511592936</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003357032616038271</v>
+        <v>0.003285301962709197</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003415780687997735</v>
+        <v>0.003340456897004078</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003369171703981003</v>
+        <v>0.003299573964464743</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003374995309137164</v>
+        <v>0.003300168901015921</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003445857260364017</v>
+        <v>0.003329147285065062</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003406808248220543</v>
+        <v>0.003343119817927472</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003399783188309238</v>
+        <v>0.003342413216856804</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003414670749174512</v>
+        <v>0.003338027439216107</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003414906797896417</v>
+        <v>0.003345727235350121</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003432872689431462</v>
+        <v>0.003325926674888853</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003408009890226155</v>
+        <v>0.003438825901471509</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003385144597240117</v>
+        <v>0.003317893642221028</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004597909056531404</v>
+        <v>0.004483032585960684</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003450988527227849</v>
+        <v>0.003326742528265093</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003371710736551476</v>
+        <v>0.003301678318412113</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003369576358528909</v>
+        <v>0.003329423010886056</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003413506883579653</v>
+        <v>0.003328735253645574</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003401005950580004</v>
+        <v>0.003336261731448303</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006294149828051279</v>
+        <v>0.006186464065030506</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003374916878344153</v>
+        <v>0.003306256002060768</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006636803964884277</v>
+        <v>0.00656273681793062</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003449958717654105</v>
+        <v>0.003359270080270003</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00346891169643978</v>
+        <v>0.003369964157403132</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005312855698961663</v>
+        <v>0.005237603456321877</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00342031835255426</v>
+        <v>0.003358726008804838</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003470145411704454</v>
+        <v>0.003376476269240985</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003298371699594719</v>
+        <v>0.003134221835546614</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003004208933947307</v>
+        <v>0.002931993128263949</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003441769106936833</v>
+        <v>0.003306594766251451</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003107649274245896</v>
+        <v>0.00301356214590464</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003149966426708381</v>
+        <v>0.003018363473734888</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003652111513107077</v>
+        <v>0.003223224000201302</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003379150899622008</v>
+        <v>0.003327222379910584</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003327749565746444</v>
+        <v>0.003321074223440317</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003431432153712386</v>
+        <v>0.003287894566393699</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003432342353680299</v>
+        <v>0.003341338568619201</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003562023114880934</v>
+        <v>0.003201515409205823</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003391735523159627</v>
+        <v>0.004008315401810131</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00322218536716361</v>
+        <v>0.003144800061043335</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0052757267252609</v>
+        <v>0.005031636533560006</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003688526525530274</v>
+        <v>0.003206072030848677</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003125952569785911</v>
+        <v>0.003028733524393093</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003111642477861923</v>
+        <v>0.003228443526636189</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003422385814601785</v>
+        <v>0.003220485701017944</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003336320513356464</v>
+        <v>0.003276836098375432</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008338884750935359</v>
+        <v>0.008010854617689731</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003147287176055699</v>
+        <v>0.003060069224933981</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008908300574105641</v>
+        <v>0.008815067586847733</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003685664047240742</v>
+        <v>0.003440713960002895</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003819431298110927</v>
+        <v>0.003515904304043751</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006402550171911663</v>
+        <v>0.006277374916751475</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003472947791977078</v>
+        <v>0.003435987969260481</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003829931809109404</v>
+        <v>0.003563428338212674</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002428446849527197</v>
+        <v>0.002023322420139962</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001951802212897825</v>
+        <v>0.00171079980373917</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002650923799625596</v>
+        <v>0.002292599245017863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002124453883964655</v>
+        <v>0.001830807714907982</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00219023418319424</v>
+        <v>0.001837527796937907</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002990652520409613</v>
+        <v>0.002164851975488173</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002549575964816008</v>
+        <v>0.002322678161851769</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002470224681430575</v>
+        <v>0.002314696777706055</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002637767262749147</v>
+        <v>0.002264738620843752</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002641052808921916</v>
+        <v>0.002352130141111874</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002843985818528678</v>
+        <v>0.002128473701994021</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002572329645581155</v>
+        <v>0.003397626491836514</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002304875061220289</v>
+        <v>0.01065751711119261</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00241711367365793</v>
+        <v>0.00196676715476014</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003048612540136</v>
+        <v>0.002137689141189749</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002153133424860852</v>
+        <v>0.001854577360794161</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002129024643233582</v>
+        <v>0.002167966425476466</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002625240132721662</v>
+        <v>0.002160197891061258</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002484036343777323</v>
+        <v>0.002245212920193913</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002946118573648483</v>
+        <v>0.002294962393668577</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002185289938972421</v>
+        <v>0.001903583873994921</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00296148283975861</v>
+        <v>0.002684824878582166</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003036980367264722</v>
+        <v>0.002505102804498443</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003240254001695554</v>
+        <v>0.002610872017120813</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002306380041698132</v>
+        <v>0.001967111821771601</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002702178808220386</v>
+        <v>0.002498957267014146</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003257646810168738</v>
+        <v>0.002693294435255652</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01282952747956325</v>
+        <v>0.00964056652239407</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005172505668847313</v>
+        <v>0.004678656628243512</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01822842655015096</v>
+        <v>0.01555883772225211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00815556672188787</v>
+        <v>0.006743981823721164</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009709633551319137</v>
+        <v>0.007150574563658591</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02200064424093838</v>
+        <v>0.01192430632710085</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01717104667194941</v>
+        <v>0.01693150447181834</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0151130025904973</v>
+        <v>0.01621764555819941</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0167544153087661</v>
+        <v>0.01436774091523692</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01640083149557325</v>
+        <v>0.01512398668851522</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02074524425736453</v>
+        <v>0.01194270281147619</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01706585642497451</v>
+        <v>0.03664125070594038</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02149137275900825</v>
+        <v>0.01065751711119261</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01212554542079595</v>
+        <v>0.008382624199860939</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02291844109811389</v>
+        <v>0.01144953533113757</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008757177077568883</v>
+        <v>0.007243416217733887</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008809131366045027</v>
+        <v>0.01366447967757795</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01613915056437291</v>
+        <v>0.01194687444844343</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01527645833276524</v>
+        <v>0.01481527616122531</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02214342525119082</v>
+        <v>0.01475673581643868</v>
       </c>
       <c r="V5" t="n">
-        <v>0.008591536369448949</v>
+        <v>0.007463173877554209</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02309925431496948</v>
+        <v>0.02197792502869768</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02503814894858483</v>
+        <v>0.01923883746522206</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02804664433258781</v>
+        <v>0.02078771564154237</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01040440591139991</v>
+        <v>0.008395774620262909</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01850953488980693</v>
+        <v>0.01869331866056792</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03111161741162916</v>
+        <v>0.02425667963346372</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00265124781912988</v>
+        <v>0.002548230975754041</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002174603182500507</v>
+        <v>0.001903470386823867</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003250815421358112</v>
+        <v>0.002817507800631943</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002347254853567337</v>
+        <v>0.00235571627052206</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002790125804926751</v>
+        <v>0.002030198380022606</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003213453490012293</v>
+        <v>0.002357522558572871</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00277237693441869</v>
+        <v>0.002515348744936469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002693025651033257</v>
+        <v>0.002507367360790756</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003237658884481657</v>
+        <v>0.002789647176457834</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003240944430654426</v>
+        <v>0.002877038696725952</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003066786788131359</v>
+        <v>0.002653382257608103</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003172221267313664</v>
+        <v>0.003590297074921213</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00252974662392599</v>
+        <v>0.01065751711119261</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002641985236363626</v>
+        <v>0.002495609333666929</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00365149406446647</v>
+        <v>0.002666983436113825</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002753025046593366</v>
+        <v>0.00237948591640824</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002728916264966094</v>
+        <v>0.002360637008561166</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002848041102324345</v>
+        <v>0.002685106446675337</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002706837313380005</v>
+        <v>0.002437883503278615</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00317972852300555</v>
+        <v>0.002502658284868104</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002785181560704932</v>
+        <v>0.002428492429609002</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003208730388266212</v>
+        <v>0.003213617019748438</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003259781336867403</v>
+        <v>0.002697773387583142</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003491637390739479</v>
+        <v>0.002835361713163064</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002529181011300814</v>
+        <v>0.00249202037738568</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003302070429952895</v>
+        <v>0.003023865822628223</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003486732407681928</v>
+        <v>0.00289144622135251</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002748903019383827</v>
+        <v>0.002333569109483807</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002272258382754454</v>
+        <v>0.002021046493083014</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002971379969482225</v>
+        <v>0.002602845934361708</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002444910053821283</v>
+        <v>0.002141054404251825</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002510690353050868</v>
+        <v>0.00214777448628175</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003311108690266245</v>
+        <v>0.00247509866483202</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002870032134672639</v>
+        <v>0.002632924851195613</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002790680851287203</v>
+        <v>0.002624943467049902</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002958223432605774</v>
+        <v>0.002574985310187598</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002961508978778544</v>
+        <v>0.002662376830455719</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003164441988385307</v>
+        <v>0.002438720391337868</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002892785815437781</v>
+        <v>0.003707873181180359</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00262533123107692</v>
+        <v>0.01065751711119261</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0027375453328709</v>
+        <v>0.002276989870026557</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00336904419934897</v>
+        <v>0.002447911856456172</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002473589594717483</v>
+        <v>0.002164824050138006</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002449480813090212</v>
+        <v>0.00247821311482031</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002945696302578291</v>
+        <v>0.002470444580405103</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002804492513633953</v>
+        <v>0.002555459609537758</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003276933548286646</v>
+        <v>0.00261986826880041</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002505746108829049</v>
+        <v>0.002213830563338766</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003281939009615242</v>
+        <v>0.002995071567926008</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003357436537121348</v>
+        <v>0.002815349493842287</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00357151915130657</v>
+        <v>0.002936144014579482</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00262683621155476</v>
+        <v>0.002277358511115446</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003022634978077012</v>
+        <v>0.00280920395635799</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003578102980025365</v>
+        <v>0.003003541124599493</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003117500797004953</v>
+        <v>0.002685221124089009</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003188282268484382</v>
+        <v>0.002891863283921219</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003887403855212154</v>
+        <v>0.003473662725199915</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003069445685221574</v>
+        <v>0.002735431266323827</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002964570720320878</v>
+        <v>0.002580306305328547</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004340644945598107</v>
+        <v>0.003453567654003582</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003786056020402565</v>
+        <v>0.003503741642033821</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003706704737017134</v>
+        <v>0.003495760257888107</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003874247318335701</v>
+        <v>0.003445802101025804</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003877532864508471</v>
+        <v>0.003533193621293924</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004080465874115233</v>
+        <v>0.003309537182176075</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003808809701167677</v>
+        <v>0.004578689972018752</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003117008300420193</v>
+        <v>0.01065751711119261</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003345861102101613</v>
+        <v>0.00285598496270568</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003948775013049164</v>
+        <v>0.002999797715908653</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002734605647945955</v>
+        <v>0.002414448337093099</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003365504698820142</v>
+        <v>0.003349029905658517</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003861720188308221</v>
+        <v>0.003341261371243307</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003720516399363881</v>
+        <v>0.003426276400375969</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003925886352127662</v>
+        <v>0.003237388626913753</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003271786337198258</v>
+        <v>0.002942459332433961</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00419807047941661</v>
+        <v>0.003865990388690213</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003668625280386742</v>
+        <v>0.003112556263621712</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00503127202817128</v>
+        <v>0.004322700919613663</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002985265268252737</v>
+        <v>0.002619366773544996</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003938658863806946</v>
+        <v>0.003680020747196196</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.005065959209894608</v>
+        <v>0.00441666893527407</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003598111969596381</v>
+        <v>0.003057841393205271</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003492651703935758</v>
+        <v>0.003074337222952187</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004191773290663528</v>
+        <v>0.003656136664230886</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003579635728171413</v>
+        <v>0.003118408939213695</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002875402067591954</v>
+        <v>0.002442588035164251</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004531502260997617</v>
+        <v>0.003528389291245924</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00409042545585394</v>
+        <v>0.003686215581064789</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004011074172468509</v>
+        <v>0.003678234196919078</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004178616753787078</v>
+        <v>0.003628276040056774</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004181902299959848</v>
+        <v>0.003715667560324894</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004384835309566608</v>
+        <v>0.003492011121207045</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004113179136619082</v>
+        <v>0.00476116391104954</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003845724552258222</v>
+        <v>0.01065751711119261</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004080973511461097</v>
+        <v>0.003439340718473408</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004739224963585625</v>
+        <v>0.003633976218086389</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003693983165448859</v>
+        <v>0.00321811467655191</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003669874134271514</v>
+        <v>0.003531503844689486</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004166089623759594</v>
+        <v>0.00352373531027428</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004024885834815255</v>
+        <v>0.003608750339406935</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004497777044440801</v>
+        <v>0.003673525120996424</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004154478292944736</v>
+        <v>0.003646800935305884</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00450233233079654</v>
+        <v>0.004048362297795186</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004577829858302649</v>
+        <v>0.003868640223711462</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.004791912472487877</v>
+        <v>0.00398943474444866</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003623438463137587</v>
+        <v>0.003132280334338391</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004243028299258318</v>
+        <v>0.003862494686227165</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.004798496301206669</v>
+        <v>0.004056831854468671</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003413635818464756</v>
+        <v>0.003305904185634161</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003343569846040829</v>
+        <v>0.003229515685633449</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003416065807379038</v>
+        <v>0.003313557578666684</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003384636986410309</v>
+        <v>0.003286538435546642</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003407405329143564</v>
+        <v>0.003299277641273737</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003458765902514962</v>
+        <v>0.003318723271666534</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003427321350302204</v>
+        <v>0.003332878889314193</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003423058147015727</v>
+        <v>0.003330350468882828</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003433379783345781</v>
+        <v>0.003329372326336312</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003453824787788834</v>
+        <v>0.003353024359908781</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003443485271773113</v>
+        <v>0.003314889170598065</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003423582093751747</v>
+        <v>0.003406075542261246</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003395978683943355</v>
+        <v>0.003300031737005483</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004617599909400528</v>
+        <v>0.004470964094324024</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003464821348962455</v>
+        <v>0.003316271659823881</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003398523427245103</v>
+        <v>0.003296397257213773</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003402713203479139</v>
+        <v>0.0033274831034184</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003433720646886697</v>
+        <v>0.003320068090045284</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003425921239426202</v>
+        <v>0.003334112376934623</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006234439180551356</v>
+        <v>0.006038464717937783</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003420822142487997</v>
+        <v>0.003314157669947535</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006584200837382901</v>
+        <v>0.006421708132379557</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003485122268828036</v>
+        <v>0.003364286402974885</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003568108420110939</v>
+        <v>0.003408986430976449</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00533568211692259</v>
+        <v>0.005223148740070726</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003449736717808679</v>
+        <v>0.003355285620747233</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003483798645834927</v>
+        <v>0.003362216552624096</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003272984189453398</v>
+        <v>0.003092002815990395</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002964604678078529</v>
+        <v>0.002841270408921323</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003292268586825797</v>
+        <v>0.003148046152945966</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003067357913833735</v>
+        <v>0.002954728321820259</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003230941190923492</v>
+        <v>0.003046446644744623</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003593177955945613</v>
+        <v>0.003182919864829147</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003375142950042325</v>
+        <v>0.003288481092036573</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003343099748957505</v>
+        <v>0.003268857279764535</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003414242268916713</v>
+        <v>0.003260126620213046</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003559457188670422</v>
+        <v>0.003427591170759428</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003486389476405832</v>
+        <v>0.00315663589007886</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003351658384942417</v>
+        <v>0.003807416272325708</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003149092436266016</v>
+        <v>0.003051700266141205</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005240159151975103</v>
+        <v>0.005012471294926194</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003636054086158391</v>
+        <v>0.003165446619528482</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003166694151370786</v>
+        <v>0.003025278968841026</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003198089436774825</v>
+        <v>0.003249171920513208</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003416129025146456</v>
+        <v>0.003192955567397094</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003363857684795557</v>
+        <v>0.003296065331273316</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008288599123406194</v>
+        <v>0.007789723768825295</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003323507999280329</v>
+        <v>0.003150229868619549</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008749437420788427</v>
+        <v>0.008516163497861804</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003784977356147318</v>
+        <v>0.003509977390233574</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004378564507930241</v>
+        <v>0.003829884147776884</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006394826143632989</v>
+        <v>0.006227847138491571</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003532792264203881</v>
+        <v>0.003446097986593053</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003776331307039923</v>
+        <v>0.003495383828472698</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00237114401635432</v>
+        <v>0.001964527801089942</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00197005744844734</v>
+        <v>0.001704990444898183</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002398591858991218</v>
+        <v>0.002050976396127042</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00204358886817745</v>
+        <v>0.001745782745166223</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0023007677733047</v>
+        <v>0.001889677934177936</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002880909076565706</v>
+        <v>0.002109325274896508</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002525728394113923</v>
+        <v>0.002269219488132668</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002477573551822775</v>
+        <v>0.002240659816229524</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002593731291565159</v>
+        <v>0.00222930285804557</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002825096912709028</v>
+        <v>0.00249677184587288</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002708307322899098</v>
+        <v>0.002066017339554521</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002493206405966104</v>
+        <v>0.003092406073240686</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002171698559251855</v>
+        <v>0.008037737290349593</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002329885294005128</v>
+        <v>0.001959419556286017</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002949308129833069</v>
+        <v>0.002081633191336577</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002200442605484836</v>
+        <v>0.001857142671178506</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002247768055440543</v>
+        <v>0.002208271604255526</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002598011392857627</v>
+        <v>0.002124515617131543</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002509913497686653</v>
+        <v>0.002283152298237773</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003105893078664719</v>
+        <v>0.002340718883332258</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002449545332593314</v>
+        <v>0.002055804126239676</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002867012184939952</v>
+        <v>0.002539892849149279</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003178616358599406</v>
+        <v>0.002623981803100291</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004108266411082659</v>
+        <v>0.003118787033606079</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002267696562047655</v>
+        <v>0.001906037005975642</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002778920281678083</v>
+        <v>0.002522313827274593</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003157167734893113</v>
+        <v>0.002594796501876434</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01114174778722722</v>
+        <v>0.008376892981279489</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004987019456947338</v>
+        <v>0.004461175760248339</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01263331306874163</v>
+        <v>0.01064211531463305</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006042729734109625</v>
+        <v>0.004995068614079026</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01115336732600149</v>
+        <v>0.007953623631553495</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01917217606652668</v>
+        <v>0.01064072146279441</v>
       </c>
       <c r="H5" t="n">
-        <v>0.016199773830721</v>
+        <v>0.01581724567926436</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01451036231897289</v>
+        <v>0.01449418103792268</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01526423030478843</v>
+        <v>0.01339177070788281</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01898529609431739</v>
+        <v>0.01742221627576744</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01729587379474458</v>
+        <v>0.01043453323787387</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01454901396933543</v>
+        <v>0.0295914212315468</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02262531156263644</v>
+        <v>0.008037737290349593</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01033520448876128</v>
+        <v>0.008185470603660719</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0202047488224768</v>
+        <v>0.0101633945391186</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008935110960964856</v>
+        <v>0.007061946912116153</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0105456643611944</v>
+        <v>0.01432512771115228</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01504980485002046</v>
+        <v>0.01113619744542811</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01525020193365786</v>
+        <v>0.0154318387621046</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02356722278382202</v>
+        <v>0.01489892225500793</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0121780321969149</v>
+        <v>0.00967221080962602</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02095101311913307</v>
+        <v>0.01932678398262727</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0263512688260732</v>
+        <v>0.02071296609664268</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04360946305478351</v>
+        <v>0.03009934645958446</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00900043835863972</v>
+        <v>0.007078616977171606</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01947028094694671</v>
+        <v>0.01910116819241443</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0282163668970956</v>
+        <v>0.02192414713943931</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003014654009254951</v>
+        <v>0.002164186684349026</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002224659815426286</v>
+        <v>0.001904649328157264</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002653194225970163</v>
+        <v>0.002578626822670505</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002687098861078081</v>
+        <v>0.002273433171709692</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002555370140283647</v>
+        <v>0.002089336817437018</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003524419069466336</v>
+        <v>0.002308984158155596</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002780330761092869</v>
+        <v>0.002796869914676126</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002732175918801719</v>
+        <v>0.002440318699488607</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00323724128446579</v>
+        <v>0.002756953284589035</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003468606905609653</v>
+        <v>0.00302442227241635</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003351817315799728</v>
+        <v>0.002265676222813609</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002747808772945049</v>
+        <v>0.003292064956499769</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002429870110668157</v>
+        <v>0.008037737290349593</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002979214127256313</v>
+        <v>0.002212015865063065</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003181673066420465</v>
+        <v>0.002614993504129999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002843952598385467</v>
+        <v>0.002384793097721968</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002891278048341173</v>
+        <v>0.002735922030798992</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003241521385758259</v>
+        <v>0.002324174500390621</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003153423490587285</v>
+        <v>0.002810802724781246</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003368212147416459</v>
+        <v>0.002878471458676393</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00270414769957226</v>
+        <v>0.002255463009498761</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00351634012060972</v>
+        <v>0.002763773595953439</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003433218725578349</v>
+        <v>0.002823640686359369</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.004393182860076442</v>
+        <v>0.003353327415884848</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002911206554948287</v>
+        <v>0.002105695889234723</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003422430274578712</v>
+        <v>0.003049964253818052</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003417940181807193</v>
+        <v>0.002799177461729478</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002669172479123141</v>
+        <v>0.002269883664683243</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002268085911216162</v>
+        <v>0.002010346308491481</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002696620321760038</v>
+        <v>0.002356332259720341</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002341617330946271</v>
+        <v>0.002051138608759522</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002598796236073523</v>
+        <v>0.002195033797771237</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003178937539334527</v>
+        <v>0.002414681138489809</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002823756856882745</v>
+        <v>0.002574575351725967</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002775602014591595</v>
+        <v>0.002546015679822824</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00289175975433398</v>
+        <v>0.002534658721638868</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003123125375477846</v>
+        <v>0.00280212770946618</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003006335785667919</v>
+        <v>0.00237137320314782</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002791234868734925</v>
+        <v>0.003397761936833983</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002469727022020678</v>
+        <v>0.008037737290349593</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002627888891864065</v>
+        <v>0.002264751284192893</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003247311727692011</v>
+        <v>0.002386964919243451</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002498471068253657</v>
+        <v>0.002162498534771805</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002545796518209363</v>
+        <v>0.002513627467848826</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002896039855626452</v>
+        <v>0.002429871480724844</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002807941960455475</v>
+        <v>0.002588508161831073</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003411212950295687</v>
+        <v>0.002655816451862682</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002747573795362137</v>
+        <v>0.002361159989832977</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003165040647708771</v>
+        <v>0.00284524871274258</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003476644821368226</v>
+        <v>0.002929337666693588</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.004414011575624279</v>
+        <v>0.003434245046000046</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002565725024816475</v>
+        <v>0.002211392869568942</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003076948744446904</v>
+        <v>0.002827669690867893</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003455196197661933</v>
+        <v>0.002900152365469731</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003055404970923468</v>
+        <v>0.002616039765353165</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003213900689617771</v>
+        <v>0.002867765195700912</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003642435100161651</v>
+        <v>0.003213751146929773</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002989471048555471</v>
+        <v>0.002636325143619876</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003072205108059309</v>
+        <v>0.002620838665241342</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004240785350138814</v>
+        <v>0.003378113694993091</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003769571635284356</v>
+        <v>0.0034319942389354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003721416792993204</v>
+        <v>0.003403434567032257</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003837574532735593</v>
+        <v>0.003392077608848301</v>
       </c>
       <c r="K8" t="n">
-        <v>0.004068940153879457</v>
+        <v>0.003659546596675611</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00395215056406953</v>
+        <v>0.003228792090357253</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003737049647136516</v>
+        <v>0.004255180824043672</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002981771912019445</v>
+        <v>0.008037737290349593</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003259162378026092</v>
+        <v>0.002834790695631443</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003849365499004803</v>
+        <v>0.002930307715745771</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002774732869135601</v>
+        <v>0.002408179829119816</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003491611296610975</v>
+        <v>0.003371046355058259</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00384185463402806</v>
+        <v>0.003287290367934275</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003753756738857085</v>
+        <v>0.003445927049040505</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00408401805380589</v>
+        <v>0.00326379460950086</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003540104020917052</v>
+        <v>0.003078555580180909</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004110965399219674</v>
+        <v>0.003702768076913206</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003804193450201101</v>
+        <v>0.003221877210810633</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005915675413996251</v>
+        <v>0.004799555021434927</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002941562988436645</v>
+        <v>0.002548052001578451</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.004022763522848513</v>
+        <v>0.003685088578077325</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004985541465122628</v>
+        <v>0.004291627983529471</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003433315150703594</v>
+        <v>0.00291985216448152</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003380301514284638</v>
+        <v>0.002966864694683609</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003808835924828518</v>
+        <v>0.003312850645912468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003373499296582244</v>
+        <v>0.002936906471115697</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002908608436322187</v>
+        <v>0.002444871133002971</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004291153370419604</v>
+        <v>0.003371199446093592</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003935972459951219</v>
+        <v>0.003531093737918094</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00388781761766007</v>
+        <v>0.003502534066014949</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004003975357402458</v>
+        <v>0.003491177107830996</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004235340978546325</v>
+        <v>0.003758646095658308</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004118551388736394</v>
+        <v>0.003327891589339951</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003903450471803401</v>
+        <v>0.004354280323026117</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003581942625089153</v>
+        <v>0.008037737290349593</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003855480577155964</v>
+        <v>0.003322883932397136</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004499990274066312</v>
+        <v>0.003467191694022115</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003610686899338735</v>
+        <v>0.003119016842375592</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003658012121277841</v>
+        <v>0.003470145854040949</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00400825545869493</v>
+        <v>0.003386389866916966</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003920157563523953</v>
+        <v>0.003545026548023198</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004523853846274813</v>
+        <v>0.003612695281918352</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004261458194035648</v>
+        <v>0.003671429910669197</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00427725625077725</v>
+        <v>0.003801767098934705</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004588860424436704</v>
+        <v>0.003885856052885719</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.005526227178692755</v>
+        <v>0.004390763432192173</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003468083692593268</v>
+        <v>0.002983088902538508</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00418916434751538</v>
+        <v>0.003784188077060013</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.00456741180073041</v>
+        <v>0.003856670751661858</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003248440077933588</v>
+        <v>0.003226329501510926</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003233842210704379</v>
+        <v>0.003212803043884234</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003266025227196108</v>
+        <v>0.003244996560040805</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003248877253571247</v>
+        <v>0.003228106496477423</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003246339729023156</v>
+        <v>0.003224772793366714</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003267434431001308</v>
+        <v>0.003232977691227173</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003274258069680541</v>
+        <v>0.003253448514126251</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003258267503816914</v>
+        <v>0.003247043713087094</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00326542589274429</v>
+        <v>0.003242019253946282</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003281800457481923</v>
+        <v>0.003262895626701891</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003279752879889518</v>
+        <v>0.003248933820480923</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003271267341650375</v>
+        <v>0.003277063452089621</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003273979045118133</v>
+        <v>0.003253611313723354</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004396074500982766</v>
+        <v>0.004366577387489541</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003269808479259128</v>
+        <v>0.003239340534660318</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003258281884346662</v>
+        <v>0.003237340784173173</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003256144355494822</v>
+        <v>0.003246735610912748</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003263768446667708</v>
+        <v>0.003240598515710454</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003253808494652091</v>
+        <v>0.003238114836485959</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006108284203276406</v>
+        <v>0.006079447800872355</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003247557610837944</v>
+        <v>0.003226739323284043</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006487224736783434</v>
+        <v>0.006467001584163666</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003272115239063018</v>
+        <v>0.003249844294457746</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00325259373452949</v>
+        <v>0.003230755458696909</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005178316764125656</v>
+        <v>0.005154493456800696</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003276405455973663</v>
+        <v>0.003266519858147543</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003295675402262591</v>
+        <v>0.003268306613645804</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002907230507640977</v>
+        <v>0.002876995985061856</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002823350404786821</v>
+        <v>0.002804436869752773</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003033740267693406</v>
+        <v>0.003011154884097253</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002910771473244276</v>
+        <v>0.002890043101837082</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002892976351274895</v>
+        <v>0.002866540906353593</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003041584518473843</v>
+        <v>0.002923960918487435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003093486388630114</v>
+        <v>0.003072456956607133</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002978410427514052</v>
+        <v>0.0030260057401794</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003028101539831085</v>
+        <v>0.002988799028318655</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003144942427564318</v>
+        <v>0.003137479855105603</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003129239730897485</v>
+        <v>0.003037277910485806</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003074134397130445</v>
+        <v>0.003240366349614838</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003089873866500117</v>
+        <v>0.003072016527493414</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004819847521666089</v>
+        <v>0.004779564047654003</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003059221824979081</v>
+        <v>0.002969554741580289</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002977799458107346</v>
+        <v>0.00295585293968509</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002963436734512787</v>
+        <v>0.003024146292417124</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003015245058510858</v>
+        <v>0.002977572134281719</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002946149192051852</v>
+        <v>0.002961637895839951</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007833052386066422</v>
+        <v>0.007751891449858581</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002900973188902646</v>
+        <v>0.002879912428710699</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008675668803819083</v>
+        <v>0.008646917803496778</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003077081676465352</v>
+        <v>0.003045622455279736</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002937329788108484</v>
+        <v>0.002908981671766458</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006153035771507225</v>
+        <v>0.006121545648834754</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003107332411036136</v>
+        <v>0.003164295484223336</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003244778129333419</v>
+        <v>0.003176983878767036</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001803598249057347</v>
+        <v>0.001656675535593346</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001679146816890058</v>
+        <v>0.001552090287818646</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002002230599545906</v>
+        <v>0.001867528548959495</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001808536348995456</v>
+        <v>0.001676747511197989</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001779873841905828</v>
+        <v>0.001639091800983336</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002018148204791393</v>
+        <v>0.001731769896756715</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002095224342702221</v>
+        <v>0.001962997258445572</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001914603545248815</v>
+        <v>0.001890652084354273</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001995011638833216</v>
+        <v>0.001833499296515821</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002180419082588636</v>
+        <v>0.002069706740873939</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002157290751750185</v>
+        <v>0.001912001716859921</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002068556020204712</v>
+        <v>0.002232837617629069</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002092072631912166</v>
+        <v>0.01028113026333441</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001841679038623355</v>
+        <v>0.001699172932095563</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002044964171979643</v>
+        <v>0.001803641140386679</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001914765979947688</v>
+        <v>0.001781053038703689</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001890621608254311</v>
+        <v>0.001887171928561013</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001976739225307265</v>
+        <v>0.001817850615047855</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001864236985486591</v>
+        <v>0.001789796315658257</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002221264806625511</v>
+        <v>0.001975828308645614</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001790728842571608</v>
+        <v>0.001658742380594802</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002671627742193017</v>
+        <v>0.002521472850207825</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002071020085126459</v>
+        <v>0.001922285939266858</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001844965976942967</v>
+        <v>0.001684851363130742</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00192872059815543</v>
+        <v>0.00178503225963625</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002119480058729533</v>
+        <v>0.002110644102281423</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002334224259484352</v>
+        <v>0.002128266683396345</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004765564716450157</v>
+        <v>0.004282669601460416</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002737373185482389</v>
+        <v>0.002593556032749946</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009079481292572442</v>
+        <v>0.008787331491077324</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005092974542807286</v>
+        <v>0.004864970115404649</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004726390983825549</v>
+        <v>0.004314602842345231</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00814951416453288</v>
+        <v>0.005433631422805584</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01138722853785358</v>
+        <v>0.0111375044482548</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00744344759822682</v>
+        <v>0.009358149505842975</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008193969004577698</v>
+        <v>0.007535579556333254</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01167757754699382</v>
+        <v>0.01181949361131763</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01063460094619218</v>
+        <v>0.008528491745601299</v>
       </c>
       <c r="M5" t="n">
-        <v>0.009841964373457272</v>
+        <v>0.01495200473673505</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0123348716268235</v>
+        <v>0.01028113026333441</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005340946457779323</v>
+        <v>0.004940820988850902</v>
       </c>
       <c r="P5" t="n">
-        <v>0.009042298304552169</v>
+        <v>0.006893725852103901</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.007049646446299839</v>
+        <v>0.006783926509543117</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007089729989435721</v>
+        <v>0.009481156746267269</v>
       </c>
       <c r="S5" t="n">
-        <v>0.007269148726498222</v>
+        <v>0.006628001240249609</v>
       </c>
       <c r="T5" t="n">
-        <v>0.006248046944041803</v>
+        <v>0.007094124670844835</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01246961353567841</v>
+        <v>0.01050049396502914</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00459693430337718</v>
+        <v>0.004362921119756622</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0215212904279047</v>
+        <v>0.02094274406809762</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0103115674491398</v>
+        <v>0.009749850293248798</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005905405804064551</v>
+        <v>0.005448956935830883</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.006807003119350283</v>
+        <v>0.006385593364224439</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01102275874614978</v>
+        <v>0.01312149345549724</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01591787447927928</v>
+        <v>0.01419267880089739</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002003753743612133</v>
+        <v>0.001837394528884004</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002216382694789458</v>
+        <v>0.001732809281109306</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002202386094100693</v>
+        <v>0.002366602025157313</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002008691843550242</v>
+        <v>0.00217582098739581</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002317109719805229</v>
+        <v>0.001819810794273993</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002555384082690792</v>
+        <v>0.001912488890047374</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002295379837257008</v>
+        <v>0.002462070734643387</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002114759039803602</v>
+        <v>0.002389725560552094</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002195167133388002</v>
+        <v>0.002014218289806478</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002380574577143424</v>
+        <v>0.002568780217071767</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002357446246304971</v>
+        <v>0.002092720710150583</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002605791898104113</v>
+        <v>0.002731911093826879</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002292964361355323</v>
+        <v>0.01028113026333441</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002382869526951178</v>
+        <v>0.002206721120442722</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002224978823226821</v>
+        <v>0.002311731642930826</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002452001857847088</v>
+        <v>0.002280126514901502</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002090777102809098</v>
+        <v>0.002386245404758833</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002176894719862052</v>
+        <v>0.001998569608338514</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00240147286338599</v>
+        <v>0.001970515308948917</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002426970035321867</v>
+        <v>0.002178364696855437</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002327964720471008</v>
+        <v>0.002157815856792613</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002895227323846329</v>
+        <v>0.0030291894215026</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002271175579681247</v>
+        <v>0.002103004932557517</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002066685140842771</v>
+        <v>0.001902499909579235</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002465956476054829</v>
+        <v>0.001965751252926908</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002656715936628933</v>
+        <v>0.00260971757847924</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002537517228471917</v>
+        <v>0.002311904800867685</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002110451927606963</v>
+        <v>0.001957914062132385</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001986000495439674</v>
+        <v>0.001853328814357687</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002309084278095522</v>
+        <v>0.002168767075498535</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00211539002754507</v>
+        <v>0.001977986037737029</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002086727520455441</v>
+        <v>0.001940330327522377</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002325001883341008</v>
+        <v>0.002033008423295756</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002402078021251835</v>
+        <v>0.002264235784984613</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00222145722379843</v>
+        <v>0.002191890610893315</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00230186531738283</v>
+        <v>0.002134737823054863</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002487272761138251</v>
+        <v>0.00237094526741298</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002464144430299799</v>
+        <v>0.002213240243398963</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002375409698754327</v>
+        <v>0.00253407614416811</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002398926310461781</v>
+        <v>0.01028113026333441</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002148507109726907</v>
+        <v>0.002000386512556174</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002351792243083198</v>
+        <v>0.00210485472084729</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002221619658497304</v>
+        <v>0.002082291565242728</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002197475286803926</v>
+        <v>0.002188410455100052</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00228359290385688</v>
+        <v>0.002119089141586897</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002171090664036207</v>
+        <v>0.002091034842197299</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002533232708410363</v>
+        <v>0.002298454631300353</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002097582521121224</v>
+        <v>0.001959980907133855</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002978481420742632</v>
+        <v>0.002822711376746865</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002377873763676074</v>
+        <v>0.002223524465805897</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002157369389634151</v>
+        <v>0.002007907284588948</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002235574276705046</v>
+        <v>0.00208627078617529</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002426333737279148</v>
+        <v>0.002411882628820463</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.002641077938033964</v>
+        <v>0.002429505209935384</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002464462370473049</v>
+        <v>0.002308464204399946</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002864672856612304</v>
+        <v>0.002718159421567039</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003187756639268151</v>
+        <v>0.003033597682707885</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00271469539396519</v>
+        <v>0.002568977467874917</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002522474158244918</v>
+        <v>0.002370999355610803</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003312466311061698</v>
+        <v>0.003004478435069943</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003280750382424465</v>
+        <v>0.003129066392193963</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00310012958497106</v>
+        <v>0.003056721218102667</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00318053767855546</v>
+        <v>0.002999568430264212</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003365945122310881</v>
+        <v>0.003235775874622332</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003342816791472431</v>
+        <v>0.003078070850608315</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003254082059926901</v>
+        <v>0.0033989067513775</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002870897910699254</v>
+        <v>0.01028113026333441</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002732269217374924</v>
+        <v>0.002576142082753042</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002908158073180807</v>
+        <v>0.002653756101967351</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002472522059846314</v>
+        <v>0.002331773858521764</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003076147647976556</v>
+        <v>0.003053241062309404</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003162265265029511</v>
+        <v>0.002983919748796247</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003049763025208836</v>
+        <v>0.00295586544940665</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003155942435099867</v>
+        <v>0.00291238780994815</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002832506493222887</v>
+        <v>0.002683905021214425</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003857256892126759</v>
+        <v>0.003687643053924523</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002676862471806202</v>
+        <v>0.002520141585042971</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003557157721245661</v>
+        <v>0.003383538780658424</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002579838855164729</v>
+        <v>0.002427267904861626</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003305006098451778</v>
+        <v>0.003276713236029815</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004067803543545112</v>
+        <v>0.003831544765370216</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002905795438849808</v>
+        <v>0.002713868601858374</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003131757706413463</v>
+        <v>0.002945242322058707</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00345484148906931</v>
+        <v>0.003260680583199553</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003180273314442497</v>
+        <v>0.002992361645961201</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002424685298506604</v>
+        <v>0.002257766620358188</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003470759261383722</v>
+        <v>0.003124922008973643</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003547835232225628</v>
+        <v>0.003356149292685631</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00336721443477222</v>
+        <v>0.003283804118594335</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003447622528356618</v>
+        <v>0.003226651330755883</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003633029972112042</v>
+        <v>0.003462858775114001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003609901641273591</v>
+        <v>0.003305153751099983</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003521166909728115</v>
+        <v>0.00362598965186913</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003544683521435572</v>
+        <v>0.01028113026333441</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003410416791845343</v>
+        <v>0.003203661432240102</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003638957489320014</v>
+        <v>0.003332343394694762</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003367377036540016</v>
+        <v>0.003174205150920613</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003343232497777716</v>
+        <v>0.003280323962801074</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00342935011483067</v>
+        <v>0.003211002649287918</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003316847875009996</v>
+        <v>0.003182948349898322</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003679425430290486</v>
+        <v>0.003390797737804843</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003647709672159818</v>
+        <v>0.003439583738203369</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004124238631716423</v>
+        <v>0.003914624884447887</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003523630974649863</v>
+        <v>0.00331543797350692</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003303126600607943</v>
+        <v>0.00309982079228997</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003170063253084247</v>
+        <v>0.002975630941788169</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003572090948252939</v>
+        <v>0.003503796136521482</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.003786835149007757</v>
+        <v>0.003521418717636404</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003220102544939891</v>
+        <v>0.003203157124925503</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003224446287979212</v>
+        <v>0.003202265814776651</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00322483238586867</v>
+        <v>0.003207073308294817</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003224466878008615</v>
+        <v>0.003207559156231922</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003225912949153983</v>
+        <v>0.003208654191841092</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003227780740363664</v>
+        <v>0.003210425760057871</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003236402580929124</v>
+        <v>0.003219435711078192</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003227934856761116</v>
+        <v>0.003217386316018049</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003230551714502022</v>
+        <v>0.003213594960971917</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00322497194639933</v>
+        <v>0.003209737658085061</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003225573877907563</v>
+        <v>0.003208714397689846</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003220432120052091</v>
+        <v>0.003203563584847784</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003231237593441961</v>
+        <v>0.003214190321843344</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004359882007103534</v>
+        <v>0.004336420233918662</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003226341074867533</v>
+        <v>0.003210148671623853</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003221264913489841</v>
+        <v>0.003204134342765221</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003234145965201572</v>
+        <v>0.003216474166497749</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003232119606988923</v>
+        <v>0.003214329625848488</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00322164942423962</v>
+        <v>0.003208282079173163</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0060411541439354</v>
+        <v>0.006017985248705103</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003229844100513549</v>
+        <v>0.003212647091354777</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006433979992998518</v>
+        <v>0.006410095202240109</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003274019741949374</v>
+        <v>0.003257151121246534</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00323671822814512</v>
+        <v>0.003219683275015207</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005146357658223283</v>
+        <v>0.005130374855165396</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003252137978735124</v>
+        <v>0.003235624983846864</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003216226994458187</v>
+        <v>0.003199230045606319</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002836130686381322</v>
+        <v>0.002818863806694968</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002854026863144224</v>
+        <v>0.002827826414095609</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002870121163122574</v>
+        <v>0.002847054703364617</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002867417228144994</v>
+        <v>0.00285041722808163</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00287793240591829</v>
+        <v>0.002858426378305105</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002890389781066638</v>
+        <v>0.002870229526717494</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002953435187990598</v>
+        <v>0.002936010713859499</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002892451688774343</v>
+        <v>0.002920892212472485</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002910409775958613</v>
+        <v>0.002893072611641552</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002870945332509265</v>
+        <v>0.002865834438576835</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002874749510781505</v>
+        <v>0.00285809187919589</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002843864428698095</v>
+        <v>0.002827022924499086</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002915637410113896</v>
+        <v>0.002897643584197484</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004773078851816327</v>
+        <v>0.004745002173299882</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002880421045487306</v>
+        <v>0.002868503709066724</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002844435625592203</v>
+        <v>0.002825855615825407</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002937025713330329</v>
+        <v>0.002914558121625123</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002921024457461941</v>
+        <v>0.002897786643616907</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002847446199761581</v>
+        <v>0.002855672825783557</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007489570490277321</v>
+        <v>0.007464034105339277</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002905170039072515</v>
+        <v>0.002886121598401055</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008430733751921266</v>
+        <v>0.00840138461159347</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003220399758295961</v>
+        <v>0.003203678784297683</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002954954018489658</v>
+        <v>0.002937046071546942</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006095600204713982</v>
+        <v>0.006079113115231733</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003064984493883777</v>
+        <v>0.003050802158548933</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002811519051162224</v>
+        <v>0.002793797267455031</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001663096967850608</v>
+        <v>0.001565712815233115</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00168472277232932</v>
+        <v>0.001586751920855377</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001716522696975508</v>
+        <v>0.001609947907922912</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001712394117554251</v>
+        <v>0.001615435783873586</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001728728156366796</v>
+        <v>0.001627804714820444</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001749825717306527</v>
+        <v>0.001647815392790584</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001847213372736028</v>
+        <v>0.001749586934347354</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001751566532912777</v>
+        <v>0.001726438074374733</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001780827491514234</v>
+        <v>0.00168331204872756</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001718099097370338</v>
+        <v>0.001640042964465173</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001724898190658034</v>
+        <v>0.001628484767578169</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001676302125479088</v>
+        <v>0.001579563136744902</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001788872463056876</v>
+        <v>0.005192330177218433</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00177853065305432</v>
+        <v>0.001681034161503713</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001733564033248899</v>
+        <v>0.001644685551461406</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001676226455338276</v>
+        <v>0.001576750940275159</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001821723859998805</v>
+        <v>0.001716134925933446</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001798835211816096</v>
+        <v>0.0016919113527626</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001680569681140689</v>
+        <v>0.001623601531055886</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001653390925014099</v>
+        <v>0.001550391944882778</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001771246426754048</v>
+        <v>0.001670997825559386</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002261263652312399</v>
+        <v>0.002162583374109192</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002272116511208773</v>
+        <v>0.002175599842144642</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001848057389377503</v>
+        <v>0.001739878103686298</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001829063358318971</v>
+        <v>0.001729995856654634</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002024951929595425</v>
+        <v>0.001932452217702934</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001624262326457247</v>
+        <v>0.001526140849835939</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003070647092542423</v>
+        <v>0.0029698369034193</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003580208392358241</v>
+        <v>0.003468632102654674</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004136505416478877</v>
+        <v>0.003877048216305484</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004014104519395578</v>
+        <v>0.003919698720438938</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004403791534236456</v>
+        <v>0.004238909345535129</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004324452034059612</v>
+        <v>0.004157200002165472</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006829899602944501</v>
+        <v>0.006722469125718626</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004853758495708521</v>
+        <v>0.006058145888499161</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005003879717733998</v>
+        <v>0.004906296917510893</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004075313642442524</v>
+        <v>0.004287099409985231</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003940684802618968</v>
+        <v>0.003854914434708589</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003423155576028674</v>
+        <v>0.003332699103673531</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00311623949573773</v>
+        <v>0.005192330177218433</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004835399402401279</v>
+        <v>0.004733224005264929</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0041955326578554</v>
+        <v>0.004232320293976674</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00330755726540424</v>
+        <v>0.00317405902533017</v>
       </c>
       <c r="R5" t="n">
-        <v>0.006221589249610546</v>
+        <v>0.005967107501642879</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005019199153229213</v>
+        <v>0.004779067945490181</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003522378534574173</v>
+        <v>0.00411390442355482</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002983479321563003</v>
+        <v>0.002945188366030437</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00476274202662546</v>
+        <v>0.004618924589016678</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01311739582271723</v>
+        <v>0.01299469170871717</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01356198397800644</v>
+        <v>0.01347536888895942</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.006512603358069603</v>
+        <v>0.006392836239392069</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005602111733471487</v>
+        <v>0.005475903302949648</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.009582233065460908</v>
+        <v>0.009566933708210464</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00257219523193224</v>
+        <v>0.002456907591272942</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001860678920361315</v>
+        <v>0.002031851530353737</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001882304724840028</v>
+        <v>0.00176252156696087</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001914104649486216</v>
+        <v>0.001785717554028403</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002211601815551069</v>
+        <v>0.001791205429979081</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002227935854363611</v>
+        <v>0.002093943429941066</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001947407669817235</v>
+        <v>0.002113954107911205</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002044795325246736</v>
+        <v>0.002215725649467977</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001949148485423485</v>
+        <v>0.002192576789495354</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001978409444024942</v>
+        <v>0.002149450763848182</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001915681049881046</v>
+        <v>0.002106181679585794</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00222410588865485</v>
+        <v>0.001804254413683661</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002175509823475905</v>
+        <v>0.002045701851865523</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001986673349532841</v>
+        <v>0.005192330177218433</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001976331539530282</v>
+        <v>0.002152775980550281</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001911472925959926</v>
+        <v>0.001806496486660925</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001873808407848984</v>
+        <v>0.002042889655395781</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002320931557995623</v>
+        <v>0.001891904572038938</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001996417164326805</v>
+        <v>0.002158050067883223</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002179777379137508</v>
+        <v>0.001799371177161379</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001853694241392856</v>
+        <v>0.001738666770202951</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002270454124750864</v>
+        <v>0.00184676747166488</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002479355227980521</v>
+        <v>0.002359021568997962</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002469698463719481</v>
+        <v>0.002641738557265263</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002063622795546052</v>
+        <v>0.001942755755853379</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002328271056315789</v>
+        <v>0.001905765502760127</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002524159627592242</v>
+        <v>0.002398590932823557</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001821370564039079</v>
+        <v>0.001702152110180644</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001925144203399806</v>
+        <v>0.00183055330281173</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001946770007878518</v>
+        <v>0.001851592408433991</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001978569932524707</v>
+        <v>0.001874788395501525</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001974441353103451</v>
+        <v>0.001880276271452203</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001990775391915994</v>
+        <v>0.001892645202399059</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002011872952855725</v>
+        <v>0.001912655880369198</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002109260608285227</v>
+        <v>0.002014427421925969</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002013613768461975</v>
+        <v>0.001991278561953348</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002042874727063433</v>
+        <v>0.001948152536306175</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001980146332919536</v>
+        <v>0.001904883452043787</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001986945426207233</v>
+        <v>0.001893325255156783</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001938349361028287</v>
+        <v>0.001844403624323518</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002050919698606076</v>
+        <v>0.005192330177218433</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002040554113136086</v>
+        <v>0.001945851224649714</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001995587493330664</v>
+        <v>0.001909502614607409</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001938273690887474</v>
+        <v>0.001841591427853774</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002083771095548004</v>
+        <v>0.00198097541351206</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002060882447365296</v>
+        <v>0.001956751840341216</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001942616916689889</v>
+        <v>0.001888442018634501</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001917774874042111</v>
+        <v>0.001827411478287819</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002033293662303247</v>
+        <v>0.001935838313138002</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002523310887861599</v>
+        <v>0.002427423861687805</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00253416374675797</v>
+        <v>0.002440440329723256</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002112825988794752</v>
+        <v>0.002017223770479594</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002091110593868171</v>
+        <v>0.00199483634423325</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002286999165144624</v>
+        <v>0.002197292705281549</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001886309562006446</v>
+        <v>0.001790981337414554</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002240494597277624</v>
+        <v>0.002140903425727512</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002724216212602538</v>
+        <v>0.002617150734932033</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002756016137248724</v>
+        <v>0.002640346721999567</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002505835169699298</v>
+        <v>0.002403449657516283</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002378114912407686</v>
+        <v>0.002273911443215481</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002885137734170605</v>
+        <v>0.002772604593224217</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002886706813009244</v>
+        <v>0.00277998574842401</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002791059973185994</v>
+        <v>0.00275683688845139</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00282032093178745</v>
+        <v>0.002713710862804216</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002757592537643553</v>
+        <v>0.002670441778541827</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00276439163093125</v>
+        <v>0.002658883581654826</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00271579556575222</v>
+        <v>0.002609961950821511</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002470164342774934</v>
+        <v>0.005192330177218433</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00255825943139505</v>
+        <v>0.002455540144835414</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002489163549214123</v>
+        <v>0.002395421922687117</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002162811711347573</v>
+        <v>0.002062482749378227</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002861217300272021</v>
+        <v>0.002746533740010102</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002838328652089313</v>
+        <v>0.002722310166839258</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002720063121413906</v>
+        <v>0.002654000345132543</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002469783261709629</v>
+        <v>0.002370880297108534</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002684133646927398</v>
+        <v>0.002576722625288312</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003300847906829871</v>
+        <v>0.003193071648828999</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002801053765970154</v>
+        <v>0.002703052387114998</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003349245107379008</v>
+        <v>0.003234983933677768</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00239787732090095</v>
+        <v>0.002296730741144123</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003064445369868642</v>
+        <v>0.00296285103177959</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003146453480195945</v>
+        <v>0.003032042695668886</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002551855559985946</v>
+        <v>0.002448022236157336</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002860718476269617</v>
+        <v>0.002752127408698357</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002892518400915807</v>
+        <v>0.002775323395765892</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002822096812711418</v>
+        <v>0.002715480923522618</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002242563677094213</v>
+        <v>0.002140635415547956</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002925821609756768</v>
+        <v>0.002813191069719202</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003023209076676326</v>
+        <v>0.002914962422190333</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002927562236853076</v>
+        <v>0.002891813562217715</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002956823195454531</v>
+        <v>0.002848687536570542</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002894094801310631</v>
+        <v>0.002805418452308152</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002900893894598333</v>
+        <v>0.002793860255421149</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002852297829419384</v>
+        <v>0.002744938624587885</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002964868166997172</v>
+        <v>0.005192330177218433</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003049716610723763</v>
+        <v>0.00294021762502855</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003025452196917047</v>
+        <v>0.002924270599100355</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002852222347788515</v>
+        <v>0.002742126617203778</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002997719563939102</v>
+        <v>0.002881510413776427</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002974830915756392</v>
+        <v>0.002857286840605583</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002856565385080985</v>
+        <v>0.002788977018898868</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002832107992822447</v>
+        <v>0.00272827261194044</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003278707777790112</v>
+        <v>0.00316302567144474</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003437259356252698</v>
+        <v>0.003327958861952172</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003448112215149068</v>
+        <v>0.003340975329987624</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003026774457185849</v>
+        <v>0.002917758770743962</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002831880700816649</v>
+        <v>0.002724707752446194</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00320094763353572</v>
+        <v>0.003097827705545916</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002800258030397543</v>
+        <v>0.002691516337678921</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003251324870157429</v>
+        <v>0.003200314382715205</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003216426575154256</v>
+        <v>0.003146676956753528</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003253183749929127</v>
+        <v>0.003202178785789363</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003256242851490673</v>
+        <v>0.003204711145734747</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003252588119749608</v>
+        <v>0.003200855999897919</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003251372844463718</v>
+        <v>0.003200345794037664</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003257567321553536</v>
+        <v>0.003206442345126956</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003251701606537472</v>
+        <v>0.003202663415594067</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003256174549732494</v>
+        <v>0.003205269234102024</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00324976517798287</v>
+        <v>0.003199383976408975</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003254312670127214</v>
+        <v>0.003203009833688263</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003248996306772379</v>
+        <v>0.003198095973605718</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003254253145918339</v>
+        <v>0.003203268340742626</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004402998456516656</v>
+        <v>0.004343374196180436</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003255732828611327</v>
+        <v>0.00320607395612925</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003248589916753859</v>
+        <v>0.003197734544877638</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003263641795620334</v>
+        <v>0.003210247758485788</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00325711415575856</v>
+        <v>0.003205295932761966</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003249341687415565</v>
+        <v>0.003199451576166169</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005972788022912991</v>
+        <v>0.005867325264571829</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003260558735286041</v>
+        <v>0.003209252937015435</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006382576469878975</v>
+        <v>0.006270125690586596</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003315774350847968</v>
+        <v>0.003264757908465393</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003262173140667698</v>
+        <v>0.003211075654434979</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005170061285675906</v>
+        <v>0.005115434014533944</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003283084122029733</v>
+        <v>0.003231921333314055</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003247103275978106</v>
+        <v>0.00319733087983513</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002890531419152468</v>
+        <v>0.002838341418643539</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002824703039634832</v>
+        <v>0.002741203172972588</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002904217222740866</v>
+        <v>0.002852051611623186</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00292561582227388</v>
+        <v>0.002869719374767307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002900104020253332</v>
+        <v>0.002842734987924612</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002890821844422358</v>
+        <v>0.00283851675034552</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002935944632960049</v>
+        <v>0.00288290928898215</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002893768873278705</v>
+        <v>0.002855662735340218</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002925179783084894</v>
+        <v>0.002873730784976933</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002879745825033724</v>
+        <v>0.002832025676012642</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002911652193157239</v>
+        <v>0.002857394993584254</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002879419765359423</v>
+        <v>0.002827551943452191</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002911747652233949</v>
+        <v>0.002859729002940514</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004832718094322943</v>
+        <v>0.004817424353753462</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002921724598551781</v>
+        <v>0.002879125683356388</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002871273578865982</v>
+        <v>0.002820180331188601</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002979362117864624</v>
+        <v>0.00291008134850137</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002931552666716137</v>
+        <v>0.002873634653797973</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002876836600496468</v>
+        <v>0.00283263037528551</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007371244316622538</v>
+        <v>0.007230784180763664</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00295604990451582</v>
+        <v>0.002901765943313727</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008271357309862191</v>
+        <v>0.008114026554593793</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003349497874625239</v>
+        <v>0.003297257014338519</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002968407219777791</v>
+        <v>0.00291558160132475</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006090960827013895</v>
+        <v>0.006031790752752369</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003117604826394767</v>
+        <v>0.003064314842143805</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002863218200728389</v>
+        <v>0.002819461806741132</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001736887845097217</v>
+        <v>0.001601453873022864</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001719235481439129</v>
+        <v>0.001583099373780075</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001757884747245513</v>
+        <v>0.001622513163413314</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001792438706639421</v>
+        <v>0.001651117333939518</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001751156830364418</v>
+        <v>0.001607571688257872</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001737429736956036</v>
+        <v>0.001601808678359979</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001807399205285787</v>
+        <v>0.001670672027465612</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001741143255817124</v>
+        <v>0.001627987279998161</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001791401878496618</v>
+        <v>0.001657146840116052</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001719270404491723</v>
+        <v>0.001590944505785971</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001770636420211833</v>
+        <v>0.001631900231732298</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001719876994747388</v>
+        <v>0.001584862265084385</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001769964066890107</v>
+        <v>0.004303681744092657</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001822459557310066</v>
+        <v>0.001793149348716569</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001786677763595071</v>
+        <v>0.001666510904269226</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001705995288263204</v>
+        <v>0.001572313417863537</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001876013184266349</v>
+        <v>0.001713655921930266</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001802280489164971</v>
+        <v>0.001657722772427294</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001714486883718738</v>
+        <v>0.001591708076140914</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001712347060006094</v>
+        <v>0.001571744863242762</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001839525280567041</v>
+        <v>0.001700693135238073</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002174304651168833</v>
+        <v>0.002031203764582525</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002464874377722759</v>
+        <v>0.002329373141857785</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001859112534386968</v>
+        <v>0.001714178909147332</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001806293207255499</v>
+        <v>0.001668745384516074</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002095623204972577</v>
+        <v>0.00195846891995255</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001693319372728909</v>
+        <v>0.001571125045037579</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003734849555067496</v>
+        <v>0.003555464880473058</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003625035978011512</v>
+        <v>0.003426459468138562</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004323291473911119</v>
+        <v>0.004137220961889085</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00470933877143814</v>
+        <v>0.004432829037260596</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004275729146345879</v>
+        <v>0.003937301764349793</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003717501802047864</v>
+        <v>0.003536423641592817</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005427905637840937</v>
+        <v>0.005211019065135088</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004094446709986232</v>
+        <v>0.00431296362449085</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00472208249407308</v>
+        <v>0.004558717648256086</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003602565249662341</v>
+        <v>0.003537812136235169</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004226391994237604</v>
+        <v>0.003998609247289536</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003671976987082558</v>
+        <v>0.00349184087320601</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003419633206489505</v>
+        <v>0.004303681744092656</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005028172852415147</v>
+        <v>0.006502426126639893</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004477287082766063</v>
+        <v>0.004539186766126538</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003324061601317644</v>
+        <v>0.003170320406113945</v>
       </c>
       <c r="R5" t="n">
-        <v>0.006674447605989378</v>
+        <v>0.005977807765536217</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004737424311504409</v>
+        <v>0.004415760745438919</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003576649090126171</v>
+        <v>0.003614663075517383</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00336232771618023</v>
+        <v>0.003234982076396922</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005378882437470147</v>
+        <v>0.005147531557996549</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01129627106993106</v>
+        <v>0.01098212650132985</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01608568593099597</v>
+        <v>0.01590077970804575</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.006135903271035643</v>
+        <v>0.005931518496719101</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004699405143313866</v>
+        <v>0.004491348736294407</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01029009804867712</v>
+        <v>0.01007354886389709</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00326483961270027</v>
+        <v>0.0033207346159095</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002289157769562619</v>
+        <v>0.002071261877721645</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002271505405904529</v>
+        <v>0.002052907378478858</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002310154671710914</v>
+        <v>0.002092321168112096</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002344708631104823</v>
+        <v>0.001830483134461876</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002303426754829819</v>
+        <v>0.002077379692956656</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002289699661421439</v>
+        <v>0.002071616683058762</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002038233330303731</v>
+        <v>0.002140480032164394</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001971977380835068</v>
+        <v>0.002097795284696941</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002022236003514563</v>
+        <v>0.001836512640638411</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002271540328957126</v>
+        <v>0.00177031030630833</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002322906344677235</v>
+        <v>0.00210170823643108</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002272146919212791</v>
+        <v>0.002054670269783167</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002000820321354517</v>
+        <v>0.004303681744092656</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002376058241029829</v>
+        <v>0.002022942172717635</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002340273312194219</v>
+        <v>0.002140936076319761</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002258265212728605</v>
+        <v>0.002042121422562319</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00210684730928429</v>
+        <v>0.002183463926629047</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002033114614182913</v>
+        <v>0.002127530777126076</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002266756808184139</v>
+        <v>0.001771073876663274</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002264928501046231</v>
+        <v>0.002050381346321516</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002070359405584986</v>
+        <v>0.001880058935760432</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002727906623074243</v>
+        <v>0.002504650367806453</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0026957085027407</v>
+        <v>0.002508738942380145</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002107961553583393</v>
+        <v>0.001923340490104532</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002037127332273441</v>
+        <v>0.001848111185038434</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00232645732999052</v>
+        <v>0.002428276924651332</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001923614838220569</v>
+        <v>0.001750097409066878</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001978928363383293</v>
+        <v>0.001862371329058192</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001961275999725204</v>
+        <v>0.001844016829815404</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001999925265531591</v>
+        <v>0.001883430619448643</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002034479224925497</v>
+        <v>0.001912034789974846</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001993197348650493</v>
+        <v>0.001868489144293202</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001979470255242114</v>
+        <v>0.001862726134395308</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002049439723571864</v>
+        <v>0.001931589483500941</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0019831837741032</v>
+        <v>0.001888904736033491</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002033442396782695</v>
+        <v>0.00191806429615138</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0019613109227778</v>
+        <v>0.0018518619618213</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002012676938497911</v>
+        <v>0.001892817687767626</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001961917513033466</v>
+        <v>0.001845779721119714</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002012004585176183</v>
+        <v>0.004303681744092656</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002064475846313884</v>
+        <v>0.002054043288529026</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00202869405259889</v>
+        <v>0.001927404844081684</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001948035806549279</v>
+        <v>0.001833230873898865</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002118053702552422</v>
+        <v>0.001974573377965595</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002044321007451046</v>
+        <v>0.001918640228462624</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001956527402004814</v>
+        <v>0.001852625532176243</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001954351171131167</v>
+        <v>0.001841216307083701</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002081565798853119</v>
+        <v>0.001961610591273401</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00241634516945491</v>
+        <v>0.002292121220617854</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002706914896008833</v>
+        <v>0.002590290597893114</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002101464569247778</v>
+        <v>0.001983924843562634</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002048333725541573</v>
+        <v>0.001929662840551402</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002337663723258652</v>
+        <v>0.002219386375987878</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001935359891014984</v>
+        <v>0.001832042501072907</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002314058759505511</v>
+        <v>0.002168818868699684</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002773118866407658</v>
+        <v>0.002599773047011535</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002811768132214044</v>
+        <v>0.002639186836644773</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002592486763345093</v>
+        <v>0.002428547390320704</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002402593976141873</v>
+        <v>0.002244933724629983</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002890162558126399</v>
+        <v>0.002711649432795075</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00286128259025432</v>
+        <v>0.002687345700697071</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002795026640785655</v>
+        <v>0.002644660953229618</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002845285263465151</v>
+        <v>0.002673820513347509</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002773153789460256</v>
+        <v>0.002607618179017429</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002824519805180367</v>
+        <v>0.002648573904963756</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002773760379715829</v>
+        <v>0.00260153593831577</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002454315534712452</v>
+        <v>0.004303681744092656</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002608361604129352</v>
+        <v>0.00255724657786194</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00254768730974169</v>
+        <v>0.002407146576929375</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002189481322008837</v>
+        <v>0.002051379003662357</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002929896569234879</v>
+        <v>0.002730329595161726</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002856163874133503</v>
+        <v>0.002674396445658754</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00276837026868727</v>
+        <v>0.002608381749372373</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002533614111537263</v>
+        <v>0.002377750946753522</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002762839272890638</v>
+        <v>0.002594349445000734</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003228281722980011</v>
+        <v>0.003047965739035826</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00299205205613083</v>
+        <v>0.002849618760243729</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003386862654135311</v>
+        <v>0.003186085720553428</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002374608942859401</v>
+        <v>0.002227764240912392</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003149506589941104</v>
+        <v>0.002975142593184009</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0032451687944658</v>
+        <v>0.003057139201783388</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002547310009086348</v>
+        <v>0.002413525911467169</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002801655085579784</v>
+        <v>0.0026584094279134</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002840304351386169</v>
+        <v>0.002697823217546638</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002812082546117786</v>
+        <v>0.002665673250415784</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002206547870613682</v>
+        <v>0.002076046063655107</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002819849516690315</v>
+        <v>0.002677118891925196</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002889818809426444</v>
+        <v>0.002745982081598936</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002823562859957779</v>
+        <v>0.002703297334131487</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002873821482637275</v>
+        <v>0.002732456894249376</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00280169000863238</v>
+        <v>0.002666254559919295</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002853056024352489</v>
+        <v>0.002707210285865623</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002802296598888045</v>
+        <v>0.00266017231921771</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002852383671030762</v>
+        <v>0.004303681744092656</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002995018990751808</v>
+        <v>0.002955696348835874</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002978841025182179</v>
+        <v>0.002848030408732855</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002788415067997487</v>
+        <v>0.002647623631428755</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002958432788407</v>
+        <v>0.002788965976063588</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002884700093305625</v>
+        <v>0.002733032826560621</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002796906487859393</v>
+        <v>0.00266701813027424</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002795078180721485</v>
+        <v>0.002655883395756059</v>
       </c>
       <c r="V9" t="n">
-        <v>0.00323582425941921</v>
+        <v>0.0030797743717194</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003256724255309488</v>
+        <v>0.003106513818715848</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003547293981863415</v>
+        <v>0.003404683195991108</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002941843655102357</v>
+        <v>0.002798317441660628</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002724722611667152</v>
+        <v>0.002585346386535226</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003178042809113233</v>
+        <v>0.003033778974085874</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002775738976869564</v>
+        <v>0.002646435099170904</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003364284648874905</v>
+        <v>0.00330103312869263</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003323973162958619</v>
+        <v>0.003269203903678956</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003367235487719653</v>
+        <v>0.003309259911379373</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003339209433714966</v>
+        <v>0.00328338628220362</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003343985306649533</v>
+        <v>0.003287154793886009</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003427876455421739</v>
+        <v>0.003321043426853932</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003389108478982829</v>
+        <v>0.003335724834273241</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003364046177860798</v>
+        <v>0.00332058941915142</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003392483329456453</v>
+        <v>0.003324848329461825</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003390501046544392</v>
+        <v>0.003343013687723111</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003418478521182893</v>
+        <v>0.003322527254917436</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00342075380793596</v>
+        <v>0.003449939258140302</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003392433053723201</v>
+        <v>0.003336548977294383</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004551124696832398</v>
+        <v>0.004469498439892629</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003404880569153875</v>
+        <v>0.003312373527760232</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00335173522133566</v>
+        <v>0.003295901285470403</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003356401655888282</v>
+        <v>0.003321647463559575</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003373801760155795</v>
+        <v>0.003308830169275876</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003367871927852867</v>
+        <v>0.00331955339351802</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006247248155862605</v>
+        <v>0.006166478276812988</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003343705263107211</v>
+        <v>0.003288722855783608</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006581178751786499</v>
+        <v>0.006521467555446244</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003409321713634098</v>
+        <v>0.003336683120661157</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003390693262864068</v>
+        <v>0.003320375502600792</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005288373105211371</v>
+        <v>0.00522469188077719</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003388642316913216</v>
+        <v>0.003341647030061297</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003442592332757898</v>
+        <v>0.003360747616317324</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003196355676711712</v>
+        <v>0.003080763369064634</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002930214376346462</v>
+        <v>0.00288145008659637</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003219979796410399</v>
+        <v>0.003141589797680078</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003018803465203758</v>
+        <v>0.002955900461409974</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003053503326504087</v>
+        <v>0.002983320363719404</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003647669670011305</v>
+        <v>0.00322272976097397</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003377689870001163</v>
+        <v>0.003332157097353357</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003197180125729495</v>
+        <v>0.003222717904771259</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003397457063684069</v>
+        <v>0.003250910863569671</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003383515071841584</v>
+        <v>0.003379925909771049</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003583136771476906</v>
+        <v>0.00323449096518249</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003602330545160935</v>
+        <v>0.004138256697900531</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003399397756761499</v>
+        <v>0.003336019478256619</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00514522986013313</v>
+        <v>0.005011725889564577</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00348551093940389</v>
+        <v>0.00316171287472291</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003108350488830704</v>
+        <v>0.003045349396708972</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003142842389083079</v>
+        <v>0.003230875252167206</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003263442274749289</v>
+        <v>0.003135753966433195</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00322450047823183</v>
+        <v>0.003215234197730229</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008212513049056991</v>
+        <v>0.008005339518428517</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003050098980303284</v>
+        <v>0.002993247989893275</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00872942037798582</v>
+        <v>0.008667821071915632</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003520536946728505</v>
+        <v>0.003337338668994016</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003386110673095545</v>
+        <v>0.003219805245524523</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006354386874070056</v>
+        <v>0.006256602044053381</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003371747760804126</v>
+        <v>0.003371838114920101</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003757617500693884</v>
+        <v>0.003508756617001958</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002289724208541371</v>
+        <v>0.001953689468048869</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001874797737702497</v>
+        <v>0.001648509607715984</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002323055290745788</v>
+        <v>0.002046614763002649</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002006488118141001</v>
+        <v>0.001754360219005062</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002060433799947034</v>
+        <v>0.001796927292058687</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003008022917164142</v>
+        <v>0.002179714990972742</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002570120789136402</v>
+        <v>0.002345548241554905</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002287030568734974</v>
+        <v>0.002174586765118983</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002607520175599614</v>
+        <v>0.002222179013804216</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002585850480357021</v>
+        <v>0.00242787919430944</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002901868926673051</v>
+        <v>0.002196475511544631</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002931385404634928</v>
+        <v>0.003626396528851452</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00260767339020886</v>
+        <v>0.01735815234726077</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002269336227665565</v>
+        <v>0.001958871535043307</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00274827380313833</v>
+        <v>0.002081784492358762</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002147972651463749</v>
+        <v>0.001895722938089319</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002200682176401557</v>
+        <v>0.002186537863433569</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00239722435854653</v>
+        <v>0.002041760628252546</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002330244174827375</v>
+        <v>0.002162884378994395</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002806297374172159</v>
+        <v>0.002329653433703652</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002052529686730408</v>
+        <v>0.001811302018909323</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002745472444614662</v>
+        <v>0.002509273309448091</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002798438573069817</v>
+        <v>0.002356372527139931</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002575771153140417</v>
+        <v>0.002148186272735926</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002252105809634461</v>
+        <v>0.001954473732869363</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002564855274114983</v>
+        <v>0.002412442167325682</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003166951262059173</v>
+        <v>0.002622535423733184</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01105123149318307</v>
+        <v>0.008784222007085739</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004117314089968066</v>
+        <v>0.003727277810263497</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01310733544299187</v>
+        <v>0.01171554366067629</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00648047746753941</v>
+        <v>0.005617923167707249</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007842076035807447</v>
+        <v>0.006714115766596573</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02321795905796067</v>
+        <v>0.01258621627237767</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01866947327724583</v>
+        <v>0.01830532505926925</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01240537932696391</v>
+        <v>0.01428474498853451</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01698735210596413</v>
+        <v>0.013968564154937</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0166790884889923</v>
+        <v>0.01749721696453695</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02262378476601991</v>
+        <v>0.01355440432645203</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0236721793256433</v>
+        <v>0.04028476197252166</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0210297323060059</v>
+        <v>0.01735815234726077</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01048784880396215</v>
+        <v>0.008704017980330507</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0193989618236929</v>
+        <v>0.01121318916699923</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009238994564488352</v>
+        <v>0.008362391156944884</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01089595426685682</v>
+        <v>0.01484776111403837</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01261805676398286</v>
+        <v>0.01008392091915375</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01323123642032086</v>
+        <v>0.01401367926765746</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02124060678894039</v>
+        <v>0.0164992522070806</v>
       </c>
       <c r="V5" t="n">
-        <v>0.006995763476761662</v>
+        <v>0.006342859922888442</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02057423577800525</v>
+        <v>0.02000440673349133</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02219909120068374</v>
+        <v>0.01758801927781768</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01740072866614136</v>
+        <v>0.01346827213136948</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01047495383486652</v>
+        <v>0.008858454427860386</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01711552674979334</v>
+        <v>0.01813194541120131</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03116326024937716</v>
+        <v>0.02414546866322453</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002895816593998983</v>
+        <v>0.002141141432502336</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002082569150654213</v>
+        <v>0.001835961572169449</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002929147676203403</v>
+        <v>0.002234066727456116</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002612580503598615</v>
+        <v>0.002294169315126245</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002666526185404646</v>
+        <v>0.00198437925651215</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003215794330115856</v>
+        <v>0.00271952408709392</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003176213174594015</v>
+        <v>0.002533000206008366</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002494801981686691</v>
+        <v>0.002362038729572448</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00281529158855133</v>
+        <v>0.00240963097825768</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002793621893308738</v>
+        <v>0.002967688290430617</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003507961312130663</v>
+        <v>0.002736284607665807</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003537477790092541</v>
+        <v>0.003813848493304919</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002817473730049427</v>
+        <v>0.01735815234726077</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002479136567506134</v>
+        <v>0.002506877309466921</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003359059786736869</v>
+        <v>0.002630335851458274</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002754065036921363</v>
+        <v>0.002083174902542784</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002806774561859172</v>
+        <v>0.002726346959554745</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003003316744004143</v>
+        <v>0.002229212592706009</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002538015587779091</v>
+        <v>0.002350336343447858</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003424640258600931</v>
+        <v>0.002893446736362105</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002658622072188023</v>
+        <v>0.001998753983362789</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002977127378923309</v>
+        <v>0.002719738142745883</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003006209986021533</v>
+        <v>0.002896181623261106</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002812860384195705</v>
+        <v>0.002376011650361547</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002459877222586178</v>
+        <v>0.002494282828990542</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003170947659572596</v>
+        <v>0.002952251263446858</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003381629631055249</v>
+        <v>0.002815365973469524</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002635534775819124</v>
+        <v>0.002282284868993958</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002220608304980251</v>
+        <v>0.001977105008661072</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002668865858023542</v>
+        <v>0.002375210163947739</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002352298685418754</v>
+        <v>0.00208295561995015</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002406244367224786</v>
+        <v>0.002125522693003775</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003353833484441895</v>
+        <v>0.002508310391917832</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002915931356414156</v>
+        <v>0.002674143642499991</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002632841136012727</v>
+        <v>0.002503182166064071</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002953330742877369</v>
+        <v>0.002550774414749303</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002931661047634776</v>
+        <v>0.002756474595254527</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003247679493950805</v>
+        <v>0.002525070912489719</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003277195971912681</v>
+        <v>0.003954991929796542</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002953483957486614</v>
+        <v>0.01735815234726077</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002615120689053711</v>
+        <v>0.002287441585052959</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003094058264526473</v>
+        <v>0.002410354542368416</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002493783218741503</v>
+        <v>0.002224318339034406</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002546492743679312</v>
+        <v>0.002515133264378658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002743034925824284</v>
+        <v>0.002370356029197632</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002676054742105129</v>
+        <v>0.002491479779939481</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003163865789457917</v>
+        <v>0.002681839963888475</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002398340254008162</v>
+        <v>0.002139897419854412</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003091283011892416</v>
+        <v>0.002837868710393178</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003144249140347571</v>
+        <v>0.002684967928085018</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002933832219389328</v>
+        <v>0.002500765880218283</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002597916376912214</v>
+        <v>0.00228306913381445</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002910665841392737</v>
+        <v>0.00274103756827077</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003512761829336928</v>
+        <v>0.002951130824678274</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003023531459734024</v>
+        <v>0.002656929238236432</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003189663934123841</v>
+        <v>0.002904398196540977</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003637921487167131</v>
+        <v>0.003302503351827642</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003011957566585367</v>
+        <v>0.002715979614213876</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002884763243729939</v>
+        <v>0.0025862632891512</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004443375471057247</v>
+        <v>0.003550198912447164</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003884986985557743</v>
+        <v>0.003601436830379893</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003601896765156316</v>
+        <v>0.003430475353943978</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003922386372020956</v>
+        <v>0.003478067602629208</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003900716676778367</v>
+        <v>0.003683767783134434</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004216735123094392</v>
+        <v>0.003452364100369623</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004246251601056223</v>
+        <v>0.004882285117676545</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00347212169480953</v>
+        <v>0.01735815234726077</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003257563279379435</v>
+        <v>0.002904091578209926</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003706159693071262</v>
+        <v>0.002998146865664198</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002767588558154429</v>
+        <v>0.002490354602075852</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003515548372822898</v>
+        <v>0.003442426452258564</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003712090554967868</v>
+        <v>0.00329764921707754</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003645110371248715</v>
+        <v>0.003418772967819389</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003849445392188135</v>
+        <v>0.003339500737376323</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003208184920400916</v>
+        <v>0.00291582902874952</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004060452834863683</v>
+        <v>0.003765270508710064</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003471309686111903</v>
+        <v>0.00300165555293221</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004480003006111633</v>
+        <v>0.003977057693117425</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002975119592692976</v>
+        <v>0.002647447767608737</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003879721470536327</v>
+        <v>0.003668330756150673</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00508878211326692</v>
+        <v>0.004455711914516579</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003634104553236127</v>
+        <v>0.00314328703524147</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003640942990599197</v>
+        <v>0.003213154427013781</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004089200543642485</v>
+        <v>0.003611259582300448</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003675291868504225</v>
+        <v>0.003232445531465731</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002854295628753529</v>
+        <v>0.00249698605717354</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004774168323377512</v>
+        <v>0.003744359640171174</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004336266042033099</v>
+        <v>0.003910193060852698</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004053175821631673</v>
+        <v>0.00373923158441678</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004373665428496315</v>
+        <v>0.003786823833102008</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004351995733253722</v>
+        <v>0.003992524013607231</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004668014179569748</v>
+        <v>0.003761120330842427</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004697530657531625</v>
+        <v>0.005191041348149249</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004373818643105559</v>
+        <v>0.01735815234726077</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004175254023011977</v>
+        <v>0.003647806296136218</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004684589695030847</v>
+        <v>0.003797750220329532</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003914118057677113</v>
+        <v>0.003460367587287747</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003966827429298256</v>
+        <v>0.003751182682731366</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004163369611443229</v>
+        <v>0.003606405447550337</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004096389427724075</v>
+        <v>0.00372752919829219</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004584693126040016</v>
+        <v>0.003918282459538719</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004305382433691511</v>
+        <v>0.003808742566924738</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00451161769751136</v>
+        <v>0.004073918128745887</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004564583825966514</v>
+        <v>0.003921017346437725</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.004354166905008277</v>
+        <v>0.003736815298570991</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003763964388564708</v>
+        <v>0.003292998342106053</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004331000527011681</v>
+        <v>0.003977086986623477</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.004933096514955876</v>
+        <v>0.00418718024303098</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003280902559926499</v>
+        <v>0.003234745904574626</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003288662323458335</v>
+        <v>0.00323578098354788</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003290507797645508</v>
+        <v>0.003243407366450839</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003287389373274919</v>
+        <v>0.003240922408617848</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003285552394997308</v>
+        <v>0.003239102853297988</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003366652225261924</v>
+        <v>0.003280039563674103</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003322461991219102</v>
+        <v>0.003276309221388649</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0032888150542363</v>
+        <v>0.003247409306034081</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003320899561921556</v>
+        <v>0.003262989610820787</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003297288989873221</v>
+        <v>0.003261182335648641</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003319804606442529</v>
+        <v>0.003260992711278936</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003289869309989604</v>
+        <v>0.00325103826571585</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003297124007695791</v>
+        <v>0.003251264755288702</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004437571762703444</v>
+        <v>0.004376447948163743</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003327205166569642</v>
+        <v>0.003264002171393228</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0032935596405936</v>
+        <v>0.003246537270668437</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003301408559839758</v>
+        <v>0.003257868115551186</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003298085346163728</v>
+        <v>0.003250483817423827</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003287718413133213</v>
+        <v>0.003249091421223743</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006124193744635193</v>
+        <v>0.00607200692916333</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003294260932803565</v>
+        <v>0.003247776025582779</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006520953530480862</v>
+        <v>0.006470841923163715</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003353341390092118</v>
+        <v>0.003303372114104746</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003373256423600498</v>
+        <v>0.003313003216046885</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005203043711383509</v>
+        <v>0.005160174538989201</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003307920674451205</v>
+        <v>0.003267518107326785</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003523013586154492</v>
+        <v>0.003445992551774768</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002871909448528157</v>
+        <v>0.002831647088678367</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002904730136117582</v>
+        <v>0.002852610048437324</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002940778823228427</v>
+        <v>0.00289376813438856</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002918285583994726</v>
+        <v>0.002875811930156296</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002905404074883623</v>
+        <v>0.002863042141641924</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00347946346096416</v>
+        <v>0.003152590866606402</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003170550724025749</v>
+        <v>0.003130308610336403</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002928832247082989</v>
+        <v>0.00292257845008261</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003156038168217353</v>
+        <v>0.00303251570681071</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002988558817820949</v>
+        <v>0.003019662888816804</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003148192119911867</v>
+        <v>0.003018090744385707</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002941950840887337</v>
+        <v>0.00295253653364459</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002988010006039421</v>
+        <v>0.002949870208938537</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004829653063312957</v>
+        <v>0.004757510461446033</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003200827147559358</v>
+        <v>0.003039467499364587</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002962024223969888</v>
+        <v>0.002915602280729379</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003019181815558422</v>
+        <v>0.002997663502898768</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0029937479451272</v>
+        <v>0.002943239480104721</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002920913924371871</v>
+        <v>0.002934498850625382</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007639901889049023</v>
+        <v>0.007573359740012504</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002966695983236182</v>
+        <v>0.002924103167335554</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008598880323767939</v>
+        <v>0.008548179512006211</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003389125419308773</v>
+        <v>0.003321646462235009</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003530938867155045</v>
+        <v>0.003390104764129173</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006120355640394721</v>
+        <v>0.006081278936107757</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003064925018117475</v>
+        <v>0.003065738556232275</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004589911601309906</v>
+        <v>0.004330239765477354</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001731298014857588</v>
+        <v>0.001565920760259637</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00177191626212828</v>
+        <v>0.001605126587621772</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00183979359352145</v>
+        <v>0.001663755956620766</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001804569555709537</v>
+        <v>0.001635687214760073</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001783820041012189</v>
+        <v>0.001615134500385445</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002699879931616154</v>
+        <v>0.002077533475900842</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002200730909590477</v>
+        <v>0.002035397543744392</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001820673278013997</v>
+        <v>0.001708959705196666</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002182499411448575</v>
+        <v>0.001884521053202871</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001916390279235987</v>
+        <v>0.001864532410599771</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002170714526081662</v>
+        <v>0.001862390516112427</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001843391701196124</v>
+        <v>0.001758368383251327</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001914526729646358</v>
+        <v>0.006083465492741448</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001831881147029265</v>
+        <v>0.001651612409203685</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002254307257143306</v>
+        <v>0.001896383752523416</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001874265563537262</v>
+        <v>0.00169910966458562</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001962922717103847</v>
+        <v>0.001827096769982453</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001925385489879271</v>
+        <v>0.00174368772568895</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001808286212274798</v>
+        <v>0.00172795997007511</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001875485243576695</v>
+        <v>0.001671028428015529</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001878367491881851</v>
+        <v>0.00171035142531664</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002510393620007962</v>
+        <v>0.002336972576236663</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002549527925086497</v>
+        <v>0.002341085366518432</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002764501901627014</v>
+        <v>0.002434634085839973</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001888321620395563</v>
+        <v>0.001714139163007249</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002036480047360867</v>
+        <v>0.00193609786630338</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004434516945488766</v>
+        <v>0.003923732860090635</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002793485119167739</v>
+        <v>0.002613754700054466</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003620516677094914</v>
+        <v>0.003412495198054146</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004876330315120931</v>
+        <v>0.004501547780412737</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004130573335060291</v>
+        <v>0.003890611121537987</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003882307353507662</v>
+        <v>0.003639281777998304</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01762062261514092</v>
+        <v>0.01046053833086613</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01214793951891989</v>
+        <v>0.01196510643328235</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004607918329509183</v>
+        <v>0.005429712060482437</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01009324524294297</v>
+        <v>0.007888858518490261</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005910955290950497</v>
+        <v>0.007551960627927539</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009858860836570019</v>
+        <v>0.007400697462158695</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004865127447112536</v>
+        <v>0.006036388733717031</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005363240113103729</v>
+        <v>0.006083465492741448</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004362414702217612</v>
+        <v>0.003949775978896975</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01124242912056163</v>
+        <v>0.007949110687948839</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005208382774841322</v>
+        <v>0.004865580680088304</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007366929011828597</v>
+        <v>0.007747183945297141</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005813784579781006</v>
+        <v>0.005379616474447802</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004341394091374964</v>
+        <v>0.005721745392870323</v>
       </c>
       <c r="U5" t="n">
-        <v>0.005334174115338724</v>
+        <v>0.004607467622441546</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005171891465715351</v>
+        <v>0.004934023212492228</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01670558311280412</v>
+        <v>0.01638198058428289</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01737738994618654</v>
+        <v>0.01643300722757499</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02118957021798121</v>
+        <v>0.01821233018004627</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005224387422156337</v>
+        <v>0.004907514427288382</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.008287491298741538</v>
+        <v>0.009261805974660397</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05432423829962695</v>
+        <v>0.04758008415668378</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001933283470863676</v>
+        <v>0.002068040097981861</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00233545389939245</v>
+        <v>0.002107245925343997</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002041779049527537</v>
+        <v>0.00216587529434299</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002368107192973709</v>
+        <v>0.001812750263347433</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002347357678276361</v>
+        <v>0.001792197548972805</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002901865387622241</v>
+        <v>0.002254596524488203</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002764268546854649</v>
+        <v>0.002212460592331752</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002384210915278169</v>
+        <v>0.002211079042918891</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002384484867454662</v>
+        <v>0.002386640390925095</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002479927916500159</v>
+        <v>0.00204159545918713</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002372699982087752</v>
+        <v>0.002364509853834651</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002406929338460295</v>
+        <v>0.001935431431838687</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002117430141696575</v>
+        <v>0.006083465492741448</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002034784559079501</v>
+        <v>0.002158867796677282</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002436316190816081</v>
+        <v>0.002059629569011869</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002437803200801434</v>
+        <v>0.00187617271317298</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002526460354368017</v>
+        <v>0.002329216107704677</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00212737094588536</v>
+        <v>0.001920750774276309</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002010271668280886</v>
+        <v>0.00190502301866247</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002087446187887448</v>
+        <v>0.002188386773378461</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002441905129146022</v>
+        <v>0.001887414473904</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002734633337937773</v>
+        <v>0.002535941769069054</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002751513381092585</v>
+        <v>0.002843204704240659</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002991944506821885</v>
+        <v>0.002641947854885769</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002090307076401652</v>
+        <v>0.002216258500729474</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002600017684625038</v>
+        <v>0.002113160914890739</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004651052348165952</v>
+        <v>0.004114172423847063</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002017357652630706</v>
+        <v>0.001847048583334613</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0020579758999014</v>
+        <v>0.00188625441069675</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002125853231294569</v>
+        <v>0.001944883779695743</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002090629193482656</v>
+        <v>0.001916815037835051</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002069879678785308</v>
+        <v>0.001896262323460423</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00298593956938927</v>
+        <v>0.00235866129897582</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002486790547363596</v>
+        <v>0.00231652536681937</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002106732915787116</v>
+        <v>0.001990087528271644</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002468559049221693</v>
+        <v>0.002165648876277849</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002202449917009107</v>
+        <v>0.002145660233674749</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002456774163854781</v>
+        <v>0.002143518339187406</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002129451338969243</v>
+        <v>0.002039496206326306</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002200586367419476</v>
+        <v>0.006083465492741448</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002117916768344467</v>
+        <v>0.001932716598411291</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002540342878458506</v>
+        <v>0.002177487941731022</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002160325201310381</v>
+        <v>0.001980237487660599</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002248982354876965</v>
+        <v>0.00210822459305743</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00221144512765239</v>
+        <v>0.002024815548763927</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002094345850047917</v>
+        <v>0.002009087793150088</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002171001764193229</v>
+        <v>0.001967008796034572</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00216442712965497</v>
+        <v>0.001991479248391618</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002796453257781079</v>
+        <v>0.002618100399311638</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002835587562859616</v>
+        <v>0.002622213189593413</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003060537027704798</v>
+        <v>0.002731000916555658</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002174381258168683</v>
+        <v>0.001995266986082226</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002322539685133986</v>
+        <v>0.002217225689378358</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.004720576583261883</v>
+        <v>0.004204860683165612</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002359367311546641</v>
+        <v>0.002175039177750454</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002902578602794072</v>
+        <v>0.002695306311876392</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002970455934187242</v>
+        <v>0.002753935680875382</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002667615926202418</v>
+        <v>0.002469715983757483</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002490187459933905</v>
+        <v>0.002299196647099967</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003934758213976076</v>
+        <v>0.00326746439587383</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003331393250256272</v>
+        <v>0.00312557726799901</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00295133561867979</v>
+        <v>0.002799139429451286</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003313161752114366</v>
+        <v>0.002974700777457488</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003047052619901779</v>
+        <v>0.002954712134854388</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003301376866747456</v>
+        <v>0.002952570240367044</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002974054041861861</v>
+        <v>0.002848548107505954</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002655595379037108</v>
+        <v>0.006083465492741448</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002680013525128957</v>
+        <v>0.002471366120549637</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003076195728360816</v>
+        <v>0.002691017879965263</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00240356385619912</v>
+        <v>0.002213688555844517</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00309358505776964</v>
+        <v>0.002917276494237072</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003056047830545062</v>
+        <v>0.002833867449943568</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002938948552940592</v>
+        <v>0.002818139694329728</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002770430820980079</v>
+        <v>0.002541366372807782</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002871240812512384</v>
+        <v>0.002668739703321035</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003641154733767689</v>
+        <v>0.003427246842000094</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003124889868375543</v>
+        <v>0.002899754481915995</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004404200849128317</v>
+        <v>0.004017880102096653</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002507054993344623</v>
+        <v>0.002314321619829582</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003167142388026659</v>
+        <v>0.003026277590557997</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.006090179745932126</v>
+        <v>0.005516421344167304</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002782625567110842</v>
+        <v>0.00252894807322037</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003159053230515613</v>
+        <v>0.002875412702764018</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003226930561908783</v>
+        <v>0.00293404207176301</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003114203244719483</v>
+        <v>0.002835059362799439</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002396824375619913</v>
+        <v>0.002177105028995951</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004087017113372998</v>
+        <v>0.003347819735549332</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00358786787797781</v>
+        <v>0.003305683658886639</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003207810246401328</v>
+        <v>0.002979245820338912</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003569636379835909</v>
+        <v>0.003154807168345114</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00330352724762332</v>
+        <v>0.003134818525742018</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003557851494468996</v>
+        <v>0.003132676631254672</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003230528669583458</v>
+        <v>0.003028654498393574</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00330166369803369</v>
+        <v>0.006083465492741448</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003330305200298408</v>
+        <v>0.003023723881463225</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00377693429560522</v>
+        <v>0.003290640461499432</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003261402745294112</v>
+        <v>0.002969395924234106</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003350059685491184</v>
+        <v>0.003097382885124699</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003312522458266606</v>
+        <v>0.003013973840831196</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003195423180662133</v>
+        <v>0.002998246085217356</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003272597700268695</v>
+        <v>0.002956553550798483</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003653021463224839</v>
+        <v>0.003335207659482919</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003897530588395296</v>
+        <v>0.003607258691378907</v>
       </c>
       <c r="X9" t="n">
-        <v>0.00393666489347383</v>
+        <v>0.003611371481660681</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.004161614358319016</v>
+        <v>0.00372015920862293</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003072995456919104</v>
+        <v>0.002799175600334605</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0034236170157482</v>
+        <v>0.003206383981445627</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.005821653913876096</v>
+        <v>0.00519401897523288</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
@@ -798,7 +798,7 @@
         <v>0.00394431406762263</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02313503278494857</v>
+        <v>0.002646148835278857</v>
       </c>
       <c r="O4" t="n">
         <v>0.00235890251553495</v>
@@ -974,7 +974,7 @@
         <v>0.00457293122467799</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02313503278494857</v>
+        <v>0.002870137972689896</v>
       </c>
       <c r="O6" t="n">
         <v>0.002582890637273386</v>
@@ -1062,7 +1062,7 @@
         <v>0.004332376397428526</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02313503278494857</v>
+        <v>0.003034211165084758</v>
       </c>
       <c r="O7" t="n">
         <v>0.002746936562052616</v>
@@ -1150,7 +1150,7 @@
         <v>0.005409553843046654</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02313503278494857</v>
+        <v>0.003612548878868472</v>
       </c>
       <c r="O8" t="n">
         <v>0.003462388048287229</v>
@@ -1238,7 +1238,7 @@
         <v>0.005930780269685488</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02313503278494857</v>
+        <v>0.004632615037341714</v>
       </c>
       <c r="O9" t="n">
         <v>0.004501705794480617</v>
@@ -1537,7 +1537,7 @@
         <v>0.002799240474143168</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002740475654368666</v>
+        <v>0.002740475654368665</v>
       </c>
       <c r="D3" t="n">
         <v>0.00284226735992899</v>
@@ -1658,7 +1658,7 @@
         <v>0.001613093312427834</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004849682996968022</v>
+        <v>0.001665161892936191</v>
       </c>
       <c r="O4" t="n">
         <v>0.001707257153246579</v>
@@ -1834,7 +1834,7 @@
         <v>0.001792592353135888</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004849682996968022</v>
+        <v>0.001847227274144215</v>
       </c>
       <c r="O6" t="n">
         <v>0.002192359159804678</v>
@@ -1922,7 +1922,7 @@
         <v>0.001881483392947543</v>
       </c>
       <c r="N7" t="n">
-        <v>0.004849682996968022</v>
+        <v>0.001933551973455899</v>
       </c>
       <c r="O7" t="n">
         <v>0.001975623651455258</v>
@@ -2010,7 +2010,7 @@
         <v>0.002654858904137335</v>
       </c>
       <c r="N8" t="n">
-        <v>0.004849682996968022</v>
+        <v>0.002350394548151587</v>
       </c>
       <c r="O8" t="n">
         <v>0.002490468154710769</v>
@@ -2098,7 +2098,7 @@
         <v>0.002703000274130523</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004849682996968022</v>
+        <v>0.00275506885463888</v>
       </c>
       <c r="O9" t="n">
         <v>0.00288561271471526</v>
@@ -2518,7 +2518,7 @@
         <v>0.003695405108040186</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01598055496191955</v>
+        <v>0.002295256090121103</v>
       </c>
       <c r="O4" t="n">
         <v>0.002123252924817895</v>
@@ -2694,7 +2694,7 @@
         <v>0.004247644387495279</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01598055496191955</v>
+        <v>0.002490226182497032</v>
       </c>
       <c r="O6" t="n">
         <v>0.002317515605447477</v>
@@ -2782,7 +2782,7 @@
         <v>0.004039663325854803</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01598055496191955</v>
+        <v>0.002639514307935717</v>
       </c>
       <c r="O7" t="n">
         <v>0.002467485534560383</v>
@@ -2870,7 +2870,7 @@
         <v>0.005000821553418062</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01598055496191955</v>
+        <v>0.003156014979729967</v>
       </c>
       <c r="O8" t="n">
         <v>0.003106207571183866</v>
@@ -2958,7 +2958,7 @@
         <v>0.005298248233674107</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01598055496191955</v>
+        <v>0.003898099215755014</v>
       </c>
       <c r="O9" t="n">
         <v>0.003853449278966805</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003316617511592936</v>
+        <v>0.003316617511592942</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003285301962709197</v>
+        <v>0.003285301962709201</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003340456897004078</v>
+        <v>0.003340456897004079</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003299573964464743</v>
+        <v>0.003299573964464749</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003300168901015921</v>
+        <v>0.003300168901015922</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003329147285065062</v>
+        <v>0.00332914728506507</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003343119817927472</v>
+        <v>0.003343119817927473</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003342413216856804</v>
+        <v>0.003342413216856811</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003338027439216107</v>
+        <v>0.00333802743921611</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003345727235350121</v>
+        <v>0.003345727235350128</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003325926674888853</v>
+        <v>0.003325926674888858</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003438825901471509</v>
+        <v>0.003438825901471511</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003317893642221028</v>
+        <v>0.003317893642221031</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004483032585960684</v>
+        <v>0.004483032585960682</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003326742528265093</v>
+        <v>0.003326742528265095</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003301678318412113</v>
+        <v>0.003301678318412119</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003329423010886056</v>
+        <v>0.003329423010886069</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003328735253645574</v>
+        <v>0.003328735253645588</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003336261731448303</v>
+        <v>0.003336261731448306</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006186464065030506</v>
+        <v>0.006186464065030507</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003306256002060768</v>
+        <v>0.003306256002060773</v>
       </c>
       <c r="W2" t="n">
         <v>0.00656273681793062</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003359270080270003</v>
+        <v>0.003359270080270011</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003369964157403132</v>
+        <v>0.003369964157403137</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005237603456321877</v>
+        <v>0.005237603456321885</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003358726008804838</v>
+        <v>0.003358726008804845</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003376476269240985</v>
+        <v>0.003376476269240986</v>
       </c>
     </row>
     <row r="3">
@@ -3254,19 +3254,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003134221835546614</v>
+        <v>0.003134221835546612</v>
       </c>
       <c r="C3" t="n">
         <v>0.002931993128263949</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003306594766251451</v>
+        <v>0.003306594766251447</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00301356214590464</v>
+        <v>0.003013562145904637</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003018363473734888</v>
+        <v>0.003018363473734883</v>
       </c>
       <c r="G3" t="n">
         <v>0.003223224000201302</v>
@@ -3275,61 +3275,61 @@
         <v>0.003327222379910584</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003321074223440317</v>
+        <v>0.003321074223440315</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003287894566393699</v>
+        <v>0.003287894566393696</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003341338568619201</v>
+        <v>0.003341338568619198</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003201515409205823</v>
+        <v>0.003201515409205818</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004008315401810131</v>
+        <v>0.00400831540181013</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003144800061043335</v>
+        <v>0.003144800061043331</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005031636533560006</v>
+        <v>0.005031636533560011</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003206072030848677</v>
+        <v>0.003206072030848678</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003028733524393093</v>
+        <v>0.00302873352439309</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003228443526636189</v>
+        <v>0.003228443526636192</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003220485701017944</v>
+        <v>0.00322048570101794</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003276836098375432</v>
+        <v>0.003276836098375428</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008010854617689731</v>
+        <v>0.008010854617689734</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003060069224933981</v>
+        <v>0.003060069224933974</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008815067586847733</v>
+        <v>0.008815067586847724</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003440713960002895</v>
+        <v>0.003440713960002894</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003515904304043751</v>
+        <v>0.003515904304043754</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006277374916751475</v>
+        <v>0.006277374916751477</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003435987969260481</v>
+        <v>0.003435987969260479</v>
       </c>
       <c r="AB3" t="n">
         <v>0.003563428338212674</v>
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002023322420139962</v>
+        <v>0.002023322420139959</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00171079980373917</v>
+        <v>0.001710799803739167</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002292599245017863</v>
+        <v>0.00229259924501786</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001830807714907982</v>
+        <v>0.001830807714907979</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001837527796937907</v>
+        <v>0.001837527796937905</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002164851975488173</v>
+        <v>0.002164851975488171</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002322678161851769</v>
+        <v>0.002322678161851767</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002314696777706055</v>
+        <v>0.002314696777706052</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002264738620843752</v>
+        <v>0.00226473862084375</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002352130141111874</v>
+        <v>0.002352130141111872</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002128473701994021</v>
+        <v>0.002128473701994012</v>
       </c>
       <c r="M4" t="n">
         <v>0.003397626491836514</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01065751711119261</v>
+        <v>0.002037736902633321</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00196676715476014</v>
+        <v>0.001966767154760136</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002137689141189749</v>
+        <v>0.002137689141189748</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001854577360794161</v>
+        <v>0.001854577360794159</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002167966425476466</v>
+        <v>0.002167966425476462</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002160197891061258</v>
+        <v>0.002160197891061255</v>
       </c>
       <c r="T4" t="n">
         <v>0.002245212920193913</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002294962393668577</v>
+        <v>0.002294962393668578</v>
       </c>
       <c r="V4" t="n">
         <v>0.001903583873994921</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002684824878582166</v>
+        <v>0.002684824878582164</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002505102804498443</v>
+        <v>0.002505102804498439</v>
       </c>
       <c r="Y4" t="n">
         <v>0.002610872017120813</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001967111821771601</v>
+        <v>0.001967111821771597</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002498957267014146</v>
+        <v>0.002498957267014142</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002693294435255652</v>
+        <v>0.002693294435255649</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00964056652239407</v>
+        <v>0.009640566522394037</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004678656628243512</v>
+        <v>0.004678656628243508</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01555883772225211</v>
+        <v>0.0155588377222521</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006743981823721164</v>
+        <v>0.006743981823721159</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007150574563658591</v>
+        <v>0.007150574563658585</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01192430632710085</v>
+        <v>0.01192430632710087</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01693150447181834</v>
+        <v>0.01693150447181838</v>
       </c>
       <c r="I5" t="n">
         <v>0.01621764555819941</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01436774091523692</v>
+        <v>0.01436774091523691</v>
       </c>
       <c r="K5" t="n">
         <v>0.01512398668851522</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01194270281147619</v>
+        <v>0.01194270281147611</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03664125070594038</v>
+        <v>0.03664125070594026</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01065751711119261</v>
+        <v>0.01065751711119262</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008382624199860939</v>
+        <v>0.008382624199860958</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01144953533113757</v>
+        <v>0.01144953533113758</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.007243416217733887</v>
+        <v>0.007243416217733878</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01366447967757795</v>
+        <v>0.01366447967757794</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01194687444844343</v>
+        <v>0.01194687444844341</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01481527616122531</v>
+        <v>0.0148152761612253</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01475673581643868</v>
+        <v>0.01475673581643882</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007463173877554209</v>
+        <v>0.007463173877554228</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02197792502869768</v>
+        <v>0.02197792502869763</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01923883746522206</v>
+        <v>0.01923883746522213</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02078771564154237</v>
+        <v>0.02078771564154236</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008395774620262909</v>
+        <v>0.008395774620262869</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01869331866056792</v>
+        <v>0.0186933186605679</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02425667963346372</v>
+        <v>0.02425667963346368</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002548230975754041</v>
+        <v>0.002548230975754039</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001903470386823867</v>
+        <v>0.001903470386823866</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002817507800631943</v>
+        <v>0.00281750780063194</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00235571627052206</v>
+        <v>0.002355716270522058</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002030198380022606</v>
+        <v>0.002030198380022604</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002357522558572871</v>
+        <v>0.00235752255857287</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002515348744936469</v>
+        <v>0.002515348744936467</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002507367360790756</v>
+        <v>0.002507367360790753</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002789647176457834</v>
+        <v>0.002789647176457829</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002877038696725952</v>
+        <v>0.002877038696725947</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002653382257608103</v>
+        <v>0.002653382257608099</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003590297074921213</v>
+        <v>0.003590297074921209</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01065751711119261</v>
+        <v>0.002233277819289652</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002495609333666929</v>
+        <v>0.002495609333666924</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002666983436113825</v>
+        <v>0.00266698343611382</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00237948591640824</v>
+        <v>0.002379485916408236</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002360637008561166</v>
+        <v>0.002360637008561163</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002685106446675337</v>
+        <v>0.002685106446675333</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002437883503278615</v>
+        <v>0.002437883503278613</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002502658284868104</v>
+        <v>0.002502658284868106</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002428492429609002</v>
+        <v>0.002428492429609</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003213617019748438</v>
+        <v>0.003213617019748436</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002697773387583142</v>
+        <v>0.002697773387583141</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002835361713163064</v>
+        <v>0.002835361713163069</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00249202037738568</v>
+        <v>0.002492020377385676</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003023865822628223</v>
+        <v>0.003023865822628219</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00289144622135251</v>
+        <v>0.002891446221352508</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002333569109483807</v>
+        <v>0.002333569109483802</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002021046493083014</v>
+        <v>0.002021046493083011</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002602845934361708</v>
+        <v>0.002602845934361709</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002141054404251825</v>
+        <v>0.002141054404251824</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00214777448628175</v>
+        <v>0.002147774486281749</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00247509866483202</v>
+        <v>0.002475098664832016</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002632924851195613</v>
+        <v>0.002632924851195612</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002624943467049902</v>
+        <v>0.002624943467049897</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002574985310187598</v>
+        <v>0.002574985310187596</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002662376830455719</v>
+        <v>0.002662376830455716</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002438720391337868</v>
+        <v>0.002438720391337862</v>
       </c>
       <c r="M7" t="n">
         <v>0.003707873181180359</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01065751711119261</v>
+        <v>0.002347983591977164</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002276989870026557</v>
+        <v>0.002276989870026556</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002447911856456172</v>
+        <v>0.002447911856456169</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002164824050138006</v>
+        <v>0.002164824050138003</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00247821311482031</v>
+        <v>0.002478213114820307</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002470444580405103</v>
+        <v>0.002470444580405099</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002555459609537758</v>
+        <v>0.002555459609537757</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00261986826880041</v>
+        <v>0.002619868268800419</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002213830563338766</v>
+        <v>0.002213830563338765</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002995071567926008</v>
+        <v>0.002995071567926005</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002815349493842287</v>
+        <v>0.002815349493842284</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002936144014579482</v>
+        <v>0.002936144014579479</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002277358511115446</v>
+        <v>0.00227735851111544</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00280920395635799</v>
+        <v>0.002809203956357986</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003003541124599493</v>
+        <v>0.00300354112459949</v>
       </c>
     </row>
     <row r="8">
@@ -3694,22 +3694,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002685221124089009</v>
+        <v>0.00268522112408901</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002891863283921219</v>
+        <v>0.00289186328392122</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003473662725199915</v>
+        <v>0.003473662725199916</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002735431266323827</v>
+        <v>0.002735431266323826</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002580306305328547</v>
+        <v>0.002580306305328546</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003453567654003582</v>
+        <v>0.003453567654003581</v>
       </c>
       <c r="H8" t="n">
         <v>0.003503741642033821</v>
@@ -3718,7 +3718,7 @@
         <v>0.003495760257888107</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003445802101025804</v>
+        <v>0.003445802101025805</v>
       </c>
       <c r="K8" t="n">
         <v>0.003533193621293924</v>
@@ -3727,43 +3727,43 @@
         <v>0.003309537182176075</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004578689972018752</v>
+        <v>0.004578689972018751</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01065751711119261</v>
+        <v>0.002816360826654344</v>
       </c>
       <c r="O8" t="n">
         <v>0.00285598496270568</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002999797715908653</v>
+        <v>0.00299979771590865</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002414448337093099</v>
+        <v>0.002414448337093095</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003349029905658517</v>
+        <v>0.003349029905658516</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003341261371243307</v>
+        <v>0.003341261371243308</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003426276400375969</v>
+        <v>0.003426276400375967</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003237388626913753</v>
+        <v>0.003237388626913749</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002942459332433961</v>
+        <v>0.002942459332433965</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003865990388690213</v>
+        <v>0.003865990388690211</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003112556263621712</v>
+        <v>0.003112556263621713</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004322700919613663</v>
+        <v>0.00432270091961366</v>
       </c>
       <c r="Z8" t="n">
         <v>0.002619366773544996</v>
@@ -3772,7 +3772,7 @@
         <v>0.003680020747196196</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00441666893527407</v>
+        <v>0.004416668935274068</v>
       </c>
     </row>
     <row r="9">
@@ -3782,55 +3782,55 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003057841393205271</v>
+        <v>0.003057841393205269</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003074337222952187</v>
+        <v>0.003074337222952185</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003656136664230886</v>
+        <v>0.003656136664230882</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003118408939213695</v>
+        <v>0.003118408939213692</v>
       </c>
       <c r="F9" t="n">
         <v>0.002442588035164251</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003528389291245924</v>
+        <v>0.00352838929124592</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003686215581064789</v>
+        <v>0.003686215581064785</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003678234196919078</v>
+        <v>0.003678234196919075</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003628276040056774</v>
+        <v>0.003628276040056772</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003715667560324894</v>
+        <v>0.003715667560324892</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003492011121207045</v>
+        <v>0.003492011121207038</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00476116391104954</v>
+        <v>0.004761163911049534</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01065751711119261</v>
+        <v>0.003401274321846343</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003439340718473408</v>
+        <v>0.003439340718473411</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003633976218086389</v>
+        <v>0.003633976218086387</v>
       </c>
       <c r="Q9" t="n">
         <v>0.00321811467655191</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003531503844689486</v>
+        <v>0.003531503844689483</v>
       </c>
       <c r="S9" t="n">
         <v>0.00352373531027428</v>
@@ -3839,28 +3839,28 @@
         <v>0.003608750339406935</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003673525120996424</v>
+        <v>0.00367352512099643</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003646800935305884</v>
+        <v>0.003646800935305883</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004048362297795186</v>
+        <v>0.004048362297795183</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003868640223711462</v>
+        <v>0.003868640223711458</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00398943474444866</v>
+        <v>0.003989434744448657</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003132280334338391</v>
+        <v>0.003132280334338387</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003862494686227165</v>
+        <v>0.003862494686227164</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.004056831854468671</v>
+        <v>0.004056831854468669</v>
       </c>
     </row>
   </sheetData>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003305904185634161</v>
+        <v>0.00330590418563416</v>
       </c>
       <c r="C2" t="n">
         <v>0.003229515685633449</v>
@@ -4041,28 +4041,28 @@
         <v>0.003299277641273737</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003318723271666534</v>
+        <v>0.003318723271666533</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003332878889314193</v>
+        <v>0.003332878889314196</v>
       </c>
       <c r="I2" t="n">
         <v>0.003330350468882828</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003329372326336312</v>
+        <v>0.003329372326336311</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003353024359908781</v>
+        <v>0.003353024359908782</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003314889170598065</v>
+        <v>0.003314889170598066</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003406075542261246</v>
+        <v>0.003406075542261245</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003300031737005483</v>
+        <v>0.003300031737005482</v>
       </c>
       <c r="O2" t="n">
         <v>0.004470964094324024</v>
@@ -4071,37 +4071,37 @@
         <v>0.003316271659823881</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003296397257213773</v>
+        <v>0.003296397257213772</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0033274831034184</v>
+        <v>0.003327483103418398</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003320068090045284</v>
+        <v>0.003320068090045286</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003334112376934623</v>
+        <v>0.003334112376934622</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006038464717937783</v>
+        <v>0.006038464717937782</v>
       </c>
       <c r="V2" t="n">
         <v>0.003314157669947535</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006421708132379557</v>
+        <v>0.006421708132379559</v>
       </c>
       <c r="X2" t="n">
         <v>0.003364286402974885</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003408986430976449</v>
+        <v>0.003408986430976448</v>
       </c>
       <c r="Z2" t="n">
         <v>0.005223148740070726</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003355285620747233</v>
+        <v>0.003355285620747234</v>
       </c>
       <c r="AB2" t="n">
         <v>0.003362216552624096</v>
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003092002815990395</v>
+        <v>0.003092002815990394</v>
       </c>
       <c r="C3" t="n">
         <v>0.002841270408921323</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003148046152945966</v>
+        <v>0.003148046152945961</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002954728321820259</v>
+        <v>0.002954728321820256</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003046446644744623</v>
+        <v>0.003046446644744622</v>
       </c>
       <c r="G3" t="n">
         <v>0.003182919864829147</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003288481092036573</v>
+        <v>0.00328848109203657</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003268857279764535</v>
+        <v>0.003268857279764533</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003260126620213046</v>
+        <v>0.003260126620213043</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003427591170759428</v>
+        <v>0.003427591170759427</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00315663589007886</v>
+        <v>0.003156635890078859</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003807416272325708</v>
+        <v>0.003807416272325705</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003051700266141205</v>
+        <v>0.003051700266141202</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005012471294926194</v>
+        <v>0.005012471294926193</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003165446619528482</v>
+        <v>0.003165446619528481</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003025278968841026</v>
+        <v>0.003025278968841025</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003249171920513208</v>
+        <v>0.003249171920513207</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003192955567397094</v>
+        <v>0.003192955567397095</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003296065331273316</v>
+        <v>0.003296065331273318</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007789723768825295</v>
+        <v>0.007789723768825297</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003150229868619549</v>
+        <v>0.00315022986861955</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008516163497861804</v>
+        <v>0.008516163497861809</v>
       </c>
       <c r="X3" t="n">
         <v>0.003509977390233574</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003829884147776884</v>
+        <v>0.00382988414777688</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006227847138491571</v>
+        <v>0.00622784713849157</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003446097986593053</v>
+        <v>0.003446097986593052</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003495383828472698</v>
+        <v>0.003495383828472697</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001964527801089942</v>
+        <v>0.001964527801089946</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001704990444898183</v>
+        <v>0.001704990444898185</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002050976396127042</v>
+        <v>0.002050976396127044</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001745782745166223</v>
+        <v>0.001745782745166227</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001889677934177936</v>
+        <v>0.001889677934177942</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002109325274896508</v>
+        <v>0.00210932527489651</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002269219488132668</v>
+        <v>0.002269219488132671</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002240659816229524</v>
+        <v>0.002240659816229527</v>
       </c>
       <c r="J4" t="n">
         <v>0.00222930285804557</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00249677184587288</v>
+        <v>0.002496771845872884</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002066017339554521</v>
+        <v>0.002066017339554525</v>
       </c>
       <c r="M4" t="n">
         <v>0.003092406073240686</v>
       </c>
       <c r="N4" t="n">
-        <v>0.008037737290349593</v>
+        <v>0.00189819579236917</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001959419556286017</v>
+        <v>0.001959419556286018</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002081633191336577</v>
+        <v>0.002081633191336579</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001857142671178506</v>
+        <v>0.001857142671178508</v>
       </c>
       <c r="R4" t="n">
         <v>0.002208271604255526</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002124515617131543</v>
+        <v>0.002124515617131546</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002283152298237773</v>
+        <v>0.002283152298237777</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002340718883332258</v>
+        <v>0.002340718883332262</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002055804126239676</v>
+        <v>0.002055804126239672</v>
       </c>
       <c r="W4" t="n">
         <v>0.002539892849149279</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002623981803100291</v>
+        <v>0.002623981803100292</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003118787033606079</v>
+        <v>0.003118787033606082</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001906037005975642</v>
+        <v>0.001906037005975646</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002522313827274593</v>
+        <v>0.002522313827274595</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002594796501876434</v>
+        <v>0.002594796501876437</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008376892981279489</v>
+        <v>0.008376892981279506</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004461175760248339</v>
+        <v>0.00446117576024834</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01064211531463305</v>
+        <v>0.01064211531463299</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004995068614079026</v>
+        <v>0.004995068614079032</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007953623631553495</v>
+        <v>0.007953623631553469</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01064072146279441</v>
+        <v>0.01064072146279436</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01581724567926436</v>
+        <v>0.01581724567926437</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01449418103792268</v>
+        <v>0.01449418103792267</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01339177070788281</v>
+        <v>0.01339177070788277</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01742221627576744</v>
+        <v>0.01742221627576747</v>
       </c>
       <c r="L5" t="n">
         <v>0.01043453323787387</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0295914212315468</v>
+        <v>0.02959142123154678</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008037737290349593</v>
+        <v>0.008037737290349591</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008185470603660719</v>
+        <v>0.008185470603660679</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0101633945391186</v>
+        <v>0.01016339453911852</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.007061946912116153</v>
+        <v>0.007061946912116143</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01432512771115228</v>
+        <v>0.01432512771115226</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01113619744542811</v>
+        <v>0.0111361974454281</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0154318387621046</v>
+        <v>0.01543183876210462</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01489892225500793</v>
+        <v>0.01489892225500795</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00967221080962602</v>
+        <v>0.009672210809626023</v>
       </c>
       <c r="W5" t="n">
         <v>0.01932678398262727</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02071296609664268</v>
+        <v>0.02071296609664262</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03009934645958446</v>
+        <v>0.03009934645958444</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.007078616977171606</v>
+        <v>0.00707861697717161</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01910116819241443</v>
+        <v>0.01910116819241442</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02192414713943931</v>
+        <v>0.02192414713943928</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002164186684349026</v>
+        <v>0.002164186684349022</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001904649328157264</v>
+        <v>0.001904649328157262</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002578626822670505</v>
+        <v>0.00257862682267051</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002273433171709692</v>
+        <v>0.002273433171709695</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002089336817437018</v>
+        <v>0.002089336817437014</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002308984158155596</v>
+        <v>0.002308984158155585</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002796869914676126</v>
+        <v>0.00279686991467614</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002440318699488607</v>
+        <v>0.002440318699488605</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002756953284589035</v>
+        <v>0.002756953284589036</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00302442227241635</v>
+        <v>0.003024422272416353</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002265676222813609</v>
+        <v>0.002265676222813602</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003292064956499769</v>
+        <v>0.003292064956499765</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008037737290349593</v>
+        <v>0.002102187900770164</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002212015865063065</v>
+        <v>0.002212015865063073</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002614993504129999</v>
+        <v>0.002614993504130001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002384793097721968</v>
+        <v>0.002384793097721974</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002735922030798992</v>
+        <v>0.002735922030798997</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002324174500390621</v>
+        <v>0.002324174500390618</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002810802724781246</v>
+        <v>0.002810802724781242</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002878471458676393</v>
+        <v>0.002878471458676398</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002255463009498761</v>
+        <v>0.002255463009498746</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002763773595953439</v>
+        <v>0.002763773595953442</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002823640686359369</v>
+        <v>0.002823640686359367</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003353327415884848</v>
+        <v>0.003353327415884841</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002105695889234723</v>
+        <v>0.002105695889234721</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003049964253818052</v>
+        <v>0.003049964253818058</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002799177461729478</v>
+        <v>0.002799177461729485</v>
       </c>
     </row>
     <row r="7">
@@ -4469,82 +4469,82 @@
         <v>0.002269883664683243</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002010346308491481</v>
+        <v>0.002010346308491483</v>
       </c>
       <c r="D7" t="n">
         <v>0.002356332259720341</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002051138608759522</v>
+        <v>0.002051138608759525</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002195033797771237</v>
+        <v>0.002195033797771242</v>
       </c>
       <c r="G7" t="n">
         <v>0.002414681138489809</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002574575351725967</v>
+        <v>0.002574575351725969</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002546015679822824</v>
+        <v>0.002546015679822827</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002534658721638868</v>
+        <v>0.002534658721638865</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00280212770946618</v>
+        <v>0.002802127709466182</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00237137320314782</v>
+        <v>0.002371373203147824</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003397761936833983</v>
+        <v>0.003397761936833985</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008037737290349593</v>
+        <v>0.00220355165596247</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002264751284192893</v>
+        <v>0.002264751284192894</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002386964919243451</v>
+        <v>0.002386964919243448</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002162498534771805</v>
+        <v>0.002162498534771806</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002513627467848826</v>
+        <v>0.002513627467848825</v>
       </c>
       <c r="S7" t="n">
         <v>0.002429871480724844</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002588508161831073</v>
+        <v>0.002588508161831074</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002655816451862682</v>
+        <v>0.002655816451862685</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002361159989832977</v>
+        <v>0.00236115998983297</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00284524871274258</v>
+        <v>0.002845248712742581</v>
       </c>
       <c r="X7" t="n">
         <v>0.002929337666693588</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003434245046000046</v>
+        <v>0.003434245046000041</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002211392869568942</v>
+        <v>0.002211392869568944</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002827669690867893</v>
+        <v>0.002827669690867892</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.002900152365469731</v>
+        <v>0.002900152365469737</v>
       </c>
     </row>
     <row r="8">
@@ -4554,43 +4554,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002616039765353165</v>
+        <v>0.002616039765353167</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002867765195700912</v>
+        <v>0.002867765195700914</v>
       </c>
       <c r="D8" t="n">
         <v>0.003213751146929773</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002636325143619876</v>
+        <v>0.002636325143619875</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002620838665241342</v>
+        <v>0.002620838665241344</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003378113694993091</v>
+        <v>0.003378113694993086</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0034319942389354</v>
+        <v>0.003431994238935397</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003403434567032257</v>
+        <v>0.003403434567032258</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003392077608848301</v>
+        <v>0.003392077608848298</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003659546596675611</v>
+        <v>0.003659546596675613</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003228792090357253</v>
+        <v>0.003228792090357255</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004255180824043672</v>
+        <v>0.004255180824043673</v>
       </c>
       <c r="N8" t="n">
-        <v>0.008037737290349593</v>
+        <v>0.002664656350998083</v>
       </c>
       <c r="O8" t="n">
         <v>0.002834790695631443</v>
@@ -4599,40 +4599,40 @@
         <v>0.002930307715745771</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002408179829119816</v>
+        <v>0.002408179829119819</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003371046355058259</v>
+        <v>0.003371046355058261</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003287290367934275</v>
+        <v>0.003287290367934276</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003445927049040505</v>
+        <v>0.003445927049040507</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00326379460950086</v>
+        <v>0.003263794609500858</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003078555580180909</v>
+        <v>0.003078555580180913</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003702768076913206</v>
+        <v>0.003702768076913208</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003221877210810633</v>
+        <v>0.003221877210810631</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004799555021434927</v>
+        <v>0.004799555021434919</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002548052001578451</v>
+        <v>0.002548052001578453</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003685088578077325</v>
+        <v>0.003685088578077322</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004291627983529471</v>
+        <v>0.00429162798352947</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00291985216448152</v>
+        <v>0.002919852164481522</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002966864694683609</v>
+        <v>0.002966864694683608</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003312850645912468</v>
+        <v>0.003312850645912472</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002936906471115697</v>
+        <v>0.002936906471115695</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002444871133002971</v>
+        <v>0.002444871133002974</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003371199446093592</v>
+        <v>0.003371199446093594</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003531093737918094</v>
+        <v>0.003531093737918095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003502534066014949</v>
+        <v>0.00350253406601495</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003491177107830996</v>
+        <v>0.003491177107830992</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003758646095658308</v>
+        <v>0.003758646095658309</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003327891589339951</v>
+        <v>0.00332789158933995</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004354280323026117</v>
+        <v>0.004354280323026113</v>
       </c>
       <c r="N9" t="n">
-        <v>0.008037737290349593</v>
+        <v>0.003160070042154596</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003322883932397136</v>
+        <v>0.003322883932397134</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003467191694022115</v>
+        <v>0.003467191694022118</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003119016842375592</v>
+        <v>0.003119016842375593</v>
       </c>
       <c r="R9" t="n">
         <v>0.003470145854040949</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003386389866916966</v>
+        <v>0.003386389866916968</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003545026548023198</v>
+        <v>0.003545026548023204</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003612695281918352</v>
+        <v>0.003612695281918355</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003671429910669197</v>
+        <v>0.00367142991066919</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003801767098934705</v>
+        <v>0.003801767098934707</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003885856052885719</v>
+        <v>0.003885856052885715</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.004390763432192173</v>
+        <v>0.00439076343219218</v>
       </c>
       <c r="Z9" t="n">
         <v>0.002983088902538508</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003784188077060013</v>
+        <v>0.003784188077060017</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.003856670751661858</v>
+        <v>0.003856670751661862</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>0.002232837617629069</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01028113026333441</v>
+        <v>0.001964836154786387</v>
       </c>
       <c r="O4" t="n">
         <v>0.001699172932095563</v>
@@ -5274,7 +5274,7 @@
         <v>0.002731911093826879</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01028113026333441</v>
+        <v>0.002146758726700981</v>
       </c>
       <c r="O6" t="n">
         <v>0.002206721120442722</v>
@@ -5362,7 +5362,7 @@
         <v>0.00253407614416811</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01028113026333441</v>
+        <v>0.002266074681325427</v>
       </c>
       <c r="O7" t="n">
         <v>0.002000386512556174</v>
@@ -5450,7 +5450,7 @@
         <v>0.0033989067513775</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01028113026333441</v>
+        <v>0.002732251890739137</v>
       </c>
       <c r="O8" t="n">
         <v>0.002576142082753042</v>
@@ -5538,7 +5538,7 @@
         <v>0.00362598965186913</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01028113026333441</v>
+        <v>0.003357988189026447</v>
       </c>
       <c r="O9" t="n">
         <v>0.003203661432240102</v>
@@ -5809,7 +5809,7 @@
         <v>0.003212647091354777</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006410095202240109</v>
+        <v>0.006410095202240108</v>
       </c>
       <c r="X2" t="n">
         <v>0.003257151121246534</v>
@@ -5958,7 +5958,7 @@
         <v>0.001579563136744902</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005192330177218433</v>
+        <v>0.0016903378499415</v>
       </c>
       <c r="O4" t="n">
         <v>0.001681034161503713</v>
@@ -6134,7 +6134,7 @@
         <v>0.002045701851865523</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005192330177218433</v>
+        <v>0.001867564739625025</v>
       </c>
       <c r="O6" t="n">
         <v>0.002152775980550281</v>
@@ -6222,7 +6222,7 @@
         <v>0.001844403624323518</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005192330177218433</v>
+        <v>0.001955178337520115</v>
       </c>
       <c r="O7" t="n">
         <v>0.001945851224649714</v>
@@ -6310,7 +6310,7 @@
         <v>0.002609961950821511</v>
       </c>
       <c r="N8" t="n">
-        <v>0.005192330177218433</v>
+        <v>0.002367874151367028</v>
       </c>
       <c r="O8" t="n">
         <v>0.002455540144835414</v>
@@ -6349,7 +6349,7 @@
         <v>0.002296730741144123</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.00296285103177959</v>
+        <v>0.002962851031779589</v>
       </c>
       <c r="AB8" t="n">
         <v>0.003032042695668886</v>
@@ -6398,7 +6398,7 @@
         <v>0.002744938624587885</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005192330177218433</v>
+        <v>0.002855713337784482</v>
       </c>
       <c r="O9" t="n">
         <v>0.00294021762502855</v>
@@ -6818,7 +6818,7 @@
         <v>0.001584862265084385</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004303681744092657</v>
+        <v>0.001634820187830444</v>
       </c>
       <c r="O4" t="n">
         <v>0.001793149348716569</v>
@@ -6906,7 +6906,7 @@
         <v>0.00349184087320601</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004303681744092656</v>
+        <v>0.004303681744092657</v>
       </c>
       <c r="O5" t="n">
         <v>0.006502426126639893</v>
@@ -6994,7 +6994,7 @@
         <v>0.002054670269783167</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004303681744092656</v>
+        <v>0.001815984160137025</v>
       </c>
       <c r="O6" t="n">
         <v>0.002022942172717635</v>
@@ -7082,7 +7082,7 @@
         <v>0.001845779721119714</v>
       </c>
       <c r="N7" t="n">
-        <v>0.004303681744092656</v>
+        <v>0.001895737643865771</v>
       </c>
       <c r="O7" t="n">
         <v>0.002054043288529026</v>
@@ -7170,7 +7170,7 @@
         <v>0.00260153593831577</v>
       </c>
       <c r="N8" t="n">
-        <v>0.004303681744092656</v>
+        <v>0.002303204468052569</v>
       </c>
       <c r="O8" t="n">
         <v>0.00255724657786194</v>
@@ -7258,7 +7258,7 @@
         <v>0.00266017231921771</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004303681744092656</v>
+        <v>0.002710130241963768</v>
       </c>
       <c r="O9" t="n">
         <v>0.002955696348835874</v>
@@ -7678,7 +7678,7 @@
         <v>0.003626396528851452</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01735815234726077</v>
+        <v>0.002354857316103231</v>
       </c>
       <c r="O4" t="n">
         <v>0.001958871535043307</v>
@@ -7854,7 +7854,7 @@
         <v>0.003813848493304919</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01735815234726077</v>
+        <v>0.002544660421663412</v>
       </c>
       <c r="O6" t="n">
         <v>0.002506877309466921</v>
@@ -7942,7 +7942,7 @@
         <v>0.003954991929796542</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01735815234726077</v>
+        <v>0.00268345271704832</v>
       </c>
       <c r="O7" t="n">
         <v>0.002287441585052959</v>
@@ -8030,7 +8030,7 @@
         <v>0.004882285117676545</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01735815234726077</v>
+        <v>0.003182350614129798</v>
       </c>
       <c r="O8" t="n">
         <v>0.002904091578209926</v>
@@ -8118,7 +8118,7 @@
         <v>0.005191041348149249</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01735815234726077</v>
+        <v>0.003919502135401025</v>
       </c>
       <c r="O9" t="n">
         <v>0.003647806296136218</v>
@@ -8538,7 +8538,7 @@
         <v>0.001758368383251327</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006083465492741448</v>
+        <v>0.001752508778121936</v>
       </c>
       <c r="O4" t="n">
         <v>0.001651612409203685</v>
@@ -8714,7 +8714,7 @@
         <v>0.001935431431838687</v>
       </c>
       <c r="N6" t="n">
-        <v>0.006083465492741448</v>
+        <v>0.001931641943219428</v>
       </c>
       <c r="O6" t="n">
         <v>0.002158867796677282</v>
@@ -8802,7 +8802,7 @@
         <v>0.002039496206326306</v>
       </c>
       <c r="N7" t="n">
-        <v>0.006083465492741448</v>
+        <v>0.002033636601196915</v>
       </c>
       <c r="O7" t="n">
         <v>0.001932716598411291</v>
@@ -8890,7 +8890,7 @@
         <v>0.002848548107505954</v>
       </c>
       <c r="N8" t="n">
-        <v>0.006083465492741448</v>
+        <v>0.002469785509627348</v>
       </c>
       <c r="O8" t="n">
         <v>0.002471366120549637</v>
@@ -8978,7 +8978,7 @@
         <v>0.003028654498393574</v>
       </c>
       <c r="N9" t="n">
-        <v>0.006083465492741448</v>
+        <v>0.003022794893264181</v>
       </c>
       <c r="O9" t="n">
         <v>0.003023723881463225</v>

--- a/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003379880253782322</v>
+        <v>0.003379880253782323</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003325854392308249</v>
+        <v>0.00332585439230825</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003376520947755857</v>
+        <v>0.00337652094775586</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003336145697251985</v>
+        <v>0.003336145697251987</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003358075331239024</v>
+        <v>0.003358075331239026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003372885293708079</v>
+        <v>0.003372885293708081</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003414882234511164</v>
+        <v>0.003414882234511165</v>
       </c>
       <c r="I2" t="n">
         <v>0.00338438098140304</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003381164599560408</v>
+        <v>0.00338116459956041</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003438115978442368</v>
+        <v>0.003438115978442369</v>
       </c>
       <c r="L2" t="n">
         <v>0.003383714169405924</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003518215749416017</v>
+        <v>0.003518215749416018</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003402459284957599</v>
+        <v>0.003402459284957601</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004595310309725842</v>
+        <v>0.004595310309725843</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003361866183865387</v>
+        <v>0.003361866183865388</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003356670465772349</v>
+        <v>0.00335667046577235</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003381856584698206</v>
+        <v>0.003381856584698207</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003374024143502304</v>
+        <v>0.003374024143502307</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003409254494469885</v>
+        <v>0.003409254494469887</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006310884754047705</v>
+        <v>0.00631088475404771</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00335061732814394</v>
+        <v>0.003350617328143941</v>
       </c>
       <c r="W2" t="n">
         <v>0.006634457555150799</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003361961458760159</v>
+        <v>0.003361961458760161</v>
       </c>
       <c r="Y2" t="n">
         <v>0.003378153022955299</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005300635787075625</v>
+        <v>0.005300635787075626</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003407770591347273</v>
+        <v>0.003407770591347275</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0034262535132357</v>
+        <v>0.003426253513235701</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003352337311084484</v>
+        <v>0.003371209645470183</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002976053014467282</v>
+        <v>0.002981790144725252</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00333172281263654</v>
+        <v>0.003350014551533379</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003042075189076776</v>
+        <v>0.003050009418424613</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00320016633694094</v>
+        <v>0.003213833605866633</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003303228733442828</v>
+        <v>0.003320360854804877</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003608207286143352</v>
+        <v>0.00363642087846948</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003388356694653492</v>
+        <v>0.00340867971482229</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003363325101682439</v>
+        <v>0.003382653502792106</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003772221670382007</v>
+        <v>0.003806108790185226</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003381514009983326</v>
+        <v>0.003401460959328479</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004342028120513455</v>
+        <v>0.004396291672156423</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003516272482026386</v>
+        <v>0.003541052296963735</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005342534090490369</v>
+        <v>0.005360675376082007</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003224551199227042</v>
+        <v>0.003238894040651161</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003189209524599309</v>
+        <v>0.003202430378911026</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003370676349071686</v>
+        <v>0.003390394967995559</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003311426071078948</v>
+        <v>0.003328883620425867</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003566217712521374</v>
+        <v>0.003592837739942883</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008399915985011925</v>
+        <v>0.008428426244662812</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003144473415467694</v>
+        <v>0.003156045498837466</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00887048952145408</v>
+        <v>0.00889610569578105</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003227216339653312</v>
+        <v>0.003241798231882749</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003342093417673242</v>
+        <v>0.003360697401171839</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00640455920333285</v>
+        <v>0.006418002790466233</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00355376391900558</v>
+        <v>0.003579824620687458</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00368657159874456</v>
+        <v>0.003717362169067294</v>
       </c>
     </row>
     <row r="4">
@@ -765,22 +765,22 @@
         <v>0.002391108291286597</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001794941720227691</v>
+        <v>0.00179494172022769</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002353163384360573</v>
+        <v>0.00235316338436057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001897106356386452</v>
+        <v>0.001897106356386451</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002144811660400106</v>
+        <v>0.002144811660400104</v>
       </c>
       <c r="G4" t="n">
         <v>0.002312096999407436</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002786471765325498</v>
+        <v>0.002786471765325497</v>
       </c>
       <c r="I4" t="n">
         <v>0.002441946080199612</v>
@@ -792,55 +792,55 @@
         <v>0.003048907591078722</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002434414131943505</v>
+        <v>0.00243441413194351</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00394431406762263</v>
+        <v>0.003944314067622624</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002646148835278857</v>
+        <v>0.002646148835278858</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00235890251553495</v>
+        <v>0.002358902515534946</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002187631084693238</v>
+        <v>0.002187631084693234</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002128943058683968</v>
+        <v>0.002128943058683963</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002413431858138653</v>
+        <v>0.002413431858138652</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002324960831729998</v>
+        <v>0.002324960831729997</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002722903852670955</v>
+        <v>0.002722903852670956</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002812666870848889</v>
+        <v>0.002812666870848883</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002058525301986644</v>
+        <v>0.002058525301986645</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00268711572074822</v>
+        <v>0.002687115720748217</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002188707258458321</v>
+        <v>0.00218870725845832</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002364202019668497</v>
+        <v>0.002364202019668494</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002145253997696869</v>
+        <v>0.002145253997696868</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002706142484271923</v>
+        <v>0.002706142484271925</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002908827023519378</v>
+        <v>0.002908827023519377</v>
       </c>
     </row>
     <row r="5">
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01634231509053272</v>
+        <v>0.01634231509053259</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005650943396059401</v>
+        <v>0.0056509433960594</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01757581713115809</v>
+        <v>0.01757581713115801</v>
       </c>
       <c r="E5" t="n">
         <v>0.007507745298858103</v>
@@ -865,70 +865,70 @@
         <v>0.01343403382877253</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01523547443083899</v>
+        <v>0.01523547443083902</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02790530562040267</v>
+        <v>0.02790530562040265</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01968253669620082</v>
+        <v>0.01968253669620084</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01771665645376183</v>
+        <v>0.01771665645376184</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03211680044687295</v>
+        <v>0.03211680044687293</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01829246396146003</v>
+        <v>0.01829246396146</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05205883368590176</v>
+        <v>0.05205883368590169</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02313503278494857</v>
+        <v>0.02313503278494855</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01542616598719596</v>
+        <v>0.01542616598719594</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01270902969991266</v>
+        <v>0.01270902969991269</v>
       </c>
       <c r="Q5" t="n">
         <v>0.01256159983914947</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01930826056945059</v>
+        <v>0.01930826056945058</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01553571865192514</v>
+        <v>0.01553571865192522</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02554102391940678</v>
+        <v>0.02554102391940677</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02555827519962865</v>
+        <v>0.0255582751996287</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0102706026909351</v>
+        <v>0.01027060269093509</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02355229933704015</v>
+        <v>0.02355229933704013</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01391058005299624</v>
+        <v>0.01391058005299621</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01718771976715741</v>
+        <v>0.01718771976715743</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01203216925278257</v>
+        <v>0.01203216925278256</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02409615131277516</v>
+        <v>0.02409615131277522</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0306753492801571</v>
+        <v>0.03067534928015714</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002612028706696427</v>
+        <v>0.002612028706696426</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002423558877283052</v>
+        <v>0.002423558877283053</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002981780541415935</v>
+        <v>0.002981780541415937</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002525723513441811</v>
+        <v>0.002525723513441813</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002365732075809936</v>
+        <v>0.002365732075809935</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002940714156462795</v>
+        <v>0.0029407141564628</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003415088922380862</v>
+        <v>0.003415088922380863</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002662866495609444</v>
+        <v>0.00266286649560944</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002626212713206394</v>
+        <v>0.002626212713206395</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003677524748134085</v>
+        <v>0.003677524748134088</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003063031288998875</v>
+        <v>0.003063031288998877</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00457293122467799</v>
+        <v>0.004572931224677984</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002870137972689896</v>
+        <v>0.002870137972689883</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002582890637273386</v>
+        <v>0.002582890637273383</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00281790585840062</v>
+        <v>0.002817905858400623</v>
       </c>
       <c r="Q6" t="n">
         <v>0.002757560215739333</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003042049015194015</v>
+        <v>0.003042049015194016</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00254588124713983</v>
+        <v>0.002545881247139828</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002943824268080785</v>
+        <v>0.002943824268080784</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003040983691120148</v>
+        <v>0.003040983691120146</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002687142459042005</v>
+        <v>0.002687142459042007</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003317390273797475</v>
+        <v>0.003317390273797472</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002817324415513685</v>
+        <v>0.002817324415513684</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002612785758773918</v>
+        <v>0.002612785758773923</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002366174413106702</v>
+        <v>0.0023661744131067</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003334759641327286</v>
+        <v>0.003334759641327285</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003136174283229182</v>
+        <v>0.003136174283229181</v>
       </c>
     </row>
     <row r="7">
@@ -1026,16 +1026,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002779170621092496</v>
+        <v>0.002779170621092495</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002183004050033592</v>
+        <v>0.00218300405003359</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002741225714166472</v>
+        <v>0.002741225714166468</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002285168686192352</v>
+        <v>0.002285168686192351</v>
       </c>
       <c r="F7" t="n">
         <v>0.002532873990206004</v>
@@ -1044,67 +1044,67 @@
         <v>0.002700159329213336</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0031745340951314</v>
+        <v>0.003174534095131397</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002830008410005515</v>
+        <v>0.002830008410005511</v>
       </c>
       <c r="J7" t="n">
         <v>0.002793354627602465</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003436969920884622</v>
+        <v>0.003436969920884624</v>
       </c>
       <c r="L7" t="n">
         <v>0.00282247646174941</v>
       </c>
       <c r="M7" t="n">
-        <v>0.004332376397428526</v>
+        <v>0.00433237639742852</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003034211165084758</v>
+        <v>0.003034211165084757</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002746936562052616</v>
+        <v>0.002746936562052611</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002575665131210903</v>
+        <v>0.002575665131210899</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002517005388489864</v>
+        <v>0.002517005388489866</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002801494187944554</v>
+        <v>0.00280149418794455</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002713023161535898</v>
+        <v>0.002713023161535897</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003110966182476857</v>
+        <v>0.003110966182476854</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003207903677788184</v>
+        <v>0.00320790367778819</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002446587631792543</v>
+        <v>0.002446587631792544</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003075178050554118</v>
+        <v>0.003075178050554117</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002576769588264223</v>
+        <v>0.002576769588264221</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002759660754335825</v>
+        <v>0.002759660754335823</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002533316327502772</v>
+        <v>0.002533316327502768</v>
       </c>
       <c r="AA7" t="n">
         <v>0.003094204814077823</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003296889353325276</v>
+        <v>0.003296889353325275</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003212822812300527</v>
+        <v>0.003212822812300526</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003260181495651696</v>
+        <v>0.003260181495651699</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003818403159784578</v>
+        <v>0.003818403159784579</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003019687916845895</v>
+        <v>0.003019687916845897</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003066779894910225</v>
+        <v>0.003066779894910228</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003910775928438573</v>
+        <v>0.00391077592843858</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004251711540749504</v>
+        <v>0.004251711540749509</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003907185855623619</v>
+        <v>0.003907185855623627</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00387053207322057</v>
+        <v>0.003870532073220577</v>
       </c>
       <c r="K8" t="n">
-        <v>0.004514147366502731</v>
+        <v>0.004514147366502738</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003899653907367517</v>
+        <v>0.003899653907367523</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005409553843046654</v>
+        <v>0.005409553843046656</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003612548878868472</v>
+        <v>0.003612548878868475</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003462388048287229</v>
+        <v>0.003462388048287225</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003257513651655025</v>
+        <v>0.003257513651655022</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002824190179732115</v>
+        <v>0.002824190179732118</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003878671633562662</v>
+        <v>0.003878671633562661</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003790200607154003</v>
+        <v>0.003790200607154</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004188143628094962</v>
+        <v>0.004188143628094965</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003971056893236998</v>
+        <v>0.003971056893237005</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003347714399158619</v>
+        <v>0.003347714399158625</v>
       </c>
       <c r="W8" t="n">
         <v>0.00415248196636969</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002942934747185879</v>
+        <v>0.002942934747185881</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004476423986979945</v>
+        <v>0.004476423986979948</v>
       </c>
       <c r="Z8" t="n">
         <v>0.002955014706818316</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.004171382259695929</v>
+        <v>0.004171382259695931</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.005046282736969936</v>
+        <v>0.005046282736969946</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003905824511852236</v>
+        <v>0.003905824511852239</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003781407922290549</v>
+        <v>0.00378140792229055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00433962958642343</v>
+        <v>0.004339629586423432</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003774694442932671</v>
+        <v>0.003774694442932675</v>
       </c>
       <c r="F9" t="n">
         <v>0.003043765646716306</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004298563014237519</v>
+        <v>0.00429856301423752</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004772937967388358</v>
+        <v>0.00477293796738836</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004428412282262469</v>
+        <v>0.004428412282262473</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004391758499859424</v>
+        <v>0.004391758499859426</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005035373793141585</v>
+        <v>0.005035373793141587</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004420880334006369</v>
+        <v>0.004420880334006373</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005930780269685488</v>
+        <v>0.005930780269685487</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004632615037341714</v>
+        <v>0.004632615037341721</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004501705794480617</v>
+        <v>0.004501705794480618</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004364435036288327</v>
+        <v>0.004364435036288332</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.004115409073514054</v>
+        <v>0.004115409073514056</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004399898060201511</v>
+        <v>0.004399898060201515</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004311427033792855</v>
+        <v>0.004311427033792862</v>
       </c>
       <c r="T9" t="n">
         <v>0.004709370054733816</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004806529477773176</v>
+        <v>0.004806529477773174</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004589379982556628</v>
+        <v>0.004589379982556633</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004673581922811075</v>
+        <v>0.004673581922811077</v>
       </c>
       <c r="X9" t="n">
-        <v>0.00417517346052118</v>
+        <v>0.004175173460521181</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.004358064626592781</v>
+        <v>0.004358064626592787</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003847296836213959</v>
+        <v>0.003847296836213957</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004692608686334782</v>
+        <v>0.004692608686334786</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.004895293225582236</v>
+        <v>0.004895293225582241</v>
       </c>
     </row>
   </sheetData>
@@ -1446,22 +1446,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003200573851843659</v>
+        <v>0.003200573851843666</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003152642105242251</v>
+        <v>0.00315264210524225</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003206575799650074</v>
+        <v>0.003206575799650073</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003202387975601704</v>
+        <v>0.00320238797560171</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003206798648925135</v>
+        <v>0.003206798648925137</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003209219060872485</v>
+        <v>0.003209219060872487</v>
       </c>
       <c r="H2" t="n">
         <v>0.003218863634937049</v>
@@ -1473,16 +1473,16 @@
         <v>0.003213842789914237</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003220093937840519</v>
+        <v>0.003220093937840516</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00321381970470412</v>
+        <v>0.003213819704704121</v>
       </c>
       <c r="M2" t="n">
         <v>0.003206719776709564</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003212076020843857</v>
+        <v>0.003212076020843856</v>
       </c>
       <c r="O2" t="n">
         <v>0.004343883978538652</v>
@@ -1497,13 +1497,13 @@
         <v>0.003217087471392941</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003213204328180961</v>
+        <v>0.003213204328180964</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003214902188449446</v>
+        <v>0.00321490218844945</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005890727067848783</v>
+        <v>0.005890727067848787</v>
       </c>
       <c r="V2" t="n">
         <v>0.003215653317197112</v>
@@ -1512,19 +1512,19 @@
         <v>0.006296979299138666</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003276556104814535</v>
+        <v>0.003276556104814541</v>
       </c>
       <c r="Y2" t="n">
         <v>0.00324442104439951</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005127629073673269</v>
+        <v>0.005127629073673276</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003247687489793039</v>
+        <v>0.00324768748979304</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003203763438100412</v>
+        <v>0.003203763438100413</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002799240474143168</v>
+        <v>0.002801718987242397</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002740475654368665</v>
+        <v>0.002743907084370274</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00284226735992899</v>
+        <v>0.002846288416785131</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002812226758712669</v>
+        <v>0.002815128327207663</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002843941740909517</v>
+        <v>0.002848033004499719</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002860584419070611</v>
+        <v>0.002865226325611554</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002930615804856276</v>
+        <v>0.00293779687582758</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002883231723208217</v>
+        <v>0.002888711394997477</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002893776158051723</v>
+        <v>0.002899606039608064</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002938095259246093</v>
+        <v>0.002945540384431147</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002893394872283814</v>
+        <v>0.002899213553697015</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002847968340273352</v>
+        <v>0.002852226758936209</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002881597936607009</v>
+        <v>0.002886998371047995</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004769342421205767</v>
+        <v>0.004775623148608546</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002882652756013272</v>
+        <v>0.002888063072987259</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002832566446595536</v>
+        <v>0.002836241413686385</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002917777246926493</v>
+        <v>0.002924488942288726</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002888888000411601</v>
+        <v>0.002894537898497904</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002901959292562491</v>
+        <v>0.002908097812898121</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007303235156345443</v>
+        <v>0.007308639032301427</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002906272196409675</v>
+        <v>0.002912528997537672</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008204309524936129</v>
+        <v>0.008220295594357812</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003340934182459194</v>
+        <v>0.003362706243448943</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003112586031364393</v>
+        <v>0.003126144399632991</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006055603773516219</v>
+        <v>0.006061560023015431</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003135819666916479</v>
+        <v>0.003150192098543201</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002824332737207742</v>
+        <v>0.002827719555303926</v>
       </c>
     </row>
     <row r="4">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001535239602819822</v>
+        <v>0.001535239602819823</v>
       </c>
       <c r="C4" t="n">
         <v>0.001576916933692524</v>
@@ -1631,13 +1631,13 @@
         <v>0.001603034364325658</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0015557309652051</v>
+        <v>0.001555730965205099</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001605551549403238</v>
+        <v>0.001605551549403237</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001632891215793057</v>
+        <v>0.001632891215793051</v>
       </c>
       <c r="H4" t="n">
         <v>0.001741831116575579</v>
@@ -1646,22 +1646,22 @@
         <v>0.001667567200413759</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001684836214024479</v>
+        <v>0.001684836214024476</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001755727953837494</v>
+        <v>0.001755727953837492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001684857604272087</v>
+        <v>0.001684857604272085</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001613093312427834</v>
+        <v>0.001613093312427832</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001665161892936191</v>
+        <v>0.001665161892936194</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001707257153246579</v>
+        <v>0.001707257153246582</v>
       </c>
       <c r="P4" t="n">
         <v>0.001668056853950879</v>
@@ -1670,22 +1670,22 @@
         <v>0.001587909940951921</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001721768532269268</v>
+        <v>0.001721768532269271</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001677906643355791</v>
+        <v>0.001677906643355794</v>
       </c>
       <c r="T4" t="n">
         <v>0.001697084756142658</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001657214531110617</v>
+        <v>0.001657214531110613</v>
       </c>
       <c r="V4" t="n">
         <v>0.001703789959482119</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002140206986097457</v>
+        <v>0.002140206986097461</v>
       </c>
       <c r="X4" t="n">
         <v>0.002393494103689128</v>
@@ -1697,10 +1697,10 @@
         <v>0.001692120214841456</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002067409816802274</v>
+        <v>0.002067409816802277</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001574802044600427</v>
+        <v>0.001574802044600426</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002413992351481186</v>
+        <v>0.002413992351481183</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003235911806793521</v>
+        <v>0.003235911806793529</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003711872294442504</v>
+        <v>0.003711872294442506</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002796519331620902</v>
+        <v>0.002796519331620906</v>
       </c>
       <c r="F5" t="n">
         <v>0.003799869115653521</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003955938359781445</v>
+        <v>0.003955938359781482</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006503335720868777</v>
+        <v>0.00650333572086877</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004951297368776421</v>
+        <v>0.004951297368776419</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004978854939300562</v>
+        <v>0.004978854939300572</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006074769450470766</v>
+        <v>0.006074769450470763</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004862316307673461</v>
+        <v>0.004862316307673462</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003937341535517464</v>
+        <v>0.003937341535517461</v>
       </c>
       <c r="N5" t="n">
         <v>0.004849682996968022</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005097737132804943</v>
+        <v>0.005097737132804945</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004499590026756218</v>
+        <v>0.004499590026756215</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003369473708959751</v>
+        <v>0.003369473708959752</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00606454850772447</v>
+        <v>0.006064548507724472</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004679833623201128</v>
+        <v>0.004679833623201129</v>
       </c>
       <c r="T5" t="n">
-        <v>0.005513198246749927</v>
+        <v>0.005513198246749926</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004520455105890222</v>
+        <v>0.004520455105890228</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005118410649835893</v>
+        <v>0.005118410649835889</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01313647206850887</v>
+        <v>0.01313647206850882</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0172850786113047</v>
+        <v>0.01728507861130473</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01138411152965548</v>
+        <v>0.0113841115296555</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004777581656879603</v>
+        <v>0.004777581656879605</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01199566175428379</v>
+        <v>0.01199566175428382</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003324952535378976</v>
+        <v>0.003324952535378979</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001714738643527875</v>
+        <v>0.001714738643527874</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002045743527791275</v>
+        <v>0.002045743527791276</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001782533405033713</v>
+        <v>0.00178253340503371</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002024557559303851</v>
+        <v>0.002024557559303848</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002074378143501988</v>
+        <v>0.00207437814350199</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001812390256501111</v>
+        <v>0.001812390256501108</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001921330157283633</v>
+        <v>0.001921330157283634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001847066241121814</v>
+        <v>0.001847066241121812</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00215366280812323</v>
+        <v>0.002153662808123228</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001935226994545548</v>
+        <v>0.001935226994545546</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002153684198370835</v>
+        <v>0.002153684198370839</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001792592353135888</v>
+        <v>0.001792592353135885</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001847227274144215</v>
+        <v>0.001847227274144214</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002192359159804678</v>
+        <v>0.002192359159804679</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001836655815542314</v>
+        <v>0.001836655815542313</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001767408981659976</v>
+        <v>0.001767408981659973</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001901267572977323</v>
+        <v>0.001901267572977318</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002146733237454541</v>
+        <v>0.002146733237454537</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001876583796850712</v>
+        <v>0.001876583796850713</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002135245992666867</v>
+        <v>0.00213524599266687</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001883289000190173</v>
+        <v>0.001883289000190172</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002341265857054062</v>
+        <v>0.00234126585705403</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002862320697787881</v>
+        <v>0.002862320697787878</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002231823467007373</v>
+        <v>0.002231823467007367</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001871619255549511</v>
+        <v>0.001871619255549508</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002536236410901024</v>
+        <v>0.002536236410901028</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001754456378348171</v>
+        <v>0.001754456378348169</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00180362968333953</v>
+        <v>0.001803629683339528</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001845307014212234</v>
+        <v>0.001845307014212233</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001871424444845367</v>
+        <v>0.001871424444845364</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00182412104572481</v>
+        <v>0.001824121045724809</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001873941629922947</v>
+        <v>0.001873941629922945</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001901281296312766</v>
+        <v>0.001901281296312763</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002010221197095286</v>
+        <v>0.002010221197095288</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001935957280933467</v>
+        <v>0.001935957280933466</v>
       </c>
       <c r="J7" t="n">
         <v>0.001953226294544187</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002024118034357203</v>
+        <v>0.002024118034357201</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001953247684791795</v>
+        <v>0.001953247684791794</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001881483392947543</v>
+        <v>0.001881483392947541</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001933551973455899</v>
+        <v>0.001933551973455902</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001975623651455258</v>
+        <v>0.001975623651455257</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001936423352159557</v>
+        <v>0.001936423352159561</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001856300021471629</v>
+        <v>0.001856300021471628</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001990158612788976</v>
+        <v>0.001990158612788977</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001946296723875499</v>
+        <v>0.001946296723875498</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001965474836662367</v>
+        <v>0.001965474836662368</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001934480068010903</v>
+        <v>0.001934480068010901</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001972180040001828</v>
+        <v>0.001972180040001827</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002408597066617167</v>
+        <v>0.002408597066617161</v>
       </c>
       <c r="X7" t="n">
         <v>0.002661884184208839</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002298903893963001</v>
+        <v>0.002298903893962999</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001960510295361164</v>
+        <v>0.001960510295361165</v>
       </c>
       <c r="AA7" t="n">
         <v>0.002335799897321983</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001843192125120136</v>
+        <v>0.001843192125120134</v>
       </c>
     </row>
     <row r="8">
@@ -1977,22 +1977,22 @@
         <v>0.002117061982309944</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002618682525402014</v>
+        <v>0.002618682525402013</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002644799956035146</v>
+        <v>0.002644799956035147</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002352590364055102</v>
+        <v>0.002352590364055105</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002259027705800724</v>
+        <v>0.002259027705800725</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0027700290287462</v>
+        <v>0.002770029028746199</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002783596708285065</v>
+        <v>0.002783596708285067</v>
       </c>
       <c r="I8" t="n">
         <v>0.002709332792123246</v>
@@ -2001,58 +2001,58 @@
         <v>0.002726601805733967</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002797493545546981</v>
+        <v>0.002797493545546982</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002726623195981575</v>
+        <v>0.002726623195981576</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002654858904137335</v>
+        <v>0.002654858904137336</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002350394548151587</v>
+        <v>0.00235039454815159</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002490468154710769</v>
+        <v>0.002490468154710768</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002427250995305812</v>
+        <v>0.002427250995305816</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002079342981781902</v>
+        <v>0.002079342981781903</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002763534123978756</v>
+        <v>0.002763534123978761</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002719672235065279</v>
+        <v>0.002719672235065284</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002738850347852146</v>
+        <v>0.002738850347852145</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002483455836918335</v>
+        <v>0.002483455836918336</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002619584720852447</v>
+        <v>0.002619584720852448</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003182062969016612</v>
+        <v>0.00318206296901661</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002927081853337594</v>
+        <v>0.002927081853337593</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003529185017053579</v>
+        <v>0.003529185017053582</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002265398913110248</v>
+        <v>0.00226539891311025</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003109175408511762</v>
+        <v>0.003109175408511765</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003097016780524015</v>
+        <v>0.003097016780524019</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002358252379033494</v>
+        <v>0.002358252379033495</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002666823895395213</v>
+        <v>0.002666823895395214</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002692941326028347</v>
+        <v>0.002692941326028348</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002584039962424808</v>
+        <v>0.002584039962424805</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002080194359298244</v>
+        <v>0.002080194359298245</v>
       </c>
       <c r="G9" t="n">
         <v>0.002722798339853609</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002831738078278267</v>
+        <v>0.002831738078278266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002757474162116447</v>
+        <v>0.00275747416211645</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002774743175727168</v>
+        <v>0.002774743175727166</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002845634915540182</v>
+        <v>0.002845634915540184</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002774764565974776</v>
+        <v>0.002774764565974777</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002703000274130523</v>
+        <v>0.002703000274130525</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00275506885463888</v>
+        <v>0.002755068854638881</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00288561271471526</v>
+        <v>0.002885612714715259</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002865648433036206</v>
+        <v>0.002865648433036205</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002677817065012473</v>
+        <v>0.00267781706501247</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002811675493971956</v>
+        <v>0.002811675493971954</v>
       </c>
       <c r="S9" t="n">
         <v>0.002767813605058479</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002786991717845346</v>
+        <v>0.002786991717845348</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002756326360270807</v>
+        <v>0.002756326360270808</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003101687238085939</v>
+        <v>0.003101687238085936</v>
       </c>
       <c r="W9" t="n">
         <v>0.003230113947800146</v>
       </c>
       <c r="X9" t="n">
-        <v>0.00348340106539182</v>
+        <v>0.003483401065391823</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003120420775145981</v>
+        <v>0.003120420775145982</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00262111378032175</v>
+        <v>0.002621113780321749</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003157316778504964</v>
+        <v>0.003157316778504968</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002664709006303116</v>
+        <v>0.002664709006303119</v>
       </c>
     </row>
   </sheetData>
@@ -2306,16 +2306,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003335920147755507</v>
+        <v>0.003335920147755508</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003293565343382777</v>
+        <v>0.003293565343382778</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003337868187543564</v>
+        <v>0.003337868187543563</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003304524596611437</v>
+        <v>0.003304524596611436</v>
       </c>
       <c r="F2" t="n">
         <v>0.0033110563259108</v>
@@ -2324,46 +2324,46 @@
         <v>0.003339599407772806</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003359814199114126</v>
+        <v>0.003359814199114125</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003338306064159599</v>
+        <v>0.003338306064159598</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003347841798345835</v>
+        <v>0.003347841798345832</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003387775152342452</v>
+        <v>0.003387775152342455</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003344487266418563</v>
+        <v>0.003344487266418567</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00347100786867144</v>
+        <v>0.003471007868671442</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003346257955834301</v>
+        <v>0.003346257955834299</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004520400051220009</v>
+        <v>0.004520400051220013</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003336433832513157</v>
+        <v>0.003336433832513158</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003316281438625586</v>
+        <v>0.003316281438625588</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003347649563789791</v>
+        <v>0.003347649563789789</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003341014857950993</v>
+        <v>0.003341014857950995</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003355518563345607</v>
+        <v>0.003355518563345606</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006215219357105718</v>
+        <v>0.006215219357105722</v>
       </c>
       <c r="V2" t="n">
         <v>0.003307531705719521</v>
@@ -2372,19 +2372,19 @@
         <v>0.006578255268157533</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003340266913832582</v>
+        <v>0.003340266913832581</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003342713469535262</v>
+        <v>0.003342713469535261</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00524697828008481</v>
+        <v>0.005246978280084814</v>
       </c>
       <c r="AA2" t="n">
         <v>0.003364966968620433</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00339152639873409</v>
+        <v>0.003391526398734105</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003227172831762293</v>
+        <v>0.003242221754744508</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002948104282955317</v>
+        <v>0.002953592124093032</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003243961314191961</v>
+        <v>0.003259721824186645</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003004673093833877</v>
+        <v>0.003011867006466575</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003052099183717246</v>
+        <v>0.003061089216156768</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003253839701840211</v>
+        <v>0.003269816763350216</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003402351108731297</v>
+        <v>0.003423821362003433</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003247382262250206</v>
+        <v>0.003263281510019147</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003313807526229689</v>
+        <v>0.003331981935342354</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003598059156096527</v>
+        <v>0.003626454395733835</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003289860534702483</v>
+        <v>0.00330715254848394</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004192739057441728</v>
+        <v>0.004242291020136484</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003303205763086549</v>
+        <v>0.003321026379920112</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00515526855885171</v>
+        <v>0.00516908114151469</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003231191660523878</v>
+        <v>0.003246341392963185</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003089043238887311</v>
+        <v>0.00309929884493051</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003314693625086578</v>
+        <v>0.003333005489937739</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003263984508188714</v>
+        <v>0.003280354127779119</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003370279343098805</v>
+        <v>0.003390534073496834</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008168103269949243</v>
+        <v>0.008191804282346005</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003025334063065592</v>
+        <v>0.003033295743705795</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008874536731466091</v>
+        <v>0.008903176746067496</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003260693024453184</v>
+        <v>0.003277048065587598</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003277203671643539</v>
+        <v>0.003294100933195483</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006288527064659035</v>
+        <v>0.006299299729567933</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003436245119460324</v>
+        <v>0.003458742801337911</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003626271080415073</v>
+        <v>0.00365550290896216</v>
       </c>
     </row>
     <row r="4">
@@ -2482,76 +2482,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002178485792244447</v>
+        <v>0.002178485792244438</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001743772433408474</v>
+        <v>0.001743772433408473</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00220048979779314</v>
+        <v>0.002200489797793141</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001823858599405105</v>
+        <v>0.001823858599405103</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001897637486585362</v>
+        <v>0.001897637486585361</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002220044726683068</v>
+        <v>0.002220044726683066</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002448380094146712</v>
+        <v>0.002448380094146711</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00220543581560443</v>
+        <v>0.002205435815604429</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002312627629690464</v>
+        <v>0.002312627629690465</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002764211923534643</v>
+        <v>0.002764211923534641</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002275255338612955</v>
+        <v>0.002275255338612976</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003695405108040186</v>
+        <v>0.003695405108040185</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002295256090121103</v>
+        <v>0.0022952560901211</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002123252924817895</v>
+        <v>0.002123252924817894</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002184288097888773</v>
+        <v>0.002184288097888772</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001956657538369455</v>
+        <v>0.001956657538369456</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002310974942149617</v>
+        <v>0.002310974942149616</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002236032887584939</v>
+        <v>0.002236032887584934</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002399858912051217</v>
+        <v>0.002399858912051216</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002540072347155859</v>
+        <v>0.002540072347155854</v>
       </c>
       <c r="V4" t="n">
         <v>0.001854458586013107</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002782649960604389</v>
+        <v>0.002782649960604385</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002227584514696172</v>
+        <v>0.00222758451469618</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002231305210856883</v>
+        <v>0.00223130521085688</v>
       </c>
       <c r="Z4" t="n">
         <v>0.001984817513931991</v>
@@ -2560,7 +2560,7 @@
         <v>0.002506582996111539</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002799423766757515</v>
+        <v>0.002799423766757513</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01252050781210806</v>
+        <v>0.01252050781210847</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005315860459276896</v>
+        <v>0.005315860459276889</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01454118202240898</v>
+        <v>0.01454118202240897</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006689452933651316</v>
+        <v>0.006689452933651416</v>
       </c>
       <c r="F5" t="n">
         <v>0.008534279843587955</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01353310346674114</v>
+        <v>0.01353310346674111</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02020710488480325</v>
+        <v>0.02020710488480322</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0147992111473389</v>
+        <v>0.01479921114733894</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01592777301711192</v>
+        <v>0.01592777301711197</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02403726431182509</v>
+        <v>0.02403726431182508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01520877716731808</v>
+        <v>0.01520877716731869</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04470927676428883</v>
+        <v>0.04470927676428879</v>
       </c>
       <c r="N5" t="n">
         <v>0.01598055496191955</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01132167026494337</v>
+        <v>0.01132167026494336</v>
       </c>
       <c r="P5" t="n">
         <v>0.01282633602362164</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009456776263102032</v>
+        <v>0.009456776263102028</v>
       </c>
       <c r="R5" t="n">
         <v>0.01714307537748683</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01385913591485955</v>
+        <v>0.01385913591485945</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01850349473645701</v>
+        <v>0.01850349473645697</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02024216284010717</v>
+        <v>0.02024216284010713</v>
       </c>
       <c r="V5" t="n">
-        <v>0.006882892436030897</v>
+        <v>0.006882892436030906</v>
       </c>
       <c r="W5" t="n">
         <v>0.02497009586165133</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01483763317281946</v>
+        <v>0.01483763317281954</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01483150605425747</v>
+        <v>0.01483150605425746</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.009342713546569546</v>
+        <v>0.009342713546569686</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01970501253926476</v>
+        <v>0.0197050125392648</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02766699187266138</v>
+        <v>0.02766699187266132</v>
       </c>
     </row>
     <row r="6">
@@ -2658,22 +2658,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002370877611488317</v>
+        <v>0.002370877611488321</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00229601171286357</v>
+        <v>0.002296011712863567</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002392881617037018</v>
+        <v>0.002392881617037016</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002376097878860201</v>
+        <v>0.002376097878860204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002090029305829241</v>
+        <v>0.002090029305829239</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002772284006138163</v>
+        <v>0.002772284006138164</v>
       </c>
       <c r="H6" t="n">
         <v>0.00300061937360181</v>
@@ -2682,61 +2682,61 @@
         <v>0.002757675095059526</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00286486690914556</v>
+        <v>0.002864866909145562</v>
       </c>
       <c r="K6" t="n">
         <v>0.002956603742778519</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00282749461806805</v>
+        <v>0.002827494618068051</v>
       </c>
       <c r="M6" t="n">
-        <v>0.004247644387495279</v>
+        <v>0.004247644387495276</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002490226182497032</v>
+        <v>0.002490226182497022</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002317515605447477</v>
+        <v>0.002317515605447432</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002742702535364356</v>
+        <v>0.002742702535364353</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002149049357613332</v>
+        <v>0.002149049357613336</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002863214221604711</v>
+        <v>0.002863214221604713</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002428424706828817</v>
+        <v>0.002428424706828813</v>
       </c>
       <c r="T6" t="n">
         <v>0.002592250731295093</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00275637844237203</v>
+        <v>0.002756378442372028</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002046850405256985</v>
+        <v>0.002046850405256984</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002999702324603123</v>
+        <v>0.002999702324603122</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002779823794151268</v>
+        <v>0.002779823794151271</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002464609751280777</v>
+        <v>0.002464609751280748</v>
       </c>
       <c r="Z6" t="n">
         <v>0.002177209333175873</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003058822275566636</v>
+        <v>0.003058822275566638</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002997827926142918</v>
+        <v>0.002997827926142916</v>
       </c>
     </row>
     <row r="7">
@@ -2746,22 +2746,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00252274401005906</v>
+        <v>0.002522744010059053</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00208803065122309</v>
+        <v>0.002088030651223089</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002544748015607756</v>
+        <v>0.002544748015607755</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00216811681721972</v>
+        <v>0.002168116817219723</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002241895704399979</v>
+        <v>0.002241895704399978</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002564302944497682</v>
+        <v>0.00256430294449768</v>
       </c>
       <c r="H7" t="n">
         <v>0.002792638311961327</v>
@@ -2770,61 +2770,61 @@
         <v>0.002549694033419046</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002656885847505078</v>
+        <v>0.002656885847505079</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003108470141349257</v>
+        <v>0.003108470141349256</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00261951355642758</v>
+        <v>0.002619513556427557</v>
       </c>
       <c r="M7" t="n">
-        <v>0.004039663325854803</v>
+        <v>0.004039663325854805</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002639514307935717</v>
+        <v>0.002639514307935715</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002467485534560383</v>
+        <v>0.00246748553456038</v>
       </c>
       <c r="P7" t="n">
         <v>0.002528520707631258</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002300915756184072</v>
+        <v>0.00230091575618407</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002655233159964232</v>
+        <v>0.002655233159964231</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002580291105399552</v>
+        <v>0.002580291105399555</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002744117129865831</v>
+        <v>0.002744117129865828</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002907922265056208</v>
+        <v>0.002907922265056207</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002198716803827716</v>
+        <v>0.002198716803827723</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003126908178419002</v>
+        <v>0.003126908178419001</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00257184273251079</v>
+        <v>0.002571842732510794</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002599477704643794</v>
+        <v>0.002599477704643792</v>
       </c>
       <c r="Z7" t="n">
         <v>0.002329075731746609</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002850841213926153</v>
+        <v>0.002850841213926154</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003143681984572129</v>
+        <v>0.003143681984572128</v>
       </c>
     </row>
     <row r="8">
@@ -2840,13 +2840,13 @@
         <v>0.003049188878786274</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003505906243170942</v>
+        <v>0.00350590624317094</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002823835131722317</v>
+        <v>0.00282383513172232</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002718790590288315</v>
+        <v>0.002718790590288314</v>
       </c>
       <c r="G8" t="n">
         <v>0.003644406645120468</v>
@@ -2855,64 +2855,64 @@
         <v>0.003753796539524511</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003510852260982231</v>
+        <v>0.003510852260982228</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003618044075068262</v>
+        <v>0.003618044075068267</v>
       </c>
       <c r="K8" t="n">
         <v>0.004069628368912447</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00358067178399075</v>
+        <v>0.003580671783990763</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005000821553418062</v>
+        <v>0.005000821553418064</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003156014979729967</v>
+        <v>0.003156014979729966</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003106207571183866</v>
+        <v>0.00310620757118387</v>
       </c>
       <c r="P8" t="n">
         <v>0.003137289611659745</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002575715159877479</v>
+        <v>0.002575715159877481</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003616391387527418</v>
+        <v>0.003616391387527417</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003541449332962738</v>
+        <v>0.00354144933296274</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003705275357429017</v>
+        <v>0.003705275357429016</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003589192824004115</v>
+        <v>0.003589192824004116</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003002840047366674</v>
+        <v>0.003002840047366679</v>
       </c>
       <c r="W8" t="n">
-        <v>0.004088179139401911</v>
+        <v>0.004088179139401914</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002899216268623945</v>
+        <v>0.002899216268623953</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004130587346904026</v>
+        <v>0.004130587346904027</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002705950669766172</v>
+        <v>0.002705950669766173</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.00381199944148934</v>
+        <v>0.003811999441489343</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004704042474607186</v>
+        <v>0.004704042474607185</v>
       </c>
     </row>
     <row r="9">
@@ -2922,16 +2922,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003397038187723336</v>
+        <v>0.003397038187723342</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003346615559042383</v>
+        <v>0.003346615559042384</v>
       </c>
       <c r="D9" t="n">
         <v>0.003803332923427054</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003338008867062955</v>
+        <v>0.003338008867062957</v>
       </c>
       <c r="F9" t="n">
         <v>0.002614585808349611</v>
@@ -2943,61 +2943,61 @@
         <v>0.004051223219780626</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003808278941238342</v>
+        <v>0.003808278941238345</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003915470755324374</v>
+        <v>0.003915470755324376</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004367055049168554</v>
+        <v>0.004367055049168553</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003878098464246865</v>
+        <v>0.003878098464246864</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005298248233674107</v>
+        <v>0.005298248233674106</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003898099215755014</v>
+        <v>0.003898099215755015</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003853449278966805</v>
+        <v>0.003853449278966804</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003942181629554222</v>
+        <v>0.003942181629554223</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003559500501563221</v>
+        <v>0.003559500501563223</v>
       </c>
       <c r="R9" t="n">
         <v>0.003913818067783527</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003838876013218847</v>
+        <v>0.003838876013218855</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004002702037685127</v>
+        <v>0.004002702037685128</v>
       </c>
       <c r="U9" t="n">
         <v>0.004166829748762064</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003900764199362263</v>
+        <v>0.003900764199362266</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004385493086238299</v>
+        <v>0.0043854930862383</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003830427640330088</v>
+        <v>0.003830427640330092</v>
       </c>
       <c r="Y9" t="n">
         <v>0.00385806261246309</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003355967437244289</v>
+        <v>0.00335596743724429</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004109426121745451</v>
+        <v>0.004109426121745453</v>
       </c>
       <c r="AB9" t="n">
         <v>0.004402266892391427</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003316617511592942</v>
+        <v>0.003316617511592932</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003285301962709201</v>
+        <v>0.003285301962709199</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003340456897004079</v>
+        <v>0.003340456897004072</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003299573964464749</v>
+        <v>0.003299573964464743</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003300168901015922</v>
+        <v>0.003300168901015919</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00332914728506507</v>
+        <v>0.003329147285065061</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003343119817927473</v>
+        <v>0.003343119817927468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003342413216856811</v>
+        <v>0.003342413216856801</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00333802743921611</v>
+        <v>0.003338027439216104</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003345727235350128</v>
+        <v>0.003345727235350118</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003325926674888858</v>
+        <v>0.003325926674888853</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003438825901471511</v>
+        <v>0.003438825901471509</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003317893642221031</v>
+        <v>0.003317893642221022</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004483032585960682</v>
+        <v>0.004483032585960683</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003326742528265095</v>
+        <v>0.003326742528265088</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003301678318412119</v>
+        <v>0.003301678318412109</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003329423010886069</v>
+        <v>0.003329423010886054</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003328735253645588</v>
+        <v>0.003328735253645571</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003336261731448306</v>
+        <v>0.003336261731448297</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006186464065030507</v>
+        <v>0.006186464065030504</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003306256002060773</v>
+        <v>0.003306256002060766</v>
       </c>
       <c r="W2" t="n">
         <v>0.00656273681793062</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003359270080270011</v>
+        <v>0.003359270080270002</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003369964157403137</v>
+        <v>0.003369964157403128</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005237603456321885</v>
+        <v>0.00523760345632188</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003358726008804845</v>
+        <v>0.003358726008804836</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003376476269240986</v>
+        <v>0.003376476269240984</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003134221835546612</v>
+        <v>0.003146281125494159</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002931993128263949</v>
+        <v>0.002937190275504576</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003306594766251447</v>
+        <v>0.003324876142654231</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003013562145904637</v>
+        <v>0.003021358482760571</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003018363473734883</v>
+        <v>0.003026447282647583</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003223224000201302</v>
+        <v>0.003238423799710496</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003327222379910584</v>
+        <v>0.003346299872884993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003321074223440315</v>
+        <v>0.003339885165820426</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003287894566393696</v>
+        <v>0.003305457410323382</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003341338568619198</v>
+        <v>0.003360932351501605</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003201515409205818</v>
+        <v>0.003215984892009903</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00400831540181013</v>
+        <v>0.00405159874959123</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003144800061043331</v>
+        <v>0.003157304350892836</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005031636533560011</v>
+        <v>0.005042433619533152</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003206072030848678</v>
+        <v>0.003220636605244975</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00302873352439309</v>
+        <v>0.003037149323561576</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003228443526636192</v>
+        <v>0.00324397906981507</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00322048570101794</v>
+        <v>0.003235617460395505</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003276836098375428</v>
+        <v>0.003294062273267666</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008010854617689734</v>
+        <v>0.008029350149526071</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003060069224933974</v>
+        <v>0.003069551001089843</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008815067586847724</v>
+        <v>0.008841972490142258</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003440713960002894</v>
+        <v>0.003463751812135399</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003515904304043754</v>
+        <v>0.003541533694444367</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006277374916751477</v>
+        <v>0.006288200529796749</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003435987969260479</v>
+        <v>0.00345876321721382</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003563428338212674</v>
+        <v>0.003590723864211039</v>
       </c>
     </row>
     <row r="4">
@@ -3342,58 +3342,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002023322420139959</v>
+        <v>0.002023322420139962</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001710799803739167</v>
+        <v>0.001710799803739169</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00229259924501786</v>
+        <v>0.002292599245017862</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001830807714907979</v>
+        <v>0.00183080771490798</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001837527796937905</v>
+        <v>0.001837527796937903</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002164851975488171</v>
+        <v>0.002164851975488176</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002322678161851767</v>
+        <v>0.002322678161851768</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002314696777706052</v>
+        <v>0.002314696777706054</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00226473862084375</v>
+        <v>0.002264738620843749</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002352130141111872</v>
+        <v>0.002352130141111873</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002128473701994012</v>
+        <v>0.00212847370199402</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003397626491836514</v>
+        <v>0.003397626491836515</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002037736902633321</v>
+        <v>0.00203773690263332</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001966767154760136</v>
+        <v>0.001966767154760135</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002137689141189748</v>
+        <v>0.002137689141189745</v>
       </c>
       <c r="Q4" t="n">
         <v>0.001854577360794159</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002167966425476462</v>
+        <v>0.002167966425476465</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002160197891061255</v>
+        <v>0.002160197891061259</v>
       </c>
       <c r="T4" t="n">
         <v>0.002245212920193913</v>
@@ -3402,22 +3402,22 @@
         <v>0.002294962393668578</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001903583873994921</v>
+        <v>0.00190358387399492</v>
       </c>
       <c r="W4" t="n">
         <v>0.002684824878582164</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002505102804498439</v>
+        <v>0.002505102804498441</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002610872017120813</v>
+        <v>0.002610872017120816</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001967111821771597</v>
+        <v>0.001967111821771602</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002498957267014142</v>
+        <v>0.002498957267014143</v>
       </c>
       <c r="AB4" t="n">
         <v>0.002693294435255649</v>
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009640566522394037</v>
+        <v>0.009640566522394062</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004678656628243508</v>
+        <v>0.004678656628243511</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0155588377222521</v>
+        <v>0.01555883772225211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006743981823721159</v>
+        <v>0.006743981823721152</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007150574563658585</v>
+        <v>0.00715057456365858</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01192430632710087</v>
+        <v>0.0119243063271008</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01693150447181838</v>
+        <v>0.01693150447181836</v>
       </c>
       <c r="I5" t="n">
         <v>0.01621764555819941</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01436774091523691</v>
+        <v>0.0143677409152369</v>
       </c>
       <c r="K5" t="n">
         <v>0.01512398668851522</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01194270281147611</v>
+        <v>0.01194270281147615</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03664125070594026</v>
+        <v>0.03664125070594032</v>
       </c>
       <c r="N5" t="n">
         <v>0.01065751711119262</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008382624199860958</v>
+        <v>0.008382624199860935</v>
       </c>
       <c r="P5" t="n">
         <v>0.01144953533113758</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.007243416217733878</v>
+        <v>0.007243416217733875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01366447967757794</v>
+        <v>0.01366447967757793</v>
       </c>
       <c r="S5" t="n">
         <v>0.01194687444844341</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0148152761612253</v>
+        <v>0.01481527616122533</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01475673581643882</v>
+        <v>0.0147567358164387</v>
       </c>
       <c r="V5" t="n">
-        <v>0.007463173877554228</v>
+        <v>0.007463173877554204</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02197792502869763</v>
+        <v>0.02197792502869766</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01923883746522213</v>
+        <v>0.01923883746522208</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02078771564154236</v>
+        <v>0.02078771564154239</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008395774620262869</v>
+        <v>0.008395774620262905</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0186933186605679</v>
+        <v>0.01869331866056792</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02425667963346368</v>
+        <v>0.02425667963346369</v>
       </c>
     </row>
     <row r="6">
@@ -3518,61 +3518,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002548230975754039</v>
+        <v>0.002548230975754037</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001903470386823866</v>
+        <v>0.001903470386823865</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00281750780063194</v>
+        <v>0.002817507800631943</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002355716270522058</v>
+        <v>0.002355716270522057</v>
       </c>
       <c r="F6" t="n">
         <v>0.002030198380022604</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00235752255857287</v>
+        <v>0.002357522558572873</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002515348744936467</v>
+        <v>0.002515348744936466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002507367360790753</v>
+        <v>0.002507367360790757</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002789647176457829</v>
+        <v>0.002789647176457832</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002877038696725947</v>
+        <v>0.002877038696725948</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002653382257608099</v>
+        <v>0.002653382257608104</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003590297074921209</v>
+        <v>0.00359029707492121</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002233277819289652</v>
+        <v>0.002233277819289648</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002495609333666924</v>
+        <v>0.002495609333666927</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00266698343611382</v>
+        <v>0.002666983436113821</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002379485916408236</v>
+        <v>0.00237948591640824</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002360637008561163</v>
+        <v>0.002360637008561164</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002685106446675333</v>
+        <v>0.002685106446675337</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002437883503278613</v>
+        <v>0.002437883503278616</v>
       </c>
       <c r="U6" t="n">
         <v>0.002502658284868106</v>
@@ -3581,22 +3581,22 @@
         <v>0.002428492429609</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003213617019748436</v>
+        <v>0.003213617019748437</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002697773387583141</v>
+        <v>0.002697773387583142</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002835361713163069</v>
+        <v>0.002835361713163064</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002492020377385676</v>
+        <v>0.00249202037738568</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003023865822628219</v>
+        <v>0.003023865822628223</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002891446221352508</v>
+        <v>0.002891446221352514</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002333569109483802</v>
+        <v>0.002333569109483806</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002021046493083011</v>
+        <v>0.002021046493083014</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002602845934361709</v>
+        <v>0.002602845934361708</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002141054404251824</v>
+        <v>0.002141054404251825</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002147774486281749</v>
+        <v>0.002147774486281751</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002475098664832016</v>
+        <v>0.00247509866483202</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002632924851195612</v>
+        <v>0.002632924851195614</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002624943467049897</v>
+        <v>0.0026249434670499</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002574985310187596</v>
+        <v>0.0025749853101876</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002662376830455716</v>
+        <v>0.002662376830455719</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002438720391337862</v>
+        <v>0.002438720391337865</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003707873181180359</v>
+        <v>0.003707873181180361</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002347983591977164</v>
+        <v>0.002347983591977167</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002276989870026556</v>
+        <v>0.002276989870026557</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002447911856456169</v>
+        <v>0.002447911856456171</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002164824050138003</v>
+        <v>0.002164824050138006</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002478213114820307</v>
+        <v>0.002478213114820311</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002470444580405099</v>
+        <v>0.002470444580405102</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002555459609537757</v>
+        <v>0.002555459609537758</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002619868268800419</v>
+        <v>0.002619868268800412</v>
       </c>
       <c r="V7" t="n">
         <v>0.002213830563338765</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002995071567926005</v>
+        <v>0.002995071567926008</v>
       </c>
       <c r="X7" t="n">
         <v>0.002815349493842284</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002936144014579479</v>
+        <v>0.002936144014579484</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00227735851111544</v>
+        <v>0.002277358511115447</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002809203956357986</v>
+        <v>0.002809203956357988</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00300354112459949</v>
+        <v>0.003003541124599495</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00268522112408901</v>
+        <v>0.002685221124089011</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00289186328392122</v>
+        <v>0.002891863283921222</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003473662725199916</v>
+        <v>0.003473662725199918</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002735431266323826</v>
+        <v>0.002735431266323827</v>
       </c>
       <c r="F8" t="n">
         <v>0.002580306305328546</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003453567654003581</v>
+        <v>0.003453567654003577</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003503741642033821</v>
+        <v>0.003503741642033822</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003495760257888107</v>
+        <v>0.003495760257888109</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003445802101025805</v>
+        <v>0.003445802101025803</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003533193621293924</v>
+        <v>0.003533193621293927</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003309537182176075</v>
+        <v>0.003309537182176077</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004578689972018751</v>
+        <v>0.004578689972018755</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002816360826654344</v>
+        <v>0.002816360826654348</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00285598496270568</v>
+        <v>0.002855984962705684</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00299979771590865</v>
+        <v>0.002999797715908657</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002414448337093095</v>
+        <v>0.002414448337093099</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003349029905658516</v>
+        <v>0.003349029905658519</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003341261371243308</v>
+        <v>0.003341261371243311</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003426276400375967</v>
+        <v>0.003426276400375969</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003237388626913749</v>
+        <v>0.00323738862691375</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002942459332433965</v>
+        <v>0.002942459332433963</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003865990388690211</v>
+        <v>0.003865990388690209</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003112556263621713</v>
+        <v>0.003112556263621711</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00432270091961366</v>
+        <v>0.004322700919613665</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002619366773544996</v>
+        <v>0.002619366773545</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003680020747196196</v>
+        <v>0.003680020747196198</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004416668935274068</v>
+        <v>0.004416668935274073</v>
       </c>
     </row>
     <row r="9">
@@ -3785,82 +3785,82 @@
         <v>0.003057841393205269</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003074337222952185</v>
+        <v>0.003074337222952187</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003656136664230882</v>
+        <v>0.003656136664230885</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003118408939213692</v>
+        <v>0.003118408939213696</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002442588035164251</v>
+        <v>0.002442588035164252</v>
       </c>
       <c r="G9" t="n">
         <v>0.00352838929124592</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003686215581064785</v>
+        <v>0.003686215581064787</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003678234196919075</v>
+        <v>0.003678234196919076</v>
       </c>
       <c r="J9" t="n">
         <v>0.003628276040056772</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003715667560324892</v>
+        <v>0.003715667560324893</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003492011121207038</v>
+        <v>0.003492011121207045</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004761163911049534</v>
+        <v>0.004761163911049538</v>
       </c>
       <c r="N9" t="n">
         <v>0.003401274321846343</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003439340718473411</v>
+        <v>0.003439340718473414</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003633976218086387</v>
+        <v>0.003633976218086392</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00321811467655191</v>
+        <v>0.003218114676551909</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003531503844689483</v>
+        <v>0.003531503844689488</v>
       </c>
       <c r="S9" t="n">
         <v>0.00352373531027428</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003608750339406935</v>
+        <v>0.003608750339406937</v>
       </c>
       <c r="U9" t="n">
-        <v>0.00367352512099643</v>
+        <v>0.003673525120996421</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003646800935305883</v>
+        <v>0.003646800935305884</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004048362297795183</v>
+        <v>0.004048362297795186</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003868640223711458</v>
+        <v>0.003868640223711463</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003989434744448657</v>
+        <v>0.003989434744448658</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003132280334338387</v>
+        <v>0.003132280334338392</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003862494686227164</v>
+        <v>0.003862494686227163</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.004056831854468669</v>
+        <v>0.004056831854468671</v>
       </c>
     </row>
   </sheetData>
@@ -4029,82 +4029,82 @@
         <v>0.00330590418563416</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003229515685633449</v>
+        <v>0.003229515685633447</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003313557578666684</v>
+        <v>0.003313557578666682</v>
       </c>
       <c r="E2" t="n">
         <v>0.003286538435546642</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003299277641273737</v>
+        <v>0.003299277641273734</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003318723271666533</v>
+        <v>0.003318723271666532</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003332878889314196</v>
+        <v>0.003332878889314192</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003330350468882828</v>
+        <v>0.003330350468882826</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003329372326336311</v>
+        <v>0.00332937232633631</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003353024359908782</v>
+        <v>0.00335302435990878</v>
       </c>
       <c r="L2" t="n">
         <v>0.003314889170598066</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003406075542261245</v>
+        <v>0.003406075542261243</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003300031737005482</v>
+        <v>0.003300031737005481</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004470964094324024</v>
+        <v>0.004470964094324021</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003316271659823881</v>
+        <v>0.00331627165982388</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003296397257213772</v>
+        <v>0.003296397257213773</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003327483103418398</v>
+        <v>0.003327483103418399</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003320068090045286</v>
+        <v>0.003320068090045284</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003334112376934622</v>
+        <v>0.003334112376934621</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006038464717937782</v>
+        <v>0.006038464717937779</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003314157669947535</v>
+        <v>0.003314157669947534</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006421708132379559</v>
+        <v>0.006421708132379553</v>
       </c>
       <c r="X2" t="n">
         <v>0.003364286402974885</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003408986430976448</v>
+        <v>0.003408986430976447</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005223148740070726</v>
+        <v>0.005223148740070724</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003355285620747234</v>
+        <v>0.003355285620747232</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003362216552624096</v>
+        <v>0.003362216552624094</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003092002815990394</v>
+        <v>0.003102677808857731</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002841270408921323</v>
+        <v>0.002846252260033545</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003148046152945961</v>
+        <v>0.003160810485846195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002954728321820256</v>
+        <v>0.002960546919784748</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003046446644744622</v>
+        <v>0.003055622929436601</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003182919864829147</v>
+        <v>0.00319680694357737</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00328848109203657</v>
+        <v>0.003306262648487408</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003268857279764533</v>
+        <v>0.003285915375078964</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003260126620213043</v>
+        <v>0.003276822570863148</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003427591170759427</v>
+        <v>0.003450347300301377</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003156635890078859</v>
+        <v>0.00316963042933072</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003807416272325705</v>
+        <v>0.003843726141627587</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003051700266141202</v>
+        <v>0.003060996261217803</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005012471294926193</v>
+        <v>0.005023023197780297</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003165446619528481</v>
+        <v>0.00317869023717588</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003025278968841025</v>
+        <v>0.003033667641560054</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003249171920513207</v>
+        <v>0.003265531614202837</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003192955567397095</v>
+        <v>0.003207211756236027</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003296065331273318</v>
+        <v>0.003314059888012902</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007789723768825297</v>
+        <v>0.007809044360432589</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00315022986861955</v>
+        <v>0.00316298706403757</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008516163497861809</v>
+        <v>0.008539750690488799</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003509977390233574</v>
+        <v>0.003535600377087561</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00382988414777688</v>
+        <v>0.003866670354337683</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00622784713849157</v>
+        <v>0.006237236331224292</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003446097986593052</v>
+        <v>0.003469310721775643</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003495383828472697</v>
+        <v>0.003520379432483449</v>
       </c>
     </row>
     <row r="4">
@@ -4202,37 +4202,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001964527801089946</v>
+        <v>0.001964527801089943</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001704990444898185</v>
+        <v>0.001704990444898183</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002050976396127044</v>
+        <v>0.002050976396127035</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001745782745166227</v>
+        <v>0.001745782745166225</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001889677934177942</v>
+        <v>0.001889677934177938</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00210932527489651</v>
+        <v>0.002109325274896505</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002269219488132671</v>
+        <v>0.002269219488132668</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002240659816229527</v>
+        <v>0.002240659816229523</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00222930285804557</v>
+        <v>0.002229302858045567</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002496771845872884</v>
+        <v>0.002496771845872882</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002066017339554525</v>
+        <v>0.002066017339554523</v>
       </c>
       <c r="M4" t="n">
         <v>0.003092406073240686</v>
@@ -4241,46 +4241,46 @@
         <v>0.00189819579236917</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001959419556286018</v>
+        <v>0.001959419556286012</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002081633191336579</v>
+        <v>0.002081633191336574</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001857142671178508</v>
+        <v>0.001857142671178506</v>
       </c>
       <c r="R4" t="n">
         <v>0.002208271604255526</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002124515617131546</v>
+        <v>0.00212451561713154</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002283152298237777</v>
+        <v>0.002283152298237774</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002340718883332262</v>
+        <v>0.002340718883332258</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002055804126239672</v>
+        <v>0.002055804126239669</v>
       </c>
       <c r="W4" t="n">
         <v>0.002539892849149279</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002623981803100292</v>
+        <v>0.002623981803100287</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003118787033606082</v>
+        <v>0.003118787033606075</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001906037005975646</v>
+        <v>0.001906037005975644</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002522313827274595</v>
+        <v>0.002522313827274592</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002594796501876437</v>
+        <v>0.002594796501876434</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008376892981279506</v>
+        <v>0.008376892981279508</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00446117576024834</v>
+        <v>0.004461175760248335</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01064211531463299</v>
+        <v>0.01064211531463288</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004995068614079032</v>
+        <v>0.00499506861407903</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007953623631553469</v>
+        <v>0.007953623631553488</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01064072146279436</v>
+        <v>0.01064072146279434</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01581724567926437</v>
+        <v>0.01581724567926438</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01449418103792267</v>
+        <v>0.01449418103792266</v>
       </c>
       <c r="J5" t="n">
         <v>0.01339177070788277</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01742221627576747</v>
+        <v>0.01742221627576742</v>
       </c>
       <c r="L5" t="n">
         <v>0.01043453323787387</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02959142123154678</v>
+        <v>0.0295914212315468</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008037737290349591</v>
+        <v>0.008037737290349574</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008185470603660679</v>
+        <v>0.008185470603660637</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01016339453911852</v>
+        <v>0.01016339453911856</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.007061946912116143</v>
+        <v>0.007061946912116156</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01432512771115226</v>
+        <v>0.01432512771115225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0111361974454281</v>
+        <v>0.01113619744542807</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01543183876210462</v>
+        <v>0.01543183876210459</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01489892225500795</v>
+        <v>0.01489892225500792</v>
       </c>
       <c r="V5" t="n">
-        <v>0.009672210809626023</v>
+        <v>0.009672210809625988</v>
       </c>
       <c r="W5" t="n">
         <v>0.01932678398262727</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02071296609664262</v>
+        <v>0.02071296609664259</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03009934645958444</v>
+        <v>0.03009934645958438</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00707861697717161</v>
+        <v>0.007078616977171607</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01910116819241442</v>
+        <v>0.01910116819241443</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02192414713943928</v>
+        <v>0.02192414713943929</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002164186684349022</v>
+        <v>0.002164186684349017</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001904649328157262</v>
+        <v>0.001904649328157256</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00257862682267051</v>
+        <v>0.002578626822670499</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002273433171709695</v>
+        <v>0.002273433171709689</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002089336817437014</v>
+        <v>0.002089336817437013</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002308984158155585</v>
+        <v>0.002308984158155579</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00279686991467614</v>
+        <v>0.002796869914676135</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002440318699488605</v>
+        <v>0.0024403186994886</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002756953284589036</v>
+        <v>0.002756953284589032</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003024422272416353</v>
+        <v>0.003024422272416347</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002265676222813602</v>
+        <v>0.002265676222813599</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003292064956499765</v>
+        <v>0.00329206495649976</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002102187900770164</v>
+        <v>0.002102187900770185</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002212015865063073</v>
+        <v>0.00221201586506308</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002614993504130001</v>
+        <v>0.002614993504129995</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002384793097721974</v>
+        <v>0.00238479309772197</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002735922030798997</v>
+        <v>0.00273592203079899</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002324174500390618</v>
+        <v>0.002324174500390614</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002810802724781242</v>
+        <v>0.002810802724781243</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002878471458676398</v>
+        <v>0.002878471458676391</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002255463009498746</v>
+        <v>0.002255463009498744</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002763773595953442</v>
+        <v>0.002763773595953437</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002823640686359367</v>
+        <v>0.002823640686359363</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003353327415884841</v>
+        <v>0.003353327415884843</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002105695889234721</v>
+        <v>0.002105695889234717</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003049964253818058</v>
+        <v>0.003049964253818056</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002799177461729485</v>
+        <v>0.002799177461729478</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002269883664683243</v>
+        <v>0.002269883664683241</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002010346308491483</v>
+        <v>0.002010346308491479</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002356332259720341</v>
+        <v>0.002356332259720332</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002051138608759525</v>
+        <v>0.002051138608759522</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002195033797771242</v>
+        <v>0.002195033797771239</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002414681138489809</v>
+        <v>0.002414681138489807</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002574575351725969</v>
+        <v>0.002574575351725966</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002546015679822827</v>
+        <v>0.002546015679822823</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002534658721638865</v>
+        <v>0.002534658721638864</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002802127709466182</v>
+        <v>0.002802127709466178</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002371373203147824</v>
+        <v>0.002371373203147823</v>
       </c>
       <c r="M7" t="n">
         <v>0.003397761936833985</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00220355165596247</v>
+        <v>0.002203551655962467</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002264751284192894</v>
+        <v>0.002264751284192886</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002386964919243448</v>
+        <v>0.002386964919243444</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002162498534771806</v>
+        <v>0.002162498534771805</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002513627467848825</v>
+        <v>0.002513627467848824</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002429871480724844</v>
+        <v>0.002429871480724839</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002588508161831074</v>
+        <v>0.002588508161831072</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002655816451862685</v>
+        <v>0.002655816451862681</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00236115998983297</v>
+        <v>0.002361159989832967</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002845248712742581</v>
+        <v>0.002845248712742575</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002929337666693588</v>
+        <v>0.002929337666693585</v>
       </c>
       <c r="Y7" t="n">
         <v>0.003434245046000041</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002211392869568944</v>
+        <v>0.002211392869568941</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002827669690867892</v>
+        <v>0.00282766969086789</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.002900152365469737</v>
+        <v>0.002900152365469731</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002616039765353167</v>
+        <v>0.002616039765353164</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002867765195700914</v>
+        <v>0.002867765195700908</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003213751146929773</v>
+        <v>0.003213751146929758</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002636325143619875</v>
+        <v>0.002636325143619872</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002620838665241344</v>
+        <v>0.00262083866524134</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003378113694993086</v>
+        <v>0.003378113694993081</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003431994238935397</v>
+        <v>0.003431994238935396</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003403434567032258</v>
+        <v>0.003403434567032253</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003392077608848298</v>
+        <v>0.003392077608848292</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003659546596675613</v>
+        <v>0.003659546596675607</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003228792090357255</v>
+        <v>0.00322879209035725</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004255180824043673</v>
+        <v>0.004255180824043667</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002664656350998083</v>
+        <v>0.002664656350998077</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002834790695631443</v>
+        <v>0.002834790695631436</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002930307715745771</v>
+        <v>0.002930307715745766</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002408179829119819</v>
+        <v>0.002408179829119814</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003371046355058261</v>
+        <v>0.003371046355058252</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003287290367934276</v>
+        <v>0.003287290367934267</v>
       </c>
       <c r="T8" t="n">
-        <v>0.003445927049040507</v>
+        <v>0.003445927049040504</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003263794609500858</v>
+        <v>0.003263794609500853</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003078555580180913</v>
+        <v>0.003078555580180908</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003702768076913208</v>
+        <v>0.003702768076913202</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003221877210810631</v>
+        <v>0.003221877210810626</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004799555021434919</v>
+        <v>0.004799555021434912</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002548052001578453</v>
+        <v>0.002548052001578449</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003685088578077322</v>
+        <v>0.003685088578077316</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00429162798352947</v>
+        <v>0.004291627983529463</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002919852164481522</v>
+        <v>0.002919852164481521</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002966864694683608</v>
+        <v>0.002966864694683605</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003312850645912472</v>
+        <v>0.003312850645912454</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002936906471115695</v>
+        <v>0.002936906471115689</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002444871133002974</v>
+        <v>0.002444871133002969</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003371199446093594</v>
+        <v>0.003371199446093587</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003531093737918095</v>
+        <v>0.00353109373791809</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00350253406601495</v>
+        <v>0.003502534066014947</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003491177107830992</v>
+        <v>0.003491177107830987</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003758646095658309</v>
+        <v>0.003758646095658303</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00332789158933995</v>
+        <v>0.003327891589339944</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004354280323026113</v>
+        <v>0.004354280323026111</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003160070042154596</v>
+        <v>0.003160070042154591</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003322883932397134</v>
+        <v>0.003322883932397123</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003467191694022118</v>
+        <v>0.003467191694022109</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003119016842375593</v>
+        <v>0.003119016842375588</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003470145854040949</v>
+        <v>0.003470145854040946</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003386389866916968</v>
+        <v>0.003386389866916959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003545026548023204</v>
+        <v>0.003545026548023195</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003612695281918355</v>
+        <v>0.003612695281918347</v>
       </c>
       <c r="V9" t="n">
-        <v>0.00367142991066919</v>
+        <v>0.003671429910669184</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003801767098934707</v>
+        <v>0.003801767098934701</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003885856052885715</v>
+        <v>0.003885856052885709</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00439076343219218</v>
+        <v>0.004390763432192167</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002983088902538508</v>
+        <v>0.002983088902538504</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003784188077060017</v>
+        <v>0.003784188077060011</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.003856670751661862</v>
+        <v>0.003856670751661853</v>
       </c>
     </row>
   </sheetData>
@@ -4889,19 +4889,19 @@
         <v>0.003226329501510926</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003212803043884234</v>
+        <v>0.003212803043884233</v>
       </c>
       <c r="D2" t="n">
         <v>0.003244996560040805</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003228106496477423</v>
+        <v>0.003228106496477424</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003224772793366714</v>
+        <v>0.003224772793366713</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003232977691227173</v>
+        <v>0.003232977691227174</v>
       </c>
       <c r="H2" t="n">
         <v>0.003253448514126251</v>
@@ -4916,16 +4916,16 @@
         <v>0.003262895626701891</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003248933820480923</v>
+        <v>0.003248933820480922</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003277063452089621</v>
+        <v>0.003277063452089622</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003253611313723354</v>
+        <v>0.003253611313723355</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004366577387489541</v>
+        <v>0.00436657738748954</v>
       </c>
       <c r="P2" t="n">
         <v>0.003239340534660318</v>
@@ -4937,31 +4937,31 @@
         <v>0.003246735610912748</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003240598515710454</v>
+        <v>0.003240598515710455</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003238114836485959</v>
+        <v>0.00323811483648596</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006079447800872355</v>
+        <v>0.006079447800872356</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003226739323284043</v>
+        <v>0.003226739323284042</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006467001584163666</v>
+        <v>0.006467001584163671</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003249844294457746</v>
+        <v>0.003249844294457747</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003230755458696909</v>
+        <v>0.003230755458696911</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005154493456800696</v>
+        <v>0.005154493456800695</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003266519858147543</v>
+        <v>0.003266519858147544</v>
       </c>
       <c r="AB2" t="n">
         <v>0.003268306613645804</v>
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002876995985061856</v>
+        <v>0.002881594067571212</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002804436869752773</v>
+        <v>0.002806736678110015</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003011154884097253</v>
+        <v>0.003020547569215427</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002890043101837082</v>
+        <v>0.002895068940796651</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002866540906353593</v>
+        <v>0.002870813350706001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002923960918487435</v>
+        <v>0.002930224084400884</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003072456956607133</v>
+        <v>0.003084066621829429</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0030260057401794</v>
+        <v>0.003035934754310947</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002988799028318655</v>
+        <v>0.002997379148775012</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003137479855105603</v>
+        <v>0.003151399667956454</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003037277910485806</v>
+        <v>0.003047585296710277</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003240366349614838</v>
+        <v>0.003258034496670699</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003072016527493414</v>
+        <v>0.003083552791341156</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004779564047654003</v>
+        <v>0.004785098016613775</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002969554741580289</v>
+        <v>0.002977392655697236</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00295585293968509</v>
+        <v>0.002963285402006966</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003024146292417124</v>
+        <v>0.003034015037844371</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002977572134281719</v>
+        <v>0.002985759655278445</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002961637895839951</v>
+        <v>0.002969287187714035</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007751891449858581</v>
+        <v>0.007764095493399373</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002879912428710699</v>
+        <v>0.002884618435935694</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008646917803496778</v>
+        <v>0.008670839164988054</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003045622455279736</v>
+        <v>0.003056237036147183</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002908981671766458</v>
+        <v>0.002914730438638029</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006121545648834754</v>
+        <v>0.006128991931067249</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003164295484223336</v>
+        <v>0.003179061447109043</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003176983878767036</v>
+        <v>0.003192241560649707</v>
       </c>
     </row>
     <row r="4">
@@ -5065,34 +5065,34 @@
         <v>0.001656675535593346</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001552090287818646</v>
+        <v>0.001552090287818647</v>
       </c>
       <c r="D4" t="n">
         <v>0.001867528548959495</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001676747511197989</v>
+        <v>0.00167674751119799</v>
       </c>
       <c r="F4" t="n">
         <v>0.001639091800983336</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001731769896756715</v>
+        <v>0.001731769896756717</v>
       </c>
       <c r="H4" t="n">
         <v>0.001962997258445572</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001890652084354273</v>
+        <v>0.001890652084354274</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001833499296515821</v>
+        <v>0.001833499296515827</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002069706740873939</v>
+        <v>0.002069706740873938</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001912001716859921</v>
+        <v>0.001912001716859924</v>
       </c>
       <c r="M4" t="n">
         <v>0.002232837617629069</v>
@@ -5101,37 +5101,37 @@
         <v>0.001964836154786387</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001699172932095563</v>
+        <v>0.001699172932095562</v>
       </c>
       <c r="P4" t="n">
         <v>0.001803641140386679</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001781053038703689</v>
+        <v>0.001781053038703687</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001887171928561013</v>
+        <v>0.001887171928561012</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001817850615047855</v>
+        <v>0.001817850615047856</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001789796315658257</v>
+        <v>0.001789796315658259</v>
       </c>
       <c r="U4" t="n">
         <v>0.001975828308645614</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001658742380594802</v>
+        <v>0.001658742380594817</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002521472850207825</v>
+        <v>0.002521472850207824</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001922285939266858</v>
+        <v>0.001922285939266857</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001684851363130742</v>
+        <v>0.001684851363130743</v>
       </c>
       <c r="Z4" t="n">
         <v>0.00178503225963625</v>
@@ -5140,7 +5140,7 @@
         <v>0.002110644102281423</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002128266683396345</v>
+        <v>0.002128266683396344</v>
       </c>
     </row>
     <row r="5">
@@ -5150,82 +5150,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004282669601460416</v>
+        <v>0.004282669601460418</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002593556032749946</v>
+        <v>0.002593556032749947</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008787331491077324</v>
+        <v>0.008787331491077303</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004864970115404649</v>
+        <v>0.004864970115404653</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004314602842345231</v>
+        <v>0.004314602842345225</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005433631422805584</v>
+        <v>0.005433631422805617</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0111375044482548</v>
+        <v>0.01113750444825479</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009358149505842975</v>
+        <v>0.009358149505842968</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007535579556333254</v>
+        <v>0.007535579556333266</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01181949361131763</v>
+        <v>0.01181949361131764</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008528491745601299</v>
+        <v>0.008528491745601309</v>
       </c>
       <c r="M5" t="n">
         <v>0.01495200473673505</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01028113026333441</v>
+        <v>0.01028113026333444</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004940820988850902</v>
+        <v>0.004940820988850888</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006893725852103901</v>
+        <v>0.006893725852103914</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.006783926509543117</v>
+        <v>0.006783926509543112</v>
       </c>
       <c r="R5" t="n">
-        <v>0.009481156746267269</v>
+        <v>0.009481156746267302</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006628001240249609</v>
+        <v>0.006628001240249613</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007094124670844835</v>
+        <v>0.007094124670844841</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01050049396502914</v>
+        <v>0.01050049396502912</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004362921119756622</v>
+        <v>0.004362921119756627</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02094274406809762</v>
+        <v>0.02094274406809768</v>
       </c>
       <c r="X5" t="n">
-        <v>0.009749850293248798</v>
+        <v>0.009749850293248812</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005448956935830883</v>
+        <v>0.005448956935830876</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.006385593364224439</v>
+        <v>0.006385593364224436</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01312149345549724</v>
+        <v>0.01312149345549723</v>
       </c>
       <c r="AB5" t="n">
         <v>0.01419267880089739</v>
@@ -5241,52 +5241,52 @@
         <v>0.001837394528884004</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001732809281109306</v>
+        <v>0.001732809281109305</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002366602025157313</v>
+        <v>0.002366602025157317</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00217582098739581</v>
+        <v>0.002175820987395812</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001819810794273993</v>
+        <v>0.001819810794273994</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001912488890047374</v>
+        <v>0.001912488890047375</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002462070734643387</v>
+        <v>0.002462070734643394</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002389725560552094</v>
+        <v>0.002389725560552098</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002014218289806478</v>
+        <v>0.002014218289806483</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002568780217071767</v>
+        <v>0.002568780217071761</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002092720710150583</v>
+        <v>0.002092720710150584</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002731911093826879</v>
+        <v>0.002731911093826892</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002146758726700981</v>
+        <v>0.002146758726700997</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002206721120442722</v>
+        <v>0.002206721120442734</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002311731642930826</v>
+        <v>0.00231173164293083</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002280126514901502</v>
+        <v>0.002280126514901512</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002386245404758833</v>
+        <v>0.002386245404758835</v>
       </c>
       <c r="S6" t="n">
         <v>0.001998569608338514</v>
@@ -5295,28 +5295,28 @@
         <v>0.001970515308948917</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002178364696855437</v>
+        <v>0.002178364696855438</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002157815856792613</v>
+        <v>0.00215781585679264</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0030291894215026</v>
+        <v>0.003029189421502594</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002103004932557517</v>
+        <v>0.002103004932557515</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001902499909579235</v>
+        <v>0.001902499909579233</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001965751252926908</v>
+        <v>0.001965751252926907</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00260971757847924</v>
+        <v>0.002609717578479246</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002311904800867685</v>
+        <v>0.002311904800867684</v>
       </c>
     </row>
     <row r="7">
@@ -5326,40 +5326,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001957914062132385</v>
+        <v>0.001957914062132386</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001853328814357687</v>
+        <v>0.001853328814357686</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002168767075498535</v>
+        <v>0.002168767075498533</v>
       </c>
       <c r="E7" t="n">
         <v>0.001977986037737029</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001940330327522377</v>
+        <v>0.001940330327522375</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002033008423295756</v>
+        <v>0.002033008423295757</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002264235784984613</v>
+        <v>0.002264235784984611</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002191890610893315</v>
+        <v>0.002191890610893314</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002134737823054863</v>
+        <v>0.002134737823054866</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00237094526741298</v>
+        <v>0.002370945267412979</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002213240243398963</v>
+        <v>0.002213240243398964</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00253407614416811</v>
+        <v>0.002534076144168109</v>
       </c>
       <c r="N7" t="n">
         <v>0.002266074681325427</v>
@@ -5371,10 +5371,10 @@
         <v>0.00210485472084729</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002082291565242728</v>
+        <v>0.002082291565242727</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002188410455100052</v>
+        <v>0.002188410455100053</v>
       </c>
       <c r="S7" t="n">
         <v>0.002119089141586897</v>
@@ -5383,13 +5383,13 @@
         <v>0.002091034842197299</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002298454631300353</v>
+        <v>0.002298454631300352</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001959980907133855</v>
+        <v>0.001959980907133856</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002822711376746865</v>
+        <v>0.002822711376746864</v>
       </c>
       <c r="X7" t="n">
         <v>0.002223524465805897</v>
@@ -5398,10 +5398,10 @@
         <v>0.002007907284588948</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00208627078617529</v>
+        <v>0.002086270786175289</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002411882628820463</v>
+        <v>0.002411882628820464</v>
       </c>
       <c r="AB7" t="n">
         <v>0.002429505209935384</v>
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002308464204399946</v>
+        <v>0.002308464204399948</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002718159421567039</v>
+        <v>0.002718159421567041</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003033597682707885</v>
+        <v>0.003033597682707888</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002568977467874917</v>
+        <v>0.002568977467874919</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002370999355610803</v>
+        <v>0.002370999355610805</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003004478435069943</v>
+        <v>0.003004478435069945</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003129066392193963</v>
+        <v>0.003129066392193966</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003056721218102667</v>
+        <v>0.003056721218102666</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002999568430264212</v>
+        <v>0.002999568430264221</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003235775874622332</v>
+        <v>0.003235775874622333</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003078070850608315</v>
+        <v>0.003078070850608318</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0033989067513775</v>
+        <v>0.003398906751377502</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002732251890739137</v>
+        <v>0.002732251890739141</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002576142082753042</v>
+        <v>0.002576142082753043</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002653756101967351</v>
+        <v>0.002653756101967352</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002331773858521764</v>
+        <v>0.002331773858521766</v>
       </c>
       <c r="R8" t="n">
         <v>0.003053241062309404</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002983919748796247</v>
+        <v>0.002983919748796249</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00295586544940665</v>
+        <v>0.002955865449406652</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00291238780994815</v>
+        <v>0.002912387809948154</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002683905021214425</v>
+        <v>0.002683905021214439</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003687643053924523</v>
+        <v>0.003687643053924525</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002520141585042971</v>
+        <v>0.002520141585042972</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003383538780658424</v>
+        <v>0.003383538780658427</v>
       </c>
       <c r="Z8" t="n">
         <v>0.002427267904861626</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003276713236029815</v>
+        <v>0.003276713236029818</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003831544765370216</v>
+        <v>0.003831544765370217</v>
       </c>
     </row>
     <row r="9">
@@ -5502,13 +5502,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002713868601858374</v>
+        <v>0.002713868601858375</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002945242322058707</v>
+        <v>0.002945242322058708</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003260680583199553</v>
+        <v>0.003260680583199554</v>
       </c>
       <c r="E9" t="n">
         <v>0.002992361645961201</v>
@@ -5517,34 +5517,34 @@
         <v>0.002257766620358188</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003124922008973643</v>
+        <v>0.003124922008973642</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003356149292685631</v>
+        <v>0.003356149292685632</v>
       </c>
       <c r="I9" t="n">
         <v>0.003283804118594335</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003226651330755883</v>
+        <v>0.003226651330755886</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003462858775114001</v>
+        <v>0.003462858775114</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003305153751099983</v>
+        <v>0.003305153751099987</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00362598965186913</v>
+        <v>0.003625989651869129</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003357988189026447</v>
+        <v>0.003357988189026448</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003203661432240102</v>
+        <v>0.0032036614322401</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003332343394694762</v>
+        <v>0.003332343394694761</v>
       </c>
       <c r="Q9" t="n">
         <v>0.003174205150920613</v>
@@ -5556,25 +5556,25 @@
         <v>0.003211002649287918</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003182948349898322</v>
+        <v>0.00318294834989832</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003390797737804843</v>
+        <v>0.003390797737804841</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003439583738203369</v>
+        <v>0.003439583738203379</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003914624884447887</v>
+        <v>0.003914624884447886</v>
       </c>
       <c r="X9" t="n">
         <v>0.00331543797350692</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00309982079228997</v>
+        <v>0.003099820792289969</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002975630941788169</v>
+        <v>0.002975630941788168</v>
       </c>
       <c r="AA9" t="n">
         <v>0.003503796136521482</v>
@@ -5749,82 +5749,82 @@
         <v>0.003203157124925503</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003202265814776651</v>
+        <v>0.003202265814776653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003207073308294817</v>
+        <v>0.003207073308294819</v>
       </c>
       <c r="E2" t="n">
         <v>0.003207559156231922</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003208654191841092</v>
+        <v>0.003208654191841093</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003210425760057871</v>
+        <v>0.003210425760057873</v>
       </c>
       <c r="H2" t="n">
         <v>0.003219435711078192</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003217386316018049</v>
+        <v>0.003217386316018043</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003213594960971917</v>
+        <v>0.003213594960971914</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003209737658085061</v>
+        <v>0.003209737658085063</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003208714397689846</v>
+        <v>0.003208714397689837</v>
       </c>
       <c r="M2" t="n">
         <v>0.003203563584847784</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003214190321843344</v>
+        <v>0.00321419032184334</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004336420233918662</v>
+        <v>0.004336420233918661</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003210148671623853</v>
+        <v>0.003210148671623855</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003204134342765221</v>
+        <v>0.003204134342765222</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003216474166497749</v>
+        <v>0.003216474166497747</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003214329625848488</v>
+        <v>0.00321432962584849</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003208282079173163</v>
+        <v>0.003208282079173157</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006017985248705103</v>
+        <v>0.006017985248705096</v>
       </c>
       <c r="V2" t="n">
         <v>0.003212647091354777</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006410095202240108</v>
+        <v>0.006410095202240107</v>
       </c>
       <c r="X2" t="n">
         <v>0.003257151121246534</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003219683275015207</v>
+        <v>0.003219683275015206</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005130374855165396</v>
+        <v>0.005130374855165394</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003235624983846864</v>
+        <v>0.003235624983846866</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003199230045606319</v>
+        <v>0.003199230045606321</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002818863806694968</v>
+        <v>0.00282201997912049</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002827826414095609</v>
+        <v>0.002831482979853496</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002847054703364617</v>
+        <v>0.002851235567836599</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00285041722808163</v>
+        <v>0.002854652601265838</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002858426378305105</v>
+        <v>0.002863025158406024</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002870229526717494</v>
+        <v>0.002875205140289979</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002936010713859499</v>
+        <v>0.002943372263331501</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002920892212472485</v>
+        <v>0.002927702403853922</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002893072611641552</v>
+        <v>0.002898866959957002</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002865834438576835</v>
+        <v>0.002870686742374714</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00285809187919589</v>
+        <v>0.002862658492862332</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002827022924499086</v>
+        <v>0.002830529354159491</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002897643584197484</v>
+        <v>0.002903611665597272</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004745002173299882</v>
+        <v>0.004750706124347936</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002868503709066724</v>
+        <v>0.002873400691408342</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002825855615825407</v>
+        <v>0.00282928452571099</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002914558121625123</v>
+        <v>0.002921147366477736</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002897786643616907</v>
+        <v>0.002903750875701007</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002855672825783557</v>
+        <v>0.002860162717734097</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007464034105339277</v>
+        <v>0.007467137881433886</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002886121598401055</v>
+        <v>0.002891657287419838</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00840138461159347</v>
+        <v>0.008417873716349457</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003203678784297683</v>
+        <v>0.003220561272016429</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.002937046071546942</v>
+        <v>0.002944392602420139</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006079113115231733</v>
+        <v>0.006085911896520889</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003050802158548933</v>
+        <v>0.003062164776982711</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002793797267455031</v>
+        <v>0.002796094259464506</v>
       </c>
     </row>
     <row r="4">
@@ -5922,64 +5922,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001565712815233115</v>
+        <v>0.001565712815233116</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001586751920855377</v>
+        <v>0.001586751920855378</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001609947907922912</v>
+        <v>0.001609947907922911</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001615435783873586</v>
+        <v>0.001615435783873588</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001627804714820444</v>
+        <v>0.001627804714820446</v>
       </c>
       <c r="G4" t="n">
         <v>0.001647815392790584</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001749586934347354</v>
+        <v>0.001749586934347355</v>
       </c>
       <c r="I4" t="n">
         <v>0.001726438074374733</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00168331204872756</v>
+        <v>0.001683312048727561</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001640042964465173</v>
+        <v>0.001640042964465172</v>
       </c>
       <c r="L4" t="n">
         <v>0.001628484767578169</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001579563136744902</v>
+        <v>0.001579563136744903</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0016903378499415</v>
+        <v>0.001690337849941499</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001681034161503713</v>
+        <v>0.001681034161503714</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001644685551461406</v>
+        <v>0.001644685551461407</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001576750940275159</v>
+        <v>0.00157675094027516</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001716134925933446</v>
+        <v>0.001716134925933445</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0016919113527626</v>
+        <v>0.001691911352762602</v>
       </c>
       <c r="T4" t="n">
         <v>0.001623601531055886</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001550391944882778</v>
+        <v>0.001550391944882779</v>
       </c>
       <c r="V4" t="n">
         <v>0.001670997825559386</v>
@@ -5994,13 +5994,13 @@
         <v>0.001739878103686298</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001729995856654634</v>
+        <v>0.001729995856654635</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001932452217702934</v>
+        <v>0.001932452217702935</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001526140849835939</v>
+        <v>0.00152614084983594</v>
       </c>
     </row>
     <row r="5">
@@ -6010,82 +6010,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0029698369034193</v>
+        <v>0.002969836903419305</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003468632102654674</v>
+        <v>0.003468632102654684</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003877048216305484</v>
+        <v>0.003877048216305481</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003919698720438938</v>
+        <v>0.003919698720438937</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004238909345535129</v>
+        <v>0.004238909345535138</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004157200002165472</v>
+        <v>0.004157200002165491</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006722469125718626</v>
+        <v>0.006722469125718639</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006058145888499161</v>
+        <v>0.006058145888499172</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004906296917510893</v>
+        <v>0.004906296917510899</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004287099409985231</v>
+        <v>0.004287099409985233</v>
       </c>
       <c r="L5" t="n">
         <v>0.003854914434708589</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003332699103673531</v>
+        <v>0.003332699103673529</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005192330177218433</v>
+        <v>0.005192330177218446</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004733224005264929</v>
+        <v>0.004733224005264935</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004232320293976674</v>
+        <v>0.004232320293976678</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00317405902533017</v>
+        <v>0.003174059025330171</v>
       </c>
       <c r="R5" t="n">
-        <v>0.005967107501642879</v>
+        <v>0.005967107501642884</v>
       </c>
       <c r="S5" t="n">
         <v>0.004779067945490181</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00411390442355482</v>
+        <v>0.004113904423554822</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002945188366030437</v>
+        <v>0.002945188366030436</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004618924589016678</v>
+        <v>0.004618924589016686</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01299469170871717</v>
+        <v>0.01299469170871716</v>
       </c>
       <c r="X5" t="n">
         <v>0.01347536888895942</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.006392836239392069</v>
+        <v>0.006392836239392071</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005475903302949648</v>
+        <v>0.005475903302949649</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.009566933708210464</v>
+        <v>0.009566933708210459</v>
       </c>
       <c r="AB5" t="n">
         <v>0.002456907591272942</v>
@@ -6098,79 +6098,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002031851530353737</v>
+        <v>0.002031851530353738</v>
       </c>
       <c r="C6" t="n">
         <v>0.00176252156696087</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001785717554028403</v>
+        <v>0.001785717554028404</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001791205429979081</v>
+        <v>0.001791205429979082</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002093943429941066</v>
+        <v>0.002093943429941067</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002113954107911205</v>
+        <v>0.002113954107911206</v>
       </c>
       <c r="H6" t="n">
         <v>0.002215725649467977</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002192576789495354</v>
+        <v>0.002192576789495355</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002149450763848182</v>
+        <v>0.002149450763848183</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002106181679585794</v>
+        <v>0.002106181679585796</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001804254413683661</v>
+        <v>0.001804254413683662</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002045701851865523</v>
+        <v>0.002045701851865525</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001867564739625025</v>
+        <v>0.001867564739625026</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002152775980550281</v>
+        <v>0.002152775980550279</v>
       </c>
       <c r="P6" t="n">
         <v>0.001806496486660925</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002042889655395781</v>
+        <v>0.002042889655395782</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001891904572038938</v>
+        <v>0.001891904572038939</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002158050067883223</v>
+        <v>0.002158050067883225</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001799371177161379</v>
+        <v>0.00179937117716138</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001738666770202951</v>
+        <v>0.001738666770202952</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00184676747166488</v>
+        <v>0.001846767471664879</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002359021568997962</v>
+        <v>0.002359021568997963</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002641738557265263</v>
+        <v>0.002641738557265265</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001942755755853379</v>
+        <v>0.00194275575585338</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001905765502760127</v>
+        <v>0.001905765502760128</v>
       </c>
       <c r="AA6" t="n">
         <v>0.002398590932823557</v>
@@ -6186,31 +6186,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00183055330281173</v>
+        <v>0.001830553302811731</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001851592408433991</v>
+        <v>0.001851592408433993</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001874788395501525</v>
+        <v>0.001874788395501527</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001880276271452203</v>
+        <v>0.001880276271452204</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001892645202399059</v>
+        <v>0.001892645202399061</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001912655880369198</v>
+        <v>0.0019126558803692</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002014427421925969</v>
+        <v>0.00201442742192597</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001991278561953348</v>
+        <v>0.001991278561953349</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001948152536306175</v>
+        <v>0.001948152536306177</v>
       </c>
       <c r="K7" t="n">
         <v>0.001904883452043787</v>
@@ -6219,28 +6219,28 @@
         <v>0.001893325255156783</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001844403624323518</v>
+        <v>0.001844403624323519</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001955178337520115</v>
+        <v>0.001955178337520116</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001945851224649714</v>
+        <v>0.001945851224649715</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001909502614607409</v>
+        <v>0.00190950261460741</v>
       </c>
       <c r="Q7" t="n">
         <v>0.001841591427853774</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00198097541351206</v>
+        <v>0.001980975413512062</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001956751840341216</v>
+        <v>0.001956751840341218</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001888442018634501</v>
+        <v>0.001888442018634502</v>
       </c>
       <c r="U7" t="n">
         <v>0.001827411478287819</v>
@@ -6249,22 +6249,22 @@
         <v>0.001935838313138002</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002427423861687805</v>
+        <v>0.002427423861687808</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002440440329723256</v>
+        <v>0.002440440329723258</v>
       </c>
       <c r="Y7" t="n">
         <v>0.002017223770479594</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00199483634423325</v>
+        <v>0.001994836344233252</v>
       </c>
       <c r="AA7" t="n">
         <v>0.002197292705281549</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001790981337414554</v>
+        <v>0.001790981337414555</v>
       </c>
     </row>
     <row r="8">
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002140903425727512</v>
+        <v>0.002140903425727514</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002617150734932033</v>
+        <v>0.002617150734932034</v>
       </c>
       <c r="D8" t="n">
         <v>0.002640346721999567</v>
@@ -6286,73 +6286,73 @@
         <v>0.002403449657516283</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002273911443215481</v>
+        <v>0.002273911443215483</v>
       </c>
       <c r="G8" t="n">
         <v>0.002772604593224217</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00277998574842401</v>
+        <v>0.002779985748424009</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00275683688845139</v>
+        <v>0.002756836888451388</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002713710862804216</v>
+        <v>0.002713710862804218</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002670441778541827</v>
+        <v>0.002670441778541828</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002658883581654826</v>
+        <v>0.002658883581654824</v>
       </c>
       <c r="M8" t="n">
         <v>0.002609961950821511</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002367874151367028</v>
+        <v>0.002367874151367029</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002455540144835414</v>
+        <v>0.002455540144835416</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002395421922687117</v>
+        <v>0.002395421922687119</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002062482749378227</v>
+        <v>0.00206248274937823</v>
       </c>
       <c r="R8" t="n">
         <v>0.002746533740010102</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002722310166839258</v>
+        <v>0.002722310166839259</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002654000345132543</v>
+        <v>0.002654000345132542</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002370880297108534</v>
+        <v>0.002370880297108535</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002576722625288312</v>
+        <v>0.002576722625288311</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003193071648828999</v>
+        <v>0.003193071648829</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002703052387114998</v>
+        <v>0.002703052387114996</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003234983933677768</v>
+        <v>0.003234983933677769</v>
       </c>
       <c r="Z8" t="n">
         <v>0.002296730741144123</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002962851031779589</v>
+        <v>0.002962851031779591</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003032042695668886</v>
+        <v>0.003032042695668884</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002448022236157336</v>
+        <v>0.002448022236157338</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002752127408698357</v>
+        <v>0.002752127408698358</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002775323395765892</v>
+        <v>0.002775323395765893</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002715480923522618</v>
+        <v>0.002715480923522619</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002140635415547956</v>
+        <v>0.002140635415547955</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002813191069719202</v>
+        <v>0.002813191069719204</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002914962422190333</v>
+        <v>0.002914962422190337</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002891813562217715</v>
+        <v>0.002891813562217716</v>
       </c>
       <c r="J9" t="n">
         <v>0.002848687536570542</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002805418452308152</v>
+        <v>0.002805418452308154</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002793860255421149</v>
+        <v>0.002793860255421151</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002744938624587885</v>
+        <v>0.002744938624587886</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002855713337784482</v>
+        <v>0.002855713337784483</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00294021762502855</v>
+        <v>0.002940217625028553</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002924270599100355</v>
+        <v>0.002924270599100357</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002742126617203778</v>
+        <v>0.00274212661720378</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002881510413776427</v>
+        <v>0.002881510413776428</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002857286840605583</v>
+        <v>0.002857286840605584</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002788977018898868</v>
+        <v>0.002788977018898873</v>
       </c>
       <c r="U9" t="n">
-        <v>0.00272827261194044</v>
+        <v>0.002728272611940441</v>
       </c>
       <c r="V9" t="n">
         <v>0.00316302567144474</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003327958861952172</v>
+        <v>0.003327958861952173</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003340975329987624</v>
+        <v>0.003340975329987621</v>
       </c>
       <c r="Y9" t="n">
         <v>0.002917758770743962</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002724707752446194</v>
+        <v>0.002724707752446195</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003097827705545916</v>
+        <v>0.003097827705545918</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002691516337678921</v>
+        <v>0.002691516337678923</v>
       </c>
     </row>
   </sheetData>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003200314382715205</v>
+        <v>0.003200314382715204</v>
       </c>
       <c r="C2" t="n">
         <v>0.003146676956753528</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003202178785789363</v>
+        <v>0.003202178785789364</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003204711145734747</v>
+        <v>0.003204711145734745</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003200855999897919</v>
+        <v>0.003200855999897918</v>
       </c>
       <c r="G2" t="n">
         <v>0.003200345794037664</v>
@@ -6630,10 +6630,10 @@
         <v>0.003202663415594067</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003205269234102024</v>
+        <v>0.003205269234102026</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003199383976408975</v>
+        <v>0.003199383976408974</v>
       </c>
       <c r="L2" t="n">
         <v>0.003203009833688263</v>
@@ -6642,7 +6642,7 @@
         <v>0.003198095973605718</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003203268340742626</v>
+        <v>0.003203268340742625</v>
       </c>
       <c r="O2" t="n">
         <v>0.004343374196180436</v>
@@ -6660,31 +6660,31 @@
         <v>0.003205295932761966</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003199451576166169</v>
+        <v>0.003199451576166168</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005867325264571829</v>
+        <v>0.005867325264571828</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003209252937015435</v>
+        <v>0.003209252937015433</v>
       </c>
       <c r="W2" t="n">
         <v>0.006270125690586596</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003264757908465393</v>
+        <v>0.003264757908465394</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003211075654434979</v>
+        <v>0.003211075654434977</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005115434014533944</v>
+        <v>0.005115434014533943</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003231921333314055</v>
+        <v>0.003231921333314056</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00319733087983513</v>
+        <v>0.003197330879835129</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002838341418643539</v>
+        <v>0.002842360475658982</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002741203172972588</v>
+        <v>0.002744849777739062</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002852051611623186</v>
+        <v>0.002856587045205784</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002869719374767307</v>
+        <v>0.002874821797572262</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002842734987924612</v>
+        <v>0.002846948858935879</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00283851675034552</v>
+        <v>0.002842545193197257</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00288290928898215</v>
+        <v>0.00288855690026103</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002855662735340218</v>
+        <v>0.002860327580799792</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002873730784976933</v>
+        <v>0.002879017748202355</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002832025676012642</v>
+        <v>0.002835847789649806</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002857394993584254</v>
+        <v>0.002862109571376432</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002827551943452191</v>
+        <v>0.002831250125220823</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002859729002940514</v>
+        <v>0.002864526215923191</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004817424353753462</v>
+        <v>0.00482567902109563</v>
       </c>
       <c r="P3" t="n">
-        <v>0.002879125683356388</v>
+        <v>0.002884576527923777</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002820180331188601</v>
+        <v>0.002823581761882368</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00291008134850137</v>
+        <v>0.002916686810442287</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002873634653797973</v>
+        <v>0.002878911588400461</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00283263037528551</v>
+        <v>0.002836474897114759</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007230784180763664</v>
+        <v>0.007234353164563588</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002901765943313727</v>
+        <v>0.002908027838410473</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008114026554593793</v>
+        <v>0.008127656213943011</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003297257014338519</v>
+        <v>0.003317665292742566</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00291558160132475</v>
+        <v>0.00292234358706149</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006031790752752369</v>
+        <v>0.006037304014842786</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003064314842143805</v>
+        <v>0.003076330360289607</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002819461806741132</v>
+        <v>0.002822842429688747</v>
       </c>
     </row>
     <row r="4">
@@ -6785,40 +6785,40 @@
         <v>0.001601453873022864</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001583099373780075</v>
+        <v>0.001583099373780076</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001622513163413314</v>
+        <v>0.001622513163413316</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001651117333939518</v>
+        <v>0.001651117333939517</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001607571688257872</v>
+        <v>0.001607571688257874</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001601808678359979</v>
+        <v>0.00160180867835998</v>
       </c>
       <c r="H4" t="n">
         <v>0.001670672027465612</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001627987279998161</v>
+        <v>0.001627987279998162</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001657146840116052</v>
+        <v>0.001657146840116053</v>
       </c>
       <c r="K4" t="n">
         <v>0.001590944505785971</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001631900231732298</v>
+        <v>0.001631900231732299</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001584862265084385</v>
+        <v>0.001584862265084387</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001634820187830444</v>
+        <v>0.001634820187830445</v>
       </c>
       <c r="O4" t="n">
         <v>0.001793149348716569</v>
@@ -6827,37 +6827,37 @@
         <v>0.001666510904269226</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001572313417863537</v>
+        <v>0.001572313417863538</v>
       </c>
       <c r="R4" t="n">
         <v>0.001713655921930266</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001657722772427294</v>
+        <v>0.001657722772427295</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001591708076140914</v>
+        <v>0.001591708076140916</v>
       </c>
       <c r="U4" t="n">
         <v>0.001571744863242762</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001700693135238073</v>
+        <v>0.001700693135238075</v>
       </c>
       <c r="W4" t="n">
         <v>0.002031203764582525</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002329373141857785</v>
+        <v>0.002329373141857784</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001714178909147332</v>
+        <v>0.001714178909147333</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001668745384516074</v>
+        <v>0.001668745384516076</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00195846891995255</v>
+        <v>0.001958468919952553</v>
       </c>
       <c r="AB4" t="n">
         <v>0.001571125045037579</v>
@@ -6870,67 +6870,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003555464880473058</v>
+        <v>0.003555464880473059</v>
       </c>
       <c r="C5" t="n">
         <v>0.003426459468138562</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004137220961889085</v>
+        <v>0.004137220961889084</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004432829037260596</v>
+        <v>0.00443282903726059</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003937301764349793</v>
+        <v>0.003937301764349796</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003536423641592817</v>
+        <v>0.00353642364159282</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005211019065135088</v>
+        <v>0.005211019065135089</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00431296362449085</v>
+        <v>0.004312963624490853</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004558717648256086</v>
+        <v>0.00455871764825609</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003537812136235169</v>
+        <v>0.003537812136235175</v>
       </c>
       <c r="L5" t="n">
         <v>0.003998609247289536</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00349184087320601</v>
+        <v>0.003491840873206014</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004303681744092657</v>
+        <v>0.004303681744092662</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006502426126639893</v>
+        <v>0.006502426126639899</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004539186766126538</v>
+        <v>0.004539186766126544</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003170320406113945</v>
+        <v>0.003170320406113946</v>
       </c>
       <c r="R5" t="n">
-        <v>0.005977807765536217</v>
+        <v>0.005977807765536222</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004415760745438919</v>
+        <v>0.00441576074543892</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003614663075517383</v>
+        <v>0.00361466307551739</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003234982076396922</v>
+        <v>0.003234982076396925</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005147531557996549</v>
+        <v>0.005147531557996547</v>
       </c>
       <c r="W5" t="n">
         <v>0.01098212650132985</v>
@@ -6939,16 +6939,16 @@
         <v>0.01590077970804575</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005931518496719101</v>
+        <v>0.005931518496719086</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004491348736294407</v>
+        <v>0.004491348736294416</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01007354886389709</v>
+        <v>0.01007354886389712</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0033207346159095</v>
+        <v>0.003320734615909498</v>
       </c>
     </row>
     <row r="6">
@@ -6958,28 +6958,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002071261877721645</v>
+        <v>0.002071261877721648</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002052907378478858</v>
+        <v>0.002052907378478859</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002092321168112096</v>
+        <v>0.002092321168112097</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001830483134461876</v>
+        <v>0.001830483134461877</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002077379692956656</v>
+        <v>0.002077379692956658</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002071616683058762</v>
+        <v>0.002071616683058763</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002140480032164394</v>
+        <v>0.002140480032164395</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002097795284696941</v>
+        <v>0.002097795284696945</v>
       </c>
       <c r="J6" t="n">
         <v>0.001836512640638411</v>
@@ -6991,25 +6991,25 @@
         <v>0.00210170823643108</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002054670269783167</v>
+        <v>0.002054670269783168</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001815984160137025</v>
+        <v>0.001815984160137026</v>
       </c>
       <c r="O6" t="n">
         <v>0.002022942172717635</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002140936076319761</v>
+        <v>0.002140936076319766</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002042121422562319</v>
+        <v>0.00204212142256232</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002183463926629047</v>
+        <v>0.00218346392662905</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002127530777126076</v>
+        <v>0.002127530777126078</v>
       </c>
       <c r="T6" t="n">
         <v>0.001771073876663274</v>
@@ -7018,22 +7018,22 @@
         <v>0.002050381346321516</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001880058935760432</v>
+        <v>0.001880058935760435</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002504650367806453</v>
+        <v>0.002504650367806456</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002508738942380145</v>
+        <v>0.002508738942380143</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001923340490104532</v>
+        <v>0.001923340490104524</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001848111185038434</v>
+        <v>0.001848111185038433</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002428276924651332</v>
+        <v>0.002428276924651336</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001750097409066878</v>
@@ -7049,28 +7049,28 @@
         <v>0.001862371329058192</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001844016829815404</v>
+        <v>0.001844016829815405</v>
       </c>
       <c r="D7" t="n">
         <v>0.001883430619448643</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001912034789974846</v>
+        <v>0.001912034789974849</v>
       </c>
       <c r="F7" t="n">
         <v>0.001868489144293202</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001862726134395308</v>
+        <v>0.001862726134395309</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001931589483500941</v>
+        <v>0.001931589483500943</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001888904736033491</v>
+        <v>0.00188890473603349</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00191806429615138</v>
+        <v>0.001918064296151381</v>
       </c>
       <c r="K7" t="n">
         <v>0.0018518619618213</v>
@@ -7079,49 +7079,49 @@
         <v>0.001892817687767626</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001845779721119714</v>
+        <v>0.001845779721119715</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001895737643865771</v>
+        <v>0.001895737643865773</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002054043288529026</v>
+        <v>0.002054043288529027</v>
       </c>
       <c r="P7" t="n">
         <v>0.001927404844081684</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001833230873898865</v>
+        <v>0.001833230873898866</v>
       </c>
       <c r="R7" t="n">
         <v>0.001974573377965595</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001918640228462624</v>
+        <v>0.001918640228462623</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001852625532176243</v>
+        <v>0.001852625532176244</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001841216307083701</v>
+        <v>0.001841216307083703</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001961610591273401</v>
+        <v>0.001961610591273405</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002292121220617854</v>
+        <v>0.002292121220617855</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002590290597893114</v>
+        <v>0.002590290597893113</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001983924843562634</v>
+        <v>0.001983924843562635</v>
       </c>
       <c r="Z7" t="n">
         <v>0.001929662840551402</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002219386375987878</v>
+        <v>0.002219386375987881</v>
       </c>
       <c r="AB7" t="n">
         <v>0.001832042501072907</v>
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002168818868699684</v>
+        <v>0.002168818868699685</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002599773047011535</v>
+        <v>0.002599773047011538</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002639186836644773</v>
+        <v>0.002639186836644776</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002428547390320704</v>
+        <v>0.002428547390320706</v>
       </c>
       <c r="F8" t="n">
         <v>0.002244933724629983</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002711649432795075</v>
+        <v>0.002711649432795078</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002687345700697071</v>
+        <v>0.002687345700697074</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002644660953229618</v>
+        <v>0.002644660953229622</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002673820513347509</v>
+        <v>0.002673820513347511</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002607618179017429</v>
+        <v>0.00260761817901743</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002648573904963756</v>
+        <v>0.002648573904963758</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00260153593831577</v>
+        <v>0.002601535938315773</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002303204468052569</v>
+        <v>0.002303204468052571</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00255724657786194</v>
+        <v>0.002557246577861943</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002407146576929375</v>
+        <v>0.002407146576929376</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002051379003662357</v>
+        <v>0.002051379003662358</v>
       </c>
       <c r="R8" t="n">
         <v>0.002730329595161726</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002674396445658754</v>
+        <v>0.002674396445658755</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002608381749372373</v>
+        <v>0.002608381749372375</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002377750946753522</v>
+        <v>0.002377750946753524</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002594349445000734</v>
+        <v>0.002594349445000735</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003047965739035826</v>
+        <v>0.00304796573903583</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002849618760243729</v>
+        <v>0.002849618760243731</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003186085720553428</v>
+        <v>0.003186085720553431</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002227764240912392</v>
+        <v>0.002227764240912393</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002975142593184009</v>
+        <v>0.002975142593184012</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003057139201783388</v>
+        <v>0.003057139201783389</v>
       </c>
     </row>
     <row r="9">
@@ -7225,82 +7225,82 @@
         <v>0.002413525911467169</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0026584094279134</v>
+        <v>0.002658409427913403</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002697823217546638</v>
+        <v>0.002697823217546639</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002665673250415784</v>
+        <v>0.002665673250415787</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002076046063655107</v>
+        <v>0.002076046063655108</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002677118891925196</v>
+        <v>0.002677118891925198</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002745982081598936</v>
+        <v>0.002745982081598939</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002703297334131487</v>
+        <v>0.002703297334131488</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002732456894249376</v>
+        <v>0.002732456894249378</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002666254559919295</v>
+        <v>0.0026662545599193</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002707210285865623</v>
+        <v>0.002707210285865624</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00266017231921771</v>
+        <v>0.002660172319217712</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002710130241963768</v>
+        <v>0.002710130241963772</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002955696348835874</v>
+        <v>0.002955696348835876</v>
       </c>
       <c r="P9" t="n">
-        <v>0.002848030408732855</v>
+        <v>0.002848030408732858</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002647623631428755</v>
+        <v>0.002647623631428758</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002788965976063588</v>
+        <v>0.002788965976063592</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002733032826560621</v>
+        <v>0.002733032826560623</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00266701813027424</v>
+        <v>0.002667018130274243</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002655883395756059</v>
+        <v>0.002655883395756061</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0030797743717194</v>
+        <v>0.003079774371719406</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003106513818715848</v>
+        <v>0.003106513818715852</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003404683195991108</v>
+        <v>0.00340468319599111</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.002798317441660628</v>
+        <v>0.002798317441660631</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002585346386535226</v>
+        <v>0.002585346386535228</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003033778974085874</v>
+        <v>0.003033778974085879</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002646435099170904</v>
+        <v>0.002646435099170906</v>
       </c>
     </row>
   </sheetData>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00330103312869263</v>
+        <v>0.003301033128692633</v>
       </c>
       <c r="C2" t="n">
         <v>0.003269203903678956</v>
@@ -7475,76 +7475,76 @@
         <v>0.003309259911379373</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00328338628220362</v>
+        <v>0.003283386282203617</v>
       </c>
       <c r="F2" t="n">
         <v>0.003287154793886009</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003321043426853932</v>
+        <v>0.003321043426853929</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003335724834273241</v>
+        <v>0.00333572483427324</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00332058941915142</v>
+        <v>0.003320589419151416</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003324848329461825</v>
+        <v>0.003324848329461826</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003343013687723111</v>
+        <v>0.003343013687723112</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003322527254917436</v>
+        <v>0.003322527254917427</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003449939258140302</v>
+        <v>0.003449939258140303</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003336548977294383</v>
+        <v>0.003336548977294385</v>
       </c>
       <c r="O2" t="n">
         <v>0.004469498439892629</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003312373527760232</v>
+        <v>0.003312373527760236</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003295901285470403</v>
+        <v>0.003295901285470401</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003321647463559575</v>
+        <v>0.003321647463559577</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003308830169275876</v>
+        <v>0.003308830169275875</v>
       </c>
       <c r="T2" t="n">
         <v>0.00331955339351802</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006166478276812988</v>
+        <v>0.006166478276812985</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003288722855783608</v>
+        <v>0.003288722855783605</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006521467555446244</v>
+        <v>0.006521467555446247</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003336683120661157</v>
+        <v>0.003336683120661155</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003320375502600792</v>
+        <v>0.003320375502600793</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00522469188077719</v>
+        <v>0.005224691880777193</v>
       </c>
       <c r="AA2" t="n">
         <v>0.003341647030061297</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003360747616317324</v>
+        <v>0.003360747616317325</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003080763369064634</v>
+        <v>0.00309110258121722</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00288145008659637</v>
+        <v>0.002885069116115684</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003141589797680078</v>
+        <v>0.003154161664722621</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002955900461409974</v>
+        <v>0.002961814693035516</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002983320363719404</v>
+        <v>0.002990307307776361</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00322272976097397</v>
+        <v>0.00323807997420299</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003332157097353357</v>
+        <v>0.003351572521951173</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003222717904771259</v>
+        <v>0.003238193562700793</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003250910863569671</v>
+        <v>0.003267331931031843</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003379925909771049</v>
+        <v>0.003401040879201635</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00323449096518249</v>
+        <v>0.003250296172453017</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004138256697900531</v>
+        <v>0.004186523144068864</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003336019478256619</v>
+        <v>0.003355443837677461</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005011725889564577</v>
+        <v>0.005022169701003282</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00316171287472291</v>
+        <v>0.003174863777892256</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003045349396708972</v>
+        <v>0.003054508546606247</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003230875252167206</v>
+        <v>0.00324665037208755</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003135753966433195</v>
+        <v>0.003148077103661716</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003215234197730229</v>
+        <v>0.003230428886724588</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008005339518428517</v>
+        <v>0.008024627411415117</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002993247989893275</v>
+        <v>0.003000518918125134</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008667821071915632</v>
+        <v>0.008690629950885273</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003337338668994016</v>
+        <v>0.003356856685921996</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003219805245524523</v>
+        <v>0.003235115468846958</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006256602044053381</v>
+        <v>0.00626696881218541</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003371838114920101</v>
+        <v>0.003392502331258956</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003508756617001958</v>
+        <v>0.00353428158723921</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001953689468048869</v>
+        <v>0.001953689468048853</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001648509607715984</v>
+        <v>0.001648509607715985</v>
       </c>
       <c r="D4" t="n">
         <v>0.002046614763002649</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001754360219005062</v>
+        <v>0.00175436021900506</v>
       </c>
       <c r="F4" t="n">
         <v>0.001796927292058687</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002179714990972742</v>
+        <v>0.002179714990972745</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002345548241554905</v>
+        <v>0.0023455482415549</v>
       </c>
       <c r="I4" t="n">
         <v>0.002174586765118983</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002222179013804216</v>
+        <v>0.002222179013804213</v>
       </c>
       <c r="K4" t="n">
         <v>0.00242787919430944</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002196475511544631</v>
+        <v>0.002196475511544593</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003626396528851452</v>
+        <v>0.003626396528851455</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002354857316103231</v>
+        <v>0.002354857316103232</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001958871535043307</v>
+        <v>0.001958871535043309</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002081784492358762</v>
+        <v>0.00208178449235876</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001895722938089319</v>
+        <v>0.001895722938089316</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002186537863433569</v>
+        <v>0.002186537863433571</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002041760628252546</v>
+        <v>0.002041760628252544</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002162884378994395</v>
+        <v>0.002162884378994394</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002329653433703652</v>
+        <v>0.002329653433703651</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001811302018909323</v>
+        <v>0.001811302018909324</v>
       </c>
       <c r="W4" t="n">
         <v>0.002509273309448091</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002356372527139931</v>
+        <v>0.00235637252713992</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002148186272735926</v>
+        <v>0.002148186272735924</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001954473732869363</v>
+        <v>0.001954473732869358</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002412442167325682</v>
+        <v>0.002412442167325681</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002622535423733184</v>
+        <v>0.002622535423733187</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008784222007085739</v>
+        <v>0.008784222007085585</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003727277810263497</v>
+        <v>0.003727277810263501</v>
       </c>
       <c r="D5" t="n">
         <v>0.01171554366067629</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005617923167707249</v>
+        <v>0.005617923167707211</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006714115766596573</v>
+        <v>0.006714115766596568</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01258621627237767</v>
+        <v>0.0125862162723777</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01830532505926925</v>
+        <v>0.01830532505926928</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01428474498853451</v>
+        <v>0.01428474498853452</v>
       </c>
       <c r="J5" t="n">
-        <v>0.013968564154937</v>
+        <v>0.01396856415493699</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01749721696453695</v>
+        <v>0.01749721696453694</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01355440432645203</v>
+        <v>0.01355440432645143</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04028476197252166</v>
+        <v>0.04028476197252167</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01735815234726077</v>
+        <v>0.01735815234726079</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008704017980330507</v>
+        <v>0.008704017980330514</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01121318916699923</v>
+        <v>0.01121318916699924</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008362391156944884</v>
+        <v>0.008362391156944824</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01484776111403837</v>
+        <v>0.01484776111403843</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01008392091915375</v>
+        <v>0.01008392091915369</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01401367926765746</v>
+        <v>0.01401367926765743</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0164992522070806</v>
+        <v>0.01649925220708058</v>
       </c>
       <c r="V5" t="n">
-        <v>0.006342859922888442</v>
+        <v>0.006342859922888458</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02000440673349133</v>
+        <v>0.02000440673349128</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01758801927781768</v>
+        <v>0.01758801927781764</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01346827213136948</v>
+        <v>0.01346827213136946</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008858454427860386</v>
+        <v>0.008858454427860242</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01813194541120131</v>
+        <v>0.01813194541120128</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02414546866322453</v>
+        <v>0.02414546866322449</v>
       </c>
     </row>
     <row r="6">
@@ -7818,82 +7818,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002141141432502336</v>
+        <v>0.002141141432502327</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001835961572169449</v>
+        <v>0.001835961572169452</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002234066727456116</v>
+        <v>0.002234066727456117</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002294169315126245</v>
+        <v>0.002294169315126239</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00198437925651215</v>
+        <v>0.001984379256512153</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00271952408709392</v>
+        <v>0.002719524087093923</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002533000206008366</v>
+        <v>0.002533000206008367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002362038729572448</v>
+        <v>0.00236203872957245</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00240963097825768</v>
+        <v>0.002409630978257679</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002967688290430617</v>
+        <v>0.002967688290430614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002736284607665807</v>
+        <v>0.00273628460766575</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003813848493304919</v>
+        <v>0.00381384849330492</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002544660421663412</v>
+        <v>0.002544660421663402</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002506877309466921</v>
+        <v>0.002506877309466919</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002630335851458274</v>
+        <v>0.002630335851458272</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002083174902542784</v>
+        <v>0.002083174902542781</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002726346959554745</v>
+        <v>0.002726346959554749</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002229212592706009</v>
+        <v>0.002229212592706008</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002350336343447858</v>
+        <v>0.002350336343447861</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002893446736362105</v>
+        <v>0.002893446736362104</v>
       </c>
       <c r="V6" t="n">
         <v>0.001998753983362789</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002719738142745883</v>
+        <v>0.002719738142745879</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002896181623261106</v>
+        <v>0.002896181623261094</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002376011650361547</v>
+        <v>0.002376011650361552</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002494282828990542</v>
+        <v>0.002494282828990534</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002952251263446858</v>
+        <v>0.002952251263446855</v>
       </c>
       <c r="AB6" t="n">
         <v>0.002815365973469524</v>
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002282284868993958</v>
+        <v>0.002282284868993945</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001977105008661072</v>
+        <v>0.001977105008661073</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002375210163947739</v>
+        <v>0.002375210163947742</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00208295561995015</v>
+        <v>0.002082955619950146</v>
       </c>
       <c r="F7" t="n">
         <v>0.002125522693003775</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002508310391917832</v>
+        <v>0.002508310391917833</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002674143642499991</v>
+        <v>0.002674143642499989</v>
       </c>
       <c r="I7" t="n">
         <v>0.002503182166064071</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002550774414749303</v>
+        <v>0.0025507744147493</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002756474595254527</v>
+        <v>0.002756474595254525</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002525070912489719</v>
+        <v>0.002525070912489663</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003954991929796542</v>
+        <v>0.003954991929796543</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00268345271704832</v>
+        <v>0.002683452717048319</v>
       </c>
       <c r="O7" t="n">
         <v>0.002287441585052959</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002410354542368416</v>
+        <v>0.002410354542368409</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002224318339034406</v>
+        <v>0.002224318339034402</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002515133264378658</v>
+        <v>0.002515133264378659</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002370356029197632</v>
+        <v>0.002370356029197631</v>
       </c>
       <c r="T7" t="n">
         <v>0.002491479779939481</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002681839963888475</v>
+        <v>0.002681839963888473</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002139897419854412</v>
+        <v>0.002139897419854411</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002837868710393178</v>
+        <v>0.002837868710393179</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002684967928085018</v>
+        <v>0.002684967928085006</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.002500765880218283</v>
+        <v>0.002500765880218284</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00228306913381445</v>
+        <v>0.002283069133814447</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00274103756827077</v>
+        <v>0.002741037568270768</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.002951130824678274</v>
+        <v>0.002951130824678277</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002656929238236432</v>
+        <v>0.002656929238236418</v>
       </c>
       <c r="C8" t="n">
         <v>0.002904398196540977</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003302503351827642</v>
+        <v>0.003302503351827644</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002715979614213876</v>
+        <v>0.002715979614213874</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0025862632891512</v>
+        <v>0.002586263289151199</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003550198912447164</v>
+        <v>0.003550198912447171</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003601436830379893</v>
+        <v>0.003601436830379895</v>
       </c>
       <c r="I8" t="n">
         <v>0.003430475353943978</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003478067602629208</v>
+        <v>0.003478067602629207</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003683767783134434</v>
+        <v>0.003683767783134432</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003452364100369623</v>
+        <v>0.003452364100369592</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004882285117676545</v>
+        <v>0.004882285117676547</v>
       </c>
       <c r="N8" t="n">
         <v>0.003182350614129798</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002904091578209926</v>
+        <v>0.002904091578209925</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002998146865664198</v>
+        <v>0.002998146865664201</v>
       </c>
       <c r="Q8" t="n">
         <v>0.002490354602075852</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003442426452258564</v>
+        <v>0.003442426452258565</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00329764921707754</v>
+        <v>0.003297649217077538</v>
       </c>
       <c r="T8" t="n">
         <v>0.003418772967819389</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003339500737376323</v>
+        <v>0.003339500737376325</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00291582902874952</v>
+        <v>0.002915829028749521</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003765270508710064</v>
+        <v>0.003765270508710067</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00300165555293221</v>
+        <v>0.003001655552932202</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003977057693117425</v>
+        <v>0.003977057693117429</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002647447767608737</v>
+        <v>0.002647447767608732</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003668330756150673</v>
+        <v>0.003668330756150671</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.004455711914516579</v>
+        <v>0.004455711914516577</v>
       </c>
     </row>
     <row r="9">
@@ -8082,61 +8082,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00314328703524147</v>
+        <v>0.003143287035241453</v>
       </c>
       <c r="C9" t="n">
         <v>0.003213154427013781</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003611259582300448</v>
+        <v>0.003611259582300449</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003232445531465731</v>
+        <v>0.003232445531465726</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00249698605717354</v>
+        <v>0.002496986057173538</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003744359640171174</v>
+        <v>0.003744359640171175</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003910193060852698</v>
+        <v>0.003910193060852697</v>
       </c>
       <c r="I9" t="n">
         <v>0.00373923158441678</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003786823833102008</v>
+        <v>0.003786823833102006</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003992524013607231</v>
+        <v>0.003992524013607232</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003761120330842427</v>
+        <v>0.003761120330842366</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005191041348149249</v>
+        <v>0.005191041348149248</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003919502135401025</v>
+        <v>0.003919502135401023</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003647806296136218</v>
+        <v>0.003647806296136216</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003797750220329532</v>
+        <v>0.003797750220329527</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003460367587287747</v>
+        <v>0.003460367587287743</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003751182682731366</v>
+        <v>0.003751182682731364</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003606405447550337</v>
+        <v>0.003606405447550333</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00372752919829219</v>
+        <v>0.003727529198292187</v>
       </c>
       <c r="U9" t="n">
         <v>0.003918282459538719</v>
@@ -8145,19 +8145,19 @@
         <v>0.003808742566924738</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004073918128745887</v>
+        <v>0.004073918128745885</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003921017346437725</v>
+        <v>0.003921017346437712</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003736815298570991</v>
+        <v>0.003736815298570993</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003292998342106053</v>
+        <v>0.003292998342106045</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003977086986623477</v>
+        <v>0.003977086986623475</v>
       </c>
       <c r="AB9" t="n">
         <v>0.00418718024303098</v>
@@ -8329,34 +8329,34 @@
         <v>0.003234745904574626</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00323578098354788</v>
+        <v>0.003235780983547877</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003243407366450839</v>
+        <v>0.00324340736645084</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003240922408617848</v>
+        <v>0.003240922408617849</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003239102853297988</v>
+        <v>0.003239102853297993</v>
       </c>
       <c r="G2" t="n">
         <v>0.003280039563674103</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003276309221388649</v>
+        <v>0.003276309221388651</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003247409306034081</v>
+        <v>0.003247409306034082</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003262989610820787</v>
+        <v>0.00326298961082079</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003261182335648641</v>
+        <v>0.003261182335648643</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003260992711278936</v>
+        <v>0.003260992711278933</v>
       </c>
       <c r="M2" t="n">
         <v>0.00325103826571585</v>
@@ -8365,43 +8365,43 @@
         <v>0.003251264755288702</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004376447948163743</v>
+        <v>0.004376447948163749</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003264002171393228</v>
+        <v>0.003264002171393234</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003246537270668437</v>
+        <v>0.003246537270668436</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003257868115551186</v>
+        <v>0.003257868115551195</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003250483817423827</v>
+        <v>0.003250483817423832</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003249091421223743</v>
+        <v>0.003249091421223744</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00607200692916333</v>
+        <v>0.006072006929163339</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003247776025582779</v>
+        <v>0.003247776025582781</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006470841923163715</v>
+        <v>0.006470841923163724</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003303372114104746</v>
+        <v>0.003303372114104749</v>
       </c>
       <c r="Y2" t="n">
         <v>0.003313003216046885</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005160174538989201</v>
+        <v>0.005160174538989203</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003267518107326785</v>
+        <v>0.003267518107326792</v>
       </c>
       <c r="AB2" t="n">
         <v>0.003445992551774768</v>
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002831647088678367</v>
+        <v>0.002834324643220922</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002852610048437324</v>
+        <v>0.002856188473419802</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00289376813438856</v>
+        <v>0.002898667318908582</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002875811930156296</v>
+        <v>0.002880010894479596</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002863042141641924</v>
+        <v>0.002866860723207876</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003152590866606402</v>
+        <v>0.003166600142775684</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003130308610336403</v>
+        <v>0.003143644275277246</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00292257845008261</v>
+        <v>0.002928502609199823</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00303251570681071</v>
+        <v>0.003042305138018685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003019662888816804</v>
+        <v>0.003029064285888411</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003018090744385707</v>
+        <v>0.003027381090426172</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00295253653364459</v>
+        <v>0.002959584704026793</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002949870208938537</v>
+        <v>0.002956740959164774</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004757510461446033</v>
+        <v>0.0047620812107888</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003039467499364587</v>
+        <v>0.003049442671005569</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002915602280729379</v>
+        <v>0.002921284963525836</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002997663502898768</v>
+        <v>0.003006263746441247</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002943239480104721</v>
+        <v>0.002949868507530726</v>
       </c>
       <c r="T3" t="n">
-        <v>0.002934498850625382</v>
+        <v>0.00294084466471647</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007573359740012504</v>
+        <v>0.007578722858119997</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002924103167335554</v>
+        <v>0.002930046043698524</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008548179512006211</v>
+        <v>0.008568072237382594</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003321646462235009</v>
+        <v>0.003341754876600464</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003390104764129173</v>
+        <v>0.003412550755695478</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006081278936107757</v>
+        <v>0.006087242539574241</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003065738556232275</v>
+        <v>0.003076694773129383</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004330239765477354</v>
+        <v>0.004385959003201537</v>
       </c>
     </row>
     <row r="4">
@@ -8502,49 +8502,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001565920760259637</v>
+        <v>0.001565920760259638</v>
       </c>
       <c r="C4" t="n">
         <v>0.001605126587621772</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001663755956620766</v>
+        <v>0.001663755956620765</v>
       </c>
       <c r="E4" t="n">
         <v>0.001635687214760073</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001615134500385445</v>
+        <v>0.001615134500385446</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002077533475900842</v>
+        <v>0.00207753347590084</v>
       </c>
       <c r="H4" t="n">
         <v>0.002035397543744392</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001708959705196666</v>
+        <v>0.001708959705196667</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001884521053202871</v>
+        <v>0.00188452105320287</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001864532410599771</v>
+        <v>0.00186453241059977</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001862390516112427</v>
+        <v>0.001862390516112426</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001758368383251327</v>
+        <v>0.001758368383251328</v>
       </c>
       <c r="N4" t="n">
         <v>0.001752508778121936</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001651612409203685</v>
+        <v>0.001651612409203686</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001896383752523416</v>
+        <v>0.001896383752523417</v>
       </c>
       <c r="Q4" t="n">
         <v>0.00169910966458562</v>
@@ -8553,34 +8553,34 @@
         <v>0.001827096769982453</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00174368772568895</v>
+        <v>0.001743687725688949</v>
       </c>
       <c r="T4" t="n">
         <v>0.00172795997007511</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001671028428015529</v>
+        <v>0.00167102842801553</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00171035142531664</v>
+        <v>0.001710351425316641</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002336972576236663</v>
+        <v>0.00233697257623666</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002341085366518432</v>
+        <v>0.002341085366518435</v>
       </c>
       <c r="Y4" t="n">
         <v>0.002434634085839973</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001714139163007249</v>
+        <v>0.001714139163007248</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00193609786630338</v>
+        <v>0.001936097866303379</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003923732860090635</v>
+        <v>0.003923732860090638</v>
       </c>
     </row>
     <row r="5">
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002613754700054466</v>
+        <v>0.002613754700054464</v>
       </c>
       <c r="C5" t="n">
         <v>0.003412495198054146</v>
@@ -8599,76 +8599,76 @@
         <v>0.004501547780412737</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003890611121537987</v>
+        <v>0.003890611121537988</v>
       </c>
       <c r="F5" t="n">
         <v>0.003639281777998304</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01046053833086613</v>
+        <v>0.01046053833086607</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01196510643328235</v>
+        <v>0.01196510643328234</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005429712060482437</v>
+        <v>0.005429712060482436</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007888858518490261</v>
+        <v>0.007888858518490239</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007551960627927539</v>
+        <v>0.007551960627927532</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007400697462158695</v>
+        <v>0.007400697462158701</v>
       </c>
       <c r="M5" t="n">
-        <v>0.006036388733717031</v>
+        <v>0.006036388733717035</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006083465492741448</v>
+        <v>0.006083465492741437</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003949775978896975</v>
+        <v>0.003949775978896977</v>
       </c>
       <c r="P5" t="n">
-        <v>0.007949110687948839</v>
+        <v>0.00794911068794883</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004865580680088304</v>
+        <v>0.004865580680088306</v>
       </c>
       <c r="R5" t="n">
-        <v>0.007747183945297141</v>
+        <v>0.007747183945297144</v>
       </c>
       <c r="S5" t="n">
         <v>0.005379616474447802</v>
       </c>
       <c r="T5" t="n">
-        <v>0.005721745392870323</v>
+        <v>0.005721745392870349</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004607467622441546</v>
+        <v>0.004607467622441553</v>
       </c>
       <c r="V5" t="n">
-        <v>0.004934023212492228</v>
+        <v>0.004934023212492226</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01638198058428289</v>
+        <v>0.01638198058428286</v>
       </c>
       <c r="X5" t="n">
         <v>0.01643300722757499</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01821233018004627</v>
+        <v>0.01821233018004625</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004907514427288382</v>
+        <v>0.004907514427288383</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.009261805974660397</v>
+        <v>0.009261805974660385</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04758008415668378</v>
+        <v>0.04758008415668386</v>
       </c>
     </row>
     <row r="6">
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002068040097981861</v>
+        <v>0.002068040097981862</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002107245925343997</v>
+        <v>0.002107245925343996</v>
       </c>
       <c r="D6" t="n">
         <v>0.00216587529434299</v>
@@ -8693,7 +8693,7 @@
         <v>0.001792197548972805</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002254596524488203</v>
+        <v>0.0022545965244882</v>
       </c>
       <c r="H6" t="n">
         <v>0.002212460592331752</v>
@@ -8702,25 +8702,25 @@
         <v>0.002211079042918891</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002386640390925095</v>
+        <v>0.002386640390925094</v>
       </c>
       <c r="K6" t="n">
         <v>0.00204159545918713</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002364509853834651</v>
+        <v>0.00236450985383465</v>
       </c>
       <c r="M6" t="n">
         <v>0.001935431431838687</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001931641943219428</v>
+        <v>0.001931641943219429</v>
       </c>
       <c r="O6" t="n">
         <v>0.002158867796677282</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002059629569011869</v>
+        <v>0.00205962956901187</v>
       </c>
       <c r="Q6" t="n">
         <v>0.00187617271317298</v>
@@ -8735,13 +8735,13 @@
         <v>0.00190502301866247</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002188386773378461</v>
+        <v>0.002188386773378462</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001887414473904</v>
+        <v>0.001887414473904001</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002535941769069054</v>
+        <v>0.002535941769069033</v>
       </c>
       <c r="X6" t="n">
         <v>0.002843204704240659</v>
@@ -8756,7 +8756,7 @@
         <v>0.002113160914890739</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004114172423847063</v>
+        <v>0.004114172423847061</v>
       </c>
     </row>
     <row r="7">
@@ -8766,61 +8766,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001847048583334613</v>
+        <v>0.001847048583334614</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00188625441069675</v>
+        <v>0.001886254410696751</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001944883779695743</v>
+        <v>0.001944883779695744</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001916815037835051</v>
+        <v>0.001916815037835052</v>
       </c>
       <c r="F7" t="n">
         <v>0.001896262323460423</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00235866129897582</v>
+        <v>0.002358661298975815</v>
       </c>
       <c r="H7" t="n">
         <v>0.00231652536681937</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001990087528271644</v>
+        <v>0.001990087528271645</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002165648876277849</v>
+        <v>0.002165648876277848</v>
       </c>
       <c r="K7" t="n">
         <v>0.002145660233674749</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002143518339187406</v>
+        <v>0.002143518339187407</v>
       </c>
       <c r="M7" t="n">
         <v>0.002039496206326306</v>
       </c>
       <c r="N7" t="n">
-        <v>0.002033636601196915</v>
+        <v>0.002033636601196916</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001932716598411291</v>
+        <v>0.001932716598411293</v>
       </c>
       <c r="P7" t="n">
         <v>0.002177487941731022</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001980237487660599</v>
+        <v>0.001980237487660597</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00210822459305743</v>
+        <v>0.002108224593057431</v>
       </c>
       <c r="S7" t="n">
         <v>0.002024815548763927</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002009087793150088</v>
+        <v>0.002009087793150087</v>
       </c>
       <c r="U7" t="n">
         <v>0.001967008796034572</v>
@@ -8832,19 +8832,19 @@
         <v>0.002618100399311638</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002622213189593413</v>
+        <v>0.002622213189593412</v>
       </c>
       <c r="Y7" t="n">
         <v>0.002731000916555658</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001995266986082226</v>
+        <v>0.001995266986082227</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002217225689378358</v>
+        <v>0.002217225689378357</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.004204860683165612</v>
+        <v>0.004204860683165613</v>
       </c>
     </row>
     <row r="8">
@@ -8857,82 +8857,82 @@
         <v>0.002175039177750454</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002695306311876392</v>
+        <v>0.002695306311876388</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002753935680875382</v>
+        <v>0.00275393568087538</v>
       </c>
       <c r="E8" t="n">
         <v>0.002469715983757483</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002299196647099967</v>
+        <v>0.002299196647099965</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00326746439587383</v>
+        <v>0.003267464395873822</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00312557726799901</v>
+        <v>0.003125577267999006</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002799139429451286</v>
+        <v>0.002799139429451282</v>
       </c>
       <c r="J8" t="n">
         <v>0.002974700777457488</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002954712134854388</v>
+        <v>0.002954712134854387</v>
       </c>
       <c r="L8" t="n">
         <v>0.002952570240367044</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002848548107505954</v>
+        <v>0.002848548107505955</v>
       </c>
       <c r="N8" t="n">
         <v>0.002469785509627348</v>
       </c>
       <c r="O8" t="n">
-        <v>0.002471366120549637</v>
+        <v>0.002471366120549638</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002691017879965263</v>
+        <v>0.002691017879965261</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002213688555844517</v>
+        <v>0.002213688555844518</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002917276494237072</v>
+        <v>0.002917276494237069</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002833867449943568</v>
+        <v>0.002833867449943565</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002818139694329728</v>
+        <v>0.002818139694329725</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002541366372807782</v>
+        <v>0.002541366372807781</v>
       </c>
       <c r="V8" t="n">
         <v>0.002668739703321035</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003427246842000094</v>
+        <v>0.003427246842000093</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002899754481915995</v>
+        <v>0.002899754481915998</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004017880102096653</v>
+        <v>0.004017880102096655</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002314321619829582</v>
+        <v>0.002314321619829581</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003026277590557997</v>
+        <v>0.003026277590557995</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.005516421344167304</v>
+        <v>0.005516421344167301</v>
       </c>
     </row>
     <row r="9">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00252894807322037</v>
+        <v>0.002528948073220372</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002875412702764018</v>
+        <v>0.002875412702764019</v>
       </c>
       <c r="D9" t="n">
         <v>0.00293404207176301</v>
@@ -8954,40 +8954,40 @@
         <v>0.002835059362799439</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002177105028995951</v>
+        <v>0.002177105028995954</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003347819735549332</v>
+        <v>0.003347819735549329</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003305683658886639</v>
+        <v>0.003305683658886638</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002979245820338912</v>
+        <v>0.00297924582033891</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003154807168345114</v>
+        <v>0.003154807168345116</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003134818525742018</v>
+        <v>0.003134818525742017</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003132676631254672</v>
+        <v>0.003132676631254675</v>
       </c>
       <c r="M9" t="n">
         <v>0.003028654498393574</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003022794893264181</v>
+        <v>0.003022794893264183</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003023723881463225</v>
+        <v>0.003023723881463231</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003290640461499432</v>
+        <v>0.003290640461499438</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002969395924234106</v>
+        <v>0.002969395924234109</v>
       </c>
       <c r="R9" t="n">
         <v>0.003097382885124699</v>
@@ -8996,31 +8996,31 @@
         <v>0.003013973840831196</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002998246085217356</v>
+        <v>0.002998246085217358</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002956553550798483</v>
+        <v>0.002956553550798484</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003335207659482919</v>
+        <v>0.003335207659482922</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003607258691378907</v>
+        <v>0.003607258691378908</v>
       </c>
       <c r="X9" t="n">
         <v>0.003611371481660681</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00372015920862293</v>
+        <v>0.003720159208622927</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002799175600334605</v>
+        <v>0.002799175600334607</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003206383981445627</v>
+        <v>0.003206383981445626</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.00519401897523288</v>
+        <v>0.005194018975232882</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
@@ -592,16 +592,16 @@
         <v>0.003325854392308248</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003376520947755859</v>
+        <v>0.003376520947755857</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003336145697251986</v>
+        <v>0.003336145697251985</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003358075331239024</v>
+        <v>0.003358075331239026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00337288529370808</v>
+        <v>0.003372885293708081</v>
       </c>
       <c r="H2" t="n">
         <v>0.003414882234511165</v>
@@ -610,61 +610,61 @@
         <v>0.00338438098140304</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00338116459956041</v>
+        <v>0.003381164599560409</v>
       </c>
       <c r="K2" t="n">
         <v>0.003438115978442368</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003383714169405925</v>
+        <v>0.003383714169405924</v>
       </c>
       <c r="M2" t="n">
         <v>0.003518215749416017</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003402459284957599</v>
+        <v>0.003402459284957597</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004595310309725841</v>
+        <v>0.00459531030972584</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003361866183865387</v>
+        <v>0.003361866183865388</v>
       </c>
       <c r="Q2" t="n">
         <v>0.003356670465772349</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003381856584698206</v>
+        <v>0.003381856584698209</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003374024143502306</v>
+        <v>0.003374024143502302</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003409254494469886</v>
+        <v>0.003409254494469884</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006310884754047709</v>
+        <v>0.006310884754047708</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00335061732814394</v>
+        <v>0.003350617328143941</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0066344575551508</v>
+        <v>0.006634457555150798</v>
       </c>
       <c r="X2" t="n">
         <v>0.003361961458760161</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003378153022955299</v>
+        <v>0.003378153022955301</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005300635787075625</v>
+        <v>0.005300635787075621</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003407770591347275</v>
+        <v>0.003407770591347276</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003426253513235702</v>
+        <v>0.0034262535132357</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005173193185592175</v>
+        <v>0.004100563691931931</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003961691179470646</v>
+        <v>0.003694464420056406</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005117216495113206</v>
+        <v>0.004099765970248397</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003866334260186541</v>
+        <v>0.003465027957725481</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004691204460332842</v>
+        <v>0.003953019829905867</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005013357689895717</v>
+        <v>0.004050889259355716</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006027327499623862</v>
+        <v>0.004427457359012806</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005303561615857977</v>
+        <v>0.00416678064163774</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005214043464944748</v>
+        <v>0.004124936150124952</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006551665083612664</v>
+        <v>0.00459915198762491</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00527149062891564</v>
+        <v>0.004145225567930355</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008421986744174591</v>
+        <v>0.005258924019994142</v>
       </c>
       <c r="N3" t="n">
-        <v>0.005714792419091484</v>
+        <v>0.004302696463979234</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006324027007734568</v>
+        <v>0.005292594304118698</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004756917878908695</v>
+        <v>0.003962513287600952</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004651244525401514</v>
+        <v>0.003934545401385306</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005247571912959068</v>
+        <v>0.004149214008199554</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005042525639100651</v>
+        <v>0.004060583895092704</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005882748865933963</v>
+        <v>0.004368269862347488</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008952627406102205</v>
+        <v>0.007304740045299154</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00450071479693986</v>
+        <v>0.003874247642343604</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009021168913183421</v>
+        <v>0.007554709528989441</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004776125288099192</v>
+        <v>0.003978758708696359</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005146873617279992</v>
+        <v>0.004102911818184784</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006615961001250065</v>
+        <v>0.005877377617382756</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005833530915536757</v>
+        <v>0.004341899960481444</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006268924775353511</v>
+        <v>0.004518290690470409</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01634231509053271</v>
+        <v>0.01634231509053267</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005650943396059399</v>
+        <v>0.005650943396059403</v>
       </c>
       <c r="D4" t="n">
         <v>0.01757581713115804</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007507745298858106</v>
+        <v>0.007507745298858136</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01343403382877253</v>
+        <v>0.01343403382877251</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01523547443083901</v>
+        <v>0.015235474430839</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02790530562040262</v>
+        <v>0.02790530562040263</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01968253669620083</v>
+        <v>0.01968253669620082</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01771665645376182</v>
+        <v>0.01771665645376184</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03211680044687302</v>
+        <v>0.03211680044687295</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01829246396146011</v>
+        <v>0.01829246396145991</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05205883368590174</v>
+        <v>0.05205883368590182</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02313503278494858</v>
+        <v>0.02313503278494859</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01542616598719583</v>
+        <v>0.01542616598719585</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01270902969991265</v>
+        <v>0.01270902969991264</v>
       </c>
       <c r="Q4" t="n">
         <v>0.01256159983914947</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01930826056945059</v>
+        <v>0.0193082605694506</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01553571865192518</v>
+        <v>0.0155357186519252</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02554102391940678</v>
+        <v>0.02554102391940674</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02555827519962863</v>
+        <v>0.02555827519962862</v>
       </c>
       <c r="V4" t="n">
         <v>0.01027060269093508</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02355229933704014</v>
+        <v>0.02355229933704016</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01391058005299624</v>
+        <v>0.01391058005299617</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01718771976715733</v>
+        <v>0.01718771976715735</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01203216925278256</v>
+        <v>0.01203216925278257</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0240961513127752</v>
+        <v>0.02409615131277516</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03067534928015713</v>
+        <v>0.03067534928015712</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003212822812300526</v>
+        <v>0.003212822812300513</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003260181495651695</v>
+        <v>0.00326018149565169</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003818403159784577</v>
+        <v>0.003818403159784575</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003019687916845894</v>
+        <v>0.00301968791684589</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003066779894910224</v>
+        <v>0.003066779894910217</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003910775928438569</v>
+        <v>0.003910775928438566</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004251711540749505</v>
+        <v>0.004251711540749499</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003907185855623618</v>
+        <v>0.003907185855623613</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00387053207322057</v>
+        <v>0.003870532073220568</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00451414736650273</v>
+        <v>0.004514147366502737</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003899653907367519</v>
+        <v>0.003899653907367513</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005409553843046648</v>
+        <v>0.005409553843046654</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02313503278494858</v>
+        <v>0.003612548878868469</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003462388048287231</v>
+        <v>0.003462388048287221</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003257513651655021</v>
+        <v>0.003257513651655012</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002824190179732116</v>
+        <v>0.002824190179732113</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003878671633562659</v>
+        <v>0.003878671633562658</v>
       </c>
       <c r="S5" t="n">
         <v>0.003790200607154</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004188143628094962</v>
+        <v>0.004188143628094966</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003971056893236998</v>
+        <v>0.003971056893236995</v>
       </c>
       <c r="V5" t="n">
         <v>0.003347714399158619</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004152481966369688</v>
+        <v>0.004152481966369679</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002942934747185879</v>
+        <v>0.00294293474718587</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004476423986979942</v>
+        <v>0.004476423986979945</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002955014706818317</v>
+        <v>0.002955014706818314</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004171382259695929</v>
+        <v>0.004171382259695934</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00504628273696994</v>
+        <v>0.005046282736969934</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003905824511852241</v>
+        <v>0.003905824511852236</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003781407922290551</v>
+        <v>0.003781407922290545</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004339629586423432</v>
+        <v>0.004339629586423425</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003774694442932675</v>
+        <v>0.003774694442932677</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003043765646716306</v>
+        <v>0.003043765646716305</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004298563014237523</v>
+        <v>0.004298563014237514</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004772937967388361</v>
+        <v>0.00477293796738836</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004428412282262473</v>
+        <v>0.004428412282262475</v>
       </c>
       <c r="J6" t="n">
-        <v>0.004391758499859424</v>
+        <v>0.004391758499859417</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005035373793141586</v>
+        <v>0.005035373793141587</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004420880334006372</v>
+        <v>0.00442088033400636</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005930780269685491</v>
+        <v>0.005930780269685485</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02313503278494858</v>
+        <v>0.004632615037341714</v>
       </c>
       <c r="O6" t="n">
-        <v>0.004501705794480618</v>
+        <v>0.004501705794480615</v>
       </c>
       <c r="P6" t="n">
-        <v>0.004364435036288329</v>
+        <v>0.004364435036288325</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.004115409073514058</v>
+        <v>0.004115409073514043</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004399898060201515</v>
+        <v>0.004399898060201506</v>
       </c>
       <c r="S6" t="n">
-        <v>0.004311427033792858</v>
+        <v>0.004311427033792856</v>
       </c>
       <c r="T6" t="n">
-        <v>0.004709370054733816</v>
+        <v>0.004709370054733809</v>
       </c>
       <c r="U6" t="n">
-        <v>0.004806529477773174</v>
+        <v>0.004806529477773178</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004589379982556633</v>
+        <v>0.004589379982556627</v>
       </c>
       <c r="W6" t="n">
-        <v>0.004673581922811077</v>
+        <v>0.004673581922811078</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004175173460521182</v>
+        <v>0.004175173460521176</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.004358064626592783</v>
+        <v>0.004358064626592772</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.003847296836213959</v>
+        <v>0.003847296836213948</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.004692608686334785</v>
+        <v>0.004692608686334779</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004895293225582237</v>
+        <v>0.004895293225582233</v>
       </c>
     </row>
   </sheetData>
@@ -1182,85 +1182,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003200573851843659</v>
+        <v>0.00320057385184366</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00315264210524225</v>
+        <v>0.003152642105242253</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003206575799650073</v>
+        <v>0.003206575799650075</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003202387975601705</v>
+        <v>0.003202387975601708</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003206798648925135</v>
+        <v>0.003206798648925136</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003209219060872483</v>
+        <v>0.003209219060872484</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003218863634937049</v>
+        <v>0.003218863634937051</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003212288965466983</v>
+        <v>0.003212288965466987</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003213842789914244</v>
+        <v>0.003213842789914237</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003220093937840513</v>
+        <v>0.003220093937840518</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003213819704704122</v>
+        <v>0.003213819704704123</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003206719776709561</v>
+        <v>0.003206719776709565</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003212076020843862</v>
+        <v>0.003212076020843858</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004343883978538649</v>
+        <v>0.004343883978538653</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003212332315054888</v>
+        <v>0.003212332315054883</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003205236817143532</v>
+        <v>0.003205236817143534</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003217087471392942</v>
+        <v>0.003217087471392943</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00321320432818096</v>
+        <v>0.003213204328180962</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003214902188449444</v>
+        <v>0.003214902188449447</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005890727067848788</v>
+        <v>0.005890727067848785</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003215653317197112</v>
+        <v>0.003215653317197113</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006296979299138668</v>
+        <v>0.006296979299138664</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003276556104814535</v>
+        <v>0.003276556104814537</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00324442104439951</v>
+        <v>0.003244421044399511</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005127629073673274</v>
+        <v>0.005127629073673279</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003247687489793038</v>
+        <v>0.003247687489793039</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003203763438100412</v>
+        <v>0.003203763438100414</v>
       </c>
     </row>
     <row r="3">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003555935659332359</v>
+        <v>0.003474972068942</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003591631892153947</v>
+        <v>0.003454135402532791</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003697413618036906</v>
+        <v>0.003524460947530894</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003327061880375209</v>
+        <v>0.003221116197643076</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003703646323710499</v>
+        <v>0.003526904838431945</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003755001214972025</v>
+        <v>0.003541342116383764</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003987458004377482</v>
+        <v>0.003627760170860664</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003831414237632153</v>
+        <v>0.003571612166514583</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003864016117864573</v>
+        <v>0.003579810111118651</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004011478108056163</v>
+        <v>0.003627596639473613</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003862888448899612</v>
+        <v>0.003577965159573518</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003718304050544166</v>
+        <v>0.00353155491880962</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003824576422639097</v>
+        <v>0.003568999711428821</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00503401701708073</v>
+        <v>0.004719475440955048</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003825926651337136</v>
+        <v>0.003565054951766454</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003665612176207343</v>
+        <v>0.003512639235616962</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003944584893460419</v>
+        <v>0.003612289236517106</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003847545525317839</v>
+        <v>0.003572146932573348</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003892115577300083</v>
+        <v>0.003593092340352302</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006503301371994142</v>
+        <v>0.006243216546268169</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003903491320192787</v>
+        <v>0.003590991077972972</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007841638461612187</v>
+        <v>0.006946380032892731</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005327613611511298</v>
+        <v>0.00407815300252786</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004575307030353278</v>
+        <v>0.003828684204512271</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005788834794242706</v>
+        <v>0.005493095241312104</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004650344967356727</v>
+        <v>0.003854181967761832</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003639031310635591</v>
+        <v>0.003505812547504791</v>
       </c>
     </row>
     <row r="4">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002413992351481189</v>
+        <v>0.002413992351481186</v>
       </c>
       <c r="C4" t="n">
         <v>0.003235911806793523</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003711872294442505</v>
+        <v>0.003711872294442507</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002796519331620905</v>
+        <v>0.002796519331620903</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00379986911565352</v>
+        <v>0.003799869115653519</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003955938359781449</v>
+        <v>0.003955938359781444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006503335720868772</v>
+        <v>0.006503335720868779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004951297368776425</v>
+        <v>0.004951297368776413</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004978854939300562</v>
+        <v>0.004978854939300559</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006074769450470769</v>
+        <v>0.006074769450470768</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004862316307673465</v>
+        <v>0.004862316307673463</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003937341535517468</v>
+        <v>0.003937341535517465</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004849682996968021</v>
+        <v>0.004849682996968017</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00509773713280495</v>
+        <v>0.005097737132804949</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004499590026756223</v>
+        <v>0.004499590026756219</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003369473708959754</v>
+        <v>0.00336947370895975</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00606454850772447</v>
+        <v>0.006064548507724467</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004679833623201133</v>
+        <v>0.004679833623201127</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005513198246749934</v>
+        <v>0.005513198246749937</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004520455105890234</v>
+        <v>0.004520455105890222</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00511841064983589</v>
+        <v>0.005118410649835877</v>
       </c>
       <c r="W4" t="n">
         <v>0.01313647206850884</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01728507861130471</v>
+        <v>0.01728507861130472</v>
       </c>
       <c r="Y4" t="n">
         <v>0.01138411152965549</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004777581656879601</v>
+        <v>0.004777581656879607</v>
       </c>
       <c r="AA4" t="n">
         <v>0.0119956617542838</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.003324952535378979</v>
+        <v>0.003324952535378978</v>
       </c>
     </row>
     <row r="5">
@@ -1446,34 +1446,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002117061982309945</v>
+        <v>0.002117061982309944</v>
       </c>
       <c r="C5" t="n">
         <v>0.00261868252540201</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002644799956035143</v>
+        <v>0.002644799956035142</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002352590364055102</v>
+        <v>0.002352590364055101</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002259027705800725</v>
+        <v>0.002259027705800724</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002770029028746198</v>
+        <v>0.002770029028746197</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002783596708285066</v>
+        <v>0.002783596708285064</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002709332792123247</v>
+        <v>0.002709332792123243</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002726601805733966</v>
+        <v>0.002726601805733962</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00279749354554698</v>
+        <v>0.002797493545546979</v>
       </c>
       <c r="L5" t="n">
         <v>0.002726623195981573</v>
@@ -1482,13 +1482,13 @@
         <v>0.002654858904137332</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004849682996968021</v>
+        <v>0.002350394548151586</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00249046815471077</v>
+        <v>0.002490468154710769</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002427250995305813</v>
+        <v>0.00242725099530581</v>
       </c>
       <c r="Q5" t="n">
         <v>0.002079342981781901</v>
@@ -1497,34 +1497,34 @@
         <v>0.002763534123978755</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002719672235065279</v>
+        <v>0.002719672235065278</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002738850347852143</v>
+        <v>0.002738850347852144</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002483455836918335</v>
+        <v>0.002483455836918333</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002619584720852446</v>
+        <v>0.002619584720852431</v>
       </c>
       <c r="W5" t="n">
         <v>0.003182062969016612</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002927081853337595</v>
+        <v>0.002927081853337593</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003529185017053578</v>
+        <v>0.003529185017053576</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002265398913110251</v>
+        <v>0.002265398913110246</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003109175408511762</v>
+        <v>0.003109175408511761</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003097016780524017</v>
+        <v>0.003097016780524015</v>
       </c>
     </row>
     <row r="6">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002358252379033496</v>
+        <v>0.002358252379033494</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002666823895395215</v>
+        <v>0.002666823895395213</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002692941326028349</v>
+        <v>0.002692941326028347</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002584039962424807</v>
+        <v>0.002584039962424808</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002080194359298246</v>
+        <v>0.002080194359298244</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002722798339853612</v>
+        <v>0.00272279833985361</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002831738078278269</v>
+        <v>0.002831738078278267</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002757474162116449</v>
+        <v>0.002757474162116448</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002774743175727166</v>
+        <v>0.002774743175727165</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002845634915540183</v>
+        <v>0.002845634915540182</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002774764565974777</v>
+        <v>0.002774764565974775</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002703000274130525</v>
+        <v>0.002703000274130522</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004849682996968021</v>
+        <v>0.002755068854638882</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002885612714715262</v>
+        <v>0.002885612714715261</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002865648433036208</v>
+        <v>0.002865648433036206</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002677817065012475</v>
+        <v>0.002677817065012474</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002811675493971957</v>
+        <v>0.002811675493971956</v>
       </c>
       <c r="S6" t="n">
         <v>0.002767813605058479</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002786991717845348</v>
+        <v>0.002786991717845346</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002756326360270811</v>
+        <v>0.002756326360270808</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003101687238085936</v>
+        <v>0.003101687238085927</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003230113947800149</v>
+        <v>0.003230113947800146</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003483401065391822</v>
+        <v>0.003483401065391819</v>
       </c>
       <c r="Y6" t="n">
         <v>0.003120420775145983</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002621113780321755</v>
+        <v>0.002621113780321751</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003157316778504968</v>
+        <v>0.003157316778504964</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002664709006303119</v>
+        <v>0.002664709006303117</v>
       </c>
     </row>
   </sheetData>
@@ -1778,34 +1778,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003335920147755508</v>
+        <v>0.003335920147755506</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003293565343382779</v>
+        <v>0.00329356534338278</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003337868187543567</v>
+        <v>0.003337868187543565</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003304524596611439</v>
+        <v>0.003304524596611437</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003311056325910803</v>
+        <v>0.003311056325910801</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003339599407772809</v>
+        <v>0.003339599407772805</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003359814199114128</v>
+        <v>0.003359814199114129</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003338306064159601</v>
+        <v>0.0033383060641596</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003347841798345835</v>
+        <v>0.003347841798345832</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003387775152342455</v>
+        <v>0.003387775152342452</v>
       </c>
       <c r="L2" t="n">
         <v>0.003344487266418565</v>
@@ -1814,46 +1814,46 @@
         <v>0.003471007868671442</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003346257955834303</v>
+        <v>0.003346257955834301</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004520400051220011</v>
+        <v>0.004520400051220009</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003336433832513159</v>
+        <v>0.003336433832513156</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003316281438625588</v>
+        <v>0.003316281438625587</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003347649563789792</v>
+        <v>0.00334764956378979</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003341014857950994</v>
+        <v>0.003341014857950995</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003355518563345608</v>
+        <v>0.003355518563345605</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006215219357105721</v>
+        <v>0.006215219357105719</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003307531705719523</v>
+        <v>0.00330753170571952</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006578255268157533</v>
+        <v>0.006578255268157528</v>
       </c>
       <c r="X2" t="n">
         <v>0.003340266913832582</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003342713469535263</v>
+        <v>0.003342713469535259</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005246978280084809</v>
+        <v>0.005246978280084811</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003364966968620436</v>
+        <v>0.003364966968620432</v>
       </c>
       <c r="AB2" t="n">
         <v>0.003391526398734105</v>
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004813443354065699</v>
+        <v>0.003956704107059999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003928457559288737</v>
+        <v>0.003659272156555891</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004876911394804323</v>
+        <v>0.003994638381413583</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003799112219053922</v>
+        <v>0.003425996184086969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004253652272377104</v>
+        <v>0.003776401041653964</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004899238279371427</v>
+        <v>0.003989233284899476</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005400134987823422</v>
+        <v>0.004183811029694054</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004889344047097044</v>
+        <v>0.004000440710179411</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005099927158456438</v>
+        <v>0.004064030702635569</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006036257960320731</v>
+        <v>0.004377796397533528</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005019540978826125</v>
+        <v>0.004037110004981698</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007981051055778086</v>
+        <v>0.005080358499364227</v>
       </c>
       <c r="N3" t="n">
-        <v>0.005067064050796538</v>
+        <v>0.004056796133555589</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005888850410704177</v>
+        <v>0.005104852815792604</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00482370929129501</v>
+        <v>0.003963456330406314</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004370907006992135</v>
+        <v>0.003815442646980734</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005110705411639325</v>
+        <v>0.004080013744676148</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004934614762938195</v>
+        <v>0.004000932089184631</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005289815972058316</v>
+        <v>0.004138472532666728</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008454466086512024</v>
+        <v>0.007080757570741736</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004160475062800538</v>
+        <v>0.003735719434610609</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009252382105193108</v>
+        <v>0.007587446769655524</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004931456846714062</v>
+        <v>0.004010840005006131</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004982055625112926</v>
+        <v>0.004023031870177819</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006347995535657436</v>
+        <v>0.005754535062298242</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00549782534704125</v>
+        <v>0.004202597773086547</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006118073018094288</v>
+        <v>0.0044440930505822</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01252050781210804</v>
+        <v>0.01252050781210795</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005315860459276887</v>
+        <v>0.005315860459276892</v>
       </c>
       <c r="D4" t="n">
-        <v>0.014541182022409</v>
+        <v>0.01454118202240895</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006689452933651375</v>
+        <v>0.006689452933651515</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008534279843587938</v>
+        <v>0.008534279843587952</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01353310346674112</v>
+        <v>0.0135331034667411</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02020710488480323</v>
+        <v>0.02020710488480325</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01479921114733889</v>
+        <v>0.0147992111473389</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01592777301711195</v>
+        <v>0.01592777301711197</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0240372643118251</v>
+        <v>0.02403726431182511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01520877716731812</v>
+        <v>0.0152087771673193</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04470927676428875</v>
+        <v>0.04470927676428881</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01598055496191954</v>
+        <v>0.01598055496191955</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01132167026494336</v>
+        <v>0.01132167026494339</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01282633602362164</v>
+        <v>0.01282633602362169</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009456776263102012</v>
+        <v>0.009456776263101978</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01714307537748686</v>
+        <v>0.01714307537748683</v>
       </c>
       <c r="S4" t="n">
         <v>0.01385913591485954</v>
       </c>
       <c r="T4" t="n">
-        <v>0.018503494736457</v>
+        <v>0.01850349473645701</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02024216284010716</v>
+        <v>0.02024216284010715</v>
       </c>
       <c r="V4" t="n">
-        <v>0.006882892436030911</v>
+        <v>0.0068828924360309</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0249700958616513</v>
+        <v>0.02497009586165132</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01483763317281942</v>
+        <v>0.01483763317281943</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01483150605425747</v>
+        <v>0.01483150605425751</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.009342713546569525</v>
+        <v>0.009342713546569646</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0197050125392648</v>
+        <v>0.01970501253926482</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02766699187266124</v>
+        <v>0.02766699187266143</v>
       </c>
     </row>
     <row r="5">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00291027437994759</v>
+        <v>0.002910274379947586</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003049188878786277</v>
+        <v>0.00304918887878628</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003505906243170943</v>
+        <v>0.003505906243170944</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002823835131722317</v>
+        <v>0.002823835131722332</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002718790590288318</v>
+        <v>0.00271879059028832</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003644406645120469</v>
+        <v>0.003644406645120472</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003753796539524516</v>
+        <v>0.003753796539524518</v>
       </c>
       <c r="I5" t="n">
         <v>0.003510852260982232</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003618044075068267</v>
+        <v>0.003618044075068265</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004069628368912449</v>
+        <v>0.004069628368912451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003580671783990761</v>
+        <v>0.003580671783990823</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005000821553418066</v>
+        <v>0.005000821553418067</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01598055496191954</v>
+        <v>0.003156014979729971</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00310620757118387</v>
+        <v>0.003106207571183869</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003137289611659745</v>
+        <v>0.003137289611659753</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00257571515987748</v>
+        <v>0.002575715159877485</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003616391387527419</v>
+        <v>0.003616391387527422</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003541449332962739</v>
+        <v>0.003541449332962742</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003705275357429015</v>
+        <v>0.003705275357429021</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003589192824004115</v>
+        <v>0.003589192824004116</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00300284004736668</v>
+        <v>0.003002840047366681</v>
       </c>
       <c r="W5" t="n">
         <v>0.004088179139401915</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002899216268623947</v>
+        <v>0.002899216268623954</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004130587346904028</v>
+        <v>0.004130587346904029</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002705950669766174</v>
+        <v>0.002705950669766176</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003811999441489343</v>
+        <v>0.003811999441489348</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004704042474607192</v>
+        <v>0.004704042474607201</v>
       </c>
     </row>
     <row r="6">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003397038187723337</v>
+        <v>0.003397038187723338</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003346615559042383</v>
+        <v>0.003346615559042386</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003803332923427054</v>
+        <v>0.003803332923427055</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003338008867062957</v>
+        <v>0.003338008867062964</v>
       </c>
       <c r="F6" t="n">
         <v>0.002614585808349612</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003822887689876832</v>
+        <v>0.003822887689876835</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004051223219780625</v>
+        <v>0.004051223219780624</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003808278941238344</v>
+        <v>0.003808278941238347</v>
       </c>
       <c r="J6" t="n">
         <v>0.003915470755324375</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004367055049168555</v>
+        <v>0.004367055049168559</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003878098464246867</v>
+        <v>0.003878098464246845</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005298248233674109</v>
+        <v>0.005298248233674106</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01598055496191954</v>
+        <v>0.003898099215755019</v>
       </c>
       <c r="O6" t="n">
         <v>0.003853449278966807</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003942181629554225</v>
+        <v>0.003942181629554229</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.003559500501563222</v>
+        <v>0.003559500501563219</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003913818067783529</v>
+        <v>0.00391381806778353</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003838876013218849</v>
+        <v>0.003838876013218848</v>
       </c>
       <c r="T6" t="n">
-        <v>0.004002702037685127</v>
+        <v>0.00400270203768513</v>
       </c>
       <c r="U6" t="n">
         <v>0.004166829748762067</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003900764199362264</v>
+        <v>0.003900764199362266</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0043854930862383</v>
+        <v>0.004385493086238301</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003830427640330088</v>
+        <v>0.003830427640330111</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003858062612463091</v>
+        <v>0.003858062612463093</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00335596743724429</v>
+        <v>0.003355967437244292</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.004109426121745453</v>
+        <v>0.004109426121745454</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00440226689239143</v>
+        <v>0.004402266892391439</v>
       </c>
     </row>
   </sheetData>
@@ -2374,85 +2374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003316617511592937</v>
+        <v>0.003316617511592941</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003285301962709199</v>
+        <v>0.0032853019627092</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003340456897004075</v>
+        <v>0.003340456897004079</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003299573964464743</v>
+        <v>0.003299573964464748</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003300168901015923</v>
+        <v>0.003300168901015926</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003329147285065065</v>
+        <v>0.003329147285065068</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003343119817927473</v>
+        <v>0.003343119817927476</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003342413216856806</v>
+        <v>0.003342413216856808</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003338027439216109</v>
+        <v>0.003338027439216111</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00334572723535012</v>
+        <v>0.003345727235350125</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003325926674888856</v>
+        <v>0.003325926674888857</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003438825901471511</v>
+        <v>0.00343882590147151</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003317893642221027</v>
+        <v>0.00331789364222103</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004483032585960684</v>
+        <v>0.004483032585960686</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003326742528265094</v>
+        <v>0.003326742528265095</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003301678318412114</v>
+        <v>0.003301678318412117</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003329423010886057</v>
+        <v>0.00332942301088606</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003328735253645576</v>
+        <v>0.003328735253645579</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003336261731448302</v>
+        <v>0.003336261731448306</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006186464065030507</v>
+        <v>0.006186464065030511</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00330625600206077</v>
+        <v>0.003306256002060773</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006562736817930617</v>
+        <v>0.006562736817930626</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003359270080270006</v>
+        <v>0.00335927008027001</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003369964157403132</v>
+        <v>0.003369964157403137</v>
       </c>
       <c r="Z2" t="n">
         <v>0.005237603456321886</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003358726008804839</v>
+        <v>0.003358726008804842</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003376476269240983</v>
+        <v>0.003376476269240984</v>
       </c>
     </row>
     <row r="3">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004521936985934749</v>
+        <v>0.003856470765965713</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003885411857951479</v>
+        <v>0.003640111675862357</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005091997550356505</v>
+        <v>0.004064422718727798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003839240769612355</v>
+        <v>0.003437077020693832</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004153857068811664</v>
+        <v>0.00373694762491777</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00481089651861524</v>
+        <v>0.003953391504458725</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00516410556819917</v>
+        <v>0.004098286348377792</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005140436328386714</v>
+        <v>0.004084066552252316</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005026873970965476</v>
+        <v>0.004034447749208398</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005210251972964086</v>
+        <v>0.00408463313727161</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0047431641732508</v>
+        <v>0.003937512965862509</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007388589585676463</v>
+        <v>0.004870321911579088</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004561617734549155</v>
+        <v>0.003878086054964358</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005576715902183267</v>
+        <v>0.004984067482037853</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004753103581020283</v>
+        <v>0.003934202121188766</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004185080957801519</v>
+        <v>0.00374586700212292</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004839135459912722</v>
+        <v>0.003980822624965785</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004804046838995414</v>
+        <v>0.003951697648231574</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004995029540539125</v>
+        <v>0.004032276481270666</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007957892186383219</v>
+        <v>0.006904588939778468</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004283742944841086</v>
+        <v>0.003772140186476986</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009074966596803073</v>
+        <v>0.00752177856120016</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005529222253663023</v>
+        <v>0.004213707126014081</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005768874686796179</v>
+        <v>0.00429039561558081</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006333420886674396</v>
+        <v>0.005738988466647404</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005507000504109113</v>
+        <v>0.004202728748167397</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.005923521871980348</v>
+        <v>0.004372422562560031</v>
       </c>
     </row>
     <row r="4">
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009640566522394046</v>
+        <v>0.009640566522394109</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004678656628243506</v>
+        <v>0.004678656628243507</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01555883772225208</v>
+        <v>0.01555883772225213</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006743981823721155</v>
+        <v>0.006743981823721152</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007150574563658577</v>
+        <v>0.007150574563658591</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01192430632710087</v>
+        <v>0.01192430632710089</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01693150447181838</v>
+        <v>0.0169315044718184</v>
       </c>
       <c r="I4" t="n">
         <v>0.0162176455581994</v>
@@ -2577,58 +2577,58 @@
         <v>0.01436774091523692</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01512398668851521</v>
+        <v>0.01512398668851524</v>
       </c>
       <c r="L4" t="n">
         <v>0.01194270281147618</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03664125070594039</v>
+        <v>0.03664125070594032</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01065751711119263</v>
+        <v>0.01065751711119264</v>
       </c>
       <c r="O4" t="n">
-        <v>0.008382624199860921</v>
+        <v>0.008382624199860956</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01144953533113756</v>
+        <v>0.01144953533113759</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007243416217733856</v>
+        <v>0.007243416217733863</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01366447967757793</v>
+        <v>0.01366447967757791</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01194687444844339</v>
+        <v>0.01194687444844342</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0148152761612253</v>
+        <v>0.01481527616122535</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01475673581643867</v>
+        <v>0.01475673581643868</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007463173877554192</v>
+        <v>0.007463173877554195</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02197792502869764</v>
+        <v>0.02197792502869759</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01923883746522204</v>
+        <v>0.01923883746522208</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02078771564154233</v>
+        <v>0.0207877156415424</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.008395774620262898</v>
+        <v>0.008395774620262891</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01869331866056791</v>
+        <v>0.01869331866056794</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02425667963346373</v>
+        <v>0.02425667963346376</v>
       </c>
     </row>
     <row r="5">
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002685221124089006</v>
+        <v>0.002685221124089013</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002891863283921216</v>
+        <v>0.00289186328392122</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003473662725199907</v>
+        <v>0.003473662725199916</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002735431266323822</v>
+        <v>0.002735431266323827</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002580306305328542</v>
+        <v>0.002580306305328546</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003453567654003577</v>
+        <v>0.00345356765400358</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00350374164203382</v>
+        <v>0.003503741642033822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003495760257888103</v>
+        <v>0.003495760257888108</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003445802101025801</v>
+        <v>0.003445802101025804</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003533193621293921</v>
+        <v>0.003533193621293923</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003309537182176069</v>
+        <v>0.003309537182176075</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004578689972018748</v>
+        <v>0.004578689972018749</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01065751711119263</v>
+        <v>0.002816360826654343</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002855984962705675</v>
+        <v>0.00285598496270568</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002999797715908648</v>
+        <v>0.002999797715908654</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002414448337093094</v>
+        <v>0.002414448337093097</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003349029905658512</v>
+        <v>0.003349029905658517</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003341261371243303</v>
+        <v>0.003341261371243309</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003426276400375963</v>
+        <v>0.003426276400375967</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003237388626913747</v>
+        <v>0.00323738862691375</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002942459332433958</v>
+        <v>0.002942459332433963</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003865990388690206</v>
+        <v>0.003865990388690208</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003112556263621708</v>
+        <v>0.003112556263621711</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004322700919613655</v>
+        <v>0.004322700919613663</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002619366773544995</v>
+        <v>0.002619366773544997</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003680020747196192</v>
+        <v>0.003680020747196196</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004416668935274068</v>
+        <v>0.004416668935274069</v>
       </c>
     </row>
     <row r="6">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003057841393205266</v>
+        <v>0.003057841393205273</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003074337222952185</v>
+        <v>0.003074337222952187</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003656136664230879</v>
+        <v>0.003656136664230883</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003118408939213692</v>
+        <v>0.003118408939213694</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002442588035164251</v>
+        <v>0.002442588035164252</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003528389291245917</v>
+        <v>0.003528389291245923</v>
       </c>
       <c r="H6" t="n">
         <v>0.003686215581064786</v>
@@ -2750,61 +2750,61 @@
         <v>0.003678234196919076</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003628276040056771</v>
+        <v>0.003628276040056774</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003715667560324893</v>
+        <v>0.003715667560324892</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003492011121207041</v>
+        <v>0.003492011121207045</v>
       </c>
       <c r="M6" t="n">
-        <v>0.004761163911049534</v>
+        <v>0.004761163911049538</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01065751711119263</v>
+        <v>0.003401274321846346</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00343934071847341</v>
+        <v>0.003439340718473413</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003633976218086386</v>
+        <v>0.003633976218086392</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.003218114676551907</v>
+        <v>0.003218114676551911</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003531503844689484</v>
+        <v>0.003531503844689485</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003523735310274276</v>
+        <v>0.003523735310274281</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003608750339406934</v>
+        <v>0.003608750339406937</v>
       </c>
       <c r="U6" t="n">
         <v>0.003673525120996422</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00364680093530588</v>
+        <v>0.003646800935305889</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00404836229779518</v>
+        <v>0.004048362297795183</v>
       </c>
       <c r="X6" t="n">
         <v>0.00386864022371146</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003989434744448654</v>
+        <v>0.003989434744448662</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.003132280334338388</v>
+        <v>0.00313228033433839</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003862494686227163</v>
+        <v>0.003862494686227166</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004056831854468667</v>
+        <v>0.00405683185446867</v>
       </c>
     </row>
   </sheetData>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003305904185634162</v>
+        <v>0.003305904185634159</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003229515685633449</v>
+        <v>0.003229515685633448</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003313557578666685</v>
+        <v>0.003313557578666682</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003286538435546643</v>
+        <v>0.00328653843554664</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00329927764127374</v>
+        <v>0.003299277641273735</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003318723271666534</v>
+        <v>0.003318723271666532</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003332878889314196</v>
+        <v>0.003332878889314194</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003330350468882829</v>
+        <v>0.003330350468882826</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003329372326336314</v>
+        <v>0.003329372326336311</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003353024359908782</v>
+        <v>0.003353024359908781</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003314889170598068</v>
+        <v>0.003314889170598065</v>
       </c>
       <c r="M2" t="n">
         <v>0.003406075542261246</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003300031737005484</v>
+        <v>0.003300031737005481</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004470964094324028</v>
+        <v>0.004470964094324023</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003316271659823883</v>
+        <v>0.00331627165982388</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003296397257213774</v>
+        <v>0.003296397257213772</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003327483103418402</v>
+        <v>0.0033274831034184</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003320068090045287</v>
+        <v>0.003320068090045283</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003334112376934624</v>
+        <v>0.003334112376934622</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006038464717937784</v>
+        <v>0.006038464717937782</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003314157669947537</v>
+        <v>0.003314157669947535</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006421708132379553</v>
+        <v>0.006421708132379557</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003364286402974888</v>
+        <v>0.003364286402974885</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003408986430976451</v>
+        <v>0.003408986430976448</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005223148740070729</v>
+        <v>0.005223148740070722</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003355285620747235</v>
+        <v>0.003355285620747231</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003362216552624097</v>
+        <v>0.003362216552624096</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00437293990687041</v>
+        <v>0.003792221958649964</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003794729235407389</v>
+        <v>0.003565188282984194</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004563065846538493</v>
+        <v>0.00386450405795448</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003649569397857124</v>
+        <v>0.003367730984467112</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004232954434322474</v>
+        <v>0.003752768916430104</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004668366370014381</v>
+        <v>0.003890309693720956</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005024027785518582</v>
+        <v>0.004038576417584944</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00495778884422382</v>
+        <v>0.0040061838310418</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004925281356274641</v>
+        <v>0.003984833259087992</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005479418634556324</v>
+        <v>0.004163861169725291</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004585677283618322</v>
+        <v>0.003868012227054627</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006724294686660065</v>
+        <v>0.00461026389742524</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004245404627136044</v>
+        <v>0.003757707772015976</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005527132189562269</v>
+        <v>0.004952616005106902</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00460974888486674</v>
+        <v>0.003870851495619393</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00416123483744143</v>
+        <v>0.003724986874975436</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004893759594030446</v>
+        <v>0.00398924113848325</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004702104798770861</v>
+        <v>0.003904448392905338</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005044583528001155</v>
+        <v>0.004038982707037657</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007865716855965547</v>
+        <v>0.006759487817476125</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004563786706932699</v>
+        <v>0.00385303770572155</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008625877170466333</v>
+        <v>0.007275854013419529</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005744613587147777</v>
+        <v>0.004269271690098653</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00677505331220417</v>
+        <v>0.004633215088662098</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006176089796219312</v>
+        <v>0.005669390521503411</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005526321761491754</v>
+        <v>0.004199828580094061</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.005690184001233979</v>
+        <v>0.004274594795277464</v>
       </c>
     </row>
     <row r="4">
@@ -3146,85 +3146,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008376892981279504</v>
+        <v>0.008376892981279506</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004461175760248333</v>
+        <v>0.004461175760248339</v>
       </c>
       <c r="D4" t="n">
-        <v>0.010642115314633</v>
+        <v>0.01064211531463304</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00499506861407903</v>
+        <v>0.004995068614079027</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007953623631553493</v>
+        <v>0.007953623631553495</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01064072146279441</v>
+        <v>0.01064072146279433</v>
       </c>
       <c r="H4" t="n">
         <v>0.01581724567926439</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01449418103792266</v>
+        <v>0.01449418103792268</v>
       </c>
       <c r="J4" t="n">
         <v>0.01339177070788279</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01742221627576747</v>
+        <v>0.01742221627576748</v>
       </c>
       <c r="L4" t="n">
         <v>0.01043453323787387</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02959142123154681</v>
+        <v>0.02959142123154678</v>
       </c>
       <c r="N4" t="n">
-        <v>0.008037737290349603</v>
+        <v>0.008037737290349602</v>
       </c>
       <c r="O4" t="n">
-        <v>0.008185470603660712</v>
+        <v>0.008185470603660715</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01016339453911859</v>
+        <v>0.0101633945391186</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007061946912116152</v>
+        <v>0.007061946912116145</v>
       </c>
       <c r="R4" t="n">
         <v>0.01432512771115228</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01113619744542811</v>
+        <v>0.01113619744542812</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01543183876210461</v>
+        <v>0.01543183876210462</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01489892225500797</v>
+        <v>0.01489892225500792</v>
       </c>
       <c r="V4" t="n">
-        <v>0.009672210809626025</v>
+        <v>0.009672210809626054</v>
       </c>
       <c r="W4" t="n">
         <v>0.01932678398262729</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02071296609664267</v>
+        <v>0.02071296609664268</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0300993464595845</v>
+        <v>0.03009934645958449</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007078616977171612</v>
+        <v>0.007078616977171609</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01910116819241441</v>
+        <v>0.01910116819241444</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0219241471394393</v>
+        <v>0.02192414713943931</v>
       </c>
     </row>
     <row r="5">
@@ -3234,85 +3234,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002616039765353161</v>
+        <v>0.002616039765353168</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002867765195700916</v>
+        <v>0.002867765195700917</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003213751146929769</v>
+        <v>0.003213751146929774</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002636325143619879</v>
+        <v>0.002636325143619877</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00262083866524134</v>
+        <v>0.002620838665241344</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003378113694993086</v>
+        <v>0.003378113694993089</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003431994238935401</v>
+        <v>0.0034319942389354</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003403434567032261</v>
+        <v>0.00340343456703226</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003392077608848295</v>
+        <v>0.003392077608848299</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003659546596675614</v>
+        <v>0.003659546596675615</v>
       </c>
       <c r="L5" t="n">
         <v>0.003228792090357258</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004255180824043671</v>
+        <v>0.004255180824043673</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008037737290349603</v>
+        <v>0.002664656350998083</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002834790695631451</v>
+        <v>0.002834790695631445</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002930307715745776</v>
+        <v>0.002930307715745771</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002408179829119822</v>
+        <v>0.002408179829119818</v>
       </c>
       <c r="R5" t="n">
         <v>0.00337104635505826</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003287290367934277</v>
+        <v>0.003287290367934276</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003445927049040508</v>
+        <v>0.00344592704904051</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003263794609500854</v>
+        <v>0.003263794609500859</v>
       </c>
       <c r="V5" t="n">
         <v>0.003078555580180915</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003702768076913213</v>
+        <v>0.003702768076913206</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003221877210810632</v>
+        <v>0.003221877210810636</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004799555021434922</v>
+        <v>0.004799555021434928</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002548052001578456</v>
+        <v>0.002548052001578453</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003685088578077319</v>
+        <v>0.003685088578077324</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004291627983529475</v>
+        <v>0.004291627983529472</v>
       </c>
     </row>
     <row r="6">
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002919852164481528</v>
+        <v>0.002919852164481524</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00296686469468361</v>
+        <v>0.002966864694683608</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003312850645912468</v>
+        <v>0.003312850645912467</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002936906471115692</v>
+        <v>0.002936906471115694</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002444871133002977</v>
+        <v>0.002444871133002973</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003371199446093592</v>
+        <v>0.003371199446093593</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003531093737918092</v>
+        <v>0.003531093737918094</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003502534066014949</v>
+        <v>0.003502534066014952</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003491177107830991</v>
+        <v>0.003491177107830993</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003758646095658305</v>
+        <v>0.00375864609565831</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003327891589339947</v>
+        <v>0.00332789158933995</v>
       </c>
       <c r="M6" t="n">
-        <v>0.004354280323026112</v>
+        <v>0.004354280323026116</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008037737290349603</v>
+        <v>0.003160070042154596</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003322883932397137</v>
+        <v>0.003322883932397134</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003467191694022122</v>
+        <v>0.003467191694022117</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.003119016842375592</v>
+        <v>0.003119016842375593</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00347014585404095</v>
+        <v>0.003470145854040951</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003386389866916961</v>
+        <v>0.003386389866916968</v>
       </c>
       <c r="T6" t="n">
         <v>0.003545026548023199</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003612695281918352</v>
+        <v>0.003612695281918351</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003671429910669192</v>
+        <v>0.003671429910669191</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003801767098934705</v>
+        <v>0.003801767098934706</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003885856052885715</v>
+        <v>0.003885856052885719</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.004390763432192173</v>
+        <v>0.004390763432192175</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002983088902538513</v>
+        <v>0.00298308890253851</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003784188077060014</v>
+        <v>0.003784188077060016</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003856670751661864</v>
+        <v>0.003856670751661858</v>
       </c>
     </row>
   </sheetData>
@@ -3566,37 +3566,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003226329501510927</v>
+        <v>0.003226329501510926</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003212803043884235</v>
+        <v>0.003212803043884234</v>
       </c>
       <c r="D2" t="n">
         <v>0.003244996560040805</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003228106496477423</v>
+        <v>0.003228106496477424</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003224772793366713</v>
+        <v>0.003224772793366716</v>
       </c>
       <c r="G2" t="n">
         <v>0.003232977691227175</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003253448514126251</v>
+        <v>0.003253448514126252</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003247043713087094</v>
+        <v>0.003247043713087095</v>
       </c>
       <c r="J2" t="n">
         <v>0.003242019253946284</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003262895626701891</v>
+        <v>0.003262895626701892</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003248933820480923</v>
+        <v>0.003248933820480922</v>
       </c>
       <c r="M2" t="n">
         <v>0.003277063452089623</v>
@@ -3605,37 +3605,37 @@
         <v>0.003253611313723355</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004366577387489542</v>
+        <v>0.00436657738748954</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003239340534660319</v>
+        <v>0.003239340534660318</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003237340784173173</v>
+        <v>0.003237340784173174</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003246735610912749</v>
+        <v>0.003246735610912748</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003240598515710455</v>
+        <v>0.003240598515710456</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003238114836485959</v>
+        <v>0.00323811483648596</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006079447800872359</v>
+        <v>0.006079447800872358</v>
       </c>
       <c r="V2" t="n">
         <v>0.003226739323284044</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006467001584163671</v>
+        <v>0.006467001584163666</v>
       </c>
       <c r="X2" t="n">
         <v>0.003249844294457746</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003230755458696911</v>
+        <v>0.003230755458696912</v>
       </c>
       <c r="Z2" t="n">
         <v>0.005154493456800698</v>
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00379545059269767</v>
+        <v>0.003574142238761873</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00357940129857535</v>
+        <v>0.00349985779831344</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004235601700235628</v>
+        <v>0.003730635719930132</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00355206365527217</v>
+        <v>0.003307538056087114</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003764657933112429</v>
+        <v>0.003566799800977658</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003948421789920074</v>
+        <v>0.003623590802954972</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004438668097474023</v>
+        <v>0.003805824923496791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004284744204248106</v>
+        <v>0.003748868014631076</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004161101089224752</v>
+        <v>0.003698290501849518</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004650427770335388</v>
+        <v>0.003862923181647397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004319522272553912</v>
+        <v>0.003746907042080476</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004992759028961443</v>
+        <v>0.003978947473274179</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004432852671763086</v>
+        <v>0.003794721886741416</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005018072574886795</v>
+        <v>0.00473869487393158</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004094164369266264</v>
+        <v>0.003675805538972575</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004055234923264184</v>
+        <v>0.003664324763409105</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004279151471501114</v>
+        <v>0.003749022072124463</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004124652520396761</v>
+        <v>0.003678583976827049</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004074965941869801</v>
+        <v>0.00367253518628878</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007317942878800005</v>
+        <v>0.006635275266292652</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003805230101301204</v>
+        <v>0.003577361513190271</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008737707440799932</v>
+        <v>0.007354657305350261</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004347911567369923</v>
+        <v>0.0037683957165121</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003900956329610376</v>
+        <v>0.003612616214511466</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005974115668041745</v>
+        <v>0.005577327381361149</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00473073702493568</v>
+        <v>0.003899036318997041</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004775347511843823</v>
+        <v>0.003922015221765797</v>
       </c>
     </row>
     <row r="4">
@@ -3742,82 +3742,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004282669601460418</v>
+        <v>0.004282669601460416</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002593556032749945</v>
+        <v>0.002593556032749948</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008787331491077311</v>
+        <v>0.008787331491077313</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004864970115404647</v>
+        <v>0.004864970115404642</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004314602842345228</v>
+        <v>0.004314602842345227</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00543363142280559</v>
+        <v>0.005433631422805583</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0111375044482548</v>
+        <v>0.01113750444825478</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009358149505842961</v>
+        <v>0.009358149505842964</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00753557955633326</v>
+        <v>0.007535579556333257</v>
       </c>
       <c r="K4" t="n">
         <v>0.01181949361131762</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008528491745601312</v>
+        <v>0.008528491745601302</v>
       </c>
       <c r="M4" t="n">
         <v>0.01495200473673504</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01028113026333442</v>
+        <v>0.0102811302633344</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00494082098885089</v>
+        <v>0.00494082098885088</v>
       </c>
       <c r="P4" t="n">
-        <v>0.006893725852103906</v>
+        <v>0.006893725852103912</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006783926509543113</v>
+        <v>0.0067839265095431</v>
       </c>
       <c r="R4" t="n">
-        <v>0.009481156746267275</v>
+        <v>0.009481156746267269</v>
       </c>
       <c r="S4" t="n">
-        <v>0.006628001240249612</v>
+        <v>0.00662800124024962</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007094124670844836</v>
+        <v>0.007094124670844832</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01050049396502912</v>
+        <v>0.01050049396502915</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004362921119756626</v>
+        <v>0.004362921119756611</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02094274406809763</v>
+        <v>0.02094274406809762</v>
       </c>
       <c r="X4" t="n">
-        <v>0.009749850293248792</v>
+        <v>0.00974985029324881</v>
       </c>
       <c r="Y4" t="n">
         <v>0.005448956935830881</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.006385593364224437</v>
+        <v>0.006385593364224433</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01312149345549724</v>
+        <v>0.01312149345549723</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0141926788008974</v>
@@ -3833,82 +3833,82 @@
         <v>0.002308464204399948</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002718159421567039</v>
+        <v>0.002718159421567038</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003033597682707888</v>
+        <v>0.003033597682707884</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002568977467874919</v>
+        <v>0.002568977467874918</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002370999355610804</v>
+        <v>0.002370999355610805</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003004478435069944</v>
+        <v>0.003004478435069942</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003129066392193966</v>
+        <v>0.00312906639219396</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003056721218102669</v>
+        <v>0.003056721218102664</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002999568430264219</v>
+        <v>0.002999568430264218</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003235775874622332</v>
+        <v>0.003235775874622333</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003078070850608318</v>
+        <v>0.003078070850608315</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003398906751377503</v>
+        <v>0.003398906751377498</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01028113026333442</v>
+        <v>0.002732251890739138</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002576142082753043</v>
+        <v>0.002576142082753042</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00265375610196735</v>
+        <v>0.002653756101967351</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002331773858521765</v>
+        <v>0.002331773858521764</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003053241062309403</v>
+        <v>0.003053241062309404</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002983919748796249</v>
+        <v>0.002983919748796247</v>
       </c>
       <c r="T5" t="n">
         <v>0.00295586544940665</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002912387809948157</v>
+        <v>0.00291238780994815</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002683905021214437</v>
+        <v>0.002683905021214436</v>
       </c>
       <c r="W5" t="n">
         <v>0.003687643053924522</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00252014158504297</v>
+        <v>0.002520141585042969</v>
       </c>
       <c r="Y5" t="n">
         <v>0.003383538780658424</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002427267904861627</v>
+        <v>0.002427267904861626</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003276713236029821</v>
+        <v>0.003276713236029816</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00383154476537022</v>
+        <v>0.003831544765370216</v>
       </c>
     </row>
     <row r="6">
@@ -3918,28 +3918,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002713868601858379</v>
+        <v>0.002713868601858375</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002945242322058705</v>
+        <v>0.002945242322058707</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003260680583199553</v>
+        <v>0.003260680583199555</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0029923616459612</v>
+        <v>0.002992361645961201</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00225776662035819</v>
+        <v>0.002257766620358188</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00312492200897364</v>
+        <v>0.003124922008973642</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003356149292685631</v>
+        <v>0.003356149292685634</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003283804118594333</v>
+        <v>0.003283804118594334</v>
       </c>
       <c r="J6" t="n">
         <v>0.003226651330755887</v>
@@ -3948,49 +3948,49 @@
         <v>0.003462858775114003</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003305153751099985</v>
+        <v>0.003305153751099987</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003625989651869129</v>
+        <v>0.003625989651869128</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01028113026333442</v>
+        <v>0.003357988189026449</v>
       </c>
       <c r="O6" t="n">
         <v>0.003203661432240102</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003332343394694759</v>
+        <v>0.003332343394694761</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00317420515092061</v>
+        <v>0.003174205150920613</v>
       </c>
       <c r="R6" t="n">
         <v>0.003280323962801074</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003211002649287916</v>
+        <v>0.003211002649287919</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00318294834989832</v>
+        <v>0.003182948349898321</v>
       </c>
       <c r="U6" t="n">
-        <v>0.003390797737804842</v>
+        <v>0.00339079773780484</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003439583738203379</v>
+        <v>0.003439583738203381</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003914624884447883</v>
+        <v>0.003914624884447886</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003315437973506918</v>
+        <v>0.003315437973506921</v>
       </c>
       <c r="Y6" t="n">
         <v>0.00309982079228997</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002975630941788164</v>
+        <v>0.002975630941788169</v>
       </c>
       <c r="AA6" t="n">
         <v>0.003503796136521483</v>
@@ -4162,25 +4162,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003203157124925502</v>
+        <v>0.003203157124925499</v>
       </c>
       <c r="C2" t="n">
         <v>0.003202265814776651</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003207073308294818</v>
+        <v>0.003207073308294816</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003207559156231922</v>
+        <v>0.00320755915623192</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003208654191841092</v>
+        <v>0.003208654191841093</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003210425760057871</v>
+        <v>0.003210425760057869</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003219435711078192</v>
+        <v>0.00321943571107819</v>
       </c>
       <c r="I2" t="n">
         <v>0.003217386316018049</v>
@@ -4189,46 +4189,46 @@
         <v>0.003213594960971919</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003209737658085062</v>
+        <v>0.00320973765808506</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003208714397689846</v>
+        <v>0.003208714397689845</v>
       </c>
       <c r="M2" t="n">
         <v>0.003203563584847784</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003214190321843344</v>
+        <v>0.003214190321843342</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004336420233918661</v>
+        <v>0.004336420233918665</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003210148671623855</v>
+        <v>0.003210148671623856</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003204134342765221</v>
+        <v>0.00320413434276522</v>
       </c>
       <c r="R2" t="n">
         <v>0.003216474166497749</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003214329625848488</v>
+        <v>0.003214329625848485</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003208282079173163</v>
+        <v>0.003208282079173161</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006017985248705104</v>
+        <v>0.006017985248705103</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003212647091354778</v>
+        <v>0.003212647091354777</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006410095202240109</v>
+        <v>0.006410095202240108</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003257151121246536</v>
+        <v>0.003257151121246533</v>
       </c>
       <c r="Y2" t="n">
         <v>0.003219683275015205</v>
@@ -4237,10 +4237,10 @@
         <v>0.005130374855165396</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003235624983846865</v>
+        <v>0.003235624983846862</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003199230045606321</v>
+        <v>0.00319923004560632</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003637018477992957</v>
+        <v>0.003510337767128921</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003679846995109945</v>
+        <v>0.003524389672641485</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00373071819733182</v>
+        <v>0.00354354585849152</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003455628417150041</v>
+        <v>0.003265012468549898</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003768832435182393</v>
+        <v>0.003556893799800708</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003804211937951925</v>
+        <v>0.00356453501944785</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004022698467728398</v>
+        <v>0.003648019260782347</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003972242539942016</v>
+        <v>0.0036278264363541</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003879339740273735</v>
+        <v>0.003591616591465514</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003792272005528524</v>
+        <v>0.003563048486122851</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003766159613613273</v>
+        <v>0.003551470489588615</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003667733550290162</v>
+        <v>0.003521122241132779</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003895123134335729</v>
+        <v>0.00359886940362723</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004994557857789631</v>
+        <v>0.004710912181105848</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003797427744989795</v>
+        <v>0.003564226615566579</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003661546725741211</v>
+        <v>0.003518324932682306</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003951887544963786</v>
+        <v>0.003621890122426635</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003894783024502638</v>
+        <v>0.003593428202375749</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003759049846728167</v>
+        <v>0.003553149011630673</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00644709107326213</v>
+        <v>0.006323808836147267</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00385574817378441</v>
+        <v>0.003582587831753486</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008016697249478823</v>
+        <v>0.007079111529500992</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004896998073226449</v>
+        <v>0.003938077815652389</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004022304243007752</v>
+        <v>0.003644295838924891</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005884627341689871</v>
+        <v>0.005533377369262612</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004391897053911393</v>
+        <v>0.003771593314886321</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003557350007623313</v>
+        <v>0.003484693755518462</v>
       </c>
     </row>
     <row r="4">
@@ -4338,82 +4338,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002969836903419301</v>
+        <v>0.002969836903419302</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003468632102654681</v>
+        <v>0.003468632102654678</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003877048216305483</v>
+        <v>0.00387704821630548</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003919698720438936</v>
+        <v>0.003919698720438938</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004238909345535132</v>
+        <v>0.004238909345535129</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004157200002165491</v>
+        <v>0.004157200002165492</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006722469125718628</v>
+        <v>0.006722469125718631</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006058145888499168</v>
+        <v>0.006058145888499156</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004906296917510898</v>
+        <v>0.004906296917510895</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004287099409985232</v>
+        <v>0.004287099409985233</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00385491443470859</v>
+        <v>0.003854914434708587</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003332699103673529</v>
+        <v>0.003332699103673528</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005192330177218438</v>
+        <v>0.005192330177218442</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00473322400526493</v>
+        <v>0.004733224005264929</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004232320293976681</v>
+        <v>0.004232320293976683</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003174059025330171</v>
+        <v>0.003174059025330172</v>
       </c>
       <c r="R4" t="n">
         <v>0.005967107501642879</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004779067945490183</v>
+        <v>0.004779067945490182</v>
       </c>
       <c r="T4" t="n">
         <v>0.004113904423554821</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002945188366030437</v>
+        <v>0.002945188366030436</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004618924589016677</v>
+        <v>0.004618924589016673</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01299469170871717</v>
+        <v>0.01299469170871716</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01347536888895941</v>
+        <v>0.01347536888895943</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.006392836239392075</v>
+        <v>0.006392836239392062</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00547590330294965</v>
+        <v>0.005475903302949639</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00956693370821045</v>
+        <v>0.009566933708210448</v>
       </c>
       <c r="AB4" t="n">
         <v>0.002456907591272943</v>
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002140903425727515</v>
+        <v>0.002140903425727513</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002617150734932038</v>
+        <v>0.002617150734932034</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002640346721999573</v>
+        <v>0.002640346721999568</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002403449657516287</v>
+        <v>0.002403449657516283</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002273911443215486</v>
+        <v>0.002273911443215482</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002772604593224223</v>
+        <v>0.002772604593224217</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002779985748424015</v>
+        <v>0.002779985748424009</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002756836888451394</v>
+        <v>0.00275683688845139</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00271371086280422</v>
+        <v>0.002713710862804217</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002670441778541834</v>
+        <v>0.002670441778541828</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002658883581654831</v>
+        <v>0.002658883581654825</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002609961950821515</v>
+        <v>0.00260996195082151</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005192330177218438</v>
+        <v>0.002367874151367029</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002455540144835418</v>
+        <v>0.002455540144835414</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002395421922687122</v>
+        <v>0.002395421922687119</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002062482749378233</v>
+        <v>0.00206248274937823</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002746533740010108</v>
+        <v>0.002746533740010102</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002722310166839263</v>
+        <v>0.002722310166839259</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002654000345132548</v>
+        <v>0.002654000345132542</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002370880297108539</v>
+        <v>0.002370880297108535</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002576722625288315</v>
+        <v>0.002576722625288312</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003193071648829005</v>
+        <v>0.003193071648829001</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002703052387115</v>
+        <v>0.002703052387114997</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003234983933677776</v>
+        <v>0.003234983933677771</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002296730741144127</v>
+        <v>0.002296730741144122</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002962851031779595</v>
+        <v>0.002962851031779591</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003032042695668893</v>
+        <v>0.003032042695668886</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002448022236157337</v>
+        <v>0.002448022236157336</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002752127408698358</v>
+        <v>0.002752127408698356</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002775323395765893</v>
+        <v>0.002775323395765891</v>
       </c>
       <c r="E6" t="n">
         <v>0.002715480923522617</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002140635415547955</v>
+        <v>0.002140635415547954</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002813191069719207</v>
+        <v>0.002813191069719201</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002914962422190336</v>
+        <v>0.002914962422190334</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002891813562217716</v>
+        <v>0.002891813562217714</v>
       </c>
       <c r="J6" t="n">
         <v>0.002848687536570541</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002805418452308155</v>
+        <v>0.002805418452308152</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002793860255421151</v>
+        <v>0.002793860255421147</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002744938624587884</v>
+        <v>0.002744938624587882</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005192330177218438</v>
+        <v>0.002855713337784479</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002940217625028552</v>
+        <v>0.002940217625028549</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002924270599100356</v>
+        <v>0.002924270599100354</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002742126617203778</v>
+        <v>0.002742126617203777</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002881510413776428</v>
+        <v>0.002881510413776425</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002857286840605584</v>
+        <v>0.002857286840605581</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002788977018898867</v>
+        <v>0.002788977018898868</v>
       </c>
       <c r="U6" t="n">
         <v>0.00272827261194044</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003163025671444738</v>
+        <v>0.003163025671444737</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003327958861952172</v>
+        <v>0.00332795886195217</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003340975329987624</v>
+        <v>0.003340975329987623</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002917758770743964</v>
+        <v>0.002917758770743961</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002724707752446196</v>
+        <v>0.002724707752446194</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003097827705545915</v>
+        <v>0.003097827705545916</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002691516337678921</v>
+        <v>0.00269151633767892</v>
       </c>
     </row>
   </sheetData>
@@ -4758,37 +4758,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003200314382715207</v>
+        <v>0.003200314382715205</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003146676956753527</v>
+        <v>0.003146676956753529</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003202178785789368</v>
+        <v>0.003202178785789366</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003204711145734749</v>
+        <v>0.003204711145734746</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003200855999897923</v>
+        <v>0.00320085599989792</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003200345794037667</v>
+        <v>0.003200345794037663</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003206442345126958</v>
+        <v>0.003206442345126957</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003202663415594069</v>
+        <v>0.003202663415594068</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003205269234102027</v>
+        <v>0.003205269234102024</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003199383976408978</v>
+        <v>0.003199383976408975</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003203009833688265</v>
+        <v>0.003203009833688264</v>
       </c>
       <c r="M2" t="n">
         <v>0.00319809597360572</v>
@@ -4797,46 +4797,46 @@
         <v>0.003203268340742627</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00434337419618044</v>
+        <v>0.004343374196180436</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003206073956129251</v>
+        <v>0.00320607395612925</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003197734544877642</v>
+        <v>0.003197734544877639</v>
       </c>
       <c r="R2" t="n">
         <v>0.003210247758485792</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003205295932761969</v>
+        <v>0.003205295932761967</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003199451576166173</v>
+        <v>0.00319945157616617</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005867325264571828</v>
+        <v>0.005867325264571829</v>
       </c>
       <c r="V2" t="n">
         <v>0.003209252937015435</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006270125690586597</v>
+        <v>0.006270125690586595</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003264757908465398</v>
+        <v>0.003264757908465395</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003211075654434981</v>
+        <v>0.00321107565443498</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005115434014533947</v>
+        <v>0.005115434014533942</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003231921333314059</v>
+        <v>0.003231921333314057</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003197330879835131</v>
+        <v>0.003197330879835126</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003692936740557456</v>
+        <v>0.003516204903684849</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003606181024652573</v>
+        <v>0.003454138893534647</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003739826948816781</v>
+        <v>0.003534265550702315</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003528181650457749</v>
+        <v>0.00328630589028428</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003710097189268734</v>
+        <v>0.003524655431330509</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003693714841458115</v>
+        <v>0.003516085655807688</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00384176638339728</v>
+        <v>0.003571681678661994</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003751726736074648</v>
+        <v>0.003539313629461983</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003809215656494341</v>
+        <v>0.00355605130118769</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003674303936619702</v>
+        <v>0.00351130171938645</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003756397719176893</v>
+        <v>0.003536377486189552</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003661998583852769</v>
+        <v>0.003507172449943521</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003764102835627843</v>
+        <v>0.003542202739692091</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0052088706418274</v>
+        <v>0.004771386831911023</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003824812916285898</v>
+        <v>0.003559765628895112</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003635628351921889</v>
+        <v>0.003497547279037308</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003929951359376884</v>
+        <v>0.003602201369920828</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003808378295687453</v>
+        <v>0.003554051246312184</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003676368967252693</v>
+        <v>0.003512783213587316</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006320121505098262</v>
+        <v>0.006171028210641649</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003899142776783012</v>
+        <v>0.003584829515921686</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007608285689663414</v>
+        <v>0.006849629447118812</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005196837908759473</v>
+        <v>0.004023889494458363</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003945104646465393</v>
+        <v>0.003605622150634083</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005739262162044585</v>
+        <v>0.005469243207992314</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004428515875711283</v>
+        <v>0.003771957081099643</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003633605103941503</v>
+        <v>0.00349894042382074</v>
       </c>
     </row>
     <row r="4">
@@ -4934,76 +4934,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003555464880473063</v>
+        <v>0.003555464880473061</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003426459468138561</v>
+        <v>0.003426459468138562</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004137220961889089</v>
+        <v>0.004137220961889086</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004432829037260597</v>
+        <v>0.004432829037260594</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003937301764349794</v>
+        <v>0.003937301764349796</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003536423641592784</v>
+        <v>0.003536423641592819</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005211019065135093</v>
+        <v>0.005211019065135097</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004312963624490854</v>
+        <v>0.004312963624490857</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004558717648256091</v>
+        <v>0.004558717648256088</v>
       </c>
       <c r="K4" t="n">
         <v>0.003537812136235175</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003998609247289538</v>
+        <v>0.003998609247289541</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003491840873206014</v>
+        <v>0.003491840873206015</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004303681744092657</v>
+        <v>0.00430368174409266</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006502426126639891</v>
+        <v>0.006502426126639893</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004539186766126542</v>
+        <v>0.004539186766126539</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003170320406113945</v>
+        <v>0.003170320406113946</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005977807765536245</v>
+        <v>0.005977807765536219</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004415760745438921</v>
+        <v>0.004415760745438926</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003614663075517388</v>
+        <v>0.003614663075517387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003234982076396926</v>
+        <v>0.003234982076396925</v>
       </c>
       <c r="V4" t="n">
         <v>0.005147531557996549</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01098212650132983</v>
+        <v>0.01098212650132985</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01590077970804575</v>
+        <v>0.01590077970804574</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.005931518496719089</v>
+        <v>0.005931518496719097</v>
       </c>
       <c r="Z4" t="n">
         <v>0.00449134873629441</v>
@@ -5025,7 +5025,7 @@
         <v>0.002168818868699685</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002599773047011537</v>
+        <v>0.002599773047011538</v>
       </c>
       <c r="D5" t="n">
         <v>0.002639186836644775</v>
@@ -5034,10 +5034,10 @@
         <v>0.002428547390320706</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002244933724629985</v>
+        <v>0.002244933724629984</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002711649432795077</v>
+        <v>0.002711649432795078</v>
       </c>
       <c r="H5" t="n">
         <v>0.002687345700697074</v>
@@ -5046,19 +5046,19 @@
         <v>0.002644660953229622</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00267382051334751</v>
+        <v>0.002673820513347511</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002607618179017431</v>
+        <v>0.002607618179017432</v>
       </c>
       <c r="L5" t="n">
         <v>0.002648573904963759</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002601535938315773</v>
+        <v>0.002601535938315774</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004303681744092657</v>
+        <v>0.002303204468052571</v>
       </c>
       <c r="O5" t="n">
         <v>0.002557246577861941</v>
@@ -5067,40 +5067,40 @@
         <v>0.002407146576929376</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002051379003662358</v>
+        <v>0.00205137900366236</v>
       </c>
       <c r="R5" t="n">
         <v>0.002730329595161727</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002674396445658755</v>
+        <v>0.002674396445658756</v>
       </c>
       <c r="T5" t="n">
         <v>0.002608381749372374</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002377750946753525</v>
+        <v>0.002377750946753522</v>
       </c>
       <c r="V5" t="n">
         <v>0.002594349445000736</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003047965739035829</v>
+        <v>0.003047965739035827</v>
       </c>
       <c r="X5" t="n">
         <v>0.00284961876024373</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003186085720553432</v>
+        <v>0.00318608572055343</v>
       </c>
       <c r="Z5" t="n">
         <v>0.002227764240912393</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002975142593184011</v>
+        <v>0.002975142593184009</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00305713920178339</v>
+        <v>0.003057139201783389</v>
       </c>
     </row>
     <row r="6">
@@ -5110,85 +5110,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002413525911467169</v>
+        <v>0.002413525911467168</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002658409427913404</v>
+        <v>0.002658409427913403</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002697823217546641</v>
+        <v>0.002697823217546638</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002665673250415788</v>
+        <v>0.002665673250415787</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002076046063655109</v>
+        <v>0.002076046063655108</v>
       </c>
       <c r="G6" t="n">
         <v>0.002677118891925197</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002745982081598941</v>
+        <v>0.00274598208159894</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00270329733413149</v>
+        <v>0.002703297334131488</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002732456894249379</v>
+        <v>0.002732456894249378</v>
       </c>
       <c r="K6" t="n">
         <v>0.0026662545599193</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002707210285865627</v>
+        <v>0.002707210285865625</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002660172319217715</v>
+        <v>0.002660172319217713</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004303681744092657</v>
+        <v>0.002710130241963772</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002955696348835876</v>
+        <v>0.002955696348835875</v>
       </c>
       <c r="P6" t="n">
         <v>0.002848030408732858</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002647623631428757</v>
+        <v>0.002647623631428756</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002788965976063594</v>
+        <v>0.002788965976063591</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002733032826560624</v>
+        <v>0.002733032826560622</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002667018130274243</v>
+        <v>0.00266701813027424</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002655883395756062</v>
+        <v>0.00265588339575606</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003079774371719402</v>
+        <v>0.003079774371719401</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003106513818715852</v>
+        <v>0.003106513818715849</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003404683195991111</v>
+        <v>0.00340468319599111</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002798317441660631</v>
+        <v>0.002798317441660633</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002585346386535229</v>
+        <v>0.002585346386535227</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003033778974085879</v>
+        <v>0.003033778974085878</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002646435099170908</v>
+        <v>0.002646435099170904</v>
       </c>
     </row>
   </sheetData>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003301033128692632</v>
+        <v>0.003301033128692629</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00326920390367895</v>
+        <v>0.003269203903678958</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003309259911379369</v>
+        <v>0.003309259911379372</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003283386282203622</v>
+        <v>0.003283386282203618</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003287154793886008</v>
+        <v>0.003287154793886006</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003321043426853926</v>
+        <v>0.003321043426853933</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003335724834273238</v>
+        <v>0.003335724834273245</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00332058941915142</v>
+        <v>0.003320589419151423</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003324848329461827</v>
+        <v>0.003324848329461823</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003343013687723116</v>
+        <v>0.003343013687723114</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003322527254917436</v>
+        <v>0.003322527254917441</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003449939258140309</v>
+        <v>0.003449939258140304</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00333654897729437</v>
+        <v>0.003336548977294388</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004469498439892632</v>
+        <v>0.004469498439892634</v>
       </c>
       <c r="P2" t="n">
         <v>0.00331237352776023</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003295901285470396</v>
+        <v>0.003295901285470407</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003321647463559582</v>
+        <v>0.003321647463559581</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003308830169275882</v>
+        <v>0.003308830169275877</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003319553393518017</v>
+        <v>0.003319553393518025</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006166478276812989</v>
+        <v>0.006166478276812998</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003288722855783607</v>
+        <v>0.003288722855783605</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006521467555446253</v>
+        <v>0.00652146755544625</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003336683120661151</v>
+        <v>0.00333668312066116</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003320375502600799</v>
+        <v>0.003320375502600791</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005224691880777187</v>
+        <v>0.005224691880777192</v>
       </c>
       <c r="AA2" t="n">
         <v>0.003341647030061299</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003360747616317323</v>
+        <v>0.003360747616317325</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004365312138783265</v>
+        <v>0.0037945259224709</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003741366519670464</v>
+        <v>0.003583625719761956</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004569343815470165</v>
+        <v>0.003876660603118846</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003669507029741101</v>
+        <v>0.00337255269543603</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004055199618832008</v>
+        <v>0.003696057053312449</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004826305779039639</v>
+        <v>0.00394799226422691</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005196944119618133</v>
+        <v>0.004101389060392857</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004835755260041348</v>
+        <v>0.00396937015048713</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004923394494324797</v>
+        <v>0.003986411961602332</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005352143789250087</v>
+        <v>0.004127008927385418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00486755227031213</v>
+        <v>0.003968917533527056</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007842670956313726</v>
+        <v>0.004978547920923579</v>
       </c>
       <c r="N3" t="n">
-        <v>0.005200161636522115</v>
+        <v>0.004092257706181337</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005542868794718855</v>
+        <v>0.004963738804986362</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004625098419401252</v>
+        <v>0.003885217600458695</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004255413744433936</v>
+        <v>0.00376292240481468</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004863190354804668</v>
+        <v>0.003982504638551212</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004546804849437367</v>
+        <v>0.003851880465011577</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004810250972822107</v>
+        <v>0.003960372477825136</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008018564408849738</v>
+        <v>0.006909793821144391</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004082495002337066</v>
+        <v>0.003698777951270717</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008683726707403892</v>
+        <v>0.007368959031862251</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005207812876395452</v>
+        <v>0.00409618470342729</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004821622352238998</v>
+        <v>0.003956910794470881</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006291315310667317</v>
+        <v>0.005719501086832527</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005314691173623583</v>
+        <v>0.004128625745456678</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.005762319498761118</v>
+        <v>0.004306108313705938</v>
       </c>
     </row>
     <row r="4">
@@ -5530,22 +5530,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008784222007085703</v>
+        <v>0.008784222007085755</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003727277810263502</v>
+        <v>0.003727277810263506</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01171554366067629</v>
+        <v>0.0117155436606763</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005617923167707208</v>
+        <v>0.005617923167707249</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006714115766596574</v>
+        <v>0.006714115766596576</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01258621627237767</v>
+        <v>0.01258621627237769</v>
       </c>
       <c r="H4" t="n">
         <v>0.01830532505926926</v>
@@ -5554,46 +5554,46 @@
         <v>0.0142847449885345</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01396856415493698</v>
+        <v>0.013968564154937</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01749721696453696</v>
+        <v>0.01749721696453697</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01355440432645183</v>
+        <v>0.01355440432645203</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04028476197252163</v>
+        <v>0.04028476197252165</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01735815234726081</v>
+        <v>0.0173581523472608</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0087040179803305</v>
+        <v>0.008704017980330499</v>
       </c>
       <c r="P4" t="n">
         <v>0.01121318916699924</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008362391156944898</v>
+        <v>0.008362391156944893</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01484776111403839</v>
+        <v>0.01484776111403837</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01008392091915374</v>
+        <v>0.01008392091915375</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01401367926765744</v>
+        <v>0.01401367926765746</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01649925220708059</v>
+        <v>0.0164992522070807</v>
       </c>
       <c r="V4" t="n">
-        <v>0.006342859922888459</v>
+        <v>0.006342859922888453</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02000440673349131</v>
+        <v>0.02000440673349134</v>
       </c>
       <c r="X4" t="n">
         <v>0.01758801927781769</v>
@@ -5602,13 +5602,13 @@
         <v>0.01346827213136948</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.008858454427860395</v>
+        <v>0.008858454427860377</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01813194541120131</v>
+        <v>0.01813194541120135</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02414546866322454</v>
+        <v>0.0241454686632245</v>
       </c>
     </row>
     <row r="5">
@@ -5621,82 +5621,82 @@
         <v>0.002656929238236434</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002904398196540979</v>
+        <v>0.00290439819654098</v>
       </c>
       <c r="D5" t="n">
         <v>0.003302503351827646</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002715979614213878</v>
+        <v>0.002715979614213884</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0025862632891512</v>
+        <v>0.002586263289151205</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00355019891244717</v>
+        <v>0.003550198912447169</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003601436830379895</v>
+        <v>0.003601436830379896</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00343047535394398</v>
+        <v>0.003430475353943981</v>
       </c>
       <c r="J5" t="n">
         <v>0.00347806760262921</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003683767783134432</v>
+        <v>0.00368376778313444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003452364100369625</v>
+        <v>0.003452364100369627</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004882285117676543</v>
+        <v>0.004882285117676542</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01735815234726081</v>
+        <v>0.0031823506141298</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002904091578209925</v>
+        <v>0.002904091578209926</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002998146865664201</v>
+        <v>0.002998146865664204</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002490354602075853</v>
+        <v>0.002490354602075855</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003442426452258565</v>
+        <v>0.003442426452258566</v>
       </c>
       <c r="S5" t="n">
         <v>0.003297649217077539</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00341877296781939</v>
+        <v>0.003418772967819391</v>
       </c>
       <c r="U5" t="n">
-        <v>0.003339500737376325</v>
+        <v>0.003339500737376329</v>
       </c>
       <c r="V5" t="n">
         <v>0.002915829028749521</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003765270508710068</v>
+        <v>0.003765270508710067</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003001655552932207</v>
+        <v>0.003001655552932211</v>
       </c>
       <c r="Y5" t="n">
         <v>0.003977057693117431</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002647447767608736</v>
+        <v>0.00264744776760874</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003668330756150676</v>
+        <v>0.003668330756150678</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00445571191451658</v>
+        <v>0.004455711914516577</v>
       </c>
     </row>
     <row r="6">
@@ -5706,85 +5706,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003143287035241472</v>
+        <v>0.003143287035241477</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003213154427013781</v>
+        <v>0.003213154427013782</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003611259582300447</v>
+        <v>0.003611259582300445</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003232445531465732</v>
+        <v>0.003232445531465729</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002496986057173539</v>
+        <v>0.002496986057173542</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003744359640171174</v>
+        <v>0.003744359640171177</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003910193060852695</v>
+        <v>0.003910193060852703</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003739231584416781</v>
+        <v>0.003739231584416779</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003786823833102009</v>
+        <v>0.003786823833102016</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003992524013607232</v>
+        <v>0.003992524013607233</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003761120330842428</v>
+        <v>0.003761120330842429</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005191041348149252</v>
+        <v>0.005191041348149255</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01735815234726081</v>
+        <v>0.003919502135401026</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003647806296136218</v>
+        <v>0.00364780629613622</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00379775022032953</v>
+        <v>0.003797750220329529</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.003460367587287746</v>
+        <v>0.003460367587287747</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003751182682731367</v>
+        <v>0.003751182682731364</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00360640544755034</v>
+        <v>0.003606405447550345</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003727529198292194</v>
+        <v>0.003727529198292192</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00391828245953872</v>
+        <v>0.003918282459538727</v>
       </c>
       <c r="V6" t="n">
         <v>0.003808742566924738</v>
       </c>
       <c r="W6" t="n">
-        <v>0.004073918128745887</v>
+        <v>0.004073918128745886</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003921017346437729</v>
+        <v>0.003921017346437724</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003736815298570991</v>
+        <v>0.003736815298570993</v>
       </c>
       <c r="Z6" t="n">
         <v>0.003292998342106052</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003977086986623477</v>
+        <v>0.003977086986623481</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004187180243030983</v>
+        <v>0.004187180243030985</v>
       </c>
     </row>
   </sheetData>
@@ -5956,79 +5956,79 @@
         <v>0.003235780983547879</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003243407366450839</v>
+        <v>0.003243407366450837</v>
       </c>
       <c r="E2" t="n">
         <v>0.003240922408617848</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003239102853297988</v>
+        <v>0.003239102853297986</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003280039563674103</v>
+        <v>0.003280039563674102</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003276309221388648</v>
+        <v>0.003276309221388649</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00324740930603408</v>
+        <v>0.003247409306034079</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003262989610820785</v>
+        <v>0.003262989610820786</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003261182335648641</v>
+        <v>0.00326118233564864</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003260992711278936</v>
+        <v>0.003260992711278935</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00325103826571585</v>
+        <v>0.003251038265715848</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003251264755288703</v>
+        <v>0.003251264755288702</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004376447948163743</v>
+        <v>0.004376447948163742</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003264002171393228</v>
+        <v>0.003264002171393225</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003246537270668437</v>
+        <v>0.003246537270668436</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003257868115551186</v>
+        <v>0.003257868115551185</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003250483817423827</v>
+        <v>0.003250483817423825</v>
       </c>
       <c r="T2" t="n">
         <v>0.003249091421223742</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006072006929163328</v>
+        <v>0.006072006929163331</v>
       </c>
       <c r="V2" t="n">
         <v>0.003247776025582778</v>
       </c>
       <c r="W2" t="n">
-        <v>0.006470841923163715</v>
+        <v>0.006470841923163713</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003303372114104746</v>
+        <v>0.003303372114104747</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003313003216046885</v>
+        <v>0.003313003216046884</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0051601745389892</v>
+        <v>0.005160174538989198</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003267518107326786</v>
+        <v>0.003267518107326784</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003445992551774766</v>
+        <v>0.003445992551774765</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003619173495173116</v>
+        <v>0.003523287324369545</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003699239689387915</v>
+        <v>0.003550194057630951</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003823060985646137</v>
+        <v>0.003594916223669513</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003474731421572372</v>
+        <v>0.003287932532143629</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003723520614778317</v>
+        <v>0.003560473191232687</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00466149576698338</v>
+        <v>0.003867595294645521</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004597933084309408</v>
+        <v>0.003871311035549363</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003917267842123996</v>
+        <v>0.003628832616942239</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004273069217532353</v>
+        <v>0.003743690411233827</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004235908455588251</v>
+        <v>0.003729696384028507</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004226875366414942</v>
+        <v>0.003726411529638342</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004018954135071725</v>
+        <v>0.003659160629579409</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004004709428640433</v>
+        <v>0.003657903540299534</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004927579216088479</v>
+        <v>0.004715384712234476</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004291429493580307</v>
+        <v>0.003749579447379916</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003894775766641006</v>
+        <v>0.003616086067464538</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00416307958751769</v>
+        <v>0.003715873525200072</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00398240535640132</v>
+        <v>0.003643523991288179</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003956036032054366</v>
+        <v>0.003641629930051185</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006692648468667026</v>
+        <v>0.006433094532945092</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003919488940797237</v>
+        <v>0.003623313128009488</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008371219788392689</v>
+        <v>0.007238838360117881</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005220440113534439</v>
+        <v>0.004073791042916562</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005437266917546443</v>
+        <v>0.004148521569345161</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005833699606523215</v>
+        <v>0.005535649360071084</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004380778361612479</v>
+        <v>0.003786824146823509</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.008499455367163313</v>
+        <v>0.005243462410333913</v>
       </c>
     </row>
     <row r="4">
@@ -6126,61 +6126,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002613754700054465</v>
+        <v>0.002613754700054464</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003412495198054144</v>
+        <v>0.003412495198054145</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004501547780412731</v>
+        <v>0.004501547780412734</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003890611121537979</v>
+        <v>0.003890611121537984</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003639281777998302</v>
+        <v>0.003639281777998304</v>
       </c>
       <c r="G4" t="n">
         <v>0.01046053833086607</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01196510643328235</v>
+        <v>0.01196510643328236</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005429712060482433</v>
+        <v>0.005429712060482435</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007888858518490246</v>
+        <v>0.007888858518490244</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007551960627927535</v>
+        <v>0.007551960627927534</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007400697462158706</v>
+        <v>0.007400697462158705</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006036388733717032</v>
+        <v>0.00603638873371703</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00608346549274144</v>
+        <v>0.006083465492741439</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003949775978896974</v>
+        <v>0.003949775978896993</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007949110687948834</v>
+        <v>0.007949110687948837</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004865580680088302</v>
+        <v>0.0048655806800883</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007747183945297149</v>
+        <v>0.007747183945297152</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005379616474447803</v>
+        <v>0.005379616474447802</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005721745392870345</v>
+        <v>0.005721745392870341</v>
       </c>
       <c r="U4" t="n">
         <v>0.004607467622441548</v>
@@ -6189,19 +6189,19 @@
         <v>0.004934023212492229</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01638198058428287</v>
+        <v>0.01638198058428286</v>
       </c>
       <c r="X4" t="n">
         <v>0.01643300722757501</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01821233018004627</v>
+        <v>0.01821233018004624</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004907514427288382</v>
+        <v>0.004907514427288378</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00926180597466039</v>
+        <v>0.009261805974660382</v>
       </c>
       <c r="AB4" t="n">
         <v>0.04758008415668379</v>
@@ -6214,85 +6214,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002175039177750453</v>
+        <v>0.002175039177750454</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002695306311876388</v>
+        <v>0.002695306311876389</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002753935680875378</v>
+        <v>0.002753935680875381</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002469715983757481</v>
+        <v>0.002469715983757483</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002299196647099964</v>
+        <v>0.002299196647099965</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003267464395873819</v>
+        <v>0.00326746439587382</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003125577267999007</v>
+        <v>0.003125577267999009</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002799139429451282</v>
+        <v>0.002799139429451284</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002974700777457483</v>
+        <v>0.002974700777457487</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002954712134854386</v>
+        <v>0.002954712134854387</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002952570240367042</v>
+        <v>0.002952570240367043</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00284854810750595</v>
+        <v>0.002848548107505951</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00608346549274144</v>
+        <v>0.002469785509627346</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002471366120549635</v>
+        <v>0.002471366120549637</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00269101787996526</v>
+        <v>0.002691017879965261</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002213688555844515</v>
+        <v>0.002213688555844517</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002917276494237067</v>
+        <v>0.002917276494237069</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002833867449943565</v>
+        <v>0.002833867449943566</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002818139694329726</v>
+        <v>0.002818139694329727</v>
       </c>
       <c r="U5" t="n">
         <v>0.002541366372807781</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002668739703321032</v>
+        <v>0.002668739703321034</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003427246842000092</v>
+        <v>0.003427246842000091</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002899754481915994</v>
+        <v>0.002899754481915995</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004017880102096647</v>
+        <v>0.004017880102096651</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002314321619829579</v>
+        <v>0.00231432161982958</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003026277590557994</v>
+        <v>0.003026277590557995</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.005516421344167301</v>
+        <v>0.005516421344167302</v>
       </c>
     </row>
     <row r="6">
@@ -6302,85 +6302,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002528948073220369</v>
+        <v>0.002528948073220367</v>
       </c>
       <c r="C6" t="n">
         <v>0.002875412702764015</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002934042071763009</v>
+        <v>0.002934042071763007</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002835059362799437</v>
+        <v>0.002835059362799436</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002177105028995949</v>
+        <v>0.00217710502899595</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003347819735549326</v>
+        <v>0.003347819735549325</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003305683658886634</v>
+        <v>0.003305683658886636</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002979245820338909</v>
+        <v>0.002979245820338907</v>
       </c>
       <c r="J6" t="n">
         <v>0.003154807168345112</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003134818525742016</v>
+        <v>0.003134818525742014</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003132676631254674</v>
+        <v>0.003132676631254671</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00302865449839357</v>
+        <v>0.003028654498393569</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00608346549274144</v>
+        <v>0.00302279489326418</v>
       </c>
       <c r="O6" t="n">
         <v>0.003023723881463226</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003290640461499433</v>
+        <v>0.003290640461499432</v>
       </c>
       <c r="Q6" t="n">
         <v>0.002969395924234105</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003097382885124696</v>
+        <v>0.003097382885124695</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003013973840831195</v>
+        <v>0.003013973840831192</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002998246085217355</v>
+        <v>0.002998246085217354</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002956553550798482</v>
+        <v>0.00295655355079848</v>
       </c>
       <c r="V6" t="n">
-        <v>0.003335207659482918</v>
+        <v>0.003335207659482919</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003607258691378907</v>
+        <v>0.003607258691378905</v>
       </c>
       <c r="X6" t="n">
         <v>0.00361137148166068</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003720159208622926</v>
+        <v>0.003720159208622925</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002799175600334604</v>
+        <v>0.002799175600334605</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003206383981445623</v>
+        <v>0.003206383981445622</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.005194018975232879</v>
+        <v>0.005194018975232878</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia photochemical ozone formation results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004100563691931931</v>
+        <v>0.003942825929091316</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003694464420056406</v>
+        <v>0.003649324697091013</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004099765970248397</v>
+        <v>0.003927846976580925</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003465027957725481</v>
+        <v>0.003400317684731597</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003953019829905867</v>
+        <v>0.003824972821037074</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004050889259355716</v>
+        <v>0.003904615510443223</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004427457359012806</v>
+        <v>0.004145160174033498</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00416678064163774</v>
+        <v>0.003972354355321276</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004124936150124952</v>
+        <v>0.003952027714631705</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00459915198762491</v>
+        <v>0.004272808515581952</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004145225567930355</v>
+        <v>0.003966219610443525</v>
       </c>
       <c r="M3" t="n">
-        <v>0.005258924019994142</v>
+        <v>0.004720141789800876</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004302696463979234</v>
+        <v>0.00407203996165036</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005292594304118698</v>
+        <v>0.005144715705587285</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003962513287600952</v>
+        <v>0.003843030287684734</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003934545401385306</v>
+        <v>0.003816052193803774</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004149214008199554</v>
+        <v>0.003958644217343615</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004060583895092704</v>
+        <v>0.003911104815721072</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004368269862347488</v>
+        <v>0.004111633955144529</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007304740045299154</v>
+        <v>0.007048995402824477</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003874247642343604</v>
+        <v>0.003780521924259854</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007554709528989441</v>
+        <v>0.007319855924734522</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003978758708696359</v>
+        <v>0.003845886080945975</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004102911818184784</v>
+        <v>0.003935527130784071</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005877377617382756</v>
+        <v>0.005764971401128796</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004341899960481444</v>
+        <v>0.004101192657421038</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004518290690470409</v>
+        <v>0.004206462206169147</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003474972068942</v>
+        <v>0.003461913862331173</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003454135402532791</v>
+        <v>0.003431096311170218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003524460947530894</v>
+        <v>0.003495667447930396</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003221116197643076</v>
+        <v>0.003203426818651714</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003526904838431945</v>
+        <v>0.003497017880313707</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003541342116383764</v>
+        <v>0.003509808444970642</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003627760170860664</v>
+        <v>0.003565033665683509</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003571612166514583</v>
+        <v>0.003527789403998968</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003579810111118651</v>
+        <v>0.003535855737020431</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003627596639473613</v>
+        <v>0.003570530137962146</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003577965159573518</v>
+        <v>0.003535501825382717</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00353155491880962</v>
+        <v>0.003500005883150307</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003568999711428821</v>
+        <v>0.003526446034760279</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004719475440955048</v>
+        <v>0.004674287131092726</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003565054951766454</v>
+        <v>0.003527016709153532</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003512639235616962</v>
+        <v>0.003488032238631383</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003612289236517106</v>
+        <v>0.003554919071548002</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003572146932573348</v>
+        <v>0.003531929006376061</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003593092340352302</v>
+        <v>0.003542459311617222</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006243216546268169</v>
+        <v>0.006204890450440716</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003590991077972972</v>
+        <v>0.003545493959287436</v>
       </c>
       <c r="W3" t="n">
-        <v>0.006946380032892731</v>
+        <v>0.006803898251965067</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00407815300252786</v>
+        <v>0.003885842158241014</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003828684204512271</v>
+        <v>0.003707215482421009</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005493095241312104</v>
+        <v>0.005451808739330658</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003854181967761832</v>
+        <v>0.003725362248621142</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003505812547504791</v>
+        <v>0.003481607390268538</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003956704107059999</v>
+        <v>0.00383139228939221</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003659272156555891</v>
+        <v>0.003614655681877433</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003994638381413583</v>
+        <v>0.003845503085136079</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003425996184086969</v>
+        <v>0.003365961547975025</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003776401041653964</v>
+        <v>0.003695256107011245</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003989233284899476</v>
+        <v>0.003852347035152894</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004183811029694054</v>
+        <v>0.00397009460210392</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004000440710179411</v>
+        <v>0.003848288748133548</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004064030702635569</v>
+        <v>0.003899704352030554</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004377796397533528</v>
+        <v>0.004122190363468716</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004037110004981698</v>
+        <v>0.003880908378621986</v>
       </c>
       <c r="M3" t="n">
-        <v>0.005080358499364227</v>
+        <v>0.004589448519480828</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004056796133555589</v>
+        <v>0.003891633576941961</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005104852815792604</v>
+        <v>0.004993172382412678</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003963456330406314</v>
+        <v>0.003834568304550772</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003815442646980734</v>
+        <v>0.003724005363591495</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004080013744676148</v>
+        <v>0.003901181697991781</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004000932089184631</v>
+        <v>0.003860350215504193</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004138472532666728</v>
+        <v>0.003944484210539353</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007080757570741736</v>
+        <v>0.006868001255138803</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003735719434610609</v>
+        <v>0.003673743806077024</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007587446769655524</v>
+        <v>0.007320941471549944</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004010840005006131</v>
+        <v>0.003858494070366784</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004023031870177819</v>
+        <v>0.003871088368337831</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005754535062298242</v>
+        <v>0.005664793025706041</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004202597773086547</v>
+        <v>0.003995559876958115</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0044440930505822</v>
+        <v>0.004145641594542726</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003856470765965713</v>
+        <v>0.003757045594291081</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003640111675862357</v>
+        <v>0.003600161630090207</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004064422718727798</v>
+        <v>0.003892735411936539</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003437077020693832</v>
+        <v>0.00337224240766736</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00373694762491777</v>
+        <v>0.003666997826759739</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003953391504458725</v>
+        <v>0.003826563103782312</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004098286348377792</v>
+        <v>0.003909424610717112</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004084066552252316</v>
+        <v>0.003904234424823946</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004034447749208398</v>
+        <v>0.003877640600660757</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00408463313727161</v>
+        <v>0.003919269981548878</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003937512965862509</v>
+        <v>0.003809983884553154</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004870321911579088</v>
+        <v>0.004443083182434034</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003878086054964358</v>
+        <v>0.003765836406088265</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004984067482037853</v>
+        <v>0.004900010495935496</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003934202121188766</v>
+        <v>0.003813099539890186</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00374586700212292</v>
+        <v>0.00367494766887588</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003980822624965785</v>
+        <v>0.003831773705619958</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003951697648231574</v>
+        <v>0.003824521020139642</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004032276481270666</v>
+        <v>0.003869494672634294</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006904588939778468</v>
+        <v>0.006743384582584357</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003772140186476986</v>
+        <v>0.003699036598545076</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00752177856120016</v>
+        <v>0.007272995427501384</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004213707126014081</v>
+        <v>0.003997663485848248</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00429039561558081</v>
+        <v>0.004056083878966758</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005738988466647404</v>
+        <v>0.005654767668896392</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004202728748167397</v>
+        <v>0.003993584789842838</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004372422562560031</v>
+        <v>0.004094597862520678</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003792221958649964</v>
+        <v>0.003708235860838655</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003565188282984194</v>
+        <v>0.003527972166848546</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00386450405795448</v>
+        <v>0.00375264700970213</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003367730984467112</v>
+        <v>0.003324207108673311</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003752768916430104</v>
+        <v>0.003673239812921336</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003890309693720956</v>
+        <v>0.003779216876583891</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004038576417584944</v>
+        <v>0.003863310692659297</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0040061838310418</v>
+        <v>0.003847477459303863</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003984833259087992</v>
+        <v>0.003840083680531814</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004163861169725291</v>
+        <v>0.003970975462148847</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003868012227054627</v>
+        <v>0.003759002980321792</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00461026389742524</v>
+        <v>0.00426932866523561</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003757707772015976</v>
+        <v>0.003677211644361854</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004952616005106902</v>
+        <v>0.004871013244248316</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003870851495619393</v>
+        <v>0.003765510423202331</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003724986874975436</v>
+        <v>0.003656447939253764</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00398924113848325</v>
+        <v>0.003832282991709905</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003904448392905338</v>
+        <v>0.003787211744930916</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004038982707037657</v>
+        <v>0.003868825349976002</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006759487817476125</v>
+        <v>0.006597013167982006</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00385303770572155</v>
+        <v>0.003753649466570642</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007275854013419529</v>
+        <v>0.007059156614013027</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004269271690098653</v>
+        <v>0.004035917869102542</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004633215088662098</v>
+        <v>0.004286249152274131</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005669390521503411</v>
+        <v>0.005601263799775874</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004199828580094061</v>
+        <v>0.003985792394359406</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004274594795277464</v>
+        <v>0.004025374164297838</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003574142238761873</v>
+        <v>0.003540962650934887</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00349985779831344</v>
+        <v>0.003485565256718758</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003730635719930132</v>
+        <v>0.003646275370177393</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003307538056087114</v>
+        <v>0.003267656892619956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003566799800977658</v>
+        <v>0.003533029987407715</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003623590802954972</v>
+        <v>0.00357758723578233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003805824923496791</v>
+        <v>0.003694589255200565</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003748868014631076</v>
+        <v>0.003657979330347248</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003698290501849518</v>
+        <v>0.003628444998120576</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003862923181647397</v>
+        <v>0.003744830372471397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003746907042080476</v>
+        <v>0.003666162080542702</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003978947473274179</v>
+        <v>0.003825460647281457</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003794721886741416</v>
+        <v>0.003693715830581995</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00473869487393158</v>
+        <v>0.004698176896985653</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003675805538972575</v>
+        <v>0.003613254816951359</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003664324763409105</v>
+        <v>0.003602813570133872</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003749022072124463</v>
+        <v>0.003656625700493804</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003678583976827049</v>
+        <v>0.003619369975244439</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00367253518628878</v>
+        <v>0.003607430751881539</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006635275266292652</v>
+        <v>0.006532045547189248</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003577361513190271</v>
+        <v>0.003543249990275935</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007354657305350261</v>
+        <v>0.007133203310634712</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0037683957165121</v>
+        <v>0.003673215155137235</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003612616214511466</v>
+        <v>0.003566130775206788</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005577327381361149</v>
+        <v>0.005520611616580829</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003899036318997041</v>
+        <v>0.003765912067909125</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003922015221765797</v>
+        <v>0.003776332855827687</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003510337767128921</v>
+        <v>0.003490569486145413</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003524389672641485</v>
+        <v>0.003498509918872239</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00354354585849152</v>
+        <v>0.003512738355287775</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003265012468549898</v>
+        <v>0.003233729579696819</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003556893799800708</v>
+        <v>0.003521685781182893</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00356453501944785</v>
+        <v>0.003530628206927653</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003648019260782347</v>
+        <v>0.00358259930037902</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0036278264363541</v>
+        <v>0.003570608401179651</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003591616591465514</v>
+        <v>0.003548581379279526</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003563048486122851</v>
+        <v>0.003527380570623097</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003551470489588615</v>
+        <v>0.00352118324666101</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003521122241132779</v>
+        <v>0.003496889387897139</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00359886940362723</v>
+        <v>0.003552265118199904</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004710912181105848</v>
+        <v>0.004670061784898798</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003564226615566579</v>
+        <v>0.003529318824585699</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003518324932682306</v>
+        <v>0.003496085435202999</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003621890122426635</v>
+        <v>0.00356570485526712</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003593428202375749</v>
+        <v>0.003552130510283684</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003553149011630673</v>
+        <v>0.003519486293105199</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006323808836147267</v>
+        <v>0.006304319841702425</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003582587831753486</v>
+        <v>0.003543071172543941</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007079111529500992</v>
+        <v>0.006938740141792881</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003938077815652389</v>
+        <v>0.003791724095633253</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003644295838924891</v>
+        <v>0.003583128325009036</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005533377369262612</v>
+        <v>0.005483652913037176</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003771593314886321</v>
+        <v>0.003672126082453063</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003484693755518462</v>
+        <v>0.003470980678395795</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003516204903684849</v>
+        <v>0.003489421117239374</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003454138893534647</v>
+        <v>0.003428770557468804</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003534265550702315</v>
+        <v>0.003500309311146951</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00328630589028428</v>
+        <v>0.003248934127368857</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003524655431330509</v>
+        <v>0.00349306543331854</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003516085655807688</v>
+        <v>0.003489549984243363</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003571681678661994</v>
+        <v>0.003524605425815101</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003539313629461983</v>
+        <v>0.00350317930866567</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00355605130118769</v>
+        <v>0.00351714629637956</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00351130171938645</v>
+        <v>0.003484609311271307</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003536377486189552</v>
+        <v>0.003504314452280798</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003507172449943521</v>
+        <v>0.00348099030360769</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003542202739692091</v>
+        <v>0.003506274559834714</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004771386831911023</v>
+        <v>0.004709357588633445</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003559765628895112</v>
+        <v>0.003521230249258097</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003497547279037308</v>
+        <v>0.003475317508551105</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003602201369920828</v>
+        <v>0.003545866180489343</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003554051246312184</v>
+        <v>0.00351698231858915</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003512783213587316</v>
+        <v>0.003485117493167519</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006171028210641649</v>
+        <v>0.006148076947026301</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003584829515921686</v>
+        <v>0.003538949428572</v>
       </c>
       <c r="W3" t="n">
-        <v>0.006849629447118812</v>
+        <v>0.006733340919259356</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004023889494458363</v>
+        <v>0.003848495574625771</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003605622150634083</v>
+        <v>0.003549998719438016</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005469243207992314</v>
+        <v>0.005431348357668791</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003771957081099643</v>
+        <v>0.003666360683701018</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00349894042382074</v>
+        <v>0.003474771347755129</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0037945259224709</v>
+        <v>0.003711123148975605</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003583625719761956</v>
+        <v>0.003556862383708387</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003876660603118846</v>
+        <v>0.003759425096851998</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00337255269543603</v>
+        <v>0.003324515204518577</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003696057053312449</v>
+        <v>0.00363546069944817</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00394799226422691</v>
+        <v>0.003821965142482357</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004101389060392857</v>
+        <v>0.003909168756482229</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00396937015048713</v>
+        <v>0.003823036009295466</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003986411961602332</v>
+        <v>0.003844413873564382</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004127008927385418</v>
+        <v>0.003945402358322391</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003968917533527056</v>
+        <v>0.003831549714633372</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004978547920923579</v>
+        <v>0.004539607381623911</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004092257706181337</v>
+        <v>0.003911438344421357</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004963738804986362</v>
+        <v>0.004881353805095315</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003885217600458695</v>
+        <v>0.003774389202677867</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00376292240481468</v>
+        <v>0.003683856771998254</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003982504638551212</v>
+        <v>0.003829601987028735</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003851880465011577</v>
+        <v>0.003754035495019416</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003960372477825136</v>
+        <v>0.003817129860609225</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006909793821144391</v>
+        <v>0.00673919772290586</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003698777951270717</v>
+        <v>0.003642778184490749</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007368959031862251</v>
+        <v>0.007158437792068266</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00409618470342729</v>
+        <v>0.003912643465745742</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003956910794470881</v>
+        <v>0.00382027993462488</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005719501086832527</v>
+        <v>0.005635222835948252</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004128625745456678</v>
+        <v>0.003939269421973243</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004306108313705938</v>
+        <v>0.004047577050787905</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003523287324369545</v>
+        <v>0.003507990234466906</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003550194057630951</v>
+        <v>0.003525180973455336</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003594916223669513</v>
+        <v>0.003556721929436246</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003287932532143629</v>
+        <v>0.003257194304845207</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003560473191232687</v>
+        <v>0.003532687066707168</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003867595294645521</v>
+        <v>0.003758466439902879</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003871311035549363</v>
+        <v>0.003742396688290254</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003628832616942239</v>
+        <v>0.003579343460474367</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003743690411233827</v>
+        <v>0.003664989553564743</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003729696384028507</v>
+        <v>0.003655049440627279</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003726411529638342</v>
+        <v>0.003653672150794413</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003659160629579409</v>
+        <v>0.003602542881278945</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003657903540299534</v>
+        <v>0.003600608628163322</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004715384712234476</v>
+        <v>0.004684093361644269</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003749579447379916</v>
+        <v>0.003670259589903567</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003616086067464538</v>
+        <v>0.003573687297428172</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003715873525200072</v>
+        <v>0.003638250400209313</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003643523991288179</v>
+        <v>0.003595119901384205</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003641629930051185</v>
+        <v>0.003588648124961983</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006433094532945092</v>
+        <v>0.006393833275993084</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003623313128009488</v>
+        <v>0.003580182643686119</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007238838360117881</v>
+        <v>0.00705728096151071</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004073791042916562</v>
+        <v>0.003891633520648425</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004148521569345161</v>
+        <v>0.003944994501602259</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005535649360071084</v>
+        <v>0.005492906429936238</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003786824146823509</v>
+        <v>0.003691220269322862</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.005243462410333913</v>
+        <v>0.004683115664868968</v>
       </c>
     </row>
     <row r="4">
